--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -1372,7 +1372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1432,26 +1432,53 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="31" customHeight="1">
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>THÉP CHỜ TRÊN BẢN VẼ</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>• QS_VEDAM: nét khuất dầm zone sau, đường MẠCH NGỪNG, dim L chờ (chờ thẳng) hoặc ký hiệu COUPLER.
+• QS_SHOPDAM: thanh chờ thẳng được cắt đủ chiều dài có đoạn chờ; dải shop có đường MẠCH NGỪNG; đầu thanh coupler vẽ ký hiệu,
+  bảng thống kê thêm dòng COUPLER theo đường kính (số cái).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="31" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BỐ CỤC SHOP</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Mặc định giống bản vẽ DCE: shop thép TRÊN phía trên MC dọc; dưới MC dọc là dải THÉP GIÁ sát trên dải THÉP DƯỚI;
+shop THÉP ĐAI bên phải khung shop trên (1:1, dim từng đoạn, tag SH / L). Thay đổi ở QS_DAMSET → trang 5 (Bố cục shop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="31" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>KÝ HIỆU THÉP</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>3t28 = 3 thanh Ø28 (t, T, d, f, Ø, %%c đều được). 2t28+1t25 = nhiều loại. '-' = không có.
 Gối: 3t28;5t28 = trái 3t28 / phải 5t28 ; ;2t28 = chỉ bên phải ; 2t25; = chỉ bên trái.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="112" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9" ht="112" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>DÒNG 11 (B11 / lưới)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>DÒNG 11
 • Ô B11: thép chạy suốt TRÊN, vd 3t28 (2t28+1t25 nếu nhiều loại).
@@ -1464,13 +1491,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="71.5" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10" ht="71.5" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>DÒNG 12 (B12 / lưới)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>DÒNG 12
 • Ô B12: thép chạy suốt DƯỚI, vd 3t28.
@@ -1480,13 +1507,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>DÒNG 13-17</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG LỚP TRÊN (dòng 13 = lớp 1 ... 17 = lớp 5)
 • Cột GỐI: thép mũ gối. 3t28 = 2 bên như nhau; 3t28;5t28 = trái;phải; ;2t28 = chỉ bên phải.
@@ -1495,13 +1522,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="44.5" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12" ht="44.5" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>DÒNG 18-22</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG LỚP DƯỚI (dòng 22 = lớp 1 ... 18 = lớp 5, giống DCE)
 • Cột NHỊP: thép tăng cường bụng nhịp phía dưới.
@@ -1509,13 +1536,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="85" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13" ht="85" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>DÒNG 23</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>DÒNG 23
 • GỐI: ẩn cột khi vẽ (1 trên · 2 dưới · 3 cả hai).
@@ -1526,13 +1553,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="44.5" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14" ht="44.5" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>DÒNG 24</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>DÒNG 24
 • GỐI: kích thước dầm giao tại cột, vd 400x600.
@@ -1540,13 +1567,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="44.5" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15" ht="44.5" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>DÒNG 25</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>DÒNG 25
 • GỐI: độ lệch dầm giao tại cột so với tim cột (mm).
@@ -1554,13 +1581,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="44.5" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>DÒNG 26</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DÒNG 26
 • GỐI: tên trục (nhiều dòng thì lấy dòng cuối).
@@ -1568,13 +1595,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>DÒNG 27</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>DÒNG 27
 • GỐI: độ lệch trục so với tim gối (mm).
@@ -1583,13 +1610,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="44.5" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18" ht="44.5" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>DÒNG 28</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DÒNG 28
 • GỐI: KT dầm giao nằm trong NHỊP BÊN PHẢI gối (400x600 hoặc 400x600/300x600).
@@ -1597,13 +1624,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="44.5" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19" ht="44.5" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>DÒNG 29</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>DÒNG 29
 • GỐI: khoảng cách từ TIM gối tới tim dầm giao trong nhịp phải (2000 hoặc 2000/5000).
@@ -1611,62 +1638,62 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>DÒNG 30</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>DÒNG 30 (chỉ cột NHỊP): thép vai bò tại dầm giao, vd 2t16.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>F2 – Tên dầm</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Tên dầm (ghi trên bản vẽ, tên file CSV).</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="31" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22" ht="31" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>F3 – b dầm (mm)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>b dầm (mm). Nhịp có b khác: nhập ở dòng 12 cột nhịp.
 Móng băng dạng 300/500/500: chưa hỗ trợ (lấy số đầu).</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>F4 – h dầm (mm)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Chiều cao dầm (mm), vd 1000.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="44.5" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24" ht="44.5" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>F5 – Số cấu kiện</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Số cấu kiện giống nhau (nhân số lượng thống kê).
 Thêm /T, /B: đặt mối nối bắt buộc cho thép chạy suốt TRÊN / DƯỚI ở mọi nhịp.
@@ -1674,25 +1701,25 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>F6 – Cao trình dầm (m)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Cao độ mặt dầm (m), vd -0.100.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="71.5" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26" ht="71.5" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>F7 – h sàn (mm)</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Chiều dày sàn (mm).
 Chỉ nhập số: phía sàn / sàn lật lấy theo ô Y2, Y3.
@@ -1702,25 +1729,25 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>F8 – Dầm ngắn L(m) &lt;</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Nhịp có Ltt nhỏ hơn giá trị này (m): đai rải đều 1 bước.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="139" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28" ht="139" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>J2 – Thép gia cường gối</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>HỆ SỐ THÉP GIA CƯỜNG GỐI (J2)
 Dấu phân cách quyết định cách đo:
@@ -1735,13 +1762,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="71.5" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29" ht="71.5" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>J3 – Thép gia cường nhịp</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>HỆ SỐ THÉP GIA CƯỜNG NHỊP (J3), cùng quy ước dấu / \ | như J2
 a = thép TC dưới bụng nhịp: L - 2aL
@@ -1751,89 +1778,89 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="31" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30" ht="31" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>J4 – Neo thép trên (d)</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>40 = 40d · 10;12-30d/40d · 10-500mm/12-600mm/...
 Trống = QS_DAMSET</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="31" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31" ht="31" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>J5 – Neo thép dưới (d)</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>40 = 40d · 10;12-30d/40d · 10-350mm/12-420mm/...
 Trống = QS_DAMSET</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="31" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32" ht="31" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>J6 – Neo thép giá (d)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>40 = 40d · 10;12-30d/40d · 10-350mm/...
 Trống = QS_DAMSET</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>J7 – Tên trục MCN dầm</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Tên trục ghi ở mặt cắt ngang (lưu, chưa dùng khi vẽ).</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="31" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34" ht="31" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>J8 – Lệch trục / Ẩn MC dọc</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Ltt = thêm dim nhịp thông thủy.
 (100, Y, 100/Y: lưu theo DCE, chưa dùng.)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>N2 – ĐK thép C đỡ lớp TC</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Ø thép C đỡ lớp tăng cường (mm). Trống = Ø đai.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="71.5" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36" ht="71.5" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>N3 – KC thép C đỡ lớp TC</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>KHOẢNG RẢI THÉP C ĐỠ LỚP TĂNG CƯỜNG (mm)
 &gt; 0 : tự phân biệt lúc cần vẽ (có ≥ 2 lớp)
@@ -1843,86 +1870,86 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>N4 – Đai C nối giữa thép giá</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>None / So le / So le 2 / Toàn bộ</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>N5 – ĐK đai C nối 2 thép giá</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Ø đai C nối thép giá (mm). Trống = Ø đai.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="31" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39" ht="31" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>N6 – KC đai C nối 2 thép giá</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>400 = móc đai C quay LÊN · 400mm = quay XUỐNG
 Trống = theo bước đai chính.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>N7 – Giật cao độ dầm</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Mép trên / Mép dưới / Tùy chỉnh (lưu, chưa dùng khi vẽ).</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>N8 – Dày BT lót dưới dầm</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>100 = BT lót dày 100 · 100/50 = dày 100, mở rộng mỗi bên 50 (mm).</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="31" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42" ht="31" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>CHƯA HỖ TRỢ</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Giật cấp mép trên / dưới (dòng 23, 25 số đầu ≠ 0), đổi tiết diện, móng băng (F3/F4/B12 dạng a/b/c), giật sàn T.LINK/-100/-200: QS_DAM cảnh báo và bỏ qua / chỉ đổi thép. Các ô J7, N7, J8 (trừ Ltt) được lưu theo DCE nhưng chưa dùng khi vẽ.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="31" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43" ht="31" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>GIÁ TRỊ MẶC ĐỊNH</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Neo, hệ số vùng, móc đai, chiều dài nối để trống = lấy theo QS_DAMSET. Các giá trị mặc định CHƯA XÁC NHẬN – kỹ sư phụ trách kiểm tra theo thuyết minh dự án trước khi phát hành.</t>
         </is>

--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -881,7 +881,8 @@
       <text>
         <t>DÒNG 27
 • GỐI: độ lệch trục so với tim gối (mm).
-• NHỊP: đai trong 6-100/200 (để trống: tự thêm đai trong khi lớp 1 trên ≥ 4 thanh)
+• NHỊP: đai trong 6-100/200 (để trống: tự thêm khi lớp 1 trên ≥ 4 thanh). Kiểu đai trong chọn ở QS_DAMSET trang 2:
+  1 nhánh tại mỗi thanh giữa (như DCE) hoặc đai kín ôm thanh 2 và n-1.
   và/hoặc mối nối bắt buộc: T, B, T/B, TL, TR, BL, BR. Ví dụ 6-100/200/B.</t>
       </text>
     </comment>
@@ -1055,7 +1056,8 @@
       <text>
         <t>DÒNG 27
 • GỐI: độ lệch trục so với tim gối (mm).
-• NHỊP: đai trong 6-100/200 (để trống: tự thêm đai trong khi lớp 1 trên ≥ 4 thanh)
+• NHỊP: đai trong 6-100/200 (để trống: tự thêm khi lớp 1 trên ≥ 4 thanh). Kiểu đai trong chọn ở QS_DAMSET trang 2:
+  1 nhánh tại mỗi thanh giữa (như DCE) hoặc đai kín ôm thanh 2 và n-1.
   và/hoặc mối nối bắt buộc: T, B, T/B, TL, TR, BL, BR. Ví dụ 6-100/200/B.</t>
       </text>
     </comment>
@@ -1595,7 +1597,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
+    <row r="17" ht="71.5" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>DÒNG 27</t>
@@ -1605,7 +1607,8 @@
         <is>
           <t>DÒNG 27
 • GỐI: độ lệch trục so với tim gối (mm).
-• NHỊP: đai trong 6-100/200 (để trống: tự thêm đai trong khi lớp 1 trên ≥ 4 thanh)
+• NHỊP: đai trong 6-100/200 (để trống: tự thêm khi lớp 1 trên ≥ 4 thanh). Kiểu đai trong chọn ở QS_DAMSET trang 2:
+  1 nhánh tại mỗi thanh giữa (như DCE) hoặc đai kín ôm thanh 2 và n-1.
   và/hoặc mối nối bắt buộc: T, B, T/B, TL, TR, BL, BR. Ví dụ 6-100/200/B.</t>
         </is>
       </c>

--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -897,7 +897,8 @@
       <text>
         <t>DÒNG 29
 • GỐI: khoảng cách từ TIM gối tới tim dầm giao trong nhịp phải (2000 hoặc 2000/5000).
-• NHỊP: đai gia cường tại dầm giao: 8t8a50 (chia 2 bên), 8t8a50L / 8t8a50R (1 bên), 8u8a50 (chữ u = đai U).</t>
+• NHỊP: đai gia cường tại dầm giao: 8t8a50 (chia 2 bên), 8t8a50L / 8t8a50R (1 bên), 8u8a50 (chữ u = đai U).
+  Mỗi đai gia cường có thêm bộ đai trong / đai 1 nhánh như đai thường (tắt được ở QS_DAMSET trang 2).</t>
       </text>
     </comment>
     <comment ref="A30" authorId="0" shapeId="0">
@@ -1072,7 +1073,8 @@
       <text>
         <t>DÒNG 29
 • GỐI: khoảng cách từ TIM gối tới tim dầm giao trong nhịp phải (2000 hoặc 2000/5000).
-• NHỊP: đai gia cường tại dầm giao: 8t8a50 (chia 2 bên), 8t8a50L / 8t8a50R (1 bên), 8u8a50 (chữ u = đai U).</t>
+• NHỊP: đai gia cường tại dầm giao: 8t8a50 (chia 2 bên), 8t8a50L / 8t8a50R (1 bên), 8u8a50 (chữ u = đai U).
+  Mỗi đai gia cường có thêm bộ đai trong / đai 1 nhánh như đai thường (tắt được ở QS_DAMSET trang 2).</t>
       </text>
     </comment>
     <comment ref="A30" authorId="0" shapeId="0">
@@ -1627,7 +1629,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="44.5" customHeight="1">
+    <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>DÒNG 29</t>
@@ -1637,7 +1639,8 @@
         <is>
           <t>DÒNG 29
 • GỐI: khoảng cách từ TIM gối tới tim dầm giao trong nhịp phải (2000 hoặc 2000/5000).
-• NHỊP: đai gia cường tại dầm giao: 8t8a50 (chia 2 bên), 8t8a50L / 8t8a50R (1 bên), 8u8a50 (chữ u = đai U).</t>
+• NHỊP: đai gia cường tại dầm giao: 8t8a50 (chia 2 bên), 8t8a50L / 8t8a50R (1 bên), 8u8a50 (chữ u = đai U).
+  Mỗi đai gia cường có thêm bộ đai trong / đai 1 nhánh như đai thường (tắt được ở QS_DAMSET trang 2).</t>
         </is>
       </c>
     </row>

--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -788,7 +788,7 @@
       <text>
         <t>THÉP CHỜ 2 ĐẦU DẦM (khi đầu dầm là mạch ngừng, chờ sang zone / đợt đổ sau)
 • Cho thang: thép kéo thẳng ra ngoài đầu dầm đoạn L chờ, không bẻ ke.
-• Coupler: thép dừng tại mép, vẽ ký hiệu coupler.
+• Coupler: thép dừng tại mép (L chờ = 0) hoặc kéo ra ngoài mép: 100, hoặc so le 100/300 (½ số thanh 100, ½ số thanh 300).
 • So le: 1/2 số thanh chờ L, 1/2 chờ 2L + KC mối nối.
 Bản vẽ có nét khuất dầm zone sau, đường MẠCH NGỪNG, dim L chờ; QS_SHOPDAM cắt đúng chiều dài.
 Để trống = theo QS_DAMSET.</t>
@@ -964,7 +964,7 @@
       <text>
         <t>THÉP CHỜ 2 ĐẦU DẦM (khi đầu dầm là mạch ngừng, chờ sang zone / đợt đổ sau)
 • Cho thang: thép kéo thẳng ra ngoài đầu dầm đoạn L chờ, không bẻ ke.
-• Coupler: thép dừng tại mép, vẽ ký hiệu coupler.
+• Coupler: thép dừng tại mép (L chờ = 0) hoặc kéo ra ngoài mép: 100, hoặc so le 100/300 (½ số thanh 100, ½ số thanh 300).
 • So le: 1/2 số thanh chờ L, 1/2 chờ 2L + KC mối nối.
 Bản vẽ có nét khuất dầm zone sau, đường MẠCH NGỪNG, dim L chờ; QS_SHOPDAM cắt đúng chiều dài.
 Để trống = theo QS_DAMSET.</t>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>• THÉP CHỜ 2 ĐẦU DẦM (S3:T7): kiểu (Khong / Cho thang / Coupler), lớp (TBG, TB, T, B), thanh (Tat ca / Chay suot), L chờ (AUTO / 40d / 1200), so le.
+          <t>• THÉP CHỜ 2 ĐẦU DẦM (S3:T7): kiểu (Khong / Cho thang / Coupler), lớp (TBG, TB, T, B), thanh (Tat ca / Chay suot), L chờ (AUTO / 40d / 1200; coupler 0 / 100 / 100/300 so le), so le.
 • TÙY CHỌN SÀN (Y2:Y3): tai sàn 2 ben / Trai / Phai / Khong, sàn lật – dùng khi F7 chỉ là số (nhập mã DCE 150/1, _150 thì bỏ qua Y2:Y3).
 • Dòng 33-35: tọa độ trục, KC trục-trục tính từ bề rộng gối + Ltt + lệch trục; nhập KC trục mặt bằng (dòng 34) → Ltt suy ra (dòng 35, vàng nếu lệch Ltt đang nhập).
 • Dòng 37-42: kiểm tra As (cm²) bố trí / yêu cầu – thép chạy suốt hiệu dụng (có tính đổi thép dòng 23/25) + tăng cường lớp 1..5; gối tách trái/phải.
@@ -13524,8 +13524,8 @@
     <dataValidation sqref="S5 T5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Thanh được chờ" prompt="Tat ca = mọi thanh tới đầu dầm&#10;Chay suot = chỉ thép chạy suốt" type="list">
       <formula1>LIST!$U$2:$U$3</formula1>
     </dataValidation>
-    <dataValidation sqref="S6 T6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="L chờ" prompt="AUTO = L nối ngoài vùng theo bảng QS_DAMNOI · 40d · 1200 (mm)" type="list">
-      <formula1>LIST!$V$2:$V$5</formula1>
+    <dataValidation sqref="S6 T6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="L chờ" prompt="Chờ thẳng: AUTO = L nối ngoài vùng · 40d · 1200 (mm)&#10;Coupler: đoạn ra ngoài mép 0 · 100 · 100/300 = so le (½ thanh 100, ½ thanh 300); AUTO = QS_DAMSET" type="list">
+      <formula1>LIST!$V$2:$V$8</formula1>
     </dataValidation>
     <dataValidation sqref="S7 T7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Chờ so le 50%" prompt="Co = 1/2 số thanh chờ L, 1/2 chờ 2L + KC mối nối" type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
@@ -24770,8 +24770,8 @@
     <dataValidation sqref="S5 T5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Thanh được chờ" prompt="Tat ca = mọi thanh tới đầu dầm&#10;Chay suot = chỉ thép chạy suốt" type="list">
       <formula1>LIST!$U$2:$U$3</formula1>
     </dataValidation>
-    <dataValidation sqref="S6 T6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="L chờ" prompt="AUTO = L nối ngoài vùng theo bảng QS_DAMNOI · 40d · 1200 (mm)" type="list">
-      <formula1>LIST!$V$2:$V$5</formula1>
+    <dataValidation sqref="S6 T6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="L chờ" prompt="Chờ thẳng: AUTO = L nối ngoài vùng · 40d · 1200 (mm)&#10;Coupler: đoạn ra ngoài mép 0 · 100 · 100/300 = so le (½ thanh 100, ½ thanh 300); AUTO = QS_DAMSET" type="list">
+      <formula1>LIST!$V$2:$V$8</formula1>
     </dataValidation>
     <dataValidation sqref="S7 T7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Chờ so le 50%" prompt="Co = 1/2 số thanh chờ L, 1/2 chờ 2L + KC mối nối" type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
@@ -25506,6 +25506,11 @@
           <t>1/T/B</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25533,6 +25538,11 @@
           <t>8u8a50</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25553,6 +25563,11 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>TL</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>100/300</t>
         </is>
       </c>
     </row>

--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -788,6 +788,7 @@
       <text>
         <t>THÉP CHỜ 2 ĐẦU DẦM (khi đầu dầm là mạch ngừng, chờ sang zone / đợt đổ sau)
 • Cho thang: thép kéo thẳng ra ngoài đầu dầm đoạn L chờ, không bẻ ke.
+• Tên dầm chờ nối (S8 / T8): ghi 'THÉP CHỜ / COUPLER NỐI DẦM …' trên MC dọc, shop và tên dầm trong vùng nét khuất.
 • Coupler: thép dừng tại mép (L chờ = 0) hoặc kéo ra ngoài mép: 100, hoặc so le 100/300 (½ số thanh 100, ½ số thanh 300).
 • So le: 1/2 số thanh chờ L, 1/2 chờ 2L + KC mối nối.
 Bản vẽ có nét khuất dầm zone sau, đường MẠCH NGỪNG, dim L chờ; QS_SHOPDAM cắt đúng chiều dài.
@@ -964,6 +965,7 @@
       <text>
         <t>THÉP CHỜ 2 ĐẦU DẦM (khi đầu dầm là mạch ngừng, chờ sang zone / đợt đổ sau)
 • Cho thang: thép kéo thẳng ra ngoài đầu dầm đoạn L chờ, không bẻ ke.
+• Tên dầm chờ nối (S8 / T8): ghi 'THÉP CHỜ / COUPLER NỐI DẦM …' trên MC dọc, shop và tên dầm trong vùng nét khuất.
 • Coupler: thép dừng tại mép (L chờ = 0) hoặc kéo ra ngoài mép: 100, hoặc so le 100/300 (½ số thanh 100, ½ số thanh 300).
 • So le: 1/2 số thanh chờ L, 1/2 chờ 2L + KC mối nối.
 Bản vẽ có nét khuất dầm zone sau, đường MẠCH NGỪNG, dim L chờ; QS_SHOPDAM cắt đúng chiều dài.
@@ -1428,7 +1430,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>• THÉP CHỜ 2 ĐẦU DẦM (S3:T7): kiểu (Khong / Cho thang / Coupler), lớp (TBG, TB, T, B), thanh (Tat ca / Chay suot), L chờ (AUTO / 40d / 1200; coupler 0 / 100 / 100/300 so le), so le.
+          <t>• THÉP CHỜ 2 ĐẦU DẦM (S3:T7): kiểu (Khong / Cho thang / Coupler), lớp (TBG, TB, T, B), thanh (Tat ca / Chay suot), L chờ (AUTO / 40d / 1200; coupler 0 / 100 / 100/300 so le), tên dầm chờ nối (S8:T8), so le.
 • TÙY CHỌN SÀN (Y2:Y3): tai sàn 2 ben / Trai / Phai / Khong, sàn lật – dùng khi F7 chỉ là số (nhập mã DCE 150/1, _150 thì bỏ qua Y2:Y3).
 • Dòng 33-35: tọa độ trục, KC trục-trục tính từ bề rộng gối + Ltt + lệch trục; nhập KC trục mặt bằng (dòng 34) → Ltt suy ra (dòng 35, vàng nếu lệch Ltt đang nhập).
 • Dòng 37-42: kiểm tra As (cm²) bố trí / yêu cầu – thép chạy suốt hiệu dụng (có tính đổi thép dòng 23/25) + tăng cường lớp 1..5; gối tách trái/phải.
@@ -2439,6 +2441,15 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
       <c r="N8" s="10" t="n"/>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t>Tên dầm chờ nối</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="14" t="inlineStr"/>
+      <c r="T8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -13302,13 +13313,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="61">
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C1:N1"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="P2:R2"/>
+    <mergeCell ref="P8:R8"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="A1:B3"/>
@@ -13471,7 +13483,7 @@
       <formula>LEFT($C$9,1)="✔"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="72">
+  <dataValidations count="73">
     <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm" prompt="Tên dầm (ghi trên bản vẽ, tên file CSV)."/>
     <dataValidation sqref="F3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="b dầm (mm)" prompt="Bề rộng dầm (mm), vd 400."/>
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="h dầm (mm)" prompt="Chiều cao dầm (mm), vd 1000."/>
@@ -13530,6 +13542,7 @@
     <dataValidation sqref="S7 T7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Chờ so le 50%" prompt="Co = 1/2 số thanh chờ L, 1/2 chờ 2L + KC mối nối" type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
     </dataValidation>
+    <dataValidation sqref="S8 T8" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm chờ nối" prompt="Tên dầm / zone sau mà thép chờ (thẳng hoặc coupler) nối sang, vd B138 – ghi lên MC dọc và shop: 'COUPLER NỐI DẦM B138'. Để trống = không ghi."/>
     <dataValidation sqref="Y2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tai sàn (phía có sàn)" prompt="2 ben / Trai / Phai / Khong&#10;Chỉ dùng khi F7 là số." type="list">
       <formula1>LIST!$X$2:$X$5</formula1>
     </dataValidation>
@@ -14013,6 +14026,15 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
       <c r="N8" s="10" t="n"/>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t>Tên dầm chờ nối</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="14" t="n"/>
+      <c r="T8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -24548,13 +24570,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="61">
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C1:N1"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="P2:R2"/>
+    <mergeCell ref="P8:R8"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="A1:B3"/>
@@ -24717,7 +24740,7 @@
       <formula>LEFT($C$9,1)="✔"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="72">
+  <dataValidations count="73">
     <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm" prompt="Tên dầm (ghi trên bản vẽ, tên file CSV)."/>
     <dataValidation sqref="F3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="b dầm (mm)" prompt="Bề rộng dầm (mm), vd 400."/>
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="h dầm (mm)" prompt="Chiều cao dầm (mm), vd 1000."/>
@@ -24776,6 +24799,7 @@
     <dataValidation sqref="S7 T7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Chờ so le 50%" prompt="Co = 1/2 số thanh chờ L, 1/2 chờ 2L + KC mối nối" type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
     </dataValidation>
+    <dataValidation sqref="S8 T8" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm chờ nối" prompt="Tên dầm / zone sau mà thép chờ (thẳng hoặc coupler) nối sang, vd B138 – ghi lên MC dọc và shop: 'COUPLER NỐI DẦM B138'. Để trống = không ghi."/>
     <dataValidation sqref="Y2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tai sàn (phía có sàn)" prompt="2 ben / Trai / Phai / Khong&#10;Chỉ dùng khi F7 là số." type="list">
       <formula1>LIST!$X$2:$X$5</formula1>
     </dataValidation>

--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -1378,7 +1378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1465,26 +1465,42 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="31" customHeight="1">
+    <row r="8" ht="71.5" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>LẤY TỪ MẶT BẰNG KC</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Lệnh QS_DAMMB (AutoCAD): mở file này (có sheet MAU) → trên MBKC pick điểm ĐẦU và CUỐI dầm trên tim dầm (ngoài 2 gối biên).
+Lệnh tự nhận dạng: bề rộng b (nét biên dầm), gối (cột / vách cắt tim; đầu dầm gối lên dầm → '400x700'), trục + lệch trục,
+dầm phụ trong nhịp (vị trí từ tim gối, b x h từ text), dầm giao tại cột, tên + b x h dầm từ text 'B137 (400x1000)'
+→ copy sheet MAU thành sheet mới tên dầm và ghi F2:F4, dòng 11, 24–29. Thép chủ, tăng cường… nhập tiếp bằng tay.
+Layer nhận dạng: QS_DAMSET trang 6 hoặc tùy chọn [Mau] của lệnh. Luôn kiểm tra lại số liệu trước khi vẽ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="31" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>KÝ HIỆU THÉP</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>3t28 = 3 thanh Ø28 (t, T, d, f, Ø, %%c đều được). 2t28+1t25 = nhiều loại. '-' = không có.
 Gối: 3t28;5t28 = trái 3t28 / phải 5t28 ; ;2t28 = chỉ bên phải ; 2t25; = chỉ bên trái.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="112" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10" ht="112" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>DÒNG 11 (B11 / lưới)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>DÒNG 11
 • Ô B11: thép chạy suốt TRÊN, vd 3t28 (2t28+1t25 nếu nhiều loại).
@@ -1497,13 +1513,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="71.5" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="71.5" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>DÒNG 12 (B12 / lưới)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>DÒNG 12
 • Ô B12: thép chạy suốt DƯỚI, vd 3t28.
@@ -1513,13 +1529,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>DÒNG 13-17</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG LỚP TRÊN (dòng 13 = lớp 1 ... 17 = lớp 5)
 • Cột GỐI: thép mũ gối. 3t28 = 2 bên như nhau; 3t28;5t28 = trái;phải; ;2t28 = chỉ bên phải.
@@ -1528,13 +1544,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="44.5" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="44.5" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>DÒNG 18-22</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG LỚP DƯỚI (dòng 22 = lớp 1 ... 18 = lớp 5, giống DCE)
 • Cột NHỊP: thép tăng cường bụng nhịp phía dưới.
@@ -1542,13 +1558,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="85" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="85" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>DÒNG 23</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>DÒNG 23
 • GỐI: ẩn cột khi vẽ (1 trên · 2 dưới · 3 cả hai).
@@ -1559,13 +1575,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="44.5" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15" ht="44.5" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>DÒNG 24</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>DÒNG 24
 • GỐI: kích thước dầm giao tại cột, vd 400x600.
@@ -1573,13 +1589,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="44.5" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>DÒNG 25</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DÒNG 25
 • GỐI: độ lệch dầm giao tại cột so với tim cột (mm).
@@ -1587,13 +1603,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="44.5" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17" ht="44.5" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>DÒNG 26</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>DÒNG 26
 • GỐI: tên trục (nhiều dòng thì lấy dòng cuối).
@@ -1601,13 +1617,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="71.5" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18" ht="71.5" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>DÒNG 27</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DÒNG 27
 • GỐI: độ lệch trục so với tim gối (mm).
@@ -1617,13 +1633,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="44.5" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19" ht="44.5" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>DÒNG 28</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>DÒNG 28
 • GỐI: KT dầm giao nằm trong NHỊP BÊN PHẢI gối (400x600 hoặc 400x600/300x600).
@@ -1631,13 +1647,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>DÒNG 29</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>DÒNG 29
 • GỐI: khoảng cách từ TIM gối tới tim dầm giao trong nhịp phải (2000 hoặc 2000/5000).
@@ -1646,62 +1662,62 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>DÒNG 30</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>DÒNG 30 (chỉ cột NHỊP): thép vai bò tại dầm giao, vd 2t16.</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>DÒNG 30</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>DÒNG 30 (chỉ cột NHỊP): thép vai bò tại dầm giao, vd 2t16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>F2 – Tên dầm</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Tên dầm (ghi trên bản vẽ, tên file CSV).</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="31" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23" ht="31" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>F3 – b dầm (mm)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>b dầm (mm). Nhịp có b khác: nhập ở dòng 12 cột nhịp.
 Móng băng dạng 300/500/500: chưa hỗ trợ (lấy số đầu).</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>F4 – h dầm (mm)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Chiều cao dầm (mm), vd 1000.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="44.5" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25" ht="44.5" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>F5 – Số cấu kiện</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Số cấu kiện giống nhau (nhân số lượng thống kê).
 Thêm /T, /B: đặt mối nối bắt buộc cho thép chạy suốt TRÊN / DƯỚI ở mọi nhịp.
@@ -1709,25 +1725,25 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>F6 – Cao trình dầm (m)</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Cao độ mặt dầm (m), vd -0.100.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="71.5" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27" ht="71.5" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>F7 – h sàn (mm)</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Chiều dày sàn (mm).
 Chỉ nhập số: phía sàn / sàn lật lấy theo ô Y2, Y3.
@@ -1737,25 +1753,25 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>F8 – Dầm ngắn L(m) &lt;</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Nhịp có Ltt nhỏ hơn giá trị này (m): đai rải đều 1 bước.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="139" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29" ht="139" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>J2 – Thép gia cường gối</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>HỆ SỐ THÉP GIA CƯỜNG GỐI (J2)
 Dấu phân cách quyết định cách đo:
@@ -1770,13 +1786,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="71.5" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30" ht="71.5" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>J3 – Thép gia cường nhịp</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>HỆ SỐ THÉP GIA CƯỜNG NHỊP (J3), cùng quy ước dấu / \ | như J2
 a = thép TC dưới bụng nhịp: L - 2aL
@@ -1786,89 +1802,89 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="31" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31" ht="31" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>J4 – Neo thép trên (d)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>40 = 40d · 10;12-30d/40d · 10-500mm/12-600mm/...
 Trống = QS_DAMSET</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="31" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32" ht="31" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>J5 – Neo thép dưới (d)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>40 = 40d · 10;12-30d/40d · 10-350mm/12-420mm/...
 Trống = QS_DAMSET</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="31" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33" ht="31" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>J6 – Neo thép giá (d)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>40 = 40d · 10;12-30d/40d · 10-350mm/...
 Trống = QS_DAMSET</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>J7 – Tên trục MCN dầm</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Tên trục ghi ở mặt cắt ngang (lưu, chưa dùng khi vẽ).</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="31" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35" ht="31" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>J8 – Lệch trục / Ẩn MC dọc</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Ltt = thêm dim nhịp thông thủy.
 (100, Y, 100/Y: lưu theo DCE, chưa dùng.)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>N2 – ĐK thép C đỡ lớp TC</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Ø thép C đỡ lớp tăng cường (mm). Trống = Ø đai.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="71.5" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37" ht="71.5" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>N3 – KC thép C đỡ lớp TC</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>KHOẢNG RẢI THÉP C ĐỠ LỚP TĂNG CƯỜNG (mm)
 &gt; 0 : tự phân biệt lúc cần vẽ (có ≥ 2 lớp)
@@ -1878,86 +1894,86 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>N4 – Đai C nối giữa thép giá</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>None / So le / So le 2 / Toàn bộ</t>
-        </is>
-      </c>
-    </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>N4 – Đai C nối giữa thép giá</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>None / So le / So le 2 / Toàn bộ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>N5 – ĐK đai C nối 2 thép giá</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Ø đai C nối thép giá (mm). Trống = Ø đai.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="31" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40" ht="31" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>N6 – KC đai C nối 2 thép giá</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>400 = móc đai C quay LÊN · 400mm = quay XUỐNG
 Trống = theo bước đai chính.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>N7 – Giật cao độ dầm</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Mép trên / Mép dưới / Tùy chỉnh (lưu, chưa dùng khi vẽ).</t>
-        </is>
-      </c>
-    </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>N7 – Giật cao độ dầm</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Mép trên / Mép dưới / Tùy chỉnh (lưu, chưa dùng khi vẽ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>N8 – Dày BT lót dưới dầm</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>100 = BT lót dày 100 · 100/50 = dày 100, mở rộng mỗi bên 50 (mm).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="31" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CHƯA HỖ TRỢ</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Giật cấp mép trên / dưới (dòng 23, 25 số đầu ≠ 0), đổi tiết diện, móng băng (F3/F4/B12 dạng a/b/c), giật sàn T.LINK/-100/-200: QS_DAM cảnh báo và bỏ qua / chỉ đổi thép. Các ô J7, N7, J8 (trừ Ltt) được lưu theo DCE nhưng chưa dùng khi vẽ.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="31" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>CHƯA HỖ TRỢ</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Giật cấp mép trên / dưới (dòng 23, 25 số đầu ≠ 0), đổi tiết diện, móng băng (F3/F4/B12 dạng a/b/c), giật sàn T.LINK/-100/-200: QS_DAM cảnh báo và bỏ qua / chỉ đổi thép. Các ô J7, N7, J8 (trừ Ltt) được lưu theo DCE nhưng chưa dùng khi vẽ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>GIÁ TRỊ MẶC ĐỊNH</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Neo, hệ số vùng, móc đai, chiều dài nối để trống = lấy theo QS_DAMSET. Các giá trị mặc định CHƯA XÁC NHẬN – kỹ sư phụ trách kiểm tra theo thuyết minh dự án trước khi phát hành.</t>
         </is>

--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -1465,7 +1465,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="71.5" customHeight="1">
+    <row r="8" ht="125.5" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>LẤY TỪ MẶT BẰNG KC</t>
@@ -1477,7 +1477,9 @@
 Lệnh tự nhận dạng: bề rộng b (nét biên dầm), gối (cột / vách cắt tim; đầu dầm gối lên dầm → '400x700'), trục + lệch trục,
 dầm phụ trong nhịp (vị trí từ tim gối, b x h từ text), dầm giao tại cột, tên + b x h dầm từ text 'B137 (400x1000)'
 → copy sheet MAU thành sheet mới tên dầm và ghi F2:F4, dòng 11, 24–29. Thép chủ, tăng cường… nhập tiếp bằng tay.
-Layer nhận dạng: QS_DAMSET trang 6 hoặc tùy chọn [Mau] của lệnh. Luôn kiểm tra lại số liệu trước khi vẽ.</t>
+Trục: tùy chọn [Truc] của lệnh → chọn BLOCK trục (tên trục = thuộc tính / text trong block / text trong bóng trục) → pick 1 đường trục (layer trục)
+→ pick 1 tên trục dạng text (layer tên trục, Enter nếu đã dùng block). [Mau] = thêm layer cột, dầm, text. Sửa ở QS_DAMSET trang 6.
+Luôn kiểm tra lại số liệu trước khi vẽ.</t>
         </is>
       </c>
     </row>

--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -407,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -451,6 +451,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -795,6 +798,18 @@
 Để trống = theo QS_DAMSET.</t>
       </text>
     </comment>
+    <comment ref="V4" authorId="0" shapeId="0">
+      <text>
+        <t>ĐAI CON (nhánh đai bên trong) theo vị trí thanh thép lớp 1 trên, đánh số 1..n từ trái sang phải:
+• 2 → đai C (1 nhánh) tại thanh số 2
+• 2_4 → đai Q (đai kín) ôm từ thanh 2 đến thanh 4
+• 2-4 → đai U từ thanh 2 đến thanh 4
+• ghép nhiều loại: 3,2_4 (đai C thanh 3 + đai Q thanh 2..4)
+• 0 = không có đai con ; AUTO / trống = tự động (QS_DAMSET trang 2)
+Vùng gối có gia cường nên số thanh khác vùng nhịp → Y4 = Khong để khai báo riêng vùng gối (Y5) và vùng nhịp (Y6).
+Chỉ số vượt số thanh thực tế được tự thu về thanh cuối.</t>
+      </text>
+    </comment>
     <comment ref="C5" authorId="0" shapeId="0">
       <text>
         <t>Số cấu kiện giống nhau (nhân số lượng thống kê).
@@ -970,6 +985,18 @@
 • So le: 1/2 số thanh chờ L, 1/2 chờ 2L + KC mối nối.
 Bản vẽ có nét khuất dầm zone sau, đường MẠCH NGỪNG, dim L chờ; QS_SHOPDAM cắt đúng chiều dài.
 Để trống = theo QS_DAMSET.</t>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0" shapeId="0">
+      <text>
+        <t>ĐAI CON (nhánh đai bên trong) theo vị trí thanh thép lớp 1 trên, đánh số 1..n từ trái sang phải:
+• 2 → đai C (1 nhánh) tại thanh số 2
+• 2_4 → đai Q (đai kín) ôm từ thanh 2 đến thanh 4
+• 2-4 → đai U từ thanh 2 đến thanh 4
+• ghép nhiều loại: 3,2_4 (đai C thanh 3 + đai Q thanh 2..4)
+• 0 = không có đai con ; AUTO / trống = tự động (QS_DAMSET trang 2)
+Vùng gối có gia cường nên số thanh khác vùng nhịp → Y4 = Khong để khai báo riêng vùng gối (Y5) và vùng nhịp (Y6).
+Chỉ số vượt số thanh thực tế được tự thu về thanh cuối.</t>
       </text>
     </comment>
     <comment ref="C5" authorId="0" shapeId="0">
@@ -1378,7 +1405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1483,26 +1510,41 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="31" customHeight="1">
+    <row r="9" ht="85" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>ĐAI CON (Y4:Y6)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Nhánh đai bên trong theo số thứ tự thanh lớp 1 trên (1..n từ trái sang phải): 2 = đai C tại thanh 2 ; 2_4 = đai Q (kín) ôm thanh 2..4 ;
+2-4 = đai U thanh 2..4 ; ghép 3,2_4 ; 0 = không có ; AUTO / trống = tự động.
+Y4 = Co: Y5 áp dụng cả dầm. Y4 = Khong: Y5 cho vùng gối (vùng đai dày 2 đầu nhịp), Y6 cho vùng nhịp. Trống = QS_DAMSET trang 2.
+Đường kính / bước đai con = đai trong dòng 27 nếu có, không thì theo đai chính của vùng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="31" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>KÝ HIỆU THÉP</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>3t28 = 3 thanh Ø28 (t, T, d, f, Ø, %%c đều được). 2t28+1t25 = nhiều loại. '-' = không có.
 Gối: 3t28;5t28 = trái 3t28 / phải 5t28 ; ;2t28 = chỉ bên phải ; 2t25; = chỉ bên trái.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="112" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="112" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>DÒNG 11 (B11 / lưới)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>DÒNG 11
 • Ô B11: thép chạy suốt TRÊN, vd 3t28 (2t28+1t25 nếu nhiều loại).
@@ -1515,13 +1557,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="71.5" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="71.5" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>DÒNG 12 (B12 / lưới)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>DÒNG 12
 • Ô B12: thép chạy suốt DƯỚI, vd 3t28.
@@ -1531,13 +1573,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>DÒNG 13-17</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG LỚP TRÊN (dòng 13 = lớp 1 ... 17 = lớp 5)
 • Cột GỐI: thép mũ gối. 3t28 = 2 bên như nhau; 3t28;5t28 = trái;phải; ;2t28 = chỉ bên phải.
@@ -1546,13 +1588,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="44.5" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="44.5" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>DÒNG 18-22</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG LỚP DƯỚI (dòng 22 = lớp 1 ... 18 = lớp 5, giống DCE)
 • Cột NHỊP: thép tăng cường bụng nhịp phía dưới.
@@ -1560,13 +1602,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="85" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15" ht="85" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>DÒNG 23</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>DÒNG 23
 • GỐI: ẩn cột khi vẽ (1 trên · 2 dưới · 3 cả hai).
@@ -1577,13 +1619,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="44.5" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>DÒNG 24</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DÒNG 24
 • GỐI: kích thước dầm giao tại cột, vd 400x600.
@@ -1591,13 +1633,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="44.5" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17" ht="44.5" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>DÒNG 25</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>DÒNG 25
 • GỐI: độ lệch dầm giao tại cột so với tim cột (mm).
@@ -1605,13 +1647,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="44.5" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18" ht="44.5" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>DÒNG 26</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DÒNG 26
 • GỐI: tên trục (nhiều dòng thì lấy dòng cuối).
@@ -1619,13 +1661,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="71.5" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19" ht="71.5" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>DÒNG 27</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>DÒNG 27
 • GỐI: độ lệch trục so với tim gối (mm).
@@ -1635,13 +1677,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="44.5" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20" ht="44.5" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>DÒNG 28</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>DÒNG 28
 • GỐI: KT dầm giao nằm trong NHỊP BÊN PHẢI gối (400x600 hoặc 400x600/300x600).
@@ -1649,13 +1691,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>DÒNG 29</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>DÒNG 29
 • GỐI: khoảng cách từ TIM gối tới tim dầm giao trong nhịp phải (2000 hoặc 2000/5000).
@@ -1664,62 +1706,62 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>DÒNG 30</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>DÒNG 30 (chỉ cột NHỊP): thép vai bò tại dầm giao, vd 2t16.</t>
-        </is>
-      </c>
-    </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>DÒNG 30</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>DÒNG 30 (chỉ cột NHỊP): thép vai bò tại dầm giao, vd 2t16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>F2 – Tên dầm</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Tên dầm (ghi trên bản vẽ, tên file CSV).</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="31" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24" ht="31" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>F3 – b dầm (mm)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>b dầm (mm). Nhịp có b khác: nhập ở dòng 12 cột nhịp.
 Móng băng dạng 300/500/500: chưa hỗ trợ (lấy số đầu).</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>F4 – h dầm (mm)</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Chiều cao dầm (mm), vd 1000.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="44.5" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26" ht="44.5" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>F5 – Số cấu kiện</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Số cấu kiện giống nhau (nhân số lượng thống kê).
 Thêm /T, /B: đặt mối nối bắt buộc cho thép chạy suốt TRÊN / DƯỚI ở mọi nhịp.
@@ -1727,25 +1769,25 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>F6 – Cao trình dầm (m)</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Cao độ mặt dầm (m), vd -0.100.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="71.5" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28" ht="71.5" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>F7 – h sàn (mm)</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Chiều dày sàn (mm).
 Chỉ nhập số: phía sàn / sàn lật lấy theo ô Y2, Y3.
@@ -1755,25 +1797,25 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>F8 – Dầm ngắn L(m) &lt;</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Nhịp có Ltt nhỏ hơn giá trị này (m): đai rải đều 1 bước.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="139" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30" ht="139" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>J2 – Thép gia cường gối</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>HỆ SỐ THÉP GIA CƯỜNG GỐI (J2)
 Dấu phân cách quyết định cách đo:
@@ -1788,13 +1830,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="71.5" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31" ht="71.5" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>J3 – Thép gia cường nhịp</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>HỆ SỐ THÉP GIA CƯỜNG NHỊP (J3), cùng quy ước dấu / \ | như J2
 a = thép TC dưới bụng nhịp: L - 2aL
@@ -1804,89 +1846,89 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="31" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32" ht="31" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>J4 – Neo thép trên (d)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>40 = 40d · 10;12-30d/40d · 10-500mm/12-600mm/...
 Trống = QS_DAMSET</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="31" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33" ht="31" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>J5 – Neo thép dưới (d)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>40 = 40d · 10;12-30d/40d · 10-350mm/12-420mm/...
 Trống = QS_DAMSET</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="31" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34" ht="31" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>J6 – Neo thép giá (d)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>40 = 40d · 10;12-30d/40d · 10-350mm/...
 Trống = QS_DAMSET</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>J7 – Tên trục MCN dầm</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Tên trục ghi ở mặt cắt ngang (lưu, chưa dùng khi vẽ).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="31" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36" ht="31" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>J8 – Lệch trục / Ẩn MC dọc</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Ltt = thêm dim nhịp thông thủy.
 (100, Y, 100/Y: lưu theo DCE, chưa dùng.)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>N2 – ĐK thép C đỡ lớp TC</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Ø thép C đỡ lớp tăng cường (mm). Trống = Ø đai.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="71.5" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38" ht="71.5" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>N3 – KC thép C đỡ lớp TC</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>KHOẢNG RẢI THÉP C ĐỠ LỚP TĂNG CƯỜNG (mm)
 &gt; 0 : tự phân biệt lúc cần vẽ (có ≥ 2 lớp)
@@ -1896,86 +1938,86 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>N4 – Đai C nối giữa thép giá</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>None / So le / So le 2 / Toàn bộ</t>
-        </is>
-      </c>
-    </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>N4 – Đai C nối giữa thép giá</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>None / So le / So le 2 / Toàn bộ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>N5 – ĐK đai C nối 2 thép giá</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Ø đai C nối thép giá (mm). Trống = Ø đai.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="31" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41" ht="31" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>N6 – KC đai C nối 2 thép giá</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>400 = móc đai C quay LÊN · 400mm = quay XUỐNG
 Trống = theo bước đai chính.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>N7 – Giật cao độ dầm</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Mép trên / Mép dưới / Tùy chỉnh (lưu, chưa dùng khi vẽ).</t>
-        </is>
-      </c>
-    </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>N7 – Giật cao độ dầm</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Mép trên / Mép dưới / Tùy chỉnh (lưu, chưa dùng khi vẽ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>N8 – Dày BT lót dưới dầm</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>100 = BT lót dày 100 · 100/50 = dày 100, mở rộng mỗi bên 50 (mm).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="31" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CHƯA HỖ TRỢ</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Giật cấp mép trên / dưới (dòng 23, 25 số đầu ≠ 0), đổi tiết diện, móng băng (F3/F4/B12 dạng a/b/c), giật sàn T.LINK/-100/-200: QS_DAM cảnh báo và bỏ qua / chỉ đổi thép. Các ô J7, N7, J8 (trừ Ltt) được lưu theo DCE nhưng chưa dùng khi vẽ.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="31" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>CHƯA HỖ TRỢ</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Giật cấp mép trên / dưới (dòng 23, 25 số đầu ≠ 0), đổi tiết diện, móng băng (F3/F4/B12 dạng a/b/c), giật sàn T.LINK/-100/-200: QS_DAM cảnh báo và bỏ qua / chỉ đổi thép. Các ô J7, N7, J8 (trừ Ltt) được lưu theo DCE nhưng chưa dùng khi vẽ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>GIÁ TRỊ MẶC ĐỊNH</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Neo, hệ số vùng, móc đai, chiều dài nối để trống = lấy theo QS_DAMSET. Các giá trị mặc định CHƯA XÁC NHẬN – kỹ sư phụ trách kiểm tra theo thuyết minh dự án trước khi phát hành.</t>
         </is>
@@ -2070,7 +2112,7 @@
       <c r="T1" s="6" t="n"/>
       <c r="V1" s="7" t="inlineStr">
         <is>
-          <t>TÙY CHỌN SÀN</t>
+          <t>TÙY CHỌN SÀN / ĐAI CON</t>
         </is>
       </c>
       <c r="W1" s="6" t="n"/>
@@ -2264,6 +2306,14 @@
           <t>TB</t>
         </is>
       </c>
+      <c r="V4" s="13" t="inlineStr">
+        <is>
+          <t>Đai con đi hết dầm</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="14" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -2324,6 +2374,14 @@
           <t>Tat ca</t>
         </is>
       </c>
+      <c r="V5" s="13" t="inlineStr">
+        <is>
+          <t>Đai con toàn dầm / vùng gối</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="17" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="C6" s="8" t="inlineStr">
@@ -2333,7 +2391,7 @@
       </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>-0.1</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -2377,6 +2435,14 @@
           <t>AUTO</t>
         </is>
       </c>
+      <c r="V6" s="13" t="inlineStr">
+        <is>
+          <t>Đai con vùng nhịp</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="17" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="C7" s="8" t="inlineStr">
@@ -2428,7 +2494,7 @@
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Ô trắng = nhập · ▼ = có danh sách</t>
         </is>
@@ -2470,332 +2536,332 @@
       <c r="T8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>TÌNH TRẠNG SỐ LIỆU:</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n"/>
-      <c r="C9" s="21">
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="22">
         <f>IF(SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)=0,"Chưa có nhịp: nhập bề rộng gối + L thông thủy ở dòng 11",IF(SUMPRODUCT((C44:AG44&lt;&gt;"")*(C44:AG44&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$125,FIND("+",$B$125&amp;"+")-1),FIND("t",LEFT($B$125,FIND("+",$B$125&amp;"+")-1))-1)*MID(LEFT($B$125,FIND("+",$B$125&amp;"+")-1),FIND("t",LEFT($B$125,FIND("+",$B$125&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$125,FIND("+",$B$125&amp;"+")+1,99),FIND("t",MID($B$125,FIND("+",$B$125&amp;"+")+1,99))-1)*MID(MID($B$125,FIND("+",$B$125&amp;"+")+1,99),FIND("t",MID($B$125,FIND("+",$B$125&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$126,FIND("+",$B$126&amp;"+")-1),FIND("t",LEFT($B$126,FIND("+",$B$126&amp;"+")-1))-1)*MID(LEFT($B$126,FIND("+",$B$126&amp;"+")-1),FIND("t",LEFT($B$126,FIND("+",$B$126&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$126,FIND("+",$B$126&amp;"+")+1,99),FIND("t",MID($B$126,FIND("+",$B$126&amp;"+")+1,99))-1)*MID(MID($B$126,FIND("+",$B$126&amp;"+")+1,99),FIND("t",MID($B$126,FIND("+",$B$126&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)=0,"✔  Số liệu hợp lệ – "&amp;SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)&amp;" nhịp, tổng chiều dài dầm L = "&amp;FIXED(SUMIF(C63:AG63,1,C60:AG60),0)&amp;" mm","✖  Có "&amp;(SUMPRODUCT((C44:AG44&lt;&gt;"")*(C44:AG44&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$125,FIND("+",$B$125&amp;"+")-1),FIND("t",LEFT($B$125,FIND("+",$B$125&amp;"+")-1))-1)*MID(LEFT($B$125,FIND("+",$B$125&amp;"+")-1),FIND("t",LEFT($B$125,FIND("+",$B$125&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$125,FIND("+",$B$125&amp;"+")+1,99),FIND("t",MID($B$125,FIND("+",$B$125&amp;"+")+1,99))-1)*MID(MID($B$125,FIND("+",$B$125&amp;"+")+1,99),FIND("t",MID($B$125,FIND("+",$B$125&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$126,FIND("+",$B$126&amp;"+")-1),FIND("t",LEFT($B$126,FIND("+",$B$126&amp;"+")-1))-1)*MID(LEFT($B$126,FIND("+",$B$126&amp;"+")-1),FIND("t",LEFT($B$126,FIND("+",$B$126&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$126,FIND("+",$B$126&amp;"+")+1,99),FIND("t",MID($B$126,FIND("+",$B$126&amp;"+")+1,99))-1)*MID(MID($B$126,FIND("+",$B$126&amp;"+")+1,99),FIND("t",MID($B$126,FIND("+",$B$126&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0))&amp;" lỗi – xem dòng 44 (KIỂM TRA SỐ LIỆU) và ô B11 / B12"))</f>
         <v/>
       </c>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="22" t="n"/>
-      <c r="K9" s="22" t="n"/>
-      <c r="L9" s="22" t="n"/>
-      <c r="M9" s="22" t="n"/>
-      <c r="N9" s="22" t="n"/>
-      <c r="O9" s="22" t="n"/>
-      <c r="P9" s="22" t="n"/>
-      <c r="Q9" s="22" t="n"/>
-      <c r="R9" s="22" t="n"/>
-      <c r="S9" s="22" t="n"/>
-      <c r="T9" s="22" t="n"/>
-      <c r="U9" s="22" t="n"/>
-      <c r="V9" s="22" t="n"/>
-      <c r="W9" s="22" t="n"/>
-      <c r="X9" s="22" t="n"/>
-      <c r="Y9" s="22" t="n"/>
-      <c r="Z9" s="22" t="n"/>
-      <c r="AA9" s="22" t="n"/>
-      <c r="AB9" s="22" t="n"/>
-      <c r="AC9" s="22" t="n"/>
-      <c r="AD9" s="22" t="n"/>
-      <c r="AE9" s="22" t="n"/>
-      <c r="AF9" s="22" t="n"/>
-      <c r="AG9" s="22" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="23" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+      <c r="R9" s="23" t="n"/>
+      <c r="S9" s="23" t="n"/>
+      <c r="T9" s="23" t="n"/>
+      <c r="U9" s="23" t="n"/>
+      <c r="V9" s="23" t="n"/>
+      <c r="W9" s="23" t="n"/>
+      <c r="X9" s="23" t="n"/>
+      <c r="Y9" s="23" t="n"/>
+      <c r="Z9" s="23" t="n"/>
+      <c r="AA9" s="23" t="n"/>
+      <c r="AB9" s="23" t="n"/>
+      <c r="AC9" s="23" t="n"/>
+      <c r="AD9" s="23" t="n"/>
+      <c r="AE9" s="23" t="n"/>
+      <c r="AF9" s="23" t="n"/>
+      <c r="AG9" s="23" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>HẠNG MỤC</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Chạy suốt</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Gối 1</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 1</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>Gối 2</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 2</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t>Gối 3</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 3</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t>Gối 4</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="J10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 4</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>Gối 5</t>
         </is>
       </c>
-      <c r="L10" s="26" t="inlineStr">
+      <c r="L10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 5</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t>Gối 6</t>
         </is>
       </c>
-      <c r="N10" s="26" t="inlineStr">
+      <c r="N10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 6</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="26" t="inlineStr">
         <is>
           <t>Gối 7</t>
         </is>
       </c>
-      <c r="P10" s="26" t="inlineStr">
+      <c r="P10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 7</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="26" t="inlineStr">
         <is>
           <t>Gối 8</t>
         </is>
       </c>
-      <c r="R10" s="26" t="inlineStr">
+      <c r="R10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 8</t>
         </is>
       </c>
-      <c r="S10" s="25" t="inlineStr">
+      <c r="S10" s="26" t="inlineStr">
         <is>
           <t>Gối 9</t>
         </is>
       </c>
-      <c r="T10" s="26" t="inlineStr">
+      <c r="T10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 9</t>
         </is>
       </c>
-      <c r="U10" s="25" t="inlineStr">
+      <c r="U10" s="26" t="inlineStr">
         <is>
           <t>Gối 10</t>
         </is>
       </c>
-      <c r="V10" s="26" t="inlineStr">
+      <c r="V10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 10</t>
         </is>
       </c>
-      <c r="W10" s="25" t="inlineStr">
+      <c r="W10" s="26" t="inlineStr">
         <is>
           <t>Gối 11</t>
         </is>
       </c>
-      <c r="X10" s="26" t="inlineStr">
+      <c r="X10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 11</t>
         </is>
       </c>
-      <c r="Y10" s="25" t="inlineStr">
+      <c r="Y10" s="26" t="inlineStr">
         <is>
           <t>Gối 12</t>
         </is>
       </c>
-      <c r="Z10" s="26" t="inlineStr">
+      <c r="Z10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 12</t>
         </is>
       </c>
-      <c r="AA10" s="25" t="inlineStr">
+      <c r="AA10" s="26" t="inlineStr">
         <is>
           <t>Gối 13</t>
         </is>
       </c>
-      <c r="AB10" s="26" t="inlineStr">
+      <c r="AB10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 13</t>
         </is>
       </c>
-      <c r="AC10" s="25" t="inlineStr">
+      <c r="AC10" s="26" t="inlineStr">
         <is>
           <t>Gối 14</t>
         </is>
       </c>
-      <c r="AD10" s="26" t="inlineStr">
+      <c r="AD10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 14</t>
         </is>
       </c>
-      <c r="AE10" s="25" t="inlineStr">
+      <c r="AE10" s="26" t="inlineStr">
         <is>
           <t>Gối 15</t>
         </is>
       </c>
-      <c r="AF10" s="26" t="inlineStr">
+      <c r="AF10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 15</t>
         </is>
       </c>
-      <c r="AG10" s="27" t="inlineStr">
+      <c r="AG10" s="28" t="inlineStr">
         <is>
           <t>Gối 16</t>
         </is>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Thép chạy suốt TRÊN  |  Gối: bề rộng  ·  Nhịp: L thông thủy</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="31" t="n">
         <v>300</v>
       </c>
-      <c r="D11" s="31" t="n">
+      <c r="D11" s="32" t="n">
         <v>7250</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="31" t="n">
         <v>900</v>
       </c>
-      <c r="F11" s="31" t="n">
+      <c r="F11" s="32" t="n">
         <v>8200</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="31" t="n">
         <v>900</v>
       </c>
-      <c r="H11" s="31" t="n">
+      <c r="H11" s="32" t="n">
         <v>7500</v>
       </c>
-      <c r="I11" s="30" t="n">
+      <c r="I11" s="31" t="n">
         <v>900</v>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="J11" s="32" t="n">
         <v>7550</v>
       </c>
-      <c r="K11" s="30" t="n">
+      <c r="K11" s="31" t="n">
         <v>800</v>
       </c>
-      <c r="L11" s="31" t="n">
+      <c r="L11" s="32" t="n">
         <v>6940</v>
       </c>
-      <c r="M11" s="30" t="n">
+      <c r="M11" s="31" t="n">
         <v>760</v>
       </c>
-      <c r="N11" s="31" t="n">
+      <c r="N11" s="32" t="n">
         <v>8700</v>
       </c>
-      <c r="O11" s="30" t="n">
+      <c r="O11" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="P11" s="31" t="n"/>
-      <c r="Q11" s="30" t="n"/>
-      <c r="R11" s="31" t="n"/>
-      <c r="S11" s="30" t="n"/>
-      <c r="T11" s="31" t="n"/>
-      <c r="U11" s="30" t="n"/>
-      <c r="V11" s="31" t="n"/>
-      <c r="W11" s="30" t="n"/>
-      <c r="X11" s="31" t="n"/>
-      <c r="Y11" s="30" t="n"/>
-      <c r="Z11" s="31" t="n"/>
-      <c r="AA11" s="30" t="n"/>
-      <c r="AB11" s="31" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="31" t="n"/>
-      <c r="AE11" s="30" t="n"/>
-      <c r="AF11" s="31" t="n"/>
-      <c r="AG11" s="32" t="n"/>
+      <c r="P11" s="32" t="n"/>
+      <c r="Q11" s="31" t="n"/>
+      <c r="R11" s="32" t="n"/>
+      <c r="S11" s="31" t="n"/>
+      <c r="T11" s="32" t="n"/>
+      <c r="U11" s="31" t="n"/>
+      <c r="V11" s="32" t="n"/>
+      <c r="W11" s="31" t="n"/>
+      <c r="X11" s="32" t="n"/>
+      <c r="Y11" s="31" t="n"/>
+      <c r="Z11" s="32" t="n"/>
+      <c r="AA11" s="31" t="n"/>
+      <c r="AB11" s="32" t="n"/>
+      <c r="AC11" s="31" t="n"/>
+      <c r="AD11" s="32" t="n"/>
+      <c r="AE11" s="31" t="n"/>
+      <c r="AF11" s="32" t="n"/>
+      <c r="AG11" s="33" t="n"/>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Thép chạy suốt DƯỚI  |  Gối: đai trong cột  ·  Nhịp: b nhịp</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="34" t="n"/>
-      <c r="G12" s="33" t="n"/>
-      <c r="H12" s="34" t="n">
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="34" t="n"/>
-      <c r="K12" s="33" t="n"/>
-      <c r="L12" s="34" t="n">
+      <c r="I12" s="34" t="n"/>
+      <c r="J12" s="35" t="n"/>
+      <c r="K12" s="34" t="n"/>
+      <c r="L12" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="M12" s="33" t="n"/>
-      <c r="N12" s="34" t="n"/>
-      <c r="O12" s="33" t="n"/>
-      <c r="P12" s="34" t="n"/>
-      <c r="Q12" s="33" t="n"/>
-      <c r="R12" s="34" t="n"/>
-      <c r="S12" s="33" t="n"/>
-      <c r="T12" s="34" t="n"/>
-      <c r="U12" s="33" t="n"/>
-      <c r="V12" s="34" t="n"/>
-      <c r="W12" s="33" t="n"/>
-      <c r="X12" s="34" t="n"/>
-      <c r="Y12" s="33" t="n"/>
-      <c r="Z12" s="34" t="n"/>
-      <c r="AA12" s="33" t="n"/>
-      <c r="AB12" s="34" t="n"/>
-      <c r="AC12" s="33" t="n"/>
-      <c r="AD12" s="34" t="n"/>
-      <c r="AE12" s="33" t="n"/>
-      <c r="AF12" s="34" t="n"/>
-      <c r="AG12" s="35" t="n"/>
+      <c r="M12" s="34" t="n"/>
+      <c r="N12" s="35" t="n"/>
+      <c r="O12" s="34" t="n"/>
+      <c r="P12" s="35" t="n"/>
+      <c r="Q12" s="34" t="n"/>
+      <c r="R12" s="35" t="n"/>
+      <c r="S12" s="34" t="n"/>
+      <c r="T12" s="35" t="n"/>
+      <c r="U12" s="34" t="n"/>
+      <c r="V12" s="35" t="n"/>
+      <c r="W12" s="34" t="n"/>
+      <c r="X12" s="35" t="n"/>
+      <c r="Y12" s="34" t="n"/>
+      <c r="Z12" s="35" t="n"/>
+      <c r="AA12" s="34" t="n"/>
+      <c r="AB12" s="35" t="n"/>
+      <c r="AC12" s="34" t="n"/>
+      <c r="AD12" s="35" t="n"/>
+      <c r="AE12" s="34" t="n"/>
+      <c r="AF12" s="35" t="n"/>
+      <c r="AG12" s="36" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG
 LỚP TRÊN</t>
@@ -2806,252 +2872,252 @@
           <t>Lớp 1</t>
         </is>
       </c>
-      <c r="C13" s="37" t="n"/>
-      <c r="D13" s="38" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="38" t="n"/>
-      <c r="G13" s="37" t="n"/>
-      <c r="H13" s="38" t="n"/>
-      <c r="I13" s="37" t="n"/>
-      <c r="J13" s="38" t="n"/>
-      <c r="K13" s="37" t="n"/>
-      <c r="L13" s="38" t="n"/>
-      <c r="M13" s="37" t="n"/>
-      <c r="N13" s="38" t="n"/>
-      <c r="O13" s="37" t="n"/>
-      <c r="P13" s="38" t="n"/>
-      <c r="Q13" s="37" t="n"/>
-      <c r="R13" s="38" t="n"/>
-      <c r="S13" s="37" t="n"/>
-      <c r="T13" s="38" t="n"/>
-      <c r="U13" s="37" t="n"/>
-      <c r="V13" s="38" t="n"/>
-      <c r="W13" s="37" t="n"/>
-      <c r="X13" s="38" t="n"/>
-      <c r="Y13" s="37" t="n"/>
-      <c r="Z13" s="38" t="n"/>
-      <c r="AA13" s="37" t="n"/>
-      <c r="AB13" s="38" t="n"/>
-      <c r="AC13" s="37" t="n"/>
-      <c r="AD13" s="38" t="n"/>
-      <c r="AE13" s="37" t="n"/>
-      <c r="AF13" s="38" t="n"/>
-      <c r="AG13" s="39" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="38" t="n"/>
+      <c r="H13" s="39" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="39" t="n"/>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="39" t="n"/>
+      <c r="M13" s="38" t="n"/>
+      <c r="N13" s="39" t="n"/>
+      <c r="O13" s="38" t="n"/>
+      <c r="P13" s="39" t="n"/>
+      <c r="Q13" s="38" t="n"/>
+      <c r="R13" s="39" t="n"/>
+      <c r="S13" s="38" t="n"/>
+      <c r="T13" s="39" t="n"/>
+      <c r="U13" s="38" t="n"/>
+      <c r="V13" s="39" t="n"/>
+      <c r="W13" s="38" t="n"/>
+      <c r="X13" s="39" t="n"/>
+      <c r="Y13" s="38" t="n"/>
+      <c r="Z13" s="39" t="n"/>
+      <c r="AA13" s="38" t="n"/>
+      <c r="AB13" s="39" t="n"/>
+      <c r="AC13" s="38" t="n"/>
+      <c r="AD13" s="39" t="n"/>
+      <c r="AE13" s="38" t="n"/>
+      <c r="AF13" s="39" t="n"/>
+      <c r="AG13" s="40" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="40" t="n"/>
+      <c r="A14" s="41" t="n"/>
       <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Lớp 2</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="37" t="inlineStr">
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="F14" s="38" t="n"/>
-      <c r="G14" s="37" t="inlineStr">
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="38" t="inlineStr">
         <is>
           <t>3t28;5t28</t>
         </is>
       </c>
-      <c r="H14" s="38" t="n"/>
-      <c r="I14" s="37" t="inlineStr">
+      <c r="H14" s="39" t="n"/>
+      <c r="I14" s="38" t="inlineStr">
         <is>
           <t>5t28</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
-      <c r="K14" s="37" t="inlineStr">
+      <c r="J14" s="39" t="n"/>
+      <c r="K14" s="38" t="inlineStr">
         <is>
           <t>5t28;3t28</t>
         </is>
       </c>
-      <c r="L14" s="38" t="n"/>
-      <c r="M14" s="37" t="inlineStr">
+      <c r="L14" s="39" t="n"/>
+      <c r="M14" s="38" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="N14" s="38" t="n"/>
-      <c r="O14" s="37" t="inlineStr">
+      <c r="N14" s="39" t="n"/>
+      <c r="O14" s="38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P14" s="38" t="n"/>
-      <c r="Q14" s="37" t="n"/>
-      <c r="R14" s="38" t="n"/>
-      <c r="S14" s="37" t="n"/>
-      <c r="T14" s="38" t="n"/>
-      <c r="U14" s="37" t="n"/>
-      <c r="V14" s="38" t="n"/>
-      <c r="W14" s="37" t="n"/>
-      <c r="X14" s="38" t="n"/>
-      <c r="Y14" s="37" t="n"/>
-      <c r="Z14" s="38" t="n"/>
-      <c r="AA14" s="37" t="n"/>
-      <c r="AB14" s="38" t="n"/>
-      <c r="AC14" s="37" t="n"/>
-      <c r="AD14" s="38" t="n"/>
-      <c r="AE14" s="37" t="n"/>
-      <c r="AF14" s="38" t="n"/>
-      <c r="AG14" s="39" t="n"/>
+      <c r="P14" s="39" t="n"/>
+      <c r="Q14" s="38" t="n"/>
+      <c r="R14" s="39" t="n"/>
+      <c r="S14" s="38" t="n"/>
+      <c r="T14" s="39" t="n"/>
+      <c r="U14" s="38" t="n"/>
+      <c r="V14" s="39" t="n"/>
+      <c r="W14" s="38" t="n"/>
+      <c r="X14" s="39" t="n"/>
+      <c r="Y14" s="38" t="n"/>
+      <c r="Z14" s="39" t="n"/>
+      <c r="AA14" s="38" t="n"/>
+      <c r="AB14" s="39" t="n"/>
+      <c r="AC14" s="38" t="n"/>
+      <c r="AD14" s="39" t="n"/>
+      <c r="AE14" s="38" t="n"/>
+      <c r="AF14" s="39" t="n"/>
+      <c r="AG14" s="40" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="40" t="n"/>
+      <c r="A15" s="41" t="n"/>
       <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Lớp 3</t>
         </is>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>2t25</t>
         </is>
       </c>
-      <c r="D15" s="38" t="n"/>
-      <c r="E15" s="37" t="inlineStr">
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="38" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="F15" s="38" t="n"/>
-      <c r="G15" s="37" t="inlineStr">
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="38" t="inlineStr">
         <is>
           <t>2t25</t>
         </is>
       </c>
-      <c r="H15" s="38" t="n"/>
-      <c r="I15" s="37" t="inlineStr">
+      <c r="H15" s="39" t="n"/>
+      <c r="I15" s="38" t="inlineStr">
         <is>
           <t>5t28</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
-      <c r="K15" s="37" t="inlineStr">
+      <c r="J15" s="39" t="n"/>
+      <c r="K15" s="38" t="inlineStr">
         <is>
           <t>;2t28</t>
         </is>
       </c>
-      <c r="L15" s="38" t="n"/>
-      <c r="M15" s="37" t="n"/>
-      <c r="N15" s="38" t="n"/>
-      <c r="O15" s="37" t="inlineStr">
+      <c r="L15" s="39" t="n"/>
+      <c r="M15" s="38" t="n"/>
+      <c r="N15" s="39" t="n"/>
+      <c r="O15" s="38" t="inlineStr">
         <is>
           <t>2t25</t>
         </is>
       </c>
-      <c r="P15" s="38" t="n"/>
-      <c r="Q15" s="37" t="n"/>
-      <c r="R15" s="38" t="n"/>
-      <c r="S15" s="37" t="n"/>
-      <c r="T15" s="38" t="n"/>
-      <c r="U15" s="37" t="n"/>
-      <c r="V15" s="38" t="n"/>
-      <c r="W15" s="37" t="n"/>
-      <c r="X15" s="38" t="n"/>
-      <c r="Y15" s="37" t="n"/>
-      <c r="Z15" s="38" t="n"/>
-      <c r="AA15" s="37" t="n"/>
-      <c r="AB15" s="38" t="n"/>
-      <c r="AC15" s="37" t="n"/>
-      <c r="AD15" s="38" t="n"/>
-      <c r="AE15" s="37" t="n"/>
-      <c r="AF15" s="38" t="n"/>
-      <c r="AG15" s="39" t="n"/>
+      <c r="P15" s="39" t="n"/>
+      <c r="Q15" s="38" t="n"/>
+      <c r="R15" s="39" t="n"/>
+      <c r="S15" s="38" t="n"/>
+      <c r="T15" s="39" t="n"/>
+      <c r="U15" s="38" t="n"/>
+      <c r="V15" s="39" t="n"/>
+      <c r="W15" s="38" t="n"/>
+      <c r="X15" s="39" t="n"/>
+      <c r="Y15" s="38" t="n"/>
+      <c r="Z15" s="39" t="n"/>
+      <c r="AA15" s="38" t="n"/>
+      <c r="AB15" s="39" t="n"/>
+      <c r="AC15" s="38" t="n"/>
+      <c r="AD15" s="39" t="n"/>
+      <c r="AE15" s="38" t="n"/>
+      <c r="AF15" s="39" t="n"/>
+      <c r="AG15" s="40" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="40" t="n"/>
+      <c r="A16" s="41" t="n"/>
       <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Lớp 4</t>
         </is>
       </c>
-      <c r="C16" s="37" t="n"/>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="37" t="n"/>
-      <c r="F16" s="38" t="n"/>
-      <c r="G16" s="37" t="n"/>
-      <c r="H16" s="38" t="n"/>
-      <c r="I16" s="37" t="inlineStr">
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="38" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="38" t="n"/>
+      <c r="H16" s="39" t="n"/>
+      <c r="I16" s="38" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
-      <c r="K16" s="37" t="n"/>
-      <c r="L16" s="38" t="n"/>
-      <c r="M16" s="37" t="n"/>
-      <c r="N16" s="38" t="n"/>
-      <c r="O16" s="37" t="n"/>
-      <c r="P16" s="38" t="n"/>
-      <c r="Q16" s="37" t="n"/>
-      <c r="R16" s="38" t="n"/>
-      <c r="S16" s="37" t="n"/>
-      <c r="T16" s="38" t="n"/>
-      <c r="U16" s="37" t="n"/>
-      <c r="V16" s="38" t="n"/>
-      <c r="W16" s="37" t="n"/>
-      <c r="X16" s="38" t="n"/>
-      <c r="Y16" s="37" t="n"/>
-      <c r="Z16" s="38" t="n"/>
-      <c r="AA16" s="37" t="n"/>
-      <c r="AB16" s="38" t="n"/>
-      <c r="AC16" s="37" t="n"/>
-      <c r="AD16" s="38" t="n"/>
-      <c r="AE16" s="37" t="n"/>
-      <c r="AF16" s="38" t="n"/>
-      <c r="AG16" s="39" t="n"/>
+      <c r="J16" s="39" t="n"/>
+      <c r="K16" s="38" t="n"/>
+      <c r="L16" s="39" t="n"/>
+      <c r="M16" s="38" t="n"/>
+      <c r="N16" s="39" t="n"/>
+      <c r="O16" s="38" t="n"/>
+      <c r="P16" s="39" t="n"/>
+      <c r="Q16" s="38" t="n"/>
+      <c r="R16" s="39" t="n"/>
+      <c r="S16" s="38" t="n"/>
+      <c r="T16" s="39" t="n"/>
+      <c r="U16" s="38" t="n"/>
+      <c r="V16" s="39" t="n"/>
+      <c r="W16" s="38" t="n"/>
+      <c r="X16" s="39" t="n"/>
+      <c r="Y16" s="38" t="n"/>
+      <c r="Z16" s="39" t="n"/>
+      <c r="AA16" s="38" t="n"/>
+      <c r="AB16" s="39" t="n"/>
+      <c r="AC16" s="38" t="n"/>
+      <c r="AD16" s="39" t="n"/>
+      <c r="AE16" s="38" t="n"/>
+      <c r="AF16" s="39" t="n"/>
+      <c r="AG16" s="40" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="40" t="n"/>
+      <c r="A17" s="41" t="n"/>
       <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Lớp 5</t>
         </is>
       </c>
-      <c r="C17" s="37" t="n"/>
-      <c r="D17" s="38" t="n"/>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="38" t="n"/>
-      <c r="G17" s="37" t="n"/>
-      <c r="H17" s="38" t="n"/>
-      <c r="I17" s="37" t="n"/>
-      <c r="J17" s="38" t="n"/>
-      <c r="K17" s="37" t="n"/>
-      <c r="L17" s="38" t="n"/>
-      <c r="M17" s="37" t="n"/>
-      <c r="N17" s="38" t="n"/>
-      <c r="O17" s="37" t="n"/>
-      <c r="P17" s="38" t="n"/>
-      <c r="Q17" s="37" t="n"/>
-      <c r="R17" s="38" t="n"/>
-      <c r="S17" s="37" t="n"/>
-      <c r="T17" s="38" t="n"/>
-      <c r="U17" s="37" t="n"/>
-      <c r="V17" s="38" t="n"/>
-      <c r="W17" s="37" t="n"/>
-      <c r="X17" s="38" t="n"/>
-      <c r="Y17" s="37" t="n"/>
-      <c r="Z17" s="38" t="n"/>
-      <c r="AA17" s="37" t="n"/>
-      <c r="AB17" s="38" t="n"/>
-      <c r="AC17" s="37" t="n"/>
-      <c r="AD17" s="38" t="n"/>
-      <c r="AE17" s="37" t="n"/>
-      <c r="AF17" s="38" t="n"/>
-      <c r="AG17" s="39" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="38" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="38" t="n"/>
+      <c r="H17" s="39" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="39" t="n"/>
+      <c r="K17" s="38" t="n"/>
+      <c r="L17" s="39" t="n"/>
+      <c r="M17" s="38" t="n"/>
+      <c r="N17" s="39" t="n"/>
+      <c r="O17" s="38" t="n"/>
+      <c r="P17" s="39" t="n"/>
+      <c r="Q17" s="38" t="n"/>
+      <c r="R17" s="39" t="n"/>
+      <c r="S17" s="38" t="n"/>
+      <c r="T17" s="39" t="n"/>
+      <c r="U17" s="38" t="n"/>
+      <c r="V17" s="39" t="n"/>
+      <c r="W17" s="38" t="n"/>
+      <c r="X17" s="39" t="n"/>
+      <c r="Y17" s="38" t="n"/>
+      <c r="Z17" s="39" t="n"/>
+      <c r="AA17" s="38" t="n"/>
+      <c r="AB17" s="39" t="n"/>
+      <c r="AC17" s="38" t="n"/>
+      <c r="AD17" s="39" t="n"/>
+      <c r="AE17" s="38" t="n"/>
+      <c r="AF17" s="39" t="n"/>
+      <c r="AG17" s="40" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG
 LỚP DƯỚI</t>
@@ -3062,1859 +3128,1859 @@
           <t>Lớp 5</t>
         </is>
       </c>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="38" t="n"/>
-      <c r="G18" s="37" t="n"/>
-      <c r="H18" s="38" t="n"/>
-      <c r="I18" s="37" t="n"/>
-      <c r="J18" s="38" t="n"/>
-      <c r="K18" s="37" t="n"/>
-      <c r="L18" s="38" t="n"/>
-      <c r="M18" s="37" t="n"/>
-      <c r="N18" s="38" t="n"/>
-      <c r="O18" s="37" t="n"/>
-      <c r="P18" s="38" t="n"/>
-      <c r="Q18" s="37" t="n"/>
-      <c r="R18" s="38" t="n"/>
-      <c r="S18" s="37" t="n"/>
-      <c r="T18" s="38" t="n"/>
-      <c r="U18" s="37" t="n"/>
-      <c r="V18" s="38" t="n"/>
-      <c r="W18" s="37" t="n"/>
-      <c r="X18" s="38" t="n"/>
-      <c r="Y18" s="37" t="n"/>
-      <c r="Z18" s="38" t="n"/>
-      <c r="AA18" s="37" t="n"/>
-      <c r="AB18" s="38" t="n"/>
-      <c r="AC18" s="37" t="n"/>
-      <c r="AD18" s="38" t="n"/>
-      <c r="AE18" s="37" t="n"/>
-      <c r="AF18" s="38" t="n"/>
-      <c r="AG18" s="39" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="38" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="39" t="n"/>
+      <c r="I18" s="38" t="n"/>
+      <c r="J18" s="39" t="n"/>
+      <c r="K18" s="38" t="n"/>
+      <c r="L18" s="39" t="n"/>
+      <c r="M18" s="38" t="n"/>
+      <c r="N18" s="39" t="n"/>
+      <c r="O18" s="38" t="n"/>
+      <c r="P18" s="39" t="n"/>
+      <c r="Q18" s="38" t="n"/>
+      <c r="R18" s="39" t="n"/>
+      <c r="S18" s="38" t="n"/>
+      <c r="T18" s="39" t="n"/>
+      <c r="U18" s="38" t="n"/>
+      <c r="V18" s="39" t="n"/>
+      <c r="W18" s="38" t="n"/>
+      <c r="X18" s="39" t="n"/>
+      <c r="Y18" s="38" t="n"/>
+      <c r="Z18" s="39" t="n"/>
+      <c r="AA18" s="38" t="n"/>
+      <c r="AB18" s="39" t="n"/>
+      <c r="AC18" s="38" t="n"/>
+      <c r="AD18" s="39" t="n"/>
+      <c r="AE18" s="38" t="n"/>
+      <c r="AF18" s="39" t="n"/>
+      <c r="AG18" s="40" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="40" t="n"/>
+      <c r="A19" s="41" t="n"/>
       <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Lớp 4</t>
         </is>
       </c>
-      <c r="C19" s="37" t="n"/>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="37" t="n"/>
-      <c r="F19" s="38" t="n"/>
-      <c r="G19" s="37" t="n"/>
-      <c r="H19" s="38" t="n"/>
-      <c r="I19" s="37" t="n"/>
-      <c r="J19" s="38" t="n"/>
-      <c r="K19" s="37" t="n"/>
-      <c r="L19" s="38" t="n"/>
-      <c r="M19" s="37" t="n"/>
-      <c r="N19" s="38" t="n"/>
-      <c r="O19" s="37" t="n"/>
-      <c r="P19" s="38" t="n"/>
-      <c r="Q19" s="37" t="n"/>
-      <c r="R19" s="38" t="n"/>
-      <c r="S19" s="37" t="n"/>
-      <c r="T19" s="38" t="n"/>
-      <c r="U19" s="37" t="n"/>
-      <c r="V19" s="38" t="n"/>
-      <c r="W19" s="37" t="n"/>
-      <c r="X19" s="38" t="n"/>
-      <c r="Y19" s="37" t="n"/>
-      <c r="Z19" s="38" t="n"/>
-      <c r="AA19" s="37" t="n"/>
-      <c r="AB19" s="38" t="n"/>
-      <c r="AC19" s="37" t="n"/>
-      <c r="AD19" s="38" t="n"/>
-      <c r="AE19" s="37" t="n"/>
-      <c r="AF19" s="38" t="n"/>
-      <c r="AG19" s="39" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="39" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="39" t="n"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="39" t="n"/>
+      <c r="M19" s="38" t="n"/>
+      <c r="N19" s="39" t="n"/>
+      <c r="O19" s="38" t="n"/>
+      <c r="P19" s="39" t="n"/>
+      <c r="Q19" s="38" t="n"/>
+      <c r="R19" s="39" t="n"/>
+      <c r="S19" s="38" t="n"/>
+      <c r="T19" s="39" t="n"/>
+      <c r="U19" s="38" t="n"/>
+      <c r="V19" s="39" t="n"/>
+      <c r="W19" s="38" t="n"/>
+      <c r="X19" s="39" t="n"/>
+      <c r="Y19" s="38" t="n"/>
+      <c r="Z19" s="39" t="n"/>
+      <c r="AA19" s="38" t="n"/>
+      <c r="AB19" s="39" t="n"/>
+      <c r="AC19" s="38" t="n"/>
+      <c r="AD19" s="39" t="n"/>
+      <c r="AE19" s="38" t="n"/>
+      <c r="AF19" s="39" t="n"/>
+      <c r="AG19" s="40" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="40" t="n"/>
+      <c r="A20" s="41" t="n"/>
       <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Lớp 3</t>
         </is>
       </c>
-      <c r="C20" s="37" t="n"/>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>3t25</t>
         </is>
       </c>
-      <c r="E20" s="37" t="n"/>
-      <c r="F20" s="38" t="inlineStr">
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="39" t="inlineStr">
         <is>
           <t>2t25</t>
         </is>
       </c>
-      <c r="G20" s="37" t="n"/>
-      <c r="H20" s="38" t="n"/>
-      <c r="I20" s="37" t="n"/>
-      <c r="J20" s="38" t="n"/>
-      <c r="K20" s="37" t="n"/>
-      <c r="L20" s="38" t="n"/>
-      <c r="M20" s="37" t="n"/>
-      <c r="N20" s="38" t="n"/>
-      <c r="O20" s="37" t="n"/>
-      <c r="P20" s="38" t="n"/>
-      <c r="Q20" s="37" t="n"/>
-      <c r="R20" s="38" t="n"/>
-      <c r="S20" s="37" t="n"/>
-      <c r="T20" s="38" t="n"/>
-      <c r="U20" s="37" t="n"/>
-      <c r="V20" s="38" t="n"/>
-      <c r="W20" s="37" t="n"/>
-      <c r="X20" s="38" t="n"/>
-      <c r="Y20" s="37" t="n"/>
-      <c r="Z20" s="38" t="n"/>
-      <c r="AA20" s="37" t="n"/>
-      <c r="AB20" s="38" t="n"/>
-      <c r="AC20" s="37" t="n"/>
-      <c r="AD20" s="38" t="n"/>
-      <c r="AE20" s="37" t="n"/>
-      <c r="AF20" s="38" t="n"/>
-      <c r="AG20" s="39" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="39" t="n"/>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="39" t="n"/>
+      <c r="K20" s="38" t="n"/>
+      <c r="L20" s="39" t="n"/>
+      <c r="M20" s="38" t="n"/>
+      <c r="N20" s="39" t="n"/>
+      <c r="O20" s="38" t="n"/>
+      <c r="P20" s="39" t="n"/>
+      <c r="Q20" s="38" t="n"/>
+      <c r="R20" s="39" t="n"/>
+      <c r="S20" s="38" t="n"/>
+      <c r="T20" s="39" t="n"/>
+      <c r="U20" s="38" t="n"/>
+      <c r="V20" s="39" t="n"/>
+      <c r="W20" s="38" t="n"/>
+      <c r="X20" s="39" t="n"/>
+      <c r="Y20" s="38" t="n"/>
+      <c r="Z20" s="39" t="n"/>
+      <c r="AA20" s="38" t="n"/>
+      <c r="AB20" s="39" t="n"/>
+      <c r="AC20" s="38" t="n"/>
+      <c r="AD20" s="39" t="n"/>
+      <c r="AE20" s="38" t="n"/>
+      <c r="AF20" s="39" t="n"/>
+      <c r="AG20" s="40" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="40" t="n"/>
+      <c r="A21" s="41" t="n"/>
       <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Lớp 2</t>
         </is>
       </c>
-      <c r="C21" s="37" t="n"/>
-      <c r="D21" s="38" t="inlineStr">
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="E21" s="37" t="n"/>
-      <c r="F21" s="38" t="inlineStr">
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="39" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="G21" s="37" t="n"/>
-      <c r="H21" s="38" t="inlineStr">
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="39" t="inlineStr">
         <is>
           <t>5t28</t>
         </is>
       </c>
-      <c r="I21" s="37" t="n"/>
-      <c r="J21" s="38" t="inlineStr">
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="39" t="inlineStr">
         <is>
           <t>3t28</t>
         </is>
       </c>
-      <c r="K21" s="37" t="n"/>
-      <c r="L21" s="38" t="inlineStr">
+      <c r="K21" s="38" t="n"/>
+      <c r="L21" s="39" t="inlineStr">
         <is>
           <t>2t25</t>
         </is>
       </c>
-      <c r="M21" s="37" t="n"/>
-      <c r="N21" s="38" t="inlineStr">
+      <c r="M21" s="38" t="n"/>
+      <c r="N21" s="39" t="inlineStr">
         <is>
           <t>2t25</t>
         </is>
       </c>
-      <c r="O21" s="37" t="n"/>
-      <c r="P21" s="38" t="n"/>
-      <c r="Q21" s="37" t="n"/>
-      <c r="R21" s="38" t="n"/>
-      <c r="S21" s="37" t="n"/>
-      <c r="T21" s="38" t="n"/>
-      <c r="U21" s="37" t="n"/>
-      <c r="V21" s="38" t="n"/>
-      <c r="W21" s="37" t="n"/>
-      <c r="X21" s="38" t="n"/>
-      <c r="Y21" s="37" t="n"/>
-      <c r="Z21" s="38" t="n"/>
-      <c r="AA21" s="37" t="n"/>
-      <c r="AB21" s="38" t="n"/>
-      <c r="AC21" s="37" t="n"/>
-      <c r="AD21" s="38" t="n"/>
-      <c r="AE21" s="37" t="n"/>
-      <c r="AF21" s="38" t="n"/>
-      <c r="AG21" s="39" t="n"/>
+      <c r="O21" s="38" t="n"/>
+      <c r="P21" s="39" t="n"/>
+      <c r="Q21" s="38" t="n"/>
+      <c r="R21" s="39" t="n"/>
+      <c r="S21" s="38" t="n"/>
+      <c r="T21" s="39" t="n"/>
+      <c r="U21" s="38" t="n"/>
+      <c r="V21" s="39" t="n"/>
+      <c r="W21" s="38" t="n"/>
+      <c r="X21" s="39" t="n"/>
+      <c r="Y21" s="38" t="n"/>
+      <c r="Z21" s="39" t="n"/>
+      <c r="AA21" s="38" t="n"/>
+      <c r="AB21" s="39" t="n"/>
+      <c r="AC21" s="38" t="n"/>
+      <c r="AD21" s="39" t="n"/>
+      <c r="AE21" s="38" t="n"/>
+      <c r="AF21" s="39" t="n"/>
+      <c r="AG21" s="40" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="40" t="n"/>
+      <c r="A22" s="41" t="n"/>
       <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Lớp 1</t>
         </is>
       </c>
-      <c r="C22" s="37" t="n"/>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="37" t="n"/>
-      <c r="F22" s="38" t="n"/>
-      <c r="G22" s="37" t="n"/>
-      <c r="H22" s="38" t="n"/>
-      <c r="I22" s="37" t="n"/>
-      <c r="J22" s="38" t="n"/>
-      <c r="K22" s="37" t="n"/>
-      <c r="L22" s="38" t="n"/>
-      <c r="M22" s="37" t="n"/>
-      <c r="N22" s="38" t="n"/>
-      <c r="O22" s="37" t="n"/>
-      <c r="P22" s="38" t="n"/>
-      <c r="Q22" s="37" t="n"/>
-      <c r="R22" s="38" t="n"/>
-      <c r="S22" s="37" t="n"/>
-      <c r="T22" s="38" t="n"/>
-      <c r="U22" s="37" t="n"/>
-      <c r="V22" s="38" t="n"/>
-      <c r="W22" s="37" t="n"/>
-      <c r="X22" s="38" t="n"/>
-      <c r="Y22" s="37" t="n"/>
-      <c r="Z22" s="38" t="n"/>
-      <c r="AA22" s="37" t="n"/>
-      <c r="AB22" s="38" t="n"/>
-      <c r="AC22" s="37" t="n"/>
-      <c r="AD22" s="38" t="n"/>
-      <c r="AE22" s="37" t="n"/>
-      <c r="AF22" s="38" t="n"/>
-      <c r="AG22" s="39" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="38" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="38" t="n"/>
+      <c r="H22" s="39" t="n"/>
+      <c r="I22" s="38" t="n"/>
+      <c r="J22" s="39" t="n"/>
+      <c r="K22" s="38" t="n"/>
+      <c r="L22" s="39" t="n"/>
+      <c r="M22" s="38" t="n"/>
+      <c r="N22" s="39" t="n"/>
+      <c r="O22" s="38" t="n"/>
+      <c r="P22" s="39" t="n"/>
+      <c r="Q22" s="38" t="n"/>
+      <c r="R22" s="39" t="n"/>
+      <c r="S22" s="38" t="n"/>
+      <c r="T22" s="39" t="n"/>
+      <c r="U22" s="38" t="n"/>
+      <c r="V22" s="39" t="n"/>
+      <c r="W22" s="38" t="n"/>
+      <c r="X22" s="39" t="n"/>
+      <c r="Y22" s="38" t="n"/>
+      <c r="Z22" s="39" t="n"/>
+      <c r="AA22" s="38" t="n"/>
+      <c r="AB22" s="39" t="n"/>
+      <c r="AC22" s="38" t="n"/>
+      <c r="AD22" s="39" t="n"/>
+      <c r="AE22" s="38" t="n"/>
+      <c r="AF22" s="39" t="n"/>
+      <c r="AG22" s="40" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>Gối: ẩn cột  ·  Nhịp: đổi thép chạy TRÊN</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="41" t="n"/>
-      <c r="D23" s="34" t="n"/>
-      <c r="E23" s="41" t="n"/>
-      <c r="F23" s="34" t="n"/>
-      <c r="G23" s="41" t="n"/>
-      <c r="H23" s="34" t="inlineStr">
+      <c r="C23" s="42" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="42" t="n"/>
+      <c r="H23" s="35" t="inlineStr">
         <is>
           <t>0;5t28</t>
         </is>
       </c>
-      <c r="I23" s="41" t="n"/>
-      <c r="J23" s="34" t="n"/>
-      <c r="K23" s="41" t="n"/>
-      <c r="L23" s="34" t="inlineStr">
+      <c r="I23" s="42" t="n"/>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="42" t="n"/>
+      <c r="L23" s="35" t="inlineStr">
         <is>
           <t>0;3t28</t>
         </is>
       </c>
-      <c r="M23" s="41" t="n"/>
-      <c r="N23" s="34" t="n"/>
-      <c r="O23" s="41" t="n"/>
-      <c r="P23" s="34" t="n"/>
-      <c r="Q23" s="41" t="n"/>
-      <c r="R23" s="34" t="n"/>
-      <c r="S23" s="41" t="n"/>
-      <c r="T23" s="34" t="n"/>
-      <c r="U23" s="41" t="n"/>
-      <c r="V23" s="34" t="n"/>
-      <c r="W23" s="41" t="n"/>
-      <c r="X23" s="34" t="n"/>
-      <c r="Y23" s="41" t="n"/>
-      <c r="Z23" s="34" t="n"/>
-      <c r="AA23" s="41" t="n"/>
-      <c r="AB23" s="34" t="n"/>
-      <c r="AC23" s="41" t="n"/>
-      <c r="AD23" s="34" t="n"/>
-      <c r="AE23" s="41" t="n"/>
-      <c r="AF23" s="34" t="n"/>
-      <c r="AG23" s="42" t="n"/>
+      <c r="M23" s="42" t="n"/>
+      <c r="N23" s="35" t="n"/>
+      <c r="O23" s="42" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="42" t="n"/>
+      <c r="R23" s="35" t="n"/>
+      <c r="S23" s="42" t="n"/>
+      <c r="T23" s="35" t="n"/>
+      <c r="U23" s="42" t="n"/>
+      <c r="V23" s="35" t="n"/>
+      <c r="W23" s="42" t="n"/>
+      <c r="X23" s="35" t="n"/>
+      <c r="Y23" s="42" t="n"/>
+      <c r="Z23" s="35" t="n"/>
+      <c r="AA23" s="42" t="n"/>
+      <c r="AB23" s="35" t="n"/>
+      <c r="AC23" s="42" t="n"/>
+      <c r="AD23" s="35" t="n"/>
+      <c r="AE23" s="42" t="n"/>
+      <c r="AF23" s="35" t="n"/>
+      <c r="AG23" s="43" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>Gối: dầm giao tại cột  ·  Nhịp: thép giá</t>
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
-      <c r="C24" s="41" t="n"/>
-      <c r="D24" s="34" t="inlineStr">
+      <c r="C24" s="42" t="n"/>
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>2x2t12</t>
         </is>
       </c>
-      <c r="E24" s="41" t="n"/>
-      <c r="F24" s="34" t="inlineStr">
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="35" t="inlineStr">
         <is>
           <t>2x2t12</t>
         </is>
       </c>
-      <c r="G24" s="41" t="n"/>
-      <c r="H24" s="34" t="inlineStr">
+      <c r="G24" s="42" t="n"/>
+      <c r="H24" s="35" t="inlineStr">
         <is>
           <t>2x2t12</t>
         </is>
       </c>
-      <c r="I24" s="41" t="n"/>
-      <c r="J24" s="34" t="inlineStr">
+      <c r="I24" s="42" t="n"/>
+      <c r="J24" s="35" t="inlineStr">
         <is>
           <t>2x2t12</t>
         </is>
       </c>
-      <c r="K24" s="41" t="n"/>
-      <c r="L24" s="34" t="inlineStr">
+      <c r="K24" s="42" t="n"/>
+      <c r="L24" s="35" t="inlineStr">
         <is>
           <t>2x2t12</t>
         </is>
       </c>
-      <c r="M24" s="41" t="n"/>
-      <c r="N24" s="34" t="inlineStr">
+      <c r="M24" s="42" t="n"/>
+      <c r="N24" s="35" t="inlineStr">
         <is>
           <t>2x2t12</t>
         </is>
       </c>
-      <c r="O24" s="41" t="n"/>
-      <c r="P24" s="34" t="n"/>
-      <c r="Q24" s="41" t="n"/>
-      <c r="R24" s="34" t="n"/>
-      <c r="S24" s="41" t="n"/>
-      <c r="T24" s="34" t="n"/>
-      <c r="U24" s="41" t="n"/>
-      <c r="V24" s="34" t="n"/>
-      <c r="W24" s="41" t="n"/>
-      <c r="X24" s="34" t="n"/>
-      <c r="Y24" s="41" t="n"/>
-      <c r="Z24" s="34" t="n"/>
-      <c r="AA24" s="41" t="n"/>
-      <c r="AB24" s="34" t="n"/>
-      <c r="AC24" s="41" t="n"/>
-      <c r="AD24" s="34" t="n"/>
-      <c r="AE24" s="41" t="n"/>
-      <c r="AF24" s="34" t="n"/>
-      <c r="AG24" s="42" t="n"/>
+      <c r="O24" s="42" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="42" t="n"/>
+      <c r="R24" s="35" t="n"/>
+      <c r="S24" s="42" t="n"/>
+      <c r="T24" s="35" t="n"/>
+      <c r="U24" s="42" t="n"/>
+      <c r="V24" s="35" t="n"/>
+      <c r="W24" s="42" t="n"/>
+      <c r="X24" s="35" t="n"/>
+      <c r="Y24" s="42" t="n"/>
+      <c r="Z24" s="35" t="n"/>
+      <c r="AA24" s="42" t="n"/>
+      <c r="AB24" s="35" t="n"/>
+      <c r="AC24" s="42" t="n"/>
+      <c r="AD24" s="35" t="n"/>
+      <c r="AE24" s="42" t="n"/>
+      <c r="AF24" s="35" t="n"/>
+      <c r="AG24" s="43" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>Gối: lệch dầm giao  ·  Nhịp: đổi thép chạy DƯỚI</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
-      <c r="C25" s="41" t="n"/>
-      <c r="D25" s="34" t="n"/>
-      <c r="E25" s="41" t="n"/>
-      <c r="F25" s="34" t="n"/>
-      <c r="G25" s="41" t="n"/>
-      <c r="H25" s="34" t="inlineStr">
+      <c r="C25" s="42" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="42" t="n"/>
+      <c r="H25" s="35" t="inlineStr">
         <is>
           <t>0;5t28</t>
         </is>
       </c>
-      <c r="I25" s="41" t="n"/>
-      <c r="J25" s="34" t="n"/>
-      <c r="K25" s="41" t="n"/>
-      <c r="L25" s="34" t="inlineStr">
+      <c r="I25" s="42" t="n"/>
+      <c r="J25" s="35" t="n"/>
+      <c r="K25" s="42" t="n"/>
+      <c r="L25" s="35" t="inlineStr">
         <is>
           <t>0;3t28</t>
         </is>
       </c>
-      <c r="M25" s="41" t="n"/>
-      <c r="N25" s="34" t="n"/>
-      <c r="O25" s="41" t="n"/>
-      <c r="P25" s="34" t="n"/>
-      <c r="Q25" s="41" t="n"/>
-      <c r="R25" s="34" t="n"/>
-      <c r="S25" s="41" t="n"/>
-      <c r="T25" s="34" t="n"/>
-      <c r="U25" s="41" t="n"/>
-      <c r="V25" s="34" t="n"/>
-      <c r="W25" s="41" t="n"/>
-      <c r="X25" s="34" t="n"/>
-      <c r="Y25" s="41" t="n"/>
-      <c r="Z25" s="34" t="n"/>
-      <c r="AA25" s="41" t="n"/>
-      <c r="AB25" s="34" t="n"/>
-      <c r="AC25" s="41" t="n"/>
-      <c r="AD25" s="34" t="n"/>
-      <c r="AE25" s="41" t="n"/>
-      <c r="AF25" s="34" t="n"/>
-      <c r="AG25" s="42" t="n"/>
+      <c r="M25" s="42" t="n"/>
+      <c r="N25" s="35" t="n"/>
+      <c r="O25" s="42" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="42" t="n"/>
+      <c r="R25" s="35" t="n"/>
+      <c r="S25" s="42" t="n"/>
+      <c r="T25" s="35" t="n"/>
+      <c r="U25" s="42" t="n"/>
+      <c r="V25" s="35" t="n"/>
+      <c r="W25" s="42" t="n"/>
+      <c r="X25" s="35" t="n"/>
+      <c r="Y25" s="42" t="n"/>
+      <c r="Z25" s="35" t="n"/>
+      <c r="AA25" s="42" t="n"/>
+      <c r="AB25" s="35" t="n"/>
+      <c r="AC25" s="42" t="n"/>
+      <c r="AD25" s="35" t="n"/>
+      <c r="AE25" s="42" t="n"/>
+      <c r="AF25" s="35" t="n"/>
+      <c r="AG25" s="43" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>Gối: tên trục  ·  Nhịp: thép đai</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
-      <c r="C26" s="41" t="inlineStr">
+      <c r="C26" s="42" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
         <is>
           <t>10-100/150</t>
         </is>
       </c>
-      <c r="E26" s="41" t="inlineStr">
+      <c r="E26" s="42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F26" s="34" t="inlineStr">
+      <c r="F26" s="35" t="inlineStr">
         <is>
           <t>10-100/150</t>
         </is>
       </c>
-      <c r="G26" s="41" t="inlineStr">
+      <c r="G26" s="42" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H26" s="34" t="inlineStr">
+      <c r="H26" s="35" t="inlineStr">
         <is>
           <t>12-100/150</t>
         </is>
       </c>
-      <c r="I26" s="41" t="inlineStr">
+      <c r="I26" s="42" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J26" s="34" t="inlineStr">
+      <c r="J26" s="35" t="inlineStr">
         <is>
           <t>12-100/150</t>
         </is>
       </c>
-      <c r="K26" s="41" t="inlineStr">
+      <c r="K26" s="42" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L26" s="34" t="inlineStr">
+      <c r="L26" s="35" t="inlineStr">
         <is>
           <t>10-100/200</t>
         </is>
       </c>
-      <c r="M26" s="41" t="inlineStr">
+      <c r="M26" s="42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N26" s="34" t="inlineStr">
+      <c r="N26" s="35" t="inlineStr">
         <is>
           <t>10-100/200</t>
         </is>
       </c>
-      <c r="O26" s="41" t="inlineStr">
+      <c r="O26" s="42" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P26" s="34" t="n"/>
-      <c r="Q26" s="41" t="n"/>
-      <c r="R26" s="34" t="n"/>
-      <c r="S26" s="41" t="n"/>
-      <c r="T26" s="34" t="n"/>
-      <c r="U26" s="41" t="n"/>
-      <c r="V26" s="34" t="n"/>
-      <c r="W26" s="41" t="n"/>
-      <c r="X26" s="34" t="n"/>
-      <c r="Y26" s="41" t="n"/>
-      <c r="Z26" s="34" t="n"/>
-      <c r="AA26" s="41" t="n"/>
-      <c r="AB26" s="34" t="n"/>
-      <c r="AC26" s="41" t="n"/>
-      <c r="AD26" s="34" t="n"/>
-      <c r="AE26" s="41" t="n"/>
-      <c r="AF26" s="34" t="n"/>
-      <c r="AG26" s="42" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="42" t="n"/>
+      <c r="R26" s="35" t="n"/>
+      <c r="S26" s="42" t="n"/>
+      <c r="T26" s="35" t="n"/>
+      <c r="U26" s="42" t="n"/>
+      <c r="V26" s="35" t="n"/>
+      <c r="W26" s="42" t="n"/>
+      <c r="X26" s="35" t="n"/>
+      <c r="Y26" s="42" t="n"/>
+      <c r="Z26" s="35" t="n"/>
+      <c r="AA26" s="42" t="n"/>
+      <c r="AB26" s="35" t="n"/>
+      <c r="AC26" s="42" t="n"/>
+      <c r="AD26" s="35" t="n"/>
+      <c r="AE26" s="42" t="n"/>
+      <c r="AF26" s="35" t="n"/>
+      <c r="AG26" s="43" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>Gối: lệch trục  ·  Nhịp: đai trong / cắt thép</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
-      <c r="C27" s="41" t="n">
+      <c r="C27" s="42" t="n">
         <v>-149.2</v>
       </c>
-      <c r="D27" s="34" t="n"/>
-      <c r="E27" s="41" t="n">
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="42" t="n">
         <v>700</v>
       </c>
-      <c r="F27" s="34" t="n"/>
-      <c r="G27" s="41" t="n">
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="42" t="n">
         <v>-0.8</v>
       </c>
-      <c r="H27" s="34" t="n"/>
-      <c r="I27" s="41" t="n">
+      <c r="H27" s="35" t="n"/>
+      <c r="I27" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="34" t="n"/>
-      <c r="K27" s="41" t="n">
+      <c r="J27" s="35" t="n"/>
+      <c r="K27" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="34" t="n"/>
-      <c r="M27" s="41" t="n">
+      <c r="L27" s="35" t="n"/>
+      <c r="M27" s="42" t="n">
         <v>-20.1</v>
       </c>
-      <c r="N27" s="34" t="n"/>
-      <c r="O27" s="41" t="n">
+      <c r="N27" s="35" t="n"/>
+      <c r="O27" s="42" t="n">
         <v>0.3</v>
       </c>
-      <c r="P27" s="34" t="n"/>
-      <c r="Q27" s="41" t="n"/>
-      <c r="R27" s="34" t="n"/>
-      <c r="S27" s="41" t="n"/>
-      <c r="T27" s="34" t="n"/>
-      <c r="U27" s="41" t="n"/>
-      <c r="V27" s="34" t="n"/>
-      <c r="W27" s="41" t="n"/>
-      <c r="X27" s="34" t="n"/>
-      <c r="Y27" s="41" t="n"/>
-      <c r="Z27" s="34" t="n"/>
-      <c r="AA27" s="41" t="n"/>
-      <c r="AB27" s="34" t="n"/>
-      <c r="AC27" s="41" t="n"/>
-      <c r="AD27" s="34" t="n"/>
-      <c r="AE27" s="41" t="n"/>
-      <c r="AF27" s="34" t="n"/>
-      <c r="AG27" s="42" t="n"/>
+      <c r="P27" s="35" t="n"/>
+      <c r="Q27" s="42" t="n"/>
+      <c r="R27" s="35" t="n"/>
+      <c r="S27" s="42" t="n"/>
+      <c r="T27" s="35" t="n"/>
+      <c r="U27" s="42" t="n"/>
+      <c r="V27" s="35" t="n"/>
+      <c r="W27" s="42" t="n"/>
+      <c r="X27" s="35" t="n"/>
+      <c r="Y27" s="42" t="n"/>
+      <c r="Z27" s="35" t="n"/>
+      <c r="AA27" s="42" t="n"/>
+      <c r="AB27" s="35" t="n"/>
+      <c r="AC27" s="42" t="n"/>
+      <c r="AD27" s="35" t="n"/>
+      <c r="AE27" s="42" t="n"/>
+      <c r="AF27" s="35" t="n"/>
+      <c r="AG27" s="43" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>Gối: dầm giao trong nhịp phải  ·  Nhịp: kiểu đai</t>
         </is>
       </c>
       <c r="B28" s="6" t="n"/>
-      <c r="C28" s="41" t="inlineStr">
+      <c r="C28" s="42" t="inlineStr">
         <is>
           <t>400x600</t>
         </is>
       </c>
-      <c r="D28" s="34" t="n"/>
-      <c r="E28" s="41" t="inlineStr">
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="42" t="inlineStr">
         <is>
           <t>400x600</t>
         </is>
       </c>
-      <c r="F28" s="34" t="n"/>
-      <c r="G28" s="41" t="inlineStr">
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="42" t="inlineStr">
         <is>
           <t>400x600</t>
         </is>
       </c>
-      <c r="H28" s="34" t="n"/>
-      <c r="I28" s="41" t="inlineStr">
+      <c r="H28" s="35" t="n"/>
+      <c r="I28" s="42" t="inlineStr">
         <is>
           <t>400x600</t>
         </is>
       </c>
-      <c r="J28" s="34" t="n"/>
-      <c r="K28" s="41" t="inlineStr">
+      <c r="J28" s="35" t="n"/>
+      <c r="K28" s="42" t="inlineStr">
         <is>
           <t>300x600</t>
         </is>
       </c>
-      <c r="L28" s="34" t="n"/>
-      <c r="M28" s="41" t="inlineStr">
+      <c r="L28" s="35" t="n"/>
+      <c r="M28" s="42" t="inlineStr">
         <is>
           <t>300x600</t>
         </is>
       </c>
-      <c r="N28" s="34" t="n"/>
-      <c r="O28" s="41" t="n"/>
-      <c r="P28" s="34" t="n"/>
-      <c r="Q28" s="41" t="n"/>
-      <c r="R28" s="34" t="n"/>
-      <c r="S28" s="41" t="n"/>
-      <c r="T28" s="34" t="n"/>
-      <c r="U28" s="41" t="n"/>
-      <c r="V28" s="34" t="n"/>
-      <c r="W28" s="41" t="n"/>
-      <c r="X28" s="34" t="n"/>
-      <c r="Y28" s="41" t="n"/>
-      <c r="Z28" s="34" t="n"/>
-      <c r="AA28" s="41" t="n"/>
-      <c r="AB28" s="34" t="n"/>
-      <c r="AC28" s="41" t="n"/>
-      <c r="AD28" s="34" t="n"/>
-      <c r="AE28" s="41" t="n"/>
-      <c r="AF28" s="34" t="n"/>
-      <c r="AG28" s="42" t="n"/>
+      <c r="N28" s="35" t="n"/>
+      <c r="O28" s="42" t="n"/>
+      <c r="P28" s="35" t="n"/>
+      <c r="Q28" s="42" t="n"/>
+      <c r="R28" s="35" t="n"/>
+      <c r="S28" s="42" t="n"/>
+      <c r="T28" s="35" t="n"/>
+      <c r="U28" s="42" t="n"/>
+      <c r="V28" s="35" t="n"/>
+      <c r="W28" s="42" t="n"/>
+      <c r="X28" s="35" t="n"/>
+      <c r="Y28" s="42" t="n"/>
+      <c r="Z28" s="35" t="n"/>
+      <c r="AA28" s="42" t="n"/>
+      <c r="AB28" s="35" t="n"/>
+      <c r="AC28" s="42" t="n"/>
+      <c r="AD28" s="35" t="n"/>
+      <c r="AE28" s="42" t="n"/>
+      <c r="AF28" s="35" t="n"/>
+      <c r="AG28" s="43" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>Gối: vị trí dầm giao  ·  Nhịp: đai gia cường</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
-      <c r="C29" s="41" t="n">
+      <c r="C29" s="42" t="n">
         <v>3950</v>
       </c>
-      <c r="D29" s="34" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
         <is>
           <t>10t10a50</t>
         </is>
       </c>
-      <c r="E29" s="41" t="n">
+      <c r="E29" s="42" t="n">
         <v>4900</v>
       </c>
-      <c r="F29" s="34" t="inlineStr">
+      <c r="F29" s="35" t="inlineStr">
         <is>
           <t>10t10a50</t>
         </is>
       </c>
-      <c r="G29" s="41" t="n">
+      <c r="G29" s="42" t="n">
         <v>4175</v>
       </c>
-      <c r="H29" s="34" t="inlineStr">
+      <c r="H29" s="35" t="inlineStr">
         <is>
           <t>10t10a50</t>
         </is>
       </c>
-      <c r="I29" s="41" t="n">
+      <c r="I29" s="42" t="n">
         <v>3120</v>
       </c>
-      <c r="J29" s="34" t="inlineStr">
+      <c r="J29" s="35" t="inlineStr">
         <is>
           <t>10t10a50</t>
         </is>
       </c>
-      <c r="K29" s="41" t="n">
+      <c r="K29" s="42" t="n">
         <v>3300</v>
       </c>
-      <c r="L29" s="34" t="inlineStr">
+      <c r="L29" s="35" t="inlineStr">
         <is>
           <t>10t10a50</t>
         </is>
       </c>
-      <c r="M29" s="41" t="n">
+      <c r="M29" s="42" t="n">
         <v>2260</v>
       </c>
-      <c r="N29" s="34" t="inlineStr">
+      <c r="N29" s="35" t="inlineStr">
         <is>
           <t>10t10a50</t>
         </is>
       </c>
-      <c r="O29" s="41" t="n"/>
-      <c r="P29" s="34" t="n"/>
-      <c r="Q29" s="41" t="n"/>
-      <c r="R29" s="34" t="n"/>
-      <c r="S29" s="41" t="n"/>
-      <c r="T29" s="34" t="n"/>
-      <c r="U29" s="41" t="n"/>
-      <c r="V29" s="34" t="n"/>
-      <c r="W29" s="41" t="n"/>
-      <c r="X29" s="34" t="n"/>
-      <c r="Y29" s="41" t="n"/>
-      <c r="Z29" s="34" t="n"/>
-      <c r="AA29" s="41" t="n"/>
-      <c r="AB29" s="34" t="n"/>
-      <c r="AC29" s="41" t="n"/>
-      <c r="AD29" s="34" t="n"/>
-      <c r="AE29" s="41" t="n"/>
-      <c r="AF29" s="34" t="n"/>
-      <c r="AG29" s="42" t="n"/>
+      <c r="O29" s="42" t="n"/>
+      <c r="P29" s="35" t="n"/>
+      <c r="Q29" s="42" t="n"/>
+      <c r="R29" s="35" t="n"/>
+      <c r="S29" s="42" t="n"/>
+      <c r="T29" s="35" t="n"/>
+      <c r="U29" s="42" t="n"/>
+      <c r="V29" s="35" t="n"/>
+      <c r="W29" s="42" t="n"/>
+      <c r="X29" s="35" t="n"/>
+      <c r="Y29" s="42" t="n"/>
+      <c r="Z29" s="35" t="n"/>
+      <c r="AA29" s="42" t="n"/>
+      <c r="AB29" s="35" t="n"/>
+      <c r="AC29" s="42" t="n"/>
+      <c r="AD29" s="35" t="n"/>
+      <c r="AE29" s="42" t="n"/>
+      <c r="AF29" s="35" t="n"/>
+      <c r="AG29" s="43" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>Nhịp: thép vai bò tại dầm giao</t>
         </is>
       </c>
-      <c r="B30" s="44" t="n"/>
-      <c r="C30" s="45" t="inlineStr"/>
-      <c r="D30" s="46" t="n"/>
-      <c r="E30" s="45" t="inlineStr"/>
-      <c r="F30" s="46" t="n"/>
-      <c r="G30" s="45" t="inlineStr"/>
-      <c r="H30" s="46" t="n"/>
-      <c r="I30" s="45" t="inlineStr"/>
-      <c r="J30" s="46" t="n"/>
-      <c r="K30" s="45" t="inlineStr"/>
-      <c r="L30" s="46" t="n"/>
-      <c r="M30" s="45" t="inlineStr"/>
-      <c r="N30" s="46" t="n"/>
-      <c r="O30" s="45" t="inlineStr"/>
-      <c r="P30" s="46" t="n"/>
-      <c r="Q30" s="45" t="inlineStr"/>
-      <c r="R30" s="46" t="n"/>
-      <c r="S30" s="45" t="inlineStr"/>
-      <c r="T30" s="46" t="n"/>
-      <c r="U30" s="45" t="inlineStr"/>
-      <c r="V30" s="46" t="n"/>
-      <c r="W30" s="45" t="inlineStr"/>
-      <c r="X30" s="46" t="n"/>
-      <c r="Y30" s="45" t="inlineStr"/>
-      <c r="Z30" s="46" t="n"/>
-      <c r="AA30" s="45" t="inlineStr"/>
-      <c r="AB30" s="46" t="n"/>
-      <c r="AC30" s="45" t="inlineStr"/>
-      <c r="AD30" s="46" t="n"/>
-      <c r="AE30" s="45" t="inlineStr"/>
-      <c r="AF30" s="46" t="n"/>
-      <c r="AG30" s="47" t="inlineStr"/>
+      <c r="B30" s="45" t="n"/>
+      <c r="C30" s="46" t="inlineStr"/>
+      <c r="D30" s="47" t="n"/>
+      <c r="E30" s="46" t="inlineStr"/>
+      <c r="F30" s="47" t="n"/>
+      <c r="G30" s="46" t="inlineStr"/>
+      <c r="H30" s="47" t="n"/>
+      <c r="I30" s="46" t="inlineStr"/>
+      <c r="J30" s="47" t="n"/>
+      <c r="K30" s="46" t="inlineStr"/>
+      <c r="L30" s="47" t="n"/>
+      <c r="M30" s="46" t="inlineStr"/>
+      <c r="N30" s="47" t="n"/>
+      <c r="O30" s="46" t="inlineStr"/>
+      <c r="P30" s="47" t="n"/>
+      <c r="Q30" s="46" t="inlineStr"/>
+      <c r="R30" s="47" t="n"/>
+      <c r="S30" s="46" t="inlineStr"/>
+      <c r="T30" s="47" t="n"/>
+      <c r="U30" s="46" t="inlineStr"/>
+      <c r="V30" s="47" t="n"/>
+      <c r="W30" s="46" t="inlineStr"/>
+      <c r="X30" s="47" t="n"/>
+      <c r="Y30" s="46" t="inlineStr"/>
+      <c r="Z30" s="47" t="n"/>
+      <c r="AA30" s="46" t="inlineStr"/>
+      <c r="AB30" s="47" t="n"/>
+      <c r="AC30" s="46" t="inlineStr"/>
+      <c r="AD30" s="47" t="n"/>
+      <c r="AE30" s="46" t="inlineStr"/>
+      <c r="AF30" s="47" t="n"/>
+      <c r="AG30" s="48" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="48" t="inlineStr">
+      <c r="A32" s="49" t="inlineStr">
         <is>
           <t>KIỂM TRA HÌNH HỌC (tự tính – đối chiếu mặt bằng kết cấu)</t>
         </is>
       </c>
-      <c r="B32" s="49" t="n"/>
-      <c r="C32" s="49" t="n"/>
-      <c r="D32" s="49" t="n"/>
-      <c r="E32" s="49" t="n"/>
-      <c r="F32" s="49" t="n"/>
-      <c r="G32" s="49" t="n"/>
-      <c r="H32" s="49" t="n"/>
-      <c r="I32" s="49" t="n"/>
-      <c r="J32" s="49" t="n"/>
-      <c r="K32" s="49" t="n"/>
-      <c r="L32" s="49" t="n"/>
-      <c r="M32" s="49" t="n"/>
-      <c r="N32" s="49" t="n"/>
-      <c r="O32" s="49" t="n"/>
-      <c r="P32" s="49" t="n"/>
-      <c r="Q32" s="49" t="n"/>
-      <c r="R32" s="49" t="n"/>
-      <c r="S32" s="49" t="n"/>
-      <c r="T32" s="49" t="n"/>
-      <c r="U32" s="49" t="n"/>
-      <c r="V32" s="49" t="n"/>
-      <c r="W32" s="49" t="n"/>
-      <c r="X32" s="49" t="n"/>
-      <c r="Y32" s="49" t="n"/>
-      <c r="Z32" s="49" t="n"/>
-      <c r="AA32" s="49" t="n"/>
-      <c r="AB32" s="49" t="n"/>
-      <c r="AC32" s="49" t="n"/>
-      <c r="AD32" s="49" t="n"/>
-      <c r="AE32" s="49" t="n"/>
-      <c r="AF32" s="49" t="n"/>
-      <c r="AG32" s="49" t="n"/>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+      <c r="E32" s="50" t="n"/>
+      <c r="F32" s="50" t="n"/>
+      <c r="G32" s="50" t="n"/>
+      <c r="H32" s="50" t="n"/>
+      <c r="I32" s="50" t="n"/>
+      <c r="J32" s="50" t="n"/>
+      <c r="K32" s="50" t="n"/>
+      <c r="L32" s="50" t="n"/>
+      <c r="M32" s="50" t="n"/>
+      <c r="N32" s="50" t="n"/>
+      <c r="O32" s="50" t="n"/>
+      <c r="P32" s="50" t="n"/>
+      <c r="Q32" s="50" t="n"/>
+      <c r="R32" s="50" t="n"/>
+      <c r="S32" s="50" t="n"/>
+      <c r="T32" s="50" t="n"/>
+      <c r="U32" s="50" t="n"/>
+      <c r="V32" s="50" t="n"/>
+      <c r="W32" s="50" t="n"/>
+      <c r="X32" s="50" t="n"/>
+      <c r="Y32" s="50" t="n"/>
+      <c r="Z32" s="50" t="n"/>
+      <c r="AA32" s="50" t="n"/>
+      <c r="AB32" s="50" t="n"/>
+      <c r="AC32" s="50" t="n"/>
+      <c r="AD32" s="50" t="n"/>
+      <c r="AE32" s="50" t="n"/>
+      <c r="AF32" s="50" t="n"/>
+      <c r="AG32" s="50" t="n"/>
     </row>
     <row r="33" ht="27" customHeight="1">
-      <c r="A33" s="50" t="inlineStr">
+      <c r="A33" s="51" t="inlineStr">
         <is>
           <t>Gối: tọa độ trục (gốc = trục gối 1)  ·  Nhịp: KC trục-trục (mm)</t>
         </is>
       </c>
       <c r="B33" s="6" t="n"/>
-      <c r="C33" s="51">
+      <c r="C33" s="52">
         <f>IF(C63=1,C62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="52">
         <f>IF(D63=1,IFERROR(E62-C62,""),"")</f>
         <v/>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="52">
         <f>IF(E63=1,E62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="F33" s="51">
+      <c r="F33" s="52">
         <f>IF(F63=1,IFERROR(G62-E62,""),"")</f>
         <v/>
       </c>
-      <c r="G33" s="51">
+      <c r="G33" s="52">
         <f>IF(G63=1,G62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="H33" s="51">
+      <c r="H33" s="52">
         <f>IF(H63=1,IFERROR(I62-G62,""),"")</f>
         <v/>
       </c>
-      <c r="I33" s="51">
+      <c r="I33" s="52">
         <f>IF(I63=1,I62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="J33" s="51">
+      <c r="J33" s="52">
         <f>IF(J63=1,IFERROR(K62-I62,""),"")</f>
         <v/>
       </c>
-      <c r="K33" s="51">
+      <c r="K33" s="52">
         <f>IF(K63=1,K62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="L33" s="51">
+      <c r="L33" s="52">
         <f>IF(L63=1,IFERROR(M62-K62,""),"")</f>
         <v/>
       </c>
-      <c r="M33" s="51">
+      <c r="M33" s="52">
         <f>IF(M63=1,M62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="N33" s="51">
+      <c r="N33" s="52">
         <f>IF(N63=1,IFERROR(O62-M62,""),"")</f>
         <v/>
       </c>
-      <c r="O33" s="51">
+      <c r="O33" s="52">
         <f>IF(O63=1,O62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="P33" s="51">
+      <c r="P33" s="52">
         <f>IF(P63=1,IFERROR(Q62-O62,""),"")</f>
         <v/>
       </c>
-      <c r="Q33" s="51">
+      <c r="Q33" s="52">
         <f>IF(Q63=1,Q62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="R33" s="51">
+      <c r="R33" s="52">
         <f>IF(R63=1,IFERROR(S62-Q62,""),"")</f>
         <v/>
       </c>
-      <c r="S33" s="51">
+      <c r="S33" s="52">
         <f>IF(S63=1,S62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="T33" s="51">
+      <c r="T33" s="52">
         <f>IF(T63=1,IFERROR(U62-S62,""),"")</f>
         <v/>
       </c>
-      <c r="U33" s="51">
+      <c r="U33" s="52">
         <f>IF(U63=1,U62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="V33" s="51">
+      <c r="V33" s="52">
         <f>IF(V63=1,IFERROR(W62-U62,""),"")</f>
         <v/>
       </c>
-      <c r="W33" s="51">
+      <c r="W33" s="52">
         <f>IF(W63=1,W62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="X33" s="51">
+      <c r="X33" s="52">
         <f>IF(X63=1,IFERROR(Y62-W62,""),"")</f>
         <v/>
       </c>
-      <c r="Y33" s="51">
+      <c r="Y33" s="52">
         <f>IF(Y63=1,Y62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="Z33" s="51">
+      <c r="Z33" s="52">
         <f>IF(Z63=1,IFERROR(AA62-Y62,""),"")</f>
         <v/>
       </c>
-      <c r="AA33" s="51">
+      <c r="AA33" s="52">
         <f>IF(AA63=1,AA62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="AB33" s="51">
+      <c r="AB33" s="52">
         <f>IF(AB63=1,IFERROR(AC62-AA62,""),"")</f>
         <v/>
       </c>
-      <c r="AC33" s="51">
+      <c r="AC33" s="52">
         <f>IF(AC63=1,AC62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="AD33" s="51">
+      <c r="AD33" s="52">
         <f>IF(AD63=1,IFERROR(AE62-AC62,""),"")</f>
         <v/>
       </c>
-      <c r="AE33" s="51">
+      <c r="AE33" s="52">
         <f>IF(AE63=1,AE62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="AF33" s="51">
+      <c r="AF33" s="52">
         <f>IF(AF63=1,IFERROR(AG62-AE62,""),"")</f>
         <v/>
       </c>
-      <c r="AG33" s="51">
+      <c r="AG33" s="52">
         <f>IF(AG63=1,AG62-$C$62,"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="27" customHeight="1">
-      <c r="A34" s="52" t="inlineStr">
+      <c r="A34" s="53" t="inlineStr">
         <is>
           <t>Nhịp: KC trục theo mặt bằng (nhập để đối chiếu)</t>
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="54" t="n"/>
-      <c r="E34" s="53" t="n"/>
-      <c r="F34" s="54" t="n"/>
-      <c r="G34" s="53" t="n"/>
-      <c r="H34" s="54" t="n"/>
-      <c r="I34" s="53" t="n"/>
-      <c r="J34" s="54" t="n"/>
-      <c r="K34" s="53" t="n"/>
-      <c r="L34" s="54" t="n"/>
-      <c r="M34" s="53" t="n"/>
-      <c r="N34" s="54" t="n"/>
-      <c r="O34" s="53" t="n"/>
-      <c r="P34" s="54" t="n"/>
-      <c r="Q34" s="53" t="n"/>
-      <c r="R34" s="54" t="n"/>
-      <c r="S34" s="53" t="n"/>
-      <c r="T34" s="54" t="n"/>
-      <c r="U34" s="53" t="n"/>
-      <c r="V34" s="54" t="n"/>
-      <c r="W34" s="53" t="n"/>
-      <c r="X34" s="54" t="n"/>
-      <c r="Y34" s="53" t="n"/>
-      <c r="Z34" s="54" t="n"/>
-      <c r="AA34" s="53" t="n"/>
-      <c r="AB34" s="54" t="n"/>
-      <c r="AC34" s="53" t="n"/>
-      <c r="AD34" s="54" t="n"/>
-      <c r="AE34" s="53" t="n"/>
-      <c r="AF34" s="54" t="n"/>
-      <c r="AG34" s="53" t="n"/>
+      <c r="C34" s="54" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="54" t="n"/>
+      <c r="F34" s="55" t="n"/>
+      <c r="G34" s="54" t="n"/>
+      <c r="H34" s="55" t="n"/>
+      <c r="I34" s="54" t="n"/>
+      <c r="J34" s="55" t="n"/>
+      <c r="K34" s="54" t="n"/>
+      <c r="L34" s="55" t="n"/>
+      <c r="M34" s="54" t="n"/>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="54" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="54" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="54" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="54" t="n"/>
+      <c r="V34" s="55" t="n"/>
+      <c r="W34" s="54" t="n"/>
+      <c r="X34" s="55" t="n"/>
+      <c r="Y34" s="54" t="n"/>
+      <c r="Z34" s="55" t="n"/>
+      <c r="AA34" s="54" t="n"/>
+      <c r="AB34" s="55" t="n"/>
+      <c r="AC34" s="54" t="n"/>
+      <c r="AD34" s="55" t="n"/>
+      <c r="AE34" s="54" t="n"/>
+      <c r="AF34" s="55" t="n"/>
+      <c r="AG34" s="54" t="n"/>
     </row>
     <row r="35" ht="27" customHeight="1">
-      <c r="A35" s="50" t="inlineStr">
+      <c r="A35" s="51" t="inlineStr">
         <is>
           <t>Nhịp: Ltt suy ra từ KC trục ở dòng 34 (mm)</t>
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
-      <c r="C35" s="51" t="n"/>
-      <c r="D35" s="51">
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52">
         <f>IF(D34="","",D34-(N(C60)/2-C67)-(N(E60)/2+E67))</f>
         <v/>
       </c>
-      <c r="E35" s="51" t="n"/>
-      <c r="F35" s="51">
+      <c r="E35" s="52" t="n"/>
+      <c r="F35" s="52">
         <f>IF(F34="","",F34-(N(E60)/2-E67)-(N(G60)/2+G67))</f>
         <v/>
       </c>
-      <c r="G35" s="51" t="n"/>
-      <c r="H35" s="51">
+      <c r="G35" s="52" t="n"/>
+      <c r="H35" s="52">
         <f>IF(H34="","",H34-(N(G60)/2-G67)-(N(I60)/2+I67))</f>
         <v/>
       </c>
-      <c r="I35" s="51" t="n"/>
-      <c r="J35" s="51">
+      <c r="I35" s="52" t="n"/>
+      <c r="J35" s="52">
         <f>IF(J34="","",J34-(N(I60)/2-I67)-(N(K60)/2+K67))</f>
         <v/>
       </c>
-      <c r="K35" s="51" t="n"/>
-      <c r="L35" s="51">
+      <c r="K35" s="52" t="n"/>
+      <c r="L35" s="52">
         <f>IF(L34="","",L34-(N(K60)/2-K67)-(N(M60)/2+M67))</f>
         <v/>
       </c>
-      <c r="M35" s="51" t="n"/>
-      <c r="N35" s="51">
+      <c r="M35" s="52" t="n"/>
+      <c r="N35" s="52">
         <f>IF(N34="","",N34-(N(M60)/2-M67)-(N(O60)/2+O67))</f>
         <v/>
       </c>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51">
+      <c r="O35" s="52" t="n"/>
+      <c r="P35" s="52">
         <f>IF(P34="","",P34-(N(O60)/2-O67)-(N(Q60)/2+Q67))</f>
         <v/>
       </c>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51">
+      <c r="Q35" s="52" t="n"/>
+      <c r="R35" s="52">
         <f>IF(R34="","",R34-(N(Q60)/2-Q67)-(N(S60)/2+S67))</f>
         <v/>
       </c>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51">
+      <c r="S35" s="52" t="n"/>
+      <c r="T35" s="52">
         <f>IF(T34="","",T34-(N(S60)/2-S67)-(N(U60)/2+U67))</f>
         <v/>
       </c>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="51">
+      <c r="U35" s="52" t="n"/>
+      <c r="V35" s="52">
         <f>IF(V34="","",V34-(N(U60)/2-U67)-(N(W60)/2+W67))</f>
         <v/>
       </c>
-      <c r="W35" s="51" t="n"/>
-      <c r="X35" s="51">
+      <c r="W35" s="52" t="n"/>
+      <c r="X35" s="52">
         <f>IF(X34="","",X34-(N(W60)/2-W67)-(N(Y60)/2+Y67))</f>
         <v/>
       </c>
-      <c r="Y35" s="51" t="n"/>
-      <c r="Z35" s="51">
+      <c r="Y35" s="52" t="n"/>
+      <c r="Z35" s="52">
         <f>IF(Z34="","",Z34-(N(Y60)/2-Y67)-(N(AA60)/2+AA67))</f>
         <v/>
       </c>
-      <c r="AA35" s="51" t="n"/>
-      <c r="AB35" s="51">
+      <c r="AA35" s="52" t="n"/>
+      <c r="AB35" s="52">
         <f>IF(AB34="","",AB34-(N(AA60)/2-AA67)-(N(AC60)/2+AC67))</f>
         <v/>
       </c>
-      <c r="AC35" s="51" t="n"/>
-      <c r="AD35" s="51">
+      <c r="AC35" s="52" t="n"/>
+      <c r="AD35" s="52">
         <f>IF(AD34="","",AD34-(N(AC60)/2-AC67)-(N(AE60)/2+AE67))</f>
         <v/>
       </c>
-      <c r="AE35" s="51" t="n"/>
-      <c r="AF35" s="51">
+      <c r="AE35" s="52" t="n"/>
+      <c r="AF35" s="52">
         <f>IF(AF34="","",AF34-(N(AE60)/2-AE67)-(N(AG60)/2+AG67))</f>
         <v/>
       </c>
-      <c r="AG35" s="51" t="n"/>
+      <c r="AG35" s="52" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="48" t="inlineStr">
+      <c r="A36" s="49" t="inlineStr">
         <is>
           <t>KIỂM TRA DIỆN TÍCH THÉP (cm²) – thép chạy suốt hiệu dụng + tăng cường lớp 1..5 (gối: trái/phải)</t>
         </is>
       </c>
-      <c r="B36" s="49" t="n"/>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="49" t="n"/>
-      <c r="E36" s="49" t="n"/>
-      <c r="F36" s="49" t="n"/>
-      <c r="G36" s="49" t="n"/>
-      <c r="H36" s="49" t="n"/>
-      <c r="I36" s="49" t="n"/>
-      <c r="J36" s="49" t="n"/>
-      <c r="K36" s="49" t="n"/>
-      <c r="L36" s="49" t="n"/>
-      <c r="M36" s="49" t="n"/>
-      <c r="N36" s="49" t="n"/>
-      <c r="O36" s="49" t="n"/>
-      <c r="P36" s="49" t="n"/>
-      <c r="Q36" s="49" t="n"/>
-      <c r="R36" s="49" t="n"/>
-      <c r="S36" s="49" t="n"/>
-      <c r="T36" s="49" t="n"/>
-      <c r="U36" s="49" t="n"/>
-      <c r="V36" s="49" t="n"/>
-      <c r="W36" s="49" t="n"/>
-      <c r="X36" s="49" t="n"/>
-      <c r="Y36" s="49" t="n"/>
-      <c r="Z36" s="49" t="n"/>
-      <c r="AA36" s="49" t="n"/>
-      <c r="AB36" s="49" t="n"/>
-      <c r="AC36" s="49" t="n"/>
-      <c r="AD36" s="49" t="n"/>
-      <c r="AE36" s="49" t="n"/>
-      <c r="AF36" s="49" t="n"/>
-      <c r="AG36" s="49" t="n"/>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+      <c r="E36" s="50" t="n"/>
+      <c r="F36" s="50" t="n"/>
+      <c r="G36" s="50" t="n"/>
+      <c r="H36" s="50" t="n"/>
+      <c r="I36" s="50" t="n"/>
+      <c r="J36" s="50" t="n"/>
+      <c r="K36" s="50" t="n"/>
+      <c r="L36" s="50" t="n"/>
+      <c r="M36" s="50" t="n"/>
+      <c r="N36" s="50" t="n"/>
+      <c r="O36" s="50" t="n"/>
+      <c r="P36" s="50" t="n"/>
+      <c r="Q36" s="50" t="n"/>
+      <c r="R36" s="50" t="n"/>
+      <c r="S36" s="50" t="n"/>
+      <c r="T36" s="50" t="n"/>
+      <c r="U36" s="50" t="n"/>
+      <c r="V36" s="50" t="n"/>
+      <c r="W36" s="50" t="n"/>
+      <c r="X36" s="50" t="n"/>
+      <c r="Y36" s="50" t="n"/>
+      <c r="Z36" s="50" t="n"/>
+      <c r="AA36" s="50" t="n"/>
+      <c r="AB36" s="50" t="n"/>
+      <c r="AC36" s="50" t="n"/>
+      <c r="AD36" s="50" t="n"/>
+      <c r="AE36" s="50" t="n"/>
+      <c r="AF36" s="50" t="n"/>
+      <c r="AG36" s="50" t="n"/>
     </row>
     <row r="37" ht="27" customHeight="1">
-      <c r="A37" s="52" t="inlineStr">
+      <c r="A37" s="53" t="inlineStr">
         <is>
           <t>As yêu cầu TRÊN (nhập; gối: trái/phải vd 2.63/1.45)</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
-      <c r="C37" s="55" t="n">
+      <c r="C37" s="56" t="n">
         <v>35.2</v>
       </c>
-      <c r="D37" s="55" t="n"/>
-      <c r="E37" s="55" t="inlineStr">
+      <c r="D37" s="56" t="n"/>
+      <c r="E37" s="56" t="inlineStr">
         <is>
           <t>48.5/50.1</t>
         </is>
       </c>
-      <c r="F37" s="55" t="n"/>
-      <c r="G37" s="55" t="inlineStr">
+      <c r="F37" s="56" t="n"/>
+      <c r="G37" s="56" t="inlineStr">
         <is>
           <t>42.0/65.0</t>
         </is>
       </c>
-      <c r="H37" s="55" t="n"/>
-      <c r="I37" s="55" t="inlineStr">
+      <c r="H37" s="56" t="n"/>
+      <c r="I37" s="56" t="inlineStr">
         <is>
           <t>98.6/101.3</t>
         </is>
       </c>
-      <c r="J37" s="55" t="n"/>
-      <c r="K37" s="55" t="inlineStr">
+      <c r="J37" s="56" t="n"/>
+      <c r="K37" s="56" t="inlineStr">
         <is>
           <t>55.0/45.0</t>
         </is>
       </c>
-      <c r="L37" s="55" t="n"/>
-      <c r="M37" s="55" t="inlineStr">
+      <c r="L37" s="56" t="n"/>
+      <c r="M37" s="56" t="inlineStr">
         <is>
           <t>30.2/31.0</t>
         </is>
       </c>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n">
+      <c r="N37" s="56" t="n"/>
+      <c r="O37" s="56" t="n">
         <v>20.5</v>
       </c>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="55" t="n"/>
-      <c r="W37" s="55" t="n"/>
-      <c r="X37" s="55" t="n"/>
-      <c r="Y37" s="55" t="n"/>
-      <c r="Z37" s="55" t="n"/>
-      <c r="AA37" s="55" t="n"/>
-      <c r="AB37" s="55" t="n"/>
-      <c r="AC37" s="55" t="n"/>
-      <c r="AD37" s="55" t="n"/>
-      <c r="AE37" s="55" t="n"/>
-      <c r="AF37" s="55" t="n"/>
-      <c r="AG37" s="55" t="n"/>
+      <c r="P37" s="56" t="n"/>
+      <c r="Q37" s="56" t="n"/>
+      <c r="R37" s="56" t="n"/>
+      <c r="S37" s="56" t="n"/>
+      <c r="T37" s="56" t="n"/>
+      <c r="U37" s="56" t="n"/>
+      <c r="V37" s="56" t="n"/>
+      <c r="W37" s="56" t="n"/>
+      <c r="X37" s="56" t="n"/>
+      <c r="Y37" s="56" t="n"/>
+      <c r="Z37" s="56" t="n"/>
+      <c r="AA37" s="56" t="n"/>
+      <c r="AB37" s="56" t="n"/>
+      <c r="AC37" s="56" t="n"/>
+      <c r="AD37" s="56" t="n"/>
+      <c r="AE37" s="56" t="n"/>
+      <c r="AF37" s="56" t="n"/>
+      <c r="AG37" s="56" t="n"/>
     </row>
     <row r="38" ht="27" customHeight="1">
-      <c r="A38" s="50" t="inlineStr">
+      <c r="A38" s="51" t="inlineStr">
         <is>
           <t>As bố trí TRÊN</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
-      <c r="C38" s="56">
+      <c r="C38" s="57">
         <f>IF(C63=1,IF(C65*C66=1,FIXED(C116,2,TRUE)&amp;"/"&amp;FIXED(C117,2,TRUE),IF(C65=1,FIXED(C116,2,TRUE),FIXED(C117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="D38" s="57">
+      <c r="D38" s="58">
         <f>IF(D63=1,ROUND(D116,2),"")</f>
         <v/>
       </c>
-      <c r="E38" s="56">
+      <c r="E38" s="57">
         <f>IF(E63=1,IF(E65*E66=1,FIXED(E116,2,TRUE)&amp;"/"&amp;FIXED(E117,2,TRUE),IF(E65=1,FIXED(E116,2,TRUE),FIXED(E117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="F38" s="57">
+      <c r="F38" s="58">
         <f>IF(F63=1,ROUND(F116,2),"")</f>
         <v/>
       </c>
-      <c r="G38" s="56">
+      <c r="G38" s="57">
         <f>IF(G63=1,IF(G65*G66=1,FIXED(G116,2,TRUE)&amp;"/"&amp;FIXED(G117,2,TRUE),IF(G65=1,FIXED(G116,2,TRUE),FIXED(G117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="H38" s="57">
+      <c r="H38" s="58">
         <f>IF(H63=1,ROUND(H116,2),"")</f>
         <v/>
       </c>
-      <c r="I38" s="56">
+      <c r="I38" s="57">
         <f>IF(I63=1,IF(I65*I66=1,FIXED(I116,2,TRUE)&amp;"/"&amp;FIXED(I117,2,TRUE),IF(I65=1,FIXED(I116,2,TRUE),FIXED(I117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="J38" s="57">
+      <c r="J38" s="58">
         <f>IF(J63=1,ROUND(J116,2),"")</f>
         <v/>
       </c>
-      <c r="K38" s="56">
+      <c r="K38" s="57">
         <f>IF(K63=1,IF(K65*K66=1,FIXED(K116,2,TRUE)&amp;"/"&amp;FIXED(K117,2,TRUE),IF(K65=1,FIXED(K116,2,TRUE),FIXED(K117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="L38" s="57">
+      <c r="L38" s="58">
         <f>IF(L63=1,ROUND(L116,2),"")</f>
         <v/>
       </c>
-      <c r="M38" s="56">
+      <c r="M38" s="57">
         <f>IF(M63=1,IF(M65*M66=1,FIXED(M116,2,TRUE)&amp;"/"&amp;FIXED(M117,2,TRUE),IF(M65=1,FIXED(M116,2,TRUE),FIXED(M117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="N38" s="57">
+      <c r="N38" s="58">
         <f>IF(N63=1,ROUND(N116,2),"")</f>
         <v/>
       </c>
-      <c r="O38" s="56">
+      <c r="O38" s="57">
         <f>IF(O63=1,IF(O65*O66=1,FIXED(O116,2,TRUE)&amp;"/"&amp;FIXED(O117,2,TRUE),IF(O65=1,FIXED(O116,2,TRUE),FIXED(O117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="P38" s="57">
+      <c r="P38" s="58">
         <f>IF(P63=1,ROUND(P116,2),"")</f>
         <v/>
       </c>
-      <c r="Q38" s="56">
+      <c r="Q38" s="57">
         <f>IF(Q63=1,IF(Q65*Q66=1,FIXED(Q116,2,TRUE)&amp;"/"&amp;FIXED(Q117,2,TRUE),IF(Q65=1,FIXED(Q116,2,TRUE),FIXED(Q117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="R38" s="57">
+      <c r="R38" s="58">
         <f>IF(R63=1,ROUND(R116,2),"")</f>
         <v/>
       </c>
-      <c r="S38" s="56">
+      <c r="S38" s="57">
         <f>IF(S63=1,IF(S65*S66=1,FIXED(S116,2,TRUE)&amp;"/"&amp;FIXED(S117,2,TRUE),IF(S65=1,FIXED(S116,2,TRUE),FIXED(S117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="T38" s="57">
+      <c r="T38" s="58">
         <f>IF(T63=1,ROUND(T116,2),"")</f>
         <v/>
       </c>
-      <c r="U38" s="56">
+      <c r="U38" s="57">
         <f>IF(U63=1,IF(U65*U66=1,FIXED(U116,2,TRUE)&amp;"/"&amp;FIXED(U117,2,TRUE),IF(U65=1,FIXED(U116,2,TRUE),FIXED(U117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="V38" s="57">
+      <c r="V38" s="58">
         <f>IF(V63=1,ROUND(V116,2),"")</f>
         <v/>
       </c>
-      <c r="W38" s="56">
+      <c r="W38" s="57">
         <f>IF(W63=1,IF(W65*W66=1,FIXED(W116,2,TRUE)&amp;"/"&amp;FIXED(W117,2,TRUE),IF(W65=1,FIXED(W116,2,TRUE),FIXED(W117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="X38" s="57">
+      <c r="X38" s="58">
         <f>IF(X63=1,ROUND(X116,2),"")</f>
         <v/>
       </c>
-      <c r="Y38" s="56">
+      <c r="Y38" s="57">
         <f>IF(Y63=1,IF(Y65*Y66=1,FIXED(Y116,2,TRUE)&amp;"/"&amp;FIXED(Y117,2,TRUE),IF(Y65=1,FIXED(Y116,2,TRUE),FIXED(Y117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="Z38" s="57">
+      <c r="Z38" s="58">
         <f>IF(Z63=1,ROUND(Z116,2),"")</f>
         <v/>
       </c>
-      <c r="AA38" s="56">
+      <c r="AA38" s="57">
         <f>IF(AA63=1,IF(AA65*AA66=1,FIXED(AA116,2,TRUE)&amp;"/"&amp;FIXED(AA117,2,TRUE),IF(AA65=1,FIXED(AA116,2,TRUE),FIXED(AA117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AB38" s="57">
+      <c r="AB38" s="58">
         <f>IF(AB63=1,ROUND(AB116,2),"")</f>
         <v/>
       </c>
-      <c r="AC38" s="56">
+      <c r="AC38" s="57">
         <f>IF(AC63=1,IF(AC65*AC66=1,FIXED(AC116,2,TRUE)&amp;"/"&amp;FIXED(AC117,2,TRUE),IF(AC65=1,FIXED(AC116,2,TRUE),FIXED(AC117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AD38" s="57">
+      <c r="AD38" s="58">
         <f>IF(AD63=1,ROUND(AD116,2),"")</f>
         <v/>
       </c>
-      <c r="AE38" s="56">
+      <c r="AE38" s="57">
         <f>IF(AE63=1,IF(AE65*AE66=1,FIXED(AE116,2,TRUE)&amp;"/"&amp;FIXED(AE117,2,TRUE),IF(AE65=1,FIXED(AE116,2,TRUE),FIXED(AE117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AF38" s="57">
+      <c r="AF38" s="58">
         <f>IF(AF63=1,ROUND(AF116,2),"")</f>
         <v/>
       </c>
-      <c r="AG38" s="56">
+      <c r="AG38" s="57">
         <f>IF(AG63=1,IF(AG65*AG66=1,FIXED(AG116,2,TRUE)&amp;"/"&amp;FIXED(AG117,2,TRUE),IF(AG65=1,FIXED(AG116,2,TRUE),FIXED(AG117,2,TRUE))),"")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="27" customHeight="1">
-      <c r="A39" s="50" t="inlineStr">
+      <c r="A39" s="51" t="inlineStr">
         <is>
           <t>Hệ số As bố trí / yêu cầu TRÊN</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
-      <c r="C39" s="57">
+      <c r="C39" s="58">
         <f>IF(OR(C63=0,C120=""),"",IF(MIN(IF(AND(C65=1,N(C120)&gt;0),C116/C120,99),IF(AND(C66=1,N(C121)&gt;0),C117/C121,99))=99,"",ROUND(MIN(IF(AND(C65=1,N(C120)&gt;0),C116/C120,99),IF(AND(C66=1,N(C121)&gt;0),C117/C121,99)),2)))</f>
         <v/>
       </c>
-      <c r="D39" s="57">
+      <c r="D39" s="58">
         <f>IF(OR(D63=0,D120=""),"",IF(MIN(IF(AND(D65=1,N(D120)&gt;0),D116/D120,99),IF(AND(D66=1,N(D121)&gt;0),D117/D121,99))=99,"",ROUND(MIN(IF(AND(D65=1,N(D120)&gt;0),D116/D120,99),IF(AND(D66=1,N(D121)&gt;0),D117/D121,99)),2)))</f>
         <v/>
       </c>
-      <c r="E39" s="57">
+      <c r="E39" s="58">
         <f>IF(OR(E63=0,E120=""),"",IF(MIN(IF(AND(E65=1,N(E120)&gt;0),E116/E120,99),IF(AND(E66=1,N(E121)&gt;0),E117/E121,99))=99,"",ROUND(MIN(IF(AND(E65=1,N(E120)&gt;0),E116/E120,99),IF(AND(E66=1,N(E121)&gt;0),E117/E121,99)),2)))</f>
         <v/>
       </c>
-      <c r="F39" s="57">
+      <c r="F39" s="58">
         <f>IF(OR(F63=0,F120=""),"",IF(MIN(IF(AND(F65=1,N(F120)&gt;0),F116/F120,99),IF(AND(F66=1,N(F121)&gt;0),F117/F121,99))=99,"",ROUND(MIN(IF(AND(F65=1,N(F120)&gt;0),F116/F120,99),IF(AND(F66=1,N(F121)&gt;0),F117/F121,99)),2)))</f>
         <v/>
       </c>
-      <c r="G39" s="57">
+      <c r="G39" s="58">
         <f>IF(OR(G63=0,G120=""),"",IF(MIN(IF(AND(G65=1,N(G120)&gt;0),G116/G120,99),IF(AND(G66=1,N(G121)&gt;0),G117/G121,99))=99,"",ROUND(MIN(IF(AND(G65=1,N(G120)&gt;0),G116/G120,99),IF(AND(G66=1,N(G121)&gt;0),G117/G121,99)),2)))</f>
         <v/>
       </c>
-      <c r="H39" s="57">
+      <c r="H39" s="58">
         <f>IF(OR(H63=0,H120=""),"",IF(MIN(IF(AND(H65=1,N(H120)&gt;0),H116/H120,99),IF(AND(H66=1,N(H121)&gt;0),H117/H121,99))=99,"",ROUND(MIN(IF(AND(H65=1,N(H120)&gt;0),H116/H120,99),IF(AND(H66=1,N(H121)&gt;0),H117/H121,99)),2)))</f>
         <v/>
       </c>
-      <c r="I39" s="57">
+      <c r="I39" s="58">
         <f>IF(OR(I63=0,I120=""),"",IF(MIN(IF(AND(I65=1,N(I120)&gt;0),I116/I120,99),IF(AND(I66=1,N(I121)&gt;0),I117/I121,99))=99,"",ROUND(MIN(IF(AND(I65=1,N(I120)&gt;0),I116/I120,99),IF(AND(I66=1,N(I121)&gt;0),I117/I121,99)),2)))</f>
         <v/>
       </c>
-      <c r="J39" s="57">
+      <c r="J39" s="58">
         <f>IF(OR(J63=0,J120=""),"",IF(MIN(IF(AND(J65=1,N(J120)&gt;0),J116/J120,99),IF(AND(J66=1,N(J121)&gt;0),J117/J121,99))=99,"",ROUND(MIN(IF(AND(J65=1,N(J120)&gt;0),J116/J120,99),IF(AND(J66=1,N(J121)&gt;0),J117/J121,99)),2)))</f>
         <v/>
       </c>
-      <c r="K39" s="57">
+      <c r="K39" s="58">
         <f>IF(OR(K63=0,K120=""),"",IF(MIN(IF(AND(K65=1,N(K120)&gt;0),K116/K120,99),IF(AND(K66=1,N(K121)&gt;0),K117/K121,99))=99,"",ROUND(MIN(IF(AND(K65=1,N(K120)&gt;0),K116/K120,99),IF(AND(K66=1,N(K121)&gt;0),K117/K121,99)),2)))</f>
         <v/>
       </c>
-      <c r="L39" s="57">
+      <c r="L39" s="58">
         <f>IF(OR(L63=0,L120=""),"",IF(MIN(IF(AND(L65=1,N(L120)&gt;0),L116/L120,99),IF(AND(L66=1,N(L121)&gt;0),L117/L121,99))=99,"",ROUND(MIN(IF(AND(L65=1,N(L120)&gt;0),L116/L120,99),IF(AND(L66=1,N(L121)&gt;0),L117/L121,99)),2)))</f>
         <v/>
       </c>
-      <c r="M39" s="57">
+      <c r="M39" s="58">
         <f>IF(OR(M63=0,M120=""),"",IF(MIN(IF(AND(M65=1,N(M120)&gt;0),M116/M120,99),IF(AND(M66=1,N(M121)&gt;0),M117/M121,99))=99,"",ROUND(MIN(IF(AND(M65=1,N(M120)&gt;0),M116/M120,99),IF(AND(M66=1,N(M121)&gt;0),M117/M121,99)),2)))</f>
         <v/>
       </c>
-      <c r="N39" s="57">
+      <c r="N39" s="58">
         <f>IF(OR(N63=0,N120=""),"",IF(MIN(IF(AND(N65=1,N(N120)&gt;0),N116/N120,99),IF(AND(N66=1,N(N121)&gt;0),N117/N121,99))=99,"",ROUND(MIN(IF(AND(N65=1,N(N120)&gt;0),N116/N120,99),IF(AND(N66=1,N(N121)&gt;0),N117/N121,99)),2)))</f>
         <v/>
       </c>
-      <c r="O39" s="57">
+      <c r="O39" s="58">
         <f>IF(OR(O63=0,O120=""),"",IF(MIN(IF(AND(O65=1,N(O120)&gt;0),O116/O120,99),IF(AND(O66=1,N(O121)&gt;0),O117/O121,99))=99,"",ROUND(MIN(IF(AND(O65=1,N(O120)&gt;0),O116/O120,99),IF(AND(O66=1,N(O121)&gt;0),O117/O121,99)),2)))</f>
         <v/>
       </c>
-      <c r="P39" s="57">
+      <c r="P39" s="58">
         <f>IF(OR(P63=0,P120=""),"",IF(MIN(IF(AND(P65=1,N(P120)&gt;0),P116/P120,99),IF(AND(P66=1,N(P121)&gt;0),P117/P121,99))=99,"",ROUND(MIN(IF(AND(P65=1,N(P120)&gt;0),P116/P120,99),IF(AND(P66=1,N(P121)&gt;0),P117/P121,99)),2)))</f>
         <v/>
       </c>
-      <c r="Q39" s="57">
+      <c r="Q39" s="58">
         <f>IF(OR(Q63=0,Q120=""),"",IF(MIN(IF(AND(Q65=1,N(Q120)&gt;0),Q116/Q120,99),IF(AND(Q66=1,N(Q121)&gt;0),Q117/Q121,99))=99,"",ROUND(MIN(IF(AND(Q65=1,N(Q120)&gt;0),Q116/Q120,99),IF(AND(Q66=1,N(Q121)&gt;0),Q117/Q121,99)),2)))</f>
         <v/>
       </c>
-      <c r="R39" s="57">
+      <c r="R39" s="58">
         <f>IF(OR(R63=0,R120=""),"",IF(MIN(IF(AND(R65=1,N(R120)&gt;0),R116/R120,99),IF(AND(R66=1,N(R121)&gt;0),R117/R121,99))=99,"",ROUND(MIN(IF(AND(R65=1,N(R120)&gt;0),R116/R120,99),IF(AND(R66=1,N(R121)&gt;0),R117/R121,99)),2)))</f>
         <v/>
       </c>
-      <c r="S39" s="57">
+      <c r="S39" s="58">
         <f>IF(OR(S63=0,S120=""),"",IF(MIN(IF(AND(S65=1,N(S120)&gt;0),S116/S120,99),IF(AND(S66=1,N(S121)&gt;0),S117/S121,99))=99,"",ROUND(MIN(IF(AND(S65=1,N(S120)&gt;0),S116/S120,99),IF(AND(S66=1,N(S121)&gt;0),S117/S121,99)),2)))</f>
         <v/>
       </c>
-      <c r="T39" s="57">
+      <c r="T39" s="58">
         <f>IF(OR(T63=0,T120=""),"",IF(MIN(IF(AND(T65=1,N(T120)&gt;0),T116/T120,99),IF(AND(T66=1,N(T121)&gt;0),T117/T121,99))=99,"",ROUND(MIN(IF(AND(T65=1,N(T120)&gt;0),T116/T120,99),IF(AND(T66=1,N(T121)&gt;0),T117/T121,99)),2)))</f>
         <v/>
       </c>
-      <c r="U39" s="57">
+      <c r="U39" s="58">
         <f>IF(OR(U63=0,U120=""),"",IF(MIN(IF(AND(U65=1,N(U120)&gt;0),U116/U120,99),IF(AND(U66=1,N(U121)&gt;0),U117/U121,99))=99,"",ROUND(MIN(IF(AND(U65=1,N(U120)&gt;0),U116/U120,99),IF(AND(U66=1,N(U121)&gt;0),U117/U121,99)),2)))</f>
         <v/>
       </c>
-      <c r="V39" s="57">
+      <c r="V39" s="58">
         <f>IF(OR(V63=0,V120=""),"",IF(MIN(IF(AND(V65=1,N(V120)&gt;0),V116/V120,99),IF(AND(V66=1,N(V121)&gt;0),V117/V121,99))=99,"",ROUND(MIN(IF(AND(V65=1,N(V120)&gt;0),V116/V120,99),IF(AND(V66=1,N(V121)&gt;0),V117/V121,99)),2)))</f>
         <v/>
       </c>
-      <c r="W39" s="57">
+      <c r="W39" s="58">
         <f>IF(OR(W63=0,W120=""),"",IF(MIN(IF(AND(W65=1,N(W120)&gt;0),W116/W120,99),IF(AND(W66=1,N(W121)&gt;0),W117/W121,99))=99,"",ROUND(MIN(IF(AND(W65=1,N(W120)&gt;0),W116/W120,99),IF(AND(W66=1,N(W121)&gt;0),W117/W121,99)),2)))</f>
         <v/>
       </c>
-      <c r="X39" s="57">
+      <c r="X39" s="58">
         <f>IF(OR(X63=0,X120=""),"",IF(MIN(IF(AND(X65=1,N(X120)&gt;0),X116/X120,99),IF(AND(X66=1,N(X121)&gt;0),X117/X121,99))=99,"",ROUND(MIN(IF(AND(X65=1,N(X120)&gt;0),X116/X120,99),IF(AND(X66=1,N(X121)&gt;0),X117/X121,99)),2)))</f>
         <v/>
       </c>
-      <c r="Y39" s="57">
+      <c r="Y39" s="58">
         <f>IF(OR(Y63=0,Y120=""),"",IF(MIN(IF(AND(Y65=1,N(Y120)&gt;0),Y116/Y120,99),IF(AND(Y66=1,N(Y121)&gt;0),Y117/Y121,99))=99,"",ROUND(MIN(IF(AND(Y65=1,N(Y120)&gt;0),Y116/Y120,99),IF(AND(Y66=1,N(Y121)&gt;0),Y117/Y121,99)),2)))</f>
         <v/>
       </c>
-      <c r="Z39" s="57">
+      <c r="Z39" s="58">
         <f>IF(OR(Z63=0,Z120=""),"",IF(MIN(IF(AND(Z65=1,N(Z120)&gt;0),Z116/Z120,99),IF(AND(Z66=1,N(Z121)&gt;0),Z117/Z121,99))=99,"",ROUND(MIN(IF(AND(Z65=1,N(Z120)&gt;0),Z116/Z120,99),IF(AND(Z66=1,N(Z121)&gt;0),Z117/Z121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AA39" s="57">
+      <c r="AA39" s="58">
         <f>IF(OR(AA63=0,AA120=""),"",IF(MIN(IF(AND(AA65=1,N(AA120)&gt;0),AA116/AA120,99),IF(AND(AA66=1,N(AA121)&gt;0),AA117/AA121,99))=99,"",ROUND(MIN(IF(AND(AA65=1,N(AA120)&gt;0),AA116/AA120,99),IF(AND(AA66=1,N(AA121)&gt;0),AA117/AA121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AB39" s="57">
+      <c r="AB39" s="58">
         <f>IF(OR(AB63=0,AB120=""),"",IF(MIN(IF(AND(AB65=1,N(AB120)&gt;0),AB116/AB120,99),IF(AND(AB66=1,N(AB121)&gt;0),AB117/AB121,99))=99,"",ROUND(MIN(IF(AND(AB65=1,N(AB120)&gt;0),AB116/AB120,99),IF(AND(AB66=1,N(AB121)&gt;0),AB117/AB121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AC39" s="57">
+      <c r="AC39" s="58">
         <f>IF(OR(AC63=0,AC120=""),"",IF(MIN(IF(AND(AC65=1,N(AC120)&gt;0),AC116/AC120,99),IF(AND(AC66=1,N(AC121)&gt;0),AC117/AC121,99))=99,"",ROUND(MIN(IF(AND(AC65=1,N(AC120)&gt;0),AC116/AC120,99),IF(AND(AC66=1,N(AC121)&gt;0),AC117/AC121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AD39" s="57">
+      <c r="AD39" s="58">
         <f>IF(OR(AD63=0,AD120=""),"",IF(MIN(IF(AND(AD65=1,N(AD120)&gt;0),AD116/AD120,99),IF(AND(AD66=1,N(AD121)&gt;0),AD117/AD121,99))=99,"",ROUND(MIN(IF(AND(AD65=1,N(AD120)&gt;0),AD116/AD120,99),IF(AND(AD66=1,N(AD121)&gt;0),AD117/AD121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AE39" s="57">
+      <c r="AE39" s="58">
         <f>IF(OR(AE63=0,AE120=""),"",IF(MIN(IF(AND(AE65=1,N(AE120)&gt;0),AE116/AE120,99),IF(AND(AE66=1,N(AE121)&gt;0),AE117/AE121,99))=99,"",ROUND(MIN(IF(AND(AE65=1,N(AE120)&gt;0),AE116/AE120,99),IF(AND(AE66=1,N(AE121)&gt;0),AE117/AE121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AF39" s="57">
+      <c r="AF39" s="58">
         <f>IF(OR(AF63=0,AF120=""),"",IF(MIN(IF(AND(AF65=1,N(AF120)&gt;0),AF116/AF120,99),IF(AND(AF66=1,N(AF121)&gt;0),AF117/AF121,99))=99,"",ROUND(MIN(IF(AND(AF65=1,N(AF120)&gt;0),AF116/AF120,99),IF(AND(AF66=1,N(AF121)&gt;0),AF117/AF121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AG39" s="57">
+      <c r="AG39" s="58">
         <f>IF(OR(AG63=0,AG120=""),"",IF(MIN(IF(AND(AG65=1,N(AG120)&gt;0),AG116/AG120,99),IF(AND(AG66=1,N(AG121)&gt;0),AG117/AG121,99))=99,"",ROUND(MIN(IF(AND(AG65=1,N(AG120)&gt;0),AG116/AG120,99),IF(AND(AG66=1,N(AG121)&gt;0),AG117/AG121,99)),2)))</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="27" customHeight="1">
-      <c r="A40" s="52" t="inlineStr">
+      <c r="A40" s="53" t="inlineStr">
         <is>
           <t>As yêu cầu DƯỚI (nhập)</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
-      <c r="C40" s="55" t="n"/>
-      <c r="D40" s="55" t="n">
+      <c r="C40" s="56" t="n"/>
+      <c r="D40" s="56" t="n">
         <v>45.3</v>
       </c>
-      <c r="E40" s="55" t="n"/>
-      <c r="F40" s="55" t="n">
+      <c r="E40" s="56" t="n"/>
+      <c r="F40" s="56" t="n">
         <v>40.2</v>
       </c>
-      <c r="G40" s="55" t="n"/>
-      <c r="H40" s="55" t="n">
+      <c r="G40" s="56" t="n"/>
+      <c r="H40" s="56" t="n">
         <v>58.1</v>
       </c>
-      <c r="I40" s="55" t="n"/>
-      <c r="J40" s="55" t="n">
+      <c r="I40" s="56" t="n"/>
+      <c r="J40" s="56" t="n">
         <v>50.2</v>
       </c>
-      <c r="K40" s="55" t="n"/>
-      <c r="L40" s="55" t="n">
+      <c r="K40" s="56" t="n"/>
+      <c r="L40" s="56" t="n">
         <v>25</v>
       </c>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n">
+      <c r="M40" s="56" t="n"/>
+      <c r="N40" s="56" t="n">
         <v>26.3</v>
       </c>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="55" t="n"/>
-      <c r="W40" s="55" t="n"/>
-      <c r="X40" s="55" t="n"/>
-      <c r="Y40" s="55" t="n"/>
-      <c r="Z40" s="55" t="n"/>
-      <c r="AA40" s="55" t="n"/>
-      <c r="AB40" s="55" t="n"/>
-      <c r="AC40" s="55" t="n"/>
-      <c r="AD40" s="55" t="n"/>
-      <c r="AE40" s="55" t="n"/>
-      <c r="AF40" s="55" t="n"/>
-      <c r="AG40" s="55" t="n"/>
+      <c r="O40" s="56" t="n"/>
+      <c r="P40" s="56" t="n"/>
+      <c r="Q40" s="56" t="n"/>
+      <c r="R40" s="56" t="n"/>
+      <c r="S40" s="56" t="n"/>
+      <c r="T40" s="56" t="n"/>
+      <c r="U40" s="56" t="n"/>
+      <c r="V40" s="56" t="n"/>
+      <c r="W40" s="56" t="n"/>
+      <c r="X40" s="56" t="n"/>
+      <c r="Y40" s="56" t="n"/>
+      <c r="Z40" s="56" t="n"/>
+      <c r="AA40" s="56" t="n"/>
+      <c r="AB40" s="56" t="n"/>
+      <c r="AC40" s="56" t="n"/>
+      <c r="AD40" s="56" t="n"/>
+      <c r="AE40" s="56" t="n"/>
+      <c r="AF40" s="56" t="n"/>
+      <c r="AG40" s="56" t="n"/>
     </row>
     <row r="41" ht="27" customHeight="1">
-      <c r="A41" s="50" t="inlineStr">
+      <c r="A41" s="51" t="inlineStr">
         <is>
           <t>As bố trí DƯỚI</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
-      <c r="C41" s="56">
+      <c r="C41" s="57">
         <f>IF(C63=1,IF(C65*C66=1,FIXED(C118,2,TRUE)&amp;"/"&amp;FIXED(C119,2,TRUE),IF(C65=1,FIXED(C118,2,TRUE),FIXED(C119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="D41" s="57">
+      <c r="D41" s="58">
         <f>IF(D63=1,ROUND(D118,2),"")</f>
         <v/>
       </c>
-      <c r="E41" s="56">
+      <c r="E41" s="57">
         <f>IF(E63=1,IF(E65*E66=1,FIXED(E118,2,TRUE)&amp;"/"&amp;FIXED(E119,2,TRUE),IF(E65=1,FIXED(E118,2,TRUE),FIXED(E119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="F41" s="57">
+      <c r="F41" s="58">
         <f>IF(F63=1,ROUND(F118,2),"")</f>
         <v/>
       </c>
-      <c r="G41" s="56">
+      <c r="G41" s="57">
         <f>IF(G63=1,IF(G65*G66=1,FIXED(G118,2,TRUE)&amp;"/"&amp;FIXED(G119,2,TRUE),IF(G65=1,FIXED(G118,2,TRUE),FIXED(G119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="H41" s="57">
+      <c r="H41" s="58">
         <f>IF(H63=1,ROUND(H118,2),"")</f>
         <v/>
       </c>
-      <c r="I41" s="56">
+      <c r="I41" s="57">
         <f>IF(I63=1,IF(I65*I66=1,FIXED(I118,2,TRUE)&amp;"/"&amp;FIXED(I119,2,TRUE),IF(I65=1,FIXED(I118,2,TRUE),FIXED(I119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="J41" s="57">
+      <c r="J41" s="58">
         <f>IF(J63=1,ROUND(J118,2),"")</f>
         <v/>
       </c>
-      <c r="K41" s="56">
+      <c r="K41" s="57">
         <f>IF(K63=1,IF(K65*K66=1,FIXED(K118,2,TRUE)&amp;"/"&amp;FIXED(K119,2,TRUE),IF(K65=1,FIXED(K118,2,TRUE),FIXED(K119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="L41" s="57">
+      <c r="L41" s="58">
         <f>IF(L63=1,ROUND(L118,2),"")</f>
         <v/>
       </c>
-      <c r="M41" s="56">
+      <c r="M41" s="57">
         <f>IF(M63=1,IF(M65*M66=1,FIXED(M118,2,TRUE)&amp;"/"&amp;FIXED(M119,2,TRUE),IF(M65=1,FIXED(M118,2,TRUE),FIXED(M119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="N41" s="57">
+      <c r="N41" s="58">
         <f>IF(N63=1,ROUND(N118,2),"")</f>
         <v/>
       </c>
-      <c r="O41" s="56">
+      <c r="O41" s="57">
         <f>IF(O63=1,IF(O65*O66=1,FIXED(O118,2,TRUE)&amp;"/"&amp;FIXED(O119,2,TRUE),IF(O65=1,FIXED(O118,2,TRUE),FIXED(O119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="P41" s="57">
+      <c r="P41" s="58">
         <f>IF(P63=1,ROUND(P118,2),"")</f>
         <v/>
       </c>
-      <c r="Q41" s="56">
+      <c r="Q41" s="57">
         <f>IF(Q63=1,IF(Q65*Q66=1,FIXED(Q118,2,TRUE)&amp;"/"&amp;FIXED(Q119,2,TRUE),IF(Q65=1,FIXED(Q118,2,TRUE),FIXED(Q119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="R41" s="57">
+      <c r="R41" s="58">
         <f>IF(R63=1,ROUND(R118,2),"")</f>
         <v/>
       </c>
-      <c r="S41" s="56">
+      <c r="S41" s="57">
         <f>IF(S63=1,IF(S65*S66=1,FIXED(S118,2,TRUE)&amp;"/"&amp;FIXED(S119,2,TRUE),IF(S65=1,FIXED(S118,2,TRUE),FIXED(S119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="T41" s="57">
+      <c r="T41" s="58">
         <f>IF(T63=1,ROUND(T118,2),"")</f>
         <v/>
       </c>
-      <c r="U41" s="56">
+      <c r="U41" s="57">
         <f>IF(U63=1,IF(U65*U66=1,FIXED(U118,2,TRUE)&amp;"/"&amp;FIXED(U119,2,TRUE),IF(U65=1,FIXED(U118,2,TRUE),FIXED(U119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="V41" s="57">
+      <c r="V41" s="58">
         <f>IF(V63=1,ROUND(V118,2),"")</f>
         <v/>
       </c>
-      <c r="W41" s="56">
+      <c r="W41" s="57">
         <f>IF(W63=1,IF(W65*W66=1,FIXED(W118,2,TRUE)&amp;"/"&amp;FIXED(W119,2,TRUE),IF(W65=1,FIXED(W118,2,TRUE),FIXED(W119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="X41" s="57">
+      <c r="X41" s="58">
         <f>IF(X63=1,ROUND(X118,2),"")</f>
         <v/>
       </c>
-      <c r="Y41" s="56">
+      <c r="Y41" s="57">
         <f>IF(Y63=1,IF(Y65*Y66=1,FIXED(Y118,2,TRUE)&amp;"/"&amp;FIXED(Y119,2,TRUE),IF(Y65=1,FIXED(Y118,2,TRUE),FIXED(Y119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="Z41" s="57">
+      <c r="Z41" s="58">
         <f>IF(Z63=1,ROUND(Z118,2),"")</f>
         <v/>
       </c>
-      <c r="AA41" s="56">
+      <c r="AA41" s="57">
         <f>IF(AA63=1,IF(AA65*AA66=1,FIXED(AA118,2,TRUE)&amp;"/"&amp;FIXED(AA119,2,TRUE),IF(AA65=1,FIXED(AA118,2,TRUE),FIXED(AA119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AB41" s="57">
+      <c r="AB41" s="58">
         <f>IF(AB63=1,ROUND(AB118,2),"")</f>
         <v/>
       </c>
-      <c r="AC41" s="56">
+      <c r="AC41" s="57">
         <f>IF(AC63=1,IF(AC65*AC66=1,FIXED(AC118,2,TRUE)&amp;"/"&amp;FIXED(AC119,2,TRUE),IF(AC65=1,FIXED(AC118,2,TRUE),FIXED(AC119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AD41" s="57">
+      <c r="AD41" s="58">
         <f>IF(AD63=1,ROUND(AD118,2),"")</f>
         <v/>
       </c>
-      <c r="AE41" s="56">
+      <c r="AE41" s="57">
         <f>IF(AE63=1,IF(AE65*AE66=1,FIXED(AE118,2,TRUE)&amp;"/"&amp;FIXED(AE119,2,TRUE),IF(AE65=1,FIXED(AE118,2,TRUE),FIXED(AE119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AF41" s="57">
+      <c r="AF41" s="58">
         <f>IF(AF63=1,ROUND(AF118,2),"")</f>
         <v/>
       </c>
-      <c r="AG41" s="56">
+      <c r="AG41" s="57">
         <f>IF(AG63=1,IF(AG65*AG66=1,FIXED(AG118,2,TRUE)&amp;"/"&amp;FIXED(AG119,2,TRUE),IF(AG65=1,FIXED(AG118,2,TRUE),FIXED(AG119,2,TRUE))),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="27" customHeight="1">
-      <c r="A42" s="50" t="inlineStr">
+      <c r="A42" s="51" t="inlineStr">
         <is>
           <t>Hệ số As bố trí / yêu cầu DƯỚI</t>
         </is>
       </c>
       <c r="B42" s="6" t="n"/>
-      <c r="C42" s="57">
+      <c r="C42" s="58">
         <f>IF(OR(C63=0,C122=""),"",IF(MIN(IF(AND(C65=1,N(C122)&gt;0),C118/C122,99),IF(AND(C66=1,N(C123)&gt;0),C119/C123,99))=99,"",ROUND(MIN(IF(AND(C65=1,N(C122)&gt;0),C118/C122,99),IF(AND(C66=1,N(C123)&gt;0),C119/C123,99)),2)))</f>
         <v/>
       </c>
-      <c r="D42" s="57">
+      <c r="D42" s="58">
         <f>IF(OR(D63=0,D122=""),"",IF(MIN(IF(AND(D65=1,N(D122)&gt;0),D118/D122,99),IF(AND(D66=1,N(D123)&gt;0),D119/D123,99))=99,"",ROUND(MIN(IF(AND(D65=1,N(D122)&gt;0),D118/D122,99),IF(AND(D66=1,N(D123)&gt;0),D119/D123,99)),2)))</f>
         <v/>
       </c>
-      <c r="E42" s="57">
+      <c r="E42" s="58">
         <f>IF(OR(E63=0,E122=""),"",IF(MIN(IF(AND(E65=1,N(E122)&gt;0),E118/E122,99),IF(AND(E66=1,N(E123)&gt;0),E119/E123,99))=99,"",ROUND(MIN(IF(AND(E65=1,N(E122)&gt;0),E118/E122,99),IF(AND(E66=1,N(E123)&gt;0),E119/E123,99)),2)))</f>
         <v/>
       </c>
-      <c r="F42" s="57">
+      <c r="F42" s="58">
         <f>IF(OR(F63=0,F122=""),"",IF(MIN(IF(AND(F65=1,N(F122)&gt;0),F118/F122,99),IF(AND(F66=1,N(F123)&gt;0),F119/F123,99))=99,"",ROUND(MIN(IF(AND(F65=1,N(F122)&gt;0),F118/F122,99),IF(AND(F66=1,N(F123)&gt;0),F119/F123,99)),2)))</f>
         <v/>
       </c>
-      <c r="G42" s="57">
+      <c r="G42" s="58">
         <f>IF(OR(G63=0,G122=""),"",IF(MIN(IF(AND(G65=1,N(G122)&gt;0),G118/G122,99),IF(AND(G66=1,N(G123)&gt;0),G119/G123,99))=99,"",ROUND(MIN(IF(AND(G65=1,N(G122)&gt;0),G118/G122,99),IF(AND(G66=1,N(G123)&gt;0),G119/G123,99)),2)))</f>
         <v/>
       </c>
-      <c r="H42" s="57">
+      <c r="H42" s="58">
         <f>IF(OR(H63=0,H122=""),"",IF(MIN(IF(AND(H65=1,N(H122)&gt;0),H118/H122,99),IF(AND(H66=1,N(H123)&gt;0),H119/H123,99))=99,"",ROUND(MIN(IF(AND(H65=1,N(H122)&gt;0),H118/H122,99),IF(AND(H66=1,N(H123)&gt;0),H119/H123,99)),2)))</f>
         <v/>
       </c>
-      <c r="I42" s="57">
+      <c r="I42" s="58">
         <f>IF(OR(I63=0,I122=""),"",IF(MIN(IF(AND(I65=1,N(I122)&gt;0),I118/I122,99),IF(AND(I66=1,N(I123)&gt;0),I119/I123,99))=99,"",ROUND(MIN(IF(AND(I65=1,N(I122)&gt;0),I118/I122,99),IF(AND(I66=1,N(I123)&gt;0),I119/I123,99)),2)))</f>
         <v/>
       </c>
-      <c r="J42" s="57">
+      <c r="J42" s="58">
         <f>IF(OR(J63=0,J122=""),"",IF(MIN(IF(AND(J65=1,N(J122)&gt;0),J118/J122,99),IF(AND(J66=1,N(J123)&gt;0),J119/J123,99))=99,"",ROUND(MIN(IF(AND(J65=1,N(J122)&gt;0),J118/J122,99),IF(AND(J66=1,N(J123)&gt;0),J119/J123,99)),2)))</f>
         <v/>
       </c>
-      <c r="K42" s="57">
+      <c r="K42" s="58">
         <f>IF(OR(K63=0,K122=""),"",IF(MIN(IF(AND(K65=1,N(K122)&gt;0),K118/K122,99),IF(AND(K66=1,N(K123)&gt;0),K119/K123,99))=99,"",ROUND(MIN(IF(AND(K65=1,N(K122)&gt;0),K118/K122,99),IF(AND(K66=1,N(K123)&gt;0),K119/K123,99)),2)))</f>
         <v/>
       </c>
-      <c r="L42" s="57">
+      <c r="L42" s="58">
         <f>IF(OR(L63=0,L122=""),"",IF(MIN(IF(AND(L65=1,N(L122)&gt;0),L118/L122,99),IF(AND(L66=1,N(L123)&gt;0),L119/L123,99))=99,"",ROUND(MIN(IF(AND(L65=1,N(L122)&gt;0),L118/L122,99),IF(AND(L66=1,N(L123)&gt;0),L119/L123,99)),2)))</f>
         <v/>
       </c>
-      <c r="M42" s="57">
+      <c r="M42" s="58">
         <f>IF(OR(M63=0,M122=""),"",IF(MIN(IF(AND(M65=1,N(M122)&gt;0),M118/M122,99),IF(AND(M66=1,N(M123)&gt;0),M119/M123,99))=99,"",ROUND(MIN(IF(AND(M65=1,N(M122)&gt;0),M118/M122,99),IF(AND(M66=1,N(M123)&gt;0),M119/M123,99)),2)))</f>
         <v/>
       </c>
-      <c r="N42" s="57">
+      <c r="N42" s="58">
         <f>IF(OR(N63=0,N122=""),"",IF(MIN(IF(AND(N65=1,N(N122)&gt;0),N118/N122,99),IF(AND(N66=1,N(N123)&gt;0),N119/N123,99))=99,"",ROUND(MIN(IF(AND(N65=1,N(N122)&gt;0),N118/N122,99),IF(AND(N66=1,N(N123)&gt;0),N119/N123,99)),2)))</f>
         <v/>
       </c>
-      <c r="O42" s="57">
+      <c r="O42" s="58">
         <f>IF(OR(O63=0,O122=""),"",IF(MIN(IF(AND(O65=1,N(O122)&gt;0),O118/O122,99),IF(AND(O66=1,N(O123)&gt;0),O119/O123,99))=99,"",ROUND(MIN(IF(AND(O65=1,N(O122)&gt;0),O118/O122,99),IF(AND(O66=1,N(O123)&gt;0),O119/O123,99)),2)))</f>
         <v/>
       </c>
-      <c r="P42" s="57">
+      <c r="P42" s="58">
         <f>IF(OR(P63=0,P122=""),"",IF(MIN(IF(AND(P65=1,N(P122)&gt;0),P118/P122,99),IF(AND(P66=1,N(P123)&gt;0),P119/P123,99))=99,"",ROUND(MIN(IF(AND(P65=1,N(P122)&gt;0),P118/P122,99),IF(AND(P66=1,N(P123)&gt;0),P119/P123,99)),2)))</f>
         <v/>
       </c>
-      <c r="Q42" s="57">
+      <c r="Q42" s="58">
         <f>IF(OR(Q63=0,Q122=""),"",IF(MIN(IF(AND(Q65=1,N(Q122)&gt;0),Q118/Q122,99),IF(AND(Q66=1,N(Q123)&gt;0),Q119/Q123,99))=99,"",ROUND(MIN(IF(AND(Q65=1,N(Q122)&gt;0),Q118/Q122,99),IF(AND(Q66=1,N(Q123)&gt;0),Q119/Q123,99)),2)))</f>
         <v/>
       </c>
-      <c r="R42" s="57">
+      <c r="R42" s="58">
         <f>IF(OR(R63=0,R122=""),"",IF(MIN(IF(AND(R65=1,N(R122)&gt;0),R118/R122,99),IF(AND(R66=1,N(R123)&gt;0),R119/R123,99))=99,"",ROUND(MIN(IF(AND(R65=1,N(R122)&gt;0),R118/R122,99),IF(AND(R66=1,N(R123)&gt;0),R119/R123,99)),2)))</f>
         <v/>
       </c>
-      <c r="S42" s="57">
+      <c r="S42" s="58">
         <f>IF(OR(S63=0,S122=""),"",IF(MIN(IF(AND(S65=1,N(S122)&gt;0),S118/S122,99),IF(AND(S66=1,N(S123)&gt;0),S119/S123,99))=99,"",ROUND(MIN(IF(AND(S65=1,N(S122)&gt;0),S118/S122,99),IF(AND(S66=1,N(S123)&gt;0),S119/S123,99)),2)))</f>
         <v/>
       </c>
-      <c r="T42" s="57">
+      <c r="T42" s="58">
         <f>IF(OR(T63=0,T122=""),"",IF(MIN(IF(AND(T65=1,N(T122)&gt;0),T118/T122,99),IF(AND(T66=1,N(T123)&gt;0),T119/T123,99))=99,"",ROUND(MIN(IF(AND(T65=1,N(T122)&gt;0),T118/T122,99),IF(AND(T66=1,N(T123)&gt;0),T119/T123,99)),2)))</f>
         <v/>
       </c>
-      <c r="U42" s="57">
+      <c r="U42" s="58">
         <f>IF(OR(U63=0,U122=""),"",IF(MIN(IF(AND(U65=1,N(U122)&gt;0),U118/U122,99),IF(AND(U66=1,N(U123)&gt;0),U119/U123,99))=99,"",ROUND(MIN(IF(AND(U65=1,N(U122)&gt;0),U118/U122,99),IF(AND(U66=1,N(U123)&gt;0),U119/U123,99)),2)))</f>
         <v/>
       </c>
-      <c r="V42" s="57">
+      <c r="V42" s="58">
         <f>IF(OR(V63=0,V122=""),"",IF(MIN(IF(AND(V65=1,N(V122)&gt;0),V118/V122,99),IF(AND(V66=1,N(V123)&gt;0),V119/V123,99))=99,"",ROUND(MIN(IF(AND(V65=1,N(V122)&gt;0),V118/V122,99),IF(AND(V66=1,N(V123)&gt;0),V119/V123,99)),2)))</f>
         <v/>
       </c>
-      <c r="W42" s="57">
+      <c r="W42" s="58">
         <f>IF(OR(W63=0,W122=""),"",IF(MIN(IF(AND(W65=1,N(W122)&gt;0),W118/W122,99),IF(AND(W66=1,N(W123)&gt;0),W119/W123,99))=99,"",ROUND(MIN(IF(AND(W65=1,N(W122)&gt;0),W118/W122,99),IF(AND(W66=1,N(W123)&gt;0),W119/W123,99)),2)))</f>
         <v/>
       </c>
-      <c r="X42" s="57">
+      <c r="X42" s="58">
         <f>IF(OR(X63=0,X122=""),"",IF(MIN(IF(AND(X65=1,N(X122)&gt;0),X118/X122,99),IF(AND(X66=1,N(X123)&gt;0),X119/X123,99))=99,"",ROUND(MIN(IF(AND(X65=1,N(X122)&gt;0),X118/X122,99),IF(AND(X66=1,N(X123)&gt;0),X119/X123,99)),2)))</f>
         <v/>
       </c>
-      <c r="Y42" s="57">
+      <c r="Y42" s="58">
         <f>IF(OR(Y63=0,Y122=""),"",IF(MIN(IF(AND(Y65=1,N(Y122)&gt;0),Y118/Y122,99),IF(AND(Y66=1,N(Y123)&gt;0),Y119/Y123,99))=99,"",ROUND(MIN(IF(AND(Y65=1,N(Y122)&gt;0),Y118/Y122,99),IF(AND(Y66=1,N(Y123)&gt;0),Y119/Y123,99)),2)))</f>
         <v/>
       </c>
-      <c r="Z42" s="57">
+      <c r="Z42" s="58">
         <f>IF(OR(Z63=0,Z122=""),"",IF(MIN(IF(AND(Z65=1,N(Z122)&gt;0),Z118/Z122,99),IF(AND(Z66=1,N(Z123)&gt;0),Z119/Z123,99))=99,"",ROUND(MIN(IF(AND(Z65=1,N(Z122)&gt;0),Z118/Z122,99),IF(AND(Z66=1,N(Z123)&gt;0),Z119/Z123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AA42" s="57">
+      <c r="AA42" s="58">
         <f>IF(OR(AA63=0,AA122=""),"",IF(MIN(IF(AND(AA65=1,N(AA122)&gt;0),AA118/AA122,99),IF(AND(AA66=1,N(AA123)&gt;0),AA119/AA123,99))=99,"",ROUND(MIN(IF(AND(AA65=1,N(AA122)&gt;0),AA118/AA122,99),IF(AND(AA66=1,N(AA123)&gt;0),AA119/AA123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AB42" s="57">
+      <c r="AB42" s="58">
         <f>IF(OR(AB63=0,AB122=""),"",IF(MIN(IF(AND(AB65=1,N(AB122)&gt;0),AB118/AB122,99),IF(AND(AB66=1,N(AB123)&gt;0),AB119/AB123,99))=99,"",ROUND(MIN(IF(AND(AB65=1,N(AB122)&gt;0),AB118/AB122,99),IF(AND(AB66=1,N(AB123)&gt;0),AB119/AB123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AC42" s="57">
+      <c r="AC42" s="58">
         <f>IF(OR(AC63=0,AC122=""),"",IF(MIN(IF(AND(AC65=1,N(AC122)&gt;0),AC118/AC122,99),IF(AND(AC66=1,N(AC123)&gt;0),AC119/AC123,99))=99,"",ROUND(MIN(IF(AND(AC65=1,N(AC122)&gt;0),AC118/AC122,99),IF(AND(AC66=1,N(AC123)&gt;0),AC119/AC123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AD42" s="57">
+      <c r="AD42" s="58">
         <f>IF(OR(AD63=0,AD122=""),"",IF(MIN(IF(AND(AD65=1,N(AD122)&gt;0),AD118/AD122,99),IF(AND(AD66=1,N(AD123)&gt;0),AD119/AD123,99))=99,"",ROUND(MIN(IF(AND(AD65=1,N(AD122)&gt;0),AD118/AD122,99),IF(AND(AD66=1,N(AD123)&gt;0),AD119/AD123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AE42" s="57">
+      <c r="AE42" s="58">
         <f>IF(OR(AE63=0,AE122=""),"",IF(MIN(IF(AND(AE65=1,N(AE122)&gt;0),AE118/AE122,99),IF(AND(AE66=1,N(AE123)&gt;0),AE119/AE123,99))=99,"",ROUND(MIN(IF(AND(AE65=1,N(AE122)&gt;0),AE118/AE122,99),IF(AND(AE66=1,N(AE123)&gt;0),AE119/AE123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AF42" s="57">
+      <c r="AF42" s="58">
         <f>IF(OR(AF63=0,AF122=""),"",IF(MIN(IF(AND(AF65=1,N(AF122)&gt;0),AF118/AF122,99),IF(AND(AF66=1,N(AF123)&gt;0),AF119/AF123,99))=99,"",ROUND(MIN(IF(AND(AF65=1,N(AF122)&gt;0),AF118/AF122,99),IF(AND(AF66=1,N(AF123)&gt;0),AF119/AF123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AG42" s="57">
+      <c r="AG42" s="58">
         <f>IF(OR(AG63=0,AG122=""),"",IF(MIN(IF(AND(AG65=1,N(AG122)&gt;0),AG118/AG122,99),IF(AND(AG66=1,N(AG123)&gt;0),AG119/AG123,99))=99,"",ROUND(MIN(IF(AND(AG65=1,N(AG122)&gt;0),AG118/AG122,99),IF(AND(AG66=1,N(AG123)&gt;0),AG119/AG123,99)),2)))</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="48" t="inlineStr">
+      <c r="A43" s="49" t="inlineStr">
         <is>
           <t>KIỂM TRA SỐ LIỆU</t>
         </is>
       </c>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="49" t="n"/>
-      <c r="D43" s="49" t="n"/>
-      <c r="E43" s="49" t="n"/>
-      <c r="F43" s="49" t="n"/>
-      <c r="G43" s="49" t="n"/>
-      <c r="H43" s="49" t="n"/>
-      <c r="I43" s="49" t="n"/>
-      <c r="J43" s="49" t="n"/>
-      <c r="K43" s="49" t="n"/>
-      <c r="L43" s="49" t="n"/>
-      <c r="M43" s="49" t="n"/>
-      <c r="N43" s="49" t="n"/>
-      <c r="O43" s="49" t="n"/>
-      <c r="P43" s="49" t="n"/>
-      <c r="Q43" s="49" t="n"/>
-      <c r="R43" s="49" t="n"/>
-      <c r="S43" s="49" t="n"/>
-      <c r="T43" s="49" t="n"/>
-      <c r="U43" s="49" t="n"/>
-      <c r="V43" s="49" t="n"/>
-      <c r="W43" s="49" t="n"/>
-      <c r="X43" s="49" t="n"/>
-      <c r="Y43" s="49" t="n"/>
-      <c r="Z43" s="49" t="n"/>
-      <c r="AA43" s="49" t="n"/>
-      <c r="AB43" s="49" t="n"/>
-      <c r="AC43" s="49" t="n"/>
-      <c r="AD43" s="49" t="n"/>
-      <c r="AE43" s="49" t="n"/>
-      <c r="AF43" s="49" t="n"/>
-      <c r="AG43" s="49" t="n"/>
+      <c r="B43" s="50" t="n"/>
+      <c r="C43" s="50" t="n"/>
+      <c r="D43" s="50" t="n"/>
+      <c r="E43" s="50" t="n"/>
+      <c r="F43" s="50" t="n"/>
+      <c r="G43" s="50" t="n"/>
+      <c r="H43" s="50" t="n"/>
+      <c r="I43" s="50" t="n"/>
+      <c r="J43" s="50" t="n"/>
+      <c r="K43" s="50" t="n"/>
+      <c r="L43" s="50" t="n"/>
+      <c r="M43" s="50" t="n"/>
+      <c r="N43" s="50" t="n"/>
+      <c r="O43" s="50" t="n"/>
+      <c r="P43" s="50" t="n"/>
+      <c r="Q43" s="50" t="n"/>
+      <c r="R43" s="50" t="n"/>
+      <c r="S43" s="50" t="n"/>
+      <c r="T43" s="50" t="n"/>
+      <c r="U43" s="50" t="n"/>
+      <c r="V43" s="50" t="n"/>
+      <c r="W43" s="50" t="n"/>
+      <c r="X43" s="50" t="n"/>
+      <c r="Y43" s="50" t="n"/>
+      <c r="Z43" s="50" t="n"/>
+      <c r="AA43" s="50" t="n"/>
+      <c r="AB43" s="50" t="n"/>
+      <c r="AC43" s="50" t="n"/>
+      <c r="AD43" s="50" t="n"/>
+      <c r="AE43" s="50" t="n"/>
+      <c r="AF43" s="50" t="n"/>
+      <c r="AG43" s="50" t="n"/>
     </row>
     <row r="44" ht="27" customHeight="1">
-      <c r="A44" s="50" t="inlineStr">
+      <c r="A44" s="51" t="inlineStr">
         <is>
           <t>Kết quả kiểm tra từng cột</t>
         </is>
       </c>
       <c r="B44" s="6" t="n"/>
-      <c r="C44" s="58">
+      <c r="C44" s="59">
         <f>IF(C63=0,"",IF(C60="","Thiếu KT gối",IF(C26="","Thiếu tên trục",IF(C124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="D44" s="58">
+      <c r="D44" s="59">
         <f>IF(D63=0,IF(D11="","","Sai Ltt"),IF(FALSE,"Nhịp đứt quãng",IF(D26="","Thiếu đai",IF(D124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="E44" s="58">
+      <c r="E44" s="59">
         <f>IF(E63=0,"",IF(E60="","Thiếu KT gối",IF(E26="","Thiếu tên trục",IF(E124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="F44" s="58">
+      <c r="F44" s="59">
         <f>IF(F63=0,IF(F11="","","Sai Ltt"),IF(AND(D$63=0,F63=1),"Nhịp đứt quãng",IF(F26="","Thiếu đai",IF(F124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="G44" s="58">
+      <c r="G44" s="59">
         <f>IF(G63=0,"",IF(G60="","Thiếu KT gối",IF(G26="","Thiếu tên trục",IF(G124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="H44" s="58">
+      <c r="H44" s="59">
         <f>IF(H63=0,IF(H11="","","Sai Ltt"),IF(AND(F$63=0,H63=1),"Nhịp đứt quãng",IF(H26="","Thiếu đai",IF(H124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="I44" s="58">
+      <c r="I44" s="59">
         <f>IF(I63=0,"",IF(I60="","Thiếu KT gối",IF(I26="","Thiếu tên trục",IF(I124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="J44" s="58">
+      <c r="J44" s="59">
         <f>IF(J63=0,IF(J11="","","Sai Ltt"),IF(AND(H$63=0,J63=1),"Nhịp đứt quãng",IF(J26="","Thiếu đai",IF(J124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="K44" s="58">
+      <c r="K44" s="59">
         <f>IF(K63=0,"",IF(K60="","Thiếu KT gối",IF(K26="","Thiếu tên trục",IF(K124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="L44" s="58">
+      <c r="L44" s="59">
         <f>IF(L63=0,IF(L11="","","Sai Ltt"),IF(AND(J$63=0,L63=1),"Nhịp đứt quãng",IF(L26="","Thiếu đai",IF(L124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="M44" s="58">
+      <c r="M44" s="59">
         <f>IF(M63=0,"",IF(M60="","Thiếu KT gối",IF(M26="","Thiếu tên trục",IF(M124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="N44" s="58">
+      <c r="N44" s="59">
         <f>IF(N63=0,IF(N11="","","Sai Ltt"),IF(AND(L$63=0,N63=1),"Nhịp đứt quãng",IF(N26="","Thiếu đai",IF(N124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="O44" s="58">
+      <c r="O44" s="59">
         <f>IF(O63=0,"",IF(O60="","Thiếu KT gối",IF(O26="","Thiếu tên trục",IF(O124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="P44" s="58">
+      <c r="P44" s="59">
         <f>IF(P63=0,IF(P11="","","Sai Ltt"),IF(AND(N$63=0,P63=1),"Nhịp đứt quãng",IF(P26="","Thiếu đai",IF(P124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Q44" s="58">
+      <c r="Q44" s="59">
         <f>IF(Q63=0,"",IF(Q60="","Thiếu KT gối",IF(Q26="","Thiếu tên trục",IF(Q124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="R44" s="58">
+      <c r="R44" s="59">
         <f>IF(R63=0,IF(R11="","","Sai Ltt"),IF(AND(P$63=0,R63=1),"Nhịp đứt quãng",IF(R26="","Thiếu đai",IF(R124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="S44" s="58">
+      <c r="S44" s="59">
         <f>IF(S63=0,"",IF(S60="","Thiếu KT gối",IF(S26="","Thiếu tên trục",IF(S124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="T44" s="58">
+      <c r="T44" s="59">
         <f>IF(T63=0,IF(T11="","","Sai Ltt"),IF(AND(R$63=0,T63=1),"Nhịp đứt quãng",IF(T26="","Thiếu đai",IF(T124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="U44" s="58">
+      <c r="U44" s="59">
         <f>IF(U63=0,"",IF(U60="","Thiếu KT gối",IF(U26="","Thiếu tên trục",IF(U124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="V44" s="58">
+      <c r="V44" s="59">
         <f>IF(V63=0,IF(V11="","","Sai Ltt"),IF(AND(T$63=0,V63=1),"Nhịp đứt quãng",IF(V26="","Thiếu đai",IF(V124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="W44" s="58">
+      <c r="W44" s="59">
         <f>IF(W63=0,"",IF(W60="","Thiếu KT gối",IF(W26="","Thiếu tên trục",IF(W124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="X44" s="58">
+      <c r="X44" s="59">
         <f>IF(X63=0,IF(X11="","","Sai Ltt"),IF(AND(V$63=0,X63=1),"Nhịp đứt quãng",IF(X26="","Thiếu đai",IF(X124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Y44" s="58">
+      <c r="Y44" s="59">
         <f>IF(Y63=0,"",IF(Y60="","Thiếu KT gối",IF(Y26="","Thiếu tên trục",IF(Y124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Z44" s="58">
+      <c r="Z44" s="59">
         <f>IF(Z63=0,IF(Z11="","","Sai Ltt"),IF(AND(X$63=0,Z63=1),"Nhịp đứt quãng",IF(Z26="","Thiếu đai",IF(Z124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AA44" s="58">
+      <c r="AA44" s="59">
         <f>IF(AA63=0,"",IF(AA60="","Thiếu KT gối",IF(AA26="","Thiếu tên trục",IF(AA124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AB44" s="58">
+      <c r="AB44" s="59">
         <f>IF(AB63=0,IF(AB11="","","Sai Ltt"),IF(AND(Z$63=0,AB63=1),"Nhịp đứt quãng",IF(AB26="","Thiếu đai",IF(AB124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AC44" s="58">
+      <c r="AC44" s="59">
         <f>IF(AC63=0,"",IF(AC60="","Thiếu KT gối",IF(AC26="","Thiếu tên trục",IF(AC124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AD44" s="58">
+      <c r="AD44" s="59">
         <f>IF(AD63=0,IF(AD11="","","Sai Ltt"),IF(AND(AB$63=0,AD63=1),"Nhịp đứt quãng",IF(AD26="","Thiếu đai",IF(AD124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AE44" s="58">
+      <c r="AE44" s="59">
         <f>IF(AE63=0,"",IF(AE60="","Thiếu KT gối",IF(AE26="","Thiếu tên trục",IF(AE124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AF44" s="58">
+      <c r="AF44" s="59">
         <f>IF(AF63=0,IF(AF11="","","Sai Ltt"),IF(AND(AD$63=0,AF63=1),"Nhịp đứt quãng",IF(AF26="","Thiếu đai",IF(AF124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AG44" s="58">
+      <c r="AG44" s="59">
         <f>IF(AG63=0,"",IF(AG60="","Thiếu KT gối",IF(AG26="","Thiếu tên trục",IF(AG124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="59" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr">
         <is>
           <t>▼ Hàng ẩn phụ trợ (dòng 60+) – dùng cho kiểm tra, không nhập.</t>
         </is>
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="1">
-      <c r="A60" s="60" t="inlineStr">
+      <c r="A60" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) W</t>
         </is>
@@ -5045,7 +5111,7 @@
       </c>
     </row>
     <row r="61" hidden="1" outlineLevel="1">
-      <c r="A61" s="60" t="inlineStr">
+      <c r="A61" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) X</t>
         </is>
@@ -5176,7 +5242,7 @@
       </c>
     </row>
     <row r="62" hidden="1" outlineLevel="1">
-      <c r="A62" s="60" t="inlineStr">
+      <c r="A62" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) AX</t>
         </is>
@@ -5247,7 +5313,7 @@
       </c>
     </row>
     <row r="63" hidden="1" outlineLevel="1">
-      <c r="A63" s="60" t="inlineStr">
+      <c r="A63" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ACT</t>
         </is>
@@ -5378,7 +5444,7 @@
       </c>
     </row>
     <row r="64" hidden="1" outlineLevel="1">
-      <c r="A64" s="60" t="inlineStr">
+      <c r="A64" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) SHOW</t>
         </is>
@@ -5509,7 +5575,7 @@
       </c>
     </row>
     <row r="65" hidden="1" outlineLevel="1">
-      <c r="A65" s="60" t="inlineStr">
+      <c r="A65" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) HASL</t>
         </is>
@@ -5640,7 +5706,7 @@
       </c>
     </row>
     <row r="66" hidden="1" outlineLevel="1">
-      <c r="A66" s="60" t="inlineStr">
+      <c r="A66" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) HASR</t>
         </is>
@@ -5771,7 +5837,7 @@
       </c>
     </row>
     <row r="67" hidden="1" outlineLevel="1">
-      <c r="A67" s="60" t="inlineStr">
+      <c r="A67" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) LECH</t>
         </is>
@@ -5842,7 +5908,7 @@
       </c>
     </row>
     <row r="68" hidden="1" outlineLevel="1">
-      <c r="A68" s="60" t="inlineStr">
+      <c r="A68" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T0L</t>
         </is>
@@ -5973,7 +6039,7 @@
       </c>
     </row>
     <row r="69" hidden="1" outlineLevel="1">
-      <c r="A69" s="60" t="inlineStr">
+      <c r="A69" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T0L</t>
         </is>
@@ -6104,7 +6170,7 @@
       </c>
     </row>
     <row r="70" hidden="1" outlineLevel="1">
-      <c r="A70" s="60" t="inlineStr">
+      <c r="A70" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T0R</t>
         </is>
@@ -6235,7 +6301,7 @@
       </c>
     </row>
     <row r="71" hidden="1" outlineLevel="1">
-      <c r="A71" s="60" t="inlineStr">
+      <c r="A71" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T0R</t>
         </is>
@@ -6366,7 +6432,7 @@
       </c>
     </row>
     <row r="72" hidden="1" outlineLevel="1">
-      <c r="A72" s="60" t="inlineStr">
+      <c r="A72" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T1L</t>
         </is>
@@ -6497,7 +6563,7 @@
       </c>
     </row>
     <row r="73" hidden="1" outlineLevel="1">
-      <c r="A73" s="60" t="inlineStr">
+      <c r="A73" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T1L</t>
         </is>
@@ -6628,7 +6694,7 @@
       </c>
     </row>
     <row r="74" hidden="1" outlineLevel="1">
-      <c r="A74" s="60" t="inlineStr">
+      <c r="A74" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T1R</t>
         </is>
@@ -6759,7 +6825,7 @@
       </c>
     </row>
     <row r="75" hidden="1" outlineLevel="1">
-      <c r="A75" s="60" t="inlineStr">
+      <c r="A75" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T1R</t>
         </is>
@@ -6890,7 +6956,7 @@
       </c>
     </row>
     <row r="76" hidden="1" outlineLevel="1">
-      <c r="A76" s="60" t="inlineStr">
+      <c r="A76" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T2L</t>
         </is>
@@ -7021,7 +7087,7 @@
       </c>
     </row>
     <row r="77" hidden="1" outlineLevel="1">
-      <c r="A77" s="60" t="inlineStr">
+      <c r="A77" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T2L</t>
         </is>
@@ -7152,7 +7218,7 @@
       </c>
     </row>
     <row r="78" hidden="1" outlineLevel="1">
-      <c r="A78" s="60" t="inlineStr">
+      <c r="A78" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T2R</t>
         </is>
@@ -7283,7 +7349,7 @@
       </c>
     </row>
     <row r="79" hidden="1" outlineLevel="1">
-      <c r="A79" s="60" t="inlineStr">
+      <c r="A79" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T2R</t>
         </is>
@@ -7414,7 +7480,7 @@
       </c>
     </row>
     <row r="80" hidden="1" outlineLevel="1">
-      <c r="A80" s="60" t="inlineStr">
+      <c r="A80" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T3L</t>
         </is>
@@ -7545,7 +7611,7 @@
       </c>
     </row>
     <row r="81" hidden="1" outlineLevel="1">
-      <c r="A81" s="60" t="inlineStr">
+      <c r="A81" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T3L</t>
         </is>
@@ -7676,7 +7742,7 @@
       </c>
     </row>
     <row r="82" hidden="1" outlineLevel="1">
-      <c r="A82" s="60" t="inlineStr">
+      <c r="A82" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T3R</t>
         </is>
@@ -7807,7 +7873,7 @@
       </c>
     </row>
     <row r="83" hidden="1" outlineLevel="1">
-      <c r="A83" s="60" t="inlineStr">
+      <c r="A83" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T3R</t>
         </is>
@@ -7938,7 +8004,7 @@
       </c>
     </row>
     <row r="84" hidden="1" outlineLevel="1">
-      <c r="A84" s="60" t="inlineStr">
+      <c r="A84" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T4L</t>
         </is>
@@ -8069,7 +8135,7 @@
       </c>
     </row>
     <row r="85" hidden="1" outlineLevel="1">
-      <c r="A85" s="60" t="inlineStr">
+      <c r="A85" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T4L</t>
         </is>
@@ -8200,7 +8266,7 @@
       </c>
     </row>
     <row r="86" hidden="1" outlineLevel="1">
-      <c r="A86" s="60" t="inlineStr">
+      <c r="A86" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T4R</t>
         </is>
@@ -8331,7 +8397,7 @@
       </c>
     </row>
     <row r="87" hidden="1" outlineLevel="1">
-      <c r="A87" s="60" t="inlineStr">
+      <c r="A87" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T4R</t>
         </is>
@@ -8462,7 +8528,7 @@
       </c>
     </row>
     <row r="88" hidden="1" outlineLevel="1">
-      <c r="A88" s="60" t="inlineStr">
+      <c r="A88" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T5L</t>
         </is>
@@ -8593,7 +8659,7 @@
       </c>
     </row>
     <row r="89" hidden="1" outlineLevel="1">
-      <c r="A89" s="60" t="inlineStr">
+      <c r="A89" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T5L</t>
         </is>
@@ -8724,7 +8790,7 @@
       </c>
     </row>
     <row r="90" hidden="1" outlineLevel="1">
-      <c r="A90" s="60" t="inlineStr">
+      <c r="A90" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T5R</t>
         </is>
@@ -8855,7 +8921,7 @@
       </c>
     </row>
     <row r="91" hidden="1" outlineLevel="1">
-      <c r="A91" s="60" t="inlineStr">
+      <c r="A91" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T5R</t>
         </is>
@@ -8986,7 +9052,7 @@
       </c>
     </row>
     <row r="92" hidden="1" outlineLevel="1">
-      <c r="A92" s="60" t="inlineStr">
+      <c r="A92" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B0L</t>
         </is>
@@ -9117,7 +9183,7 @@
       </c>
     </row>
     <row r="93" hidden="1" outlineLevel="1">
-      <c r="A93" s="60" t="inlineStr">
+      <c r="A93" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B0L</t>
         </is>
@@ -9248,7 +9314,7 @@
       </c>
     </row>
     <row r="94" hidden="1" outlineLevel="1">
-      <c r="A94" s="60" t="inlineStr">
+      <c r="A94" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B0R</t>
         </is>
@@ -9379,7 +9445,7 @@
       </c>
     </row>
     <row r="95" hidden="1" outlineLevel="1">
-      <c r="A95" s="60" t="inlineStr">
+      <c r="A95" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B0R</t>
         </is>
@@ -9510,7 +9576,7 @@
       </c>
     </row>
     <row r="96" hidden="1" outlineLevel="1">
-      <c r="A96" s="60" t="inlineStr">
+      <c r="A96" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B1L</t>
         </is>
@@ -9641,7 +9707,7 @@
       </c>
     </row>
     <row r="97" hidden="1" outlineLevel="1">
-      <c r="A97" s="60" t="inlineStr">
+      <c r="A97" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B1L</t>
         </is>
@@ -9772,7 +9838,7 @@
       </c>
     </row>
     <row r="98" hidden="1" outlineLevel="1">
-      <c r="A98" s="60" t="inlineStr">
+      <c r="A98" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B1R</t>
         </is>
@@ -9903,7 +9969,7 @@
       </c>
     </row>
     <row r="99" hidden="1" outlineLevel="1">
-      <c r="A99" s="60" t="inlineStr">
+      <c r="A99" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B1R</t>
         </is>
@@ -10034,7 +10100,7 @@
       </c>
     </row>
     <row r="100" hidden="1" outlineLevel="1">
-      <c r="A100" s="60" t="inlineStr">
+      <c r="A100" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B2L</t>
         </is>
@@ -10165,7 +10231,7 @@
       </c>
     </row>
     <row r="101" hidden="1" outlineLevel="1">
-      <c r="A101" s="60" t="inlineStr">
+      <c r="A101" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B2L</t>
         </is>
@@ -10296,7 +10362,7 @@
       </c>
     </row>
     <row r="102" hidden="1" outlineLevel="1">
-      <c r="A102" s="60" t="inlineStr">
+      <c r="A102" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B2R</t>
         </is>
@@ -10427,7 +10493,7 @@
       </c>
     </row>
     <row r="103" hidden="1" outlineLevel="1">
-      <c r="A103" s="60" t="inlineStr">
+      <c r="A103" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B2R</t>
         </is>
@@ -10558,7 +10624,7 @@
       </c>
     </row>
     <row r="104" hidden="1" outlineLevel="1">
-      <c r="A104" s="60" t="inlineStr">
+      <c r="A104" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B3L</t>
         </is>
@@ -10689,7 +10755,7 @@
       </c>
     </row>
     <row r="105" hidden="1" outlineLevel="1">
-      <c r="A105" s="60" t="inlineStr">
+      <c r="A105" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B3L</t>
         </is>
@@ -10820,7 +10886,7 @@
       </c>
     </row>
     <row r="106" hidden="1" outlineLevel="1">
-      <c r="A106" s="60" t="inlineStr">
+      <c r="A106" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B3R</t>
         </is>
@@ -10951,7 +11017,7 @@
       </c>
     </row>
     <row r="107" hidden="1" outlineLevel="1">
-      <c r="A107" s="60" t="inlineStr">
+      <c r="A107" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B3R</t>
         </is>
@@ -11082,7 +11148,7 @@
       </c>
     </row>
     <row r="108" hidden="1" outlineLevel="1">
-      <c r="A108" s="60" t="inlineStr">
+      <c r="A108" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B4L</t>
         </is>
@@ -11213,7 +11279,7 @@
       </c>
     </row>
     <row r="109" hidden="1" outlineLevel="1">
-      <c r="A109" s="60" t="inlineStr">
+      <c r="A109" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B4L</t>
         </is>
@@ -11344,7 +11410,7 @@
       </c>
     </row>
     <row r="110" hidden="1" outlineLevel="1">
-      <c r="A110" s="60" t="inlineStr">
+      <c r="A110" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B4R</t>
         </is>
@@ -11475,7 +11541,7 @@
       </c>
     </row>
     <row r="111" hidden="1" outlineLevel="1">
-      <c r="A111" s="60" t="inlineStr">
+      <c r="A111" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B4R</t>
         </is>
@@ -11606,7 +11672,7 @@
       </c>
     </row>
     <row r="112" hidden="1" outlineLevel="1">
-      <c r="A112" s="60" t="inlineStr">
+      <c r="A112" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B5L</t>
         </is>
@@ -11737,7 +11803,7 @@
       </c>
     </row>
     <row r="113" hidden="1" outlineLevel="1">
-      <c r="A113" s="60" t="inlineStr">
+      <c r="A113" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B5L</t>
         </is>
@@ -11868,7 +11934,7 @@
       </c>
     </row>
     <row r="114" hidden="1" outlineLevel="1">
-      <c r="A114" s="60" t="inlineStr">
+      <c r="A114" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B5R</t>
         </is>
@@ -11999,7 +12065,7 @@
       </c>
     </row>
     <row r="115" hidden="1" outlineLevel="1">
-      <c r="A115" s="60" t="inlineStr">
+      <c r="A115" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B5R</t>
         </is>
@@ -12130,7 +12196,7 @@
       </c>
     </row>
     <row r="116" hidden="1" outlineLevel="1">
-      <c r="A116" s="60" t="inlineStr">
+      <c r="A116" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ASTL</t>
         </is>
@@ -12261,7 +12327,7 @@
       </c>
     </row>
     <row r="117" hidden="1" outlineLevel="1">
-      <c r="A117" s="60" t="inlineStr">
+      <c r="A117" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ASTR</t>
         </is>
@@ -12392,7 +12458,7 @@
       </c>
     </row>
     <row r="118" hidden="1" outlineLevel="1">
-      <c r="A118" s="60" t="inlineStr">
+      <c r="A118" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ASBL</t>
         </is>
@@ -12523,7 +12589,7 @@
       </c>
     </row>
     <row r="119" hidden="1" outlineLevel="1">
-      <c r="A119" s="60" t="inlineStr">
+      <c r="A119" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ASBR</t>
         </is>
@@ -12654,7 +12720,7 @@
       </c>
     </row>
     <row r="120" hidden="1" outlineLevel="1">
-      <c r="A120" s="60" t="inlineStr">
+      <c r="A120" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) YTL</t>
         </is>
@@ -12785,7 +12851,7 @@
       </c>
     </row>
     <row r="121" hidden="1" outlineLevel="1">
-      <c r="A121" s="60" t="inlineStr">
+      <c r="A121" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) YTR</t>
         </is>
@@ -12916,7 +12982,7 @@
       </c>
     </row>
     <row r="122" hidden="1" outlineLevel="1">
-      <c r="A122" s="60" t="inlineStr">
+      <c r="A122" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) YBL</t>
         </is>
@@ -13047,7 +13113,7 @@
       </c>
     </row>
     <row r="123" hidden="1" outlineLevel="1">
-      <c r="A123" s="60" t="inlineStr">
+      <c r="A123" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) YBR</t>
         </is>
@@ -13178,7 +13244,7 @@
       </c>
     </row>
     <row r="124" hidden="1" outlineLevel="1">
-      <c r="A124" s="60" t="inlineStr">
+      <c r="A124" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) BAD</t>
         </is>
@@ -13309,7 +13375,7 @@
       </c>
     </row>
     <row r="125" hidden="1" outlineLevel="1">
-      <c r="A125" s="60" t="inlineStr">
+      <c r="A125" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) NB11</t>
         </is>
@@ -13320,7 +13386,7 @@
       </c>
     </row>
     <row r="126" hidden="1" outlineLevel="1">
-      <c r="A126" s="60" t="inlineStr">
+      <c r="A126" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) NB12</t>
         </is>
@@ -13331,7 +13397,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="64">
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
@@ -13342,6 +13408,7 @@
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="A1:B3"/>
+    <mergeCell ref="V6:X6"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="P7:R7"/>
     <mergeCell ref="K8:M8"/>
@@ -13381,11 +13448,13 @@
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="C5:E5"/>
+    <mergeCell ref="V5:X5"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="A5:B7"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="G8:I8"/>
+    <mergeCell ref="V4:X4"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="C9:AG9"/>
@@ -13501,7 +13570,7 @@
       <formula>LEFT($C$9,1)="✔"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="73">
+  <dataValidations count="76">
     <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm" prompt="Tên dầm (ghi trên bản vẽ, tên file CSV)."/>
     <dataValidation sqref="F3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="b dầm (mm)" prompt="Bề rộng dầm (mm), vd 400."/>
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="h dầm (mm)" prompt="Chiều cao dầm (mm), vd 1000."/>
@@ -13562,10 +13631,19 @@
     </dataValidation>
     <dataValidation sqref="S8 T8" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm chờ nối" prompt="Tên dầm / zone sau mà thép chờ (thẳng hoặc coupler) nối sang, vd B138 – ghi lên MC dọc và shop: 'COUPLER NỐI DẦM B138'. Để trống = không ghi."/>
     <dataValidation sqref="Y2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tai sàn (phía có sàn)" prompt="2 ben / Trai / Phai / Khong&#10;Chỉ dùng khi F7 là số." type="list">
-      <formula1>LIST!$X$2:$X$5</formula1>
+      <formula1>LIST!$Y$2:$Y$5</formula1>
     </dataValidation>
     <dataValidation sqref="Y3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Sàn lật (dầm úp)" prompt="Co = sàn nằm ở đáy dầm. Chỉ dùng khi F7 là số." type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Đai con đi hết dầm" prompt="Co = 1 khai báo (Y5) cho cả dầm.&#10;Khong = vùng gối (vùng đai dày 2 đầu nhịp) dùng Y5, vùng nhịp dùng Y6.&#10;Trống = theo QS_DAMSET trang 2." type="list">
+      <formula1>LIST!$W$2:$W$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="Theo số thứ tự thanh lớp 1 trên (trái → phải):&#10;3 = đai C tại thanh 3&#10;2_4 = đai Q (kín) ôm thanh 2..4&#10;2-4 = đai U thanh 2..4&#10;Ghép: 3,2_4 · 0 = không có · AUTO/trống = tự động" type="list">
+      <formula1>LIST!$X$2:$X$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con vùng nhịp" prompt="Dùng khi Y4 = Khong. Cú pháp như Y5: 2 · 2_4 · 2-4 · 3,2_4 · 0 · AUTO" type="list">
+      <formula1>LIST!$X$2:$X$10</formula1>
     </dataValidation>
     <dataValidation sqref="C11 E11 G11 I11 K11 M11 O11 Q11 S11 U11 W11 Y11 AA11 AC11 AE11 AG11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Gối: bề rộng (mm)" prompt="300 = cột 300&#10;0 = console (đầu tự do)&#10;220x500 = gối là DẦM 220x500&#10;1000/220 = cột dưới 1000, cột trên 220&#10;1000/200/-400 = cột trên 200 lệch tim -400"/>
     <dataValidation sqref="D11 F11 H11 J11 L11 N11 P11 R11 T11 V11 X11 Z11 AB11 AD11 AF11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Nhịp: L thông thủy (mm)" prompt="Khoảng cách 2 mép gối (mm).&#10;Để trống = hết dầm (các nhịp phải liền nhau).&#10;Dòng 34-35: suy Ltt từ khoảng cách trục."/>
@@ -13761,7 +13839,7 @@
       <c r="T1" s="6" t="n"/>
       <c r="V1" s="7" t="inlineStr">
         <is>
-          <t>TÙY CHỌN SÀN</t>
+          <t>TÙY CHỌN SÀN / ĐAI CON</t>
         </is>
       </c>
       <c r="W1" s="6" t="n"/>
@@ -13901,6 +13979,14 @@
       <c r="R4" s="6" t="n"/>
       <c r="S4" s="14" t="n"/>
       <c r="T4" s="14" t="n"/>
+      <c r="V4" s="13" t="inlineStr">
+        <is>
+          <t>Đai con đi hết dầm</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="14" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -13943,6 +14029,14 @@
       <c r="R5" s="6" t="n"/>
       <c r="S5" s="14" t="n"/>
       <c r="T5" s="14" t="n"/>
+      <c r="V5" s="13" t="inlineStr">
+        <is>
+          <t>Đai con toàn dầm / vùng gối</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="17" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="C6" s="8" t="inlineStr">
@@ -13952,7 +14046,7 @@
       </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
-      <c r="F6" s="17" t="n"/>
+      <c r="F6" s="18" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Neo thép giá (d):</t>
@@ -13978,6 +14072,14 @@
       <c r="R6" s="6" t="n"/>
       <c r="S6" s="14" t="n"/>
       <c r="T6" s="14" t="n"/>
+      <c r="V6" s="13" t="inlineStr">
+        <is>
+          <t>Đai con vùng nhịp</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="17" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="C7" s="8" t="inlineStr">
@@ -14015,7 +14117,7 @@
       <c r="T7" s="14" t="n"/>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Ô trắng = nhập · ▼ = có danh sách</t>
         </is>
@@ -14055,294 +14157,294 @@
       <c r="T8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>TÌNH TRẠNG SỐ LIỆU:</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n"/>
-      <c r="C9" s="21">
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="22">
         <f>IF(SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)=0,"Chưa có nhịp: nhập bề rộng gối + L thông thủy ở dòng 11",IF(SUMPRODUCT((C44:AG44&lt;&gt;"")*(C44:AG44&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$125,FIND("+",$B$125&amp;"+")-1),FIND("t",LEFT($B$125,FIND("+",$B$125&amp;"+")-1))-1)*MID(LEFT($B$125,FIND("+",$B$125&amp;"+")-1),FIND("t",LEFT($B$125,FIND("+",$B$125&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$125,FIND("+",$B$125&amp;"+")+1,99),FIND("t",MID($B$125,FIND("+",$B$125&amp;"+")+1,99))-1)*MID(MID($B$125,FIND("+",$B$125&amp;"+")+1,99),FIND("t",MID($B$125,FIND("+",$B$125&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$126,FIND("+",$B$126&amp;"+")-1),FIND("t",LEFT($B$126,FIND("+",$B$126&amp;"+")-1))-1)*MID(LEFT($B$126,FIND("+",$B$126&amp;"+")-1),FIND("t",LEFT($B$126,FIND("+",$B$126&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$126,FIND("+",$B$126&amp;"+")+1,99),FIND("t",MID($B$126,FIND("+",$B$126&amp;"+")+1,99))-1)*MID(MID($B$126,FIND("+",$B$126&amp;"+")+1,99),FIND("t",MID($B$126,FIND("+",$B$126&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)=0,"✔  Số liệu hợp lệ – "&amp;SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)&amp;" nhịp, tổng chiều dài dầm L = "&amp;FIXED(SUMIF(C63:AG63,1,C60:AG60),0)&amp;" mm","✖  Có "&amp;(SUMPRODUCT((C44:AG44&lt;&gt;"")*(C44:AG44&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$125,FIND("+",$B$125&amp;"+")-1),FIND("t",LEFT($B$125,FIND("+",$B$125&amp;"+")-1))-1)*MID(LEFT($B$125,FIND("+",$B$125&amp;"+")-1),FIND("t",LEFT($B$125,FIND("+",$B$125&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$125,FIND("+",$B$125&amp;"+")+1,99),FIND("t",MID($B$125,FIND("+",$B$125&amp;"+")+1,99))-1)*MID(MID($B$125,FIND("+",$B$125&amp;"+")+1,99),FIND("t",MID($B$125,FIND("+",$B$125&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$126,FIND("+",$B$126&amp;"+")-1),FIND("t",LEFT($B$126,FIND("+",$B$126&amp;"+")-1))-1)*MID(LEFT($B$126,FIND("+",$B$126&amp;"+")-1),FIND("t",LEFT($B$126,FIND("+",$B$126&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$126,FIND("+",$B$126&amp;"+")+1,99),FIND("t",MID($B$126,FIND("+",$B$126&amp;"+")+1,99))-1)*MID(MID($B$126,FIND("+",$B$126&amp;"+")+1,99),FIND("t",MID($B$126,FIND("+",$B$126&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0))&amp;" lỗi – xem dòng 44 (KIỂM TRA SỐ LIỆU) và ô B11 / B12"))</f>
         <v/>
       </c>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="22" t="n"/>
-      <c r="K9" s="22" t="n"/>
-      <c r="L9" s="22" t="n"/>
-      <c r="M9" s="22" t="n"/>
-      <c r="N9" s="22" t="n"/>
-      <c r="O9" s="22" t="n"/>
-      <c r="P9" s="22" t="n"/>
-      <c r="Q9" s="22" t="n"/>
-      <c r="R9" s="22" t="n"/>
-      <c r="S9" s="22" t="n"/>
-      <c r="T9" s="22" t="n"/>
-      <c r="U9" s="22" t="n"/>
-      <c r="V9" s="22" t="n"/>
-      <c r="W9" s="22" t="n"/>
-      <c r="X9" s="22" t="n"/>
-      <c r="Y9" s="22" t="n"/>
-      <c r="Z9" s="22" t="n"/>
-      <c r="AA9" s="22" t="n"/>
-      <c r="AB9" s="22" t="n"/>
-      <c r="AC9" s="22" t="n"/>
-      <c r="AD9" s="22" t="n"/>
-      <c r="AE9" s="22" t="n"/>
-      <c r="AF9" s="22" t="n"/>
-      <c r="AG9" s="22" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="23" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+      <c r="R9" s="23" t="n"/>
+      <c r="S9" s="23" t="n"/>
+      <c r="T9" s="23" t="n"/>
+      <c r="U9" s="23" t="n"/>
+      <c r="V9" s="23" t="n"/>
+      <c r="W9" s="23" t="n"/>
+      <c r="X9" s="23" t="n"/>
+      <c r="Y9" s="23" t="n"/>
+      <c r="Z9" s="23" t="n"/>
+      <c r="AA9" s="23" t="n"/>
+      <c r="AB9" s="23" t="n"/>
+      <c r="AC9" s="23" t="n"/>
+      <c r="AD9" s="23" t="n"/>
+      <c r="AE9" s="23" t="n"/>
+      <c r="AF9" s="23" t="n"/>
+      <c r="AG9" s="23" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>HẠNG MỤC</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Chạy suốt</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Gối 1</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 1</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>Gối 2</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 2</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t>Gối 3</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 3</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t>Gối 4</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="J10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 4</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>Gối 5</t>
         </is>
       </c>
-      <c r="L10" s="26" t="inlineStr">
+      <c r="L10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 5</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t>Gối 6</t>
         </is>
       </c>
-      <c r="N10" s="26" t="inlineStr">
+      <c r="N10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 6</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="26" t="inlineStr">
         <is>
           <t>Gối 7</t>
         </is>
       </c>
-      <c r="P10" s="26" t="inlineStr">
+      <c r="P10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 7</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="26" t="inlineStr">
         <is>
           <t>Gối 8</t>
         </is>
       </c>
-      <c r="R10" s="26" t="inlineStr">
+      <c r="R10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 8</t>
         </is>
       </c>
-      <c r="S10" s="25" t="inlineStr">
+      <c r="S10" s="26" t="inlineStr">
         <is>
           <t>Gối 9</t>
         </is>
       </c>
-      <c r="T10" s="26" t="inlineStr">
+      <c r="T10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 9</t>
         </is>
       </c>
-      <c r="U10" s="25" t="inlineStr">
+      <c r="U10" s="26" t="inlineStr">
         <is>
           <t>Gối 10</t>
         </is>
       </c>
-      <c r="V10" s="26" t="inlineStr">
+      <c r="V10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 10</t>
         </is>
       </c>
-      <c r="W10" s="25" t="inlineStr">
+      <c r="W10" s="26" t="inlineStr">
         <is>
           <t>Gối 11</t>
         </is>
       </c>
-      <c r="X10" s="26" t="inlineStr">
+      <c r="X10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 11</t>
         </is>
       </c>
-      <c r="Y10" s="25" t="inlineStr">
+      <c r="Y10" s="26" t="inlineStr">
         <is>
           <t>Gối 12</t>
         </is>
       </c>
-      <c r="Z10" s="26" t="inlineStr">
+      <c r="Z10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 12</t>
         </is>
       </c>
-      <c r="AA10" s="25" t="inlineStr">
+      <c r="AA10" s="26" t="inlineStr">
         <is>
           <t>Gối 13</t>
         </is>
       </c>
-      <c r="AB10" s="26" t="inlineStr">
+      <c r="AB10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 13</t>
         </is>
       </c>
-      <c r="AC10" s="25" t="inlineStr">
+      <c r="AC10" s="26" t="inlineStr">
         <is>
           <t>Gối 14</t>
         </is>
       </c>
-      <c r="AD10" s="26" t="inlineStr">
+      <c r="AD10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 14</t>
         </is>
       </c>
-      <c r="AE10" s="25" t="inlineStr">
+      <c r="AE10" s="26" t="inlineStr">
         <is>
           <t>Gối 15</t>
         </is>
       </c>
-      <c r="AF10" s="26" t="inlineStr">
+      <c r="AF10" s="27" t="inlineStr">
         <is>
           <t>Nhịp 15</t>
         </is>
       </c>
-      <c r="AG10" s="27" t="inlineStr">
+      <c r="AG10" s="28" t="inlineStr">
         <is>
           <t>Gối 16</t>
         </is>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Thép chạy suốt TRÊN  |  Gối: bề rộng  ·  Nhịp: L thông thủy</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n"/>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="31" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="31" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="31" t="n"/>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="31" t="n"/>
-      <c r="M11" s="30" t="n"/>
-      <c r="N11" s="31" t="n"/>
-      <c r="O11" s="30" t="n"/>
-      <c r="P11" s="31" t="n"/>
-      <c r="Q11" s="30" t="n"/>
-      <c r="R11" s="31" t="n"/>
-      <c r="S11" s="30" t="n"/>
-      <c r="T11" s="31" t="n"/>
-      <c r="U11" s="30" t="n"/>
-      <c r="V11" s="31" t="n"/>
-      <c r="W11" s="30" t="n"/>
-      <c r="X11" s="31" t="n"/>
-      <c r="Y11" s="30" t="n"/>
-      <c r="Z11" s="31" t="n"/>
-      <c r="AA11" s="30" t="n"/>
-      <c r="AB11" s="31" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="31" t="n"/>
-      <c r="AE11" s="30" t="n"/>
-      <c r="AF11" s="31" t="n"/>
-      <c r="AG11" s="32" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="31" t="n"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="31" t="n"/>
+      <c r="J11" s="32" t="n"/>
+      <c r="K11" s="31" t="n"/>
+      <c r="L11" s="32" t="n"/>
+      <c r="M11" s="31" t="n"/>
+      <c r="N11" s="32" t="n"/>
+      <c r="O11" s="31" t="n"/>
+      <c r="P11" s="32" t="n"/>
+      <c r="Q11" s="31" t="n"/>
+      <c r="R11" s="32" t="n"/>
+      <c r="S11" s="31" t="n"/>
+      <c r="T11" s="32" t="n"/>
+      <c r="U11" s="31" t="n"/>
+      <c r="V11" s="32" t="n"/>
+      <c r="W11" s="31" t="n"/>
+      <c r="X11" s="32" t="n"/>
+      <c r="Y11" s="31" t="n"/>
+      <c r="Z11" s="32" t="n"/>
+      <c r="AA11" s="31" t="n"/>
+      <c r="AB11" s="32" t="n"/>
+      <c r="AC11" s="31" t="n"/>
+      <c r="AD11" s="32" t="n"/>
+      <c r="AE11" s="31" t="n"/>
+      <c r="AF11" s="32" t="n"/>
+      <c r="AG11" s="33" t="n"/>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Thép chạy suốt DƯỚI  |  Gối: đai trong cột  ·  Nhịp: b nhịp</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="34" t="n"/>
-      <c r="G12" s="33" t="n"/>
-      <c r="H12" s="34" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="34" t="n"/>
-      <c r="K12" s="33" t="n"/>
-      <c r="L12" s="34" t="n"/>
-      <c r="M12" s="33" t="n"/>
-      <c r="N12" s="34" t="n"/>
-      <c r="O12" s="33" t="n"/>
-      <c r="P12" s="34" t="n"/>
-      <c r="Q12" s="33" t="n"/>
-      <c r="R12" s="34" t="n"/>
-      <c r="S12" s="33" t="n"/>
-      <c r="T12" s="34" t="n"/>
-      <c r="U12" s="33" t="n"/>
-      <c r="V12" s="34" t="n"/>
-      <c r="W12" s="33" t="n"/>
-      <c r="X12" s="34" t="n"/>
-      <c r="Y12" s="33" t="n"/>
-      <c r="Z12" s="34" t="n"/>
-      <c r="AA12" s="33" t="n"/>
-      <c r="AB12" s="34" t="n"/>
-      <c r="AC12" s="33" t="n"/>
-      <c r="AD12" s="34" t="n"/>
-      <c r="AE12" s="33" t="n"/>
-      <c r="AF12" s="34" t="n"/>
-      <c r="AG12" s="35" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="35" t="n"/>
+      <c r="I12" s="34" t="n"/>
+      <c r="J12" s="35" t="n"/>
+      <c r="K12" s="34" t="n"/>
+      <c r="L12" s="35" t="n"/>
+      <c r="M12" s="34" t="n"/>
+      <c r="N12" s="35" t="n"/>
+      <c r="O12" s="34" t="n"/>
+      <c r="P12" s="35" t="n"/>
+      <c r="Q12" s="34" t="n"/>
+      <c r="R12" s="35" t="n"/>
+      <c r="S12" s="34" t="n"/>
+      <c r="T12" s="35" t="n"/>
+      <c r="U12" s="34" t="n"/>
+      <c r="V12" s="35" t="n"/>
+      <c r="W12" s="34" t="n"/>
+      <c r="X12" s="35" t="n"/>
+      <c r="Y12" s="34" t="n"/>
+      <c r="Z12" s="35" t="n"/>
+      <c r="AA12" s="34" t="n"/>
+      <c r="AB12" s="35" t="n"/>
+      <c r="AC12" s="34" t="n"/>
+      <c r="AD12" s="35" t="n"/>
+      <c r="AE12" s="34" t="n"/>
+      <c r="AF12" s="35" t="n"/>
+      <c r="AG12" s="36" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG
 LỚP TRÊN</t>
@@ -14353,196 +14455,196 @@
           <t>Lớp 1</t>
         </is>
       </c>
-      <c r="C13" s="37" t="n"/>
-      <c r="D13" s="38" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="38" t="n"/>
-      <c r="G13" s="37" t="n"/>
-      <c r="H13" s="38" t="n"/>
-      <c r="I13" s="37" t="n"/>
-      <c r="J13" s="38" t="n"/>
-      <c r="K13" s="37" t="n"/>
-      <c r="L13" s="38" t="n"/>
-      <c r="M13" s="37" t="n"/>
-      <c r="N13" s="38" t="n"/>
-      <c r="O13" s="37" t="n"/>
-      <c r="P13" s="38" t="n"/>
-      <c r="Q13" s="37" t="n"/>
-      <c r="R13" s="38" t="n"/>
-      <c r="S13" s="37" t="n"/>
-      <c r="T13" s="38" t="n"/>
-      <c r="U13" s="37" t="n"/>
-      <c r="V13" s="38" t="n"/>
-      <c r="W13" s="37" t="n"/>
-      <c r="X13" s="38" t="n"/>
-      <c r="Y13" s="37" t="n"/>
-      <c r="Z13" s="38" t="n"/>
-      <c r="AA13" s="37" t="n"/>
-      <c r="AB13" s="38" t="n"/>
-      <c r="AC13" s="37" t="n"/>
-      <c r="AD13" s="38" t="n"/>
-      <c r="AE13" s="37" t="n"/>
-      <c r="AF13" s="38" t="n"/>
-      <c r="AG13" s="39" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="38" t="n"/>
+      <c r="H13" s="39" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="39" t="n"/>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="39" t="n"/>
+      <c r="M13" s="38" t="n"/>
+      <c r="N13" s="39" t="n"/>
+      <c r="O13" s="38" t="n"/>
+      <c r="P13" s="39" t="n"/>
+      <c r="Q13" s="38" t="n"/>
+      <c r="R13" s="39" t="n"/>
+      <c r="S13" s="38" t="n"/>
+      <c r="T13" s="39" t="n"/>
+      <c r="U13" s="38" t="n"/>
+      <c r="V13" s="39" t="n"/>
+      <c r="W13" s="38" t="n"/>
+      <c r="X13" s="39" t="n"/>
+      <c r="Y13" s="38" t="n"/>
+      <c r="Z13" s="39" t="n"/>
+      <c r="AA13" s="38" t="n"/>
+      <c r="AB13" s="39" t="n"/>
+      <c r="AC13" s="38" t="n"/>
+      <c r="AD13" s="39" t="n"/>
+      <c r="AE13" s="38" t="n"/>
+      <c r="AF13" s="39" t="n"/>
+      <c r="AG13" s="40" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="40" t="n"/>
+      <c r="A14" s="41" t="n"/>
       <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Lớp 2</t>
         </is>
       </c>
-      <c r="C14" s="37" t="n"/>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="38" t="n"/>
-      <c r="G14" s="37" t="n"/>
-      <c r="H14" s="38" t="n"/>
-      <c r="I14" s="37" t="n"/>
-      <c r="J14" s="38" t="n"/>
-      <c r="K14" s="37" t="n"/>
-      <c r="L14" s="38" t="n"/>
-      <c r="M14" s="37" t="n"/>
-      <c r="N14" s="38" t="n"/>
-      <c r="O14" s="37" t="n"/>
-      <c r="P14" s="38" t="n"/>
-      <c r="Q14" s="37" t="n"/>
-      <c r="R14" s="38" t="n"/>
-      <c r="S14" s="37" t="n"/>
-      <c r="T14" s="38" t="n"/>
-      <c r="U14" s="37" t="n"/>
-      <c r="V14" s="38" t="n"/>
-      <c r="W14" s="37" t="n"/>
-      <c r="X14" s="38" t="n"/>
-      <c r="Y14" s="37" t="n"/>
-      <c r="Z14" s="38" t="n"/>
-      <c r="AA14" s="37" t="n"/>
-      <c r="AB14" s="38" t="n"/>
-      <c r="AC14" s="37" t="n"/>
-      <c r="AD14" s="38" t="n"/>
-      <c r="AE14" s="37" t="n"/>
-      <c r="AF14" s="38" t="n"/>
-      <c r="AG14" s="39" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="38" t="n"/>
+      <c r="H14" s="39" t="n"/>
+      <c r="I14" s="38" t="n"/>
+      <c r="J14" s="39" t="n"/>
+      <c r="K14" s="38" t="n"/>
+      <c r="L14" s="39" t="n"/>
+      <c r="M14" s="38" t="n"/>
+      <c r="N14" s="39" t="n"/>
+      <c r="O14" s="38" t="n"/>
+      <c r="P14" s="39" t="n"/>
+      <c r="Q14" s="38" t="n"/>
+      <c r="R14" s="39" t="n"/>
+      <c r="S14" s="38" t="n"/>
+      <c r="T14" s="39" t="n"/>
+      <c r="U14" s="38" t="n"/>
+      <c r="V14" s="39" t="n"/>
+      <c r="W14" s="38" t="n"/>
+      <c r="X14" s="39" t="n"/>
+      <c r="Y14" s="38" t="n"/>
+      <c r="Z14" s="39" t="n"/>
+      <c r="AA14" s="38" t="n"/>
+      <c r="AB14" s="39" t="n"/>
+      <c r="AC14" s="38" t="n"/>
+      <c r="AD14" s="39" t="n"/>
+      <c r="AE14" s="38" t="n"/>
+      <c r="AF14" s="39" t="n"/>
+      <c r="AG14" s="40" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="40" t="n"/>
+      <c r="A15" s="41" t="n"/>
       <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Lớp 3</t>
         </is>
       </c>
-      <c r="C15" s="37" t="n"/>
-      <c r="D15" s="38" t="n"/>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="38" t="n"/>
-      <c r="G15" s="37" t="n"/>
-      <c r="H15" s="38" t="n"/>
-      <c r="I15" s="37" t="n"/>
-      <c r="J15" s="38" t="n"/>
-      <c r="K15" s="37" t="n"/>
-      <c r="L15" s="38" t="n"/>
-      <c r="M15" s="37" t="n"/>
-      <c r="N15" s="38" t="n"/>
-      <c r="O15" s="37" t="n"/>
-      <c r="P15" s="38" t="n"/>
-      <c r="Q15" s="37" t="n"/>
-      <c r="R15" s="38" t="n"/>
-      <c r="S15" s="37" t="n"/>
-      <c r="T15" s="38" t="n"/>
-      <c r="U15" s="37" t="n"/>
-      <c r="V15" s="38" t="n"/>
-      <c r="W15" s="37" t="n"/>
-      <c r="X15" s="38" t="n"/>
-      <c r="Y15" s="37" t="n"/>
-      <c r="Z15" s="38" t="n"/>
-      <c r="AA15" s="37" t="n"/>
-      <c r="AB15" s="38" t="n"/>
-      <c r="AC15" s="37" t="n"/>
-      <c r="AD15" s="38" t="n"/>
-      <c r="AE15" s="37" t="n"/>
-      <c r="AF15" s="38" t="n"/>
-      <c r="AG15" s="39" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="H15" s="39" t="n"/>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="39" t="n"/>
+      <c r="K15" s="38" t="n"/>
+      <c r="L15" s="39" t="n"/>
+      <c r="M15" s="38" t="n"/>
+      <c r="N15" s="39" t="n"/>
+      <c r="O15" s="38" t="n"/>
+      <c r="P15" s="39" t="n"/>
+      <c r="Q15" s="38" t="n"/>
+      <c r="R15" s="39" t="n"/>
+      <c r="S15" s="38" t="n"/>
+      <c r="T15" s="39" t="n"/>
+      <c r="U15" s="38" t="n"/>
+      <c r="V15" s="39" t="n"/>
+      <c r="W15" s="38" t="n"/>
+      <c r="X15" s="39" t="n"/>
+      <c r="Y15" s="38" t="n"/>
+      <c r="Z15" s="39" t="n"/>
+      <c r="AA15" s="38" t="n"/>
+      <c r="AB15" s="39" t="n"/>
+      <c r="AC15" s="38" t="n"/>
+      <c r="AD15" s="39" t="n"/>
+      <c r="AE15" s="38" t="n"/>
+      <c r="AF15" s="39" t="n"/>
+      <c r="AG15" s="40" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="40" t="n"/>
+      <c r="A16" s="41" t="n"/>
       <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Lớp 4</t>
         </is>
       </c>
-      <c r="C16" s="37" t="n"/>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="37" t="n"/>
-      <c r="F16" s="38" t="n"/>
-      <c r="G16" s="37" t="n"/>
-      <c r="H16" s="38" t="n"/>
-      <c r="I16" s="37" t="n"/>
-      <c r="J16" s="38" t="n"/>
-      <c r="K16" s="37" t="n"/>
-      <c r="L16" s="38" t="n"/>
-      <c r="M16" s="37" t="n"/>
-      <c r="N16" s="38" t="n"/>
-      <c r="O16" s="37" t="n"/>
-      <c r="P16" s="38" t="n"/>
-      <c r="Q16" s="37" t="n"/>
-      <c r="R16" s="38" t="n"/>
-      <c r="S16" s="37" t="n"/>
-      <c r="T16" s="38" t="n"/>
-      <c r="U16" s="37" t="n"/>
-      <c r="V16" s="38" t="n"/>
-      <c r="W16" s="37" t="n"/>
-      <c r="X16" s="38" t="n"/>
-      <c r="Y16" s="37" t="n"/>
-      <c r="Z16" s="38" t="n"/>
-      <c r="AA16" s="37" t="n"/>
-      <c r="AB16" s="38" t="n"/>
-      <c r="AC16" s="37" t="n"/>
-      <c r="AD16" s="38" t="n"/>
-      <c r="AE16" s="37" t="n"/>
-      <c r="AF16" s="38" t="n"/>
-      <c r="AG16" s="39" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="38" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="38" t="n"/>
+      <c r="H16" s="39" t="n"/>
+      <c r="I16" s="38" t="n"/>
+      <c r="J16" s="39" t="n"/>
+      <c r="K16" s="38" t="n"/>
+      <c r="L16" s="39" t="n"/>
+      <c r="M16" s="38" t="n"/>
+      <c r="N16" s="39" t="n"/>
+      <c r="O16" s="38" t="n"/>
+      <c r="P16" s="39" t="n"/>
+      <c r="Q16" s="38" t="n"/>
+      <c r="R16" s="39" t="n"/>
+      <c r="S16" s="38" t="n"/>
+      <c r="T16" s="39" t="n"/>
+      <c r="U16" s="38" t="n"/>
+      <c r="V16" s="39" t="n"/>
+      <c r="W16" s="38" t="n"/>
+      <c r="X16" s="39" t="n"/>
+      <c r="Y16" s="38" t="n"/>
+      <c r="Z16" s="39" t="n"/>
+      <c r="AA16" s="38" t="n"/>
+      <c r="AB16" s="39" t="n"/>
+      <c r="AC16" s="38" t="n"/>
+      <c r="AD16" s="39" t="n"/>
+      <c r="AE16" s="38" t="n"/>
+      <c r="AF16" s="39" t="n"/>
+      <c r="AG16" s="40" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="40" t="n"/>
+      <c r="A17" s="41" t="n"/>
       <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Lớp 5</t>
         </is>
       </c>
-      <c r="C17" s="37" t="n"/>
-      <c r="D17" s="38" t="n"/>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="38" t="n"/>
-      <c r="G17" s="37" t="n"/>
-      <c r="H17" s="38" t="n"/>
-      <c r="I17" s="37" t="n"/>
-      <c r="J17" s="38" t="n"/>
-      <c r="K17" s="37" t="n"/>
-      <c r="L17" s="38" t="n"/>
-      <c r="M17" s="37" t="n"/>
-      <c r="N17" s="38" t="n"/>
-      <c r="O17" s="37" t="n"/>
-      <c r="P17" s="38" t="n"/>
-      <c r="Q17" s="37" t="n"/>
-      <c r="R17" s="38" t="n"/>
-      <c r="S17" s="37" t="n"/>
-      <c r="T17" s="38" t="n"/>
-      <c r="U17" s="37" t="n"/>
-      <c r="V17" s="38" t="n"/>
-      <c r="W17" s="37" t="n"/>
-      <c r="X17" s="38" t="n"/>
-      <c r="Y17" s="37" t="n"/>
-      <c r="Z17" s="38" t="n"/>
-      <c r="AA17" s="37" t="n"/>
-      <c r="AB17" s="38" t="n"/>
-      <c r="AC17" s="37" t="n"/>
-      <c r="AD17" s="38" t="n"/>
-      <c r="AE17" s="37" t="n"/>
-      <c r="AF17" s="38" t="n"/>
-      <c r="AG17" s="39" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="38" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="38" t="n"/>
+      <c r="H17" s="39" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="39" t="n"/>
+      <c r="K17" s="38" t="n"/>
+      <c r="L17" s="39" t="n"/>
+      <c r="M17" s="38" t="n"/>
+      <c r="N17" s="39" t="n"/>
+      <c r="O17" s="38" t="n"/>
+      <c r="P17" s="39" t="n"/>
+      <c r="Q17" s="38" t="n"/>
+      <c r="R17" s="39" t="n"/>
+      <c r="S17" s="38" t="n"/>
+      <c r="T17" s="39" t="n"/>
+      <c r="U17" s="38" t="n"/>
+      <c r="V17" s="39" t="n"/>
+      <c r="W17" s="38" t="n"/>
+      <c r="X17" s="39" t="n"/>
+      <c r="Y17" s="38" t="n"/>
+      <c r="Z17" s="39" t="n"/>
+      <c r="AA17" s="38" t="n"/>
+      <c r="AB17" s="39" t="n"/>
+      <c r="AC17" s="38" t="n"/>
+      <c r="AD17" s="39" t="n"/>
+      <c r="AE17" s="38" t="n"/>
+      <c r="AF17" s="39" t="n"/>
+      <c r="AG17" s="40" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>THÉP TĂNG CƯỜNG
 LỚP DƯỚI</t>
@@ -14553,1625 +14655,1625 @@
           <t>Lớp 5</t>
         </is>
       </c>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="38" t="n"/>
-      <c r="G18" s="37" t="n"/>
-      <c r="H18" s="38" t="n"/>
-      <c r="I18" s="37" t="n"/>
-      <c r="J18" s="38" t="n"/>
-      <c r="K18" s="37" t="n"/>
-      <c r="L18" s="38" t="n"/>
-      <c r="M18" s="37" t="n"/>
-      <c r="N18" s="38" t="n"/>
-      <c r="O18" s="37" t="n"/>
-      <c r="P18" s="38" t="n"/>
-      <c r="Q18" s="37" t="n"/>
-      <c r="R18" s="38" t="n"/>
-      <c r="S18" s="37" t="n"/>
-      <c r="T18" s="38" t="n"/>
-      <c r="U18" s="37" t="n"/>
-      <c r="V18" s="38" t="n"/>
-      <c r="W18" s="37" t="n"/>
-      <c r="X18" s="38" t="n"/>
-      <c r="Y18" s="37" t="n"/>
-      <c r="Z18" s="38" t="n"/>
-      <c r="AA18" s="37" t="n"/>
-      <c r="AB18" s="38" t="n"/>
-      <c r="AC18" s="37" t="n"/>
-      <c r="AD18" s="38" t="n"/>
-      <c r="AE18" s="37" t="n"/>
-      <c r="AF18" s="38" t="n"/>
-      <c r="AG18" s="39" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="38" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="39" t="n"/>
+      <c r="I18" s="38" t="n"/>
+      <c r="J18" s="39" t="n"/>
+      <c r="K18" s="38" t="n"/>
+      <c r="L18" s="39" t="n"/>
+      <c r="M18" s="38" t="n"/>
+      <c r="N18" s="39" t="n"/>
+      <c r="O18" s="38" t="n"/>
+      <c r="P18" s="39" t="n"/>
+      <c r="Q18" s="38" t="n"/>
+      <c r="R18" s="39" t="n"/>
+      <c r="S18" s="38" t="n"/>
+      <c r="T18" s="39" t="n"/>
+      <c r="U18" s="38" t="n"/>
+      <c r="V18" s="39" t="n"/>
+      <c r="W18" s="38" t="n"/>
+      <c r="X18" s="39" t="n"/>
+      <c r="Y18" s="38" t="n"/>
+      <c r="Z18" s="39" t="n"/>
+      <c r="AA18" s="38" t="n"/>
+      <c r="AB18" s="39" t="n"/>
+      <c r="AC18" s="38" t="n"/>
+      <c r="AD18" s="39" t="n"/>
+      <c r="AE18" s="38" t="n"/>
+      <c r="AF18" s="39" t="n"/>
+      <c r="AG18" s="40" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="40" t="n"/>
+      <c r="A19" s="41" t="n"/>
       <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Lớp 4</t>
         </is>
       </c>
-      <c r="C19" s="37" t="n"/>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="37" t="n"/>
-      <c r="F19" s="38" t="n"/>
-      <c r="G19" s="37" t="n"/>
-      <c r="H19" s="38" t="n"/>
-      <c r="I19" s="37" t="n"/>
-      <c r="J19" s="38" t="n"/>
-      <c r="K19" s="37" t="n"/>
-      <c r="L19" s="38" t="n"/>
-      <c r="M19" s="37" t="n"/>
-      <c r="N19" s="38" t="n"/>
-      <c r="O19" s="37" t="n"/>
-      <c r="P19" s="38" t="n"/>
-      <c r="Q19" s="37" t="n"/>
-      <c r="R19" s="38" t="n"/>
-      <c r="S19" s="37" t="n"/>
-      <c r="T19" s="38" t="n"/>
-      <c r="U19" s="37" t="n"/>
-      <c r="V19" s="38" t="n"/>
-      <c r="W19" s="37" t="n"/>
-      <c r="X19" s="38" t="n"/>
-      <c r="Y19" s="37" t="n"/>
-      <c r="Z19" s="38" t="n"/>
-      <c r="AA19" s="37" t="n"/>
-      <c r="AB19" s="38" t="n"/>
-      <c r="AC19" s="37" t="n"/>
-      <c r="AD19" s="38" t="n"/>
-      <c r="AE19" s="37" t="n"/>
-      <c r="AF19" s="38" t="n"/>
-      <c r="AG19" s="39" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="39" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="39" t="n"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="39" t="n"/>
+      <c r="M19" s="38" t="n"/>
+      <c r="N19" s="39" t="n"/>
+      <c r="O19" s="38" t="n"/>
+      <c r="P19" s="39" t="n"/>
+      <c r="Q19" s="38" t="n"/>
+      <c r="R19" s="39" t="n"/>
+      <c r="S19" s="38" t="n"/>
+      <c r="T19" s="39" t="n"/>
+      <c r="U19" s="38" t="n"/>
+      <c r="V19" s="39" t="n"/>
+      <c r="W19" s="38" t="n"/>
+      <c r="X19" s="39" t="n"/>
+      <c r="Y19" s="38" t="n"/>
+      <c r="Z19" s="39" t="n"/>
+      <c r="AA19" s="38" t="n"/>
+      <c r="AB19" s="39" t="n"/>
+      <c r="AC19" s="38" t="n"/>
+      <c r="AD19" s="39" t="n"/>
+      <c r="AE19" s="38" t="n"/>
+      <c r="AF19" s="39" t="n"/>
+      <c r="AG19" s="40" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="40" t="n"/>
+      <c r="A20" s="41" t="n"/>
       <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Lớp 3</t>
         </is>
       </c>
-      <c r="C20" s="37" t="n"/>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="37" t="n"/>
-      <c r="F20" s="38" t="n"/>
-      <c r="G20" s="37" t="n"/>
-      <c r="H20" s="38" t="n"/>
-      <c r="I20" s="37" t="n"/>
-      <c r="J20" s="38" t="n"/>
-      <c r="K20" s="37" t="n"/>
-      <c r="L20" s="38" t="n"/>
-      <c r="M20" s="37" t="n"/>
-      <c r="N20" s="38" t="n"/>
-      <c r="O20" s="37" t="n"/>
-      <c r="P20" s="38" t="n"/>
-      <c r="Q20" s="37" t="n"/>
-      <c r="R20" s="38" t="n"/>
-      <c r="S20" s="37" t="n"/>
-      <c r="T20" s="38" t="n"/>
-      <c r="U20" s="37" t="n"/>
-      <c r="V20" s="38" t="n"/>
-      <c r="W20" s="37" t="n"/>
-      <c r="X20" s="38" t="n"/>
-      <c r="Y20" s="37" t="n"/>
-      <c r="Z20" s="38" t="n"/>
-      <c r="AA20" s="37" t="n"/>
-      <c r="AB20" s="38" t="n"/>
-      <c r="AC20" s="37" t="n"/>
-      <c r="AD20" s="38" t="n"/>
-      <c r="AE20" s="37" t="n"/>
-      <c r="AF20" s="38" t="n"/>
-      <c r="AG20" s="39" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="39" t="n"/>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="39" t="n"/>
+      <c r="K20" s="38" t="n"/>
+      <c r="L20" s="39" t="n"/>
+      <c r="M20" s="38" t="n"/>
+      <c r="N20" s="39" t="n"/>
+      <c r="O20" s="38" t="n"/>
+      <c r="P20" s="39" t="n"/>
+      <c r="Q20" s="38" t="n"/>
+      <c r="R20" s="39" t="n"/>
+      <c r="S20" s="38" t="n"/>
+      <c r="T20" s="39" t="n"/>
+      <c r="U20" s="38" t="n"/>
+      <c r="V20" s="39" t="n"/>
+      <c r="W20" s="38" t="n"/>
+      <c r="X20" s="39" t="n"/>
+      <c r="Y20" s="38" t="n"/>
+      <c r="Z20" s="39" t="n"/>
+      <c r="AA20" s="38" t="n"/>
+      <c r="AB20" s="39" t="n"/>
+      <c r="AC20" s="38" t="n"/>
+      <c r="AD20" s="39" t="n"/>
+      <c r="AE20" s="38" t="n"/>
+      <c r="AF20" s="39" t="n"/>
+      <c r="AG20" s="40" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="40" t="n"/>
+      <c r="A21" s="41" t="n"/>
       <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Lớp 2</t>
         </is>
       </c>
-      <c r="C21" s="37" t="n"/>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="37" t="n"/>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="37" t="n"/>
-      <c r="H21" s="38" t="n"/>
-      <c r="I21" s="37" t="n"/>
-      <c r="J21" s="38" t="n"/>
-      <c r="K21" s="37" t="n"/>
-      <c r="L21" s="38" t="n"/>
-      <c r="M21" s="37" t="n"/>
-      <c r="N21" s="38" t="n"/>
-      <c r="O21" s="37" t="n"/>
-      <c r="P21" s="38" t="n"/>
-      <c r="Q21" s="37" t="n"/>
-      <c r="R21" s="38" t="n"/>
-      <c r="S21" s="37" t="n"/>
-      <c r="T21" s="38" t="n"/>
-      <c r="U21" s="37" t="n"/>
-      <c r="V21" s="38" t="n"/>
-      <c r="W21" s="37" t="n"/>
-      <c r="X21" s="38" t="n"/>
-      <c r="Y21" s="37" t="n"/>
-      <c r="Z21" s="38" t="n"/>
-      <c r="AA21" s="37" t="n"/>
-      <c r="AB21" s="38" t="n"/>
-      <c r="AC21" s="37" t="n"/>
-      <c r="AD21" s="38" t="n"/>
-      <c r="AE21" s="37" t="n"/>
-      <c r="AF21" s="38" t="n"/>
-      <c r="AG21" s="39" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="39" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="39" t="n"/>
+      <c r="K21" s="38" t="n"/>
+      <c r="L21" s="39" t="n"/>
+      <c r="M21" s="38" t="n"/>
+      <c r="N21" s="39" t="n"/>
+      <c r="O21" s="38" t="n"/>
+      <c r="P21" s="39" t="n"/>
+      <c r="Q21" s="38" t="n"/>
+      <c r="R21" s="39" t="n"/>
+      <c r="S21" s="38" t="n"/>
+      <c r="T21" s="39" t="n"/>
+      <c r="U21" s="38" t="n"/>
+      <c r="V21" s="39" t="n"/>
+      <c r="W21" s="38" t="n"/>
+      <c r="X21" s="39" t="n"/>
+      <c r="Y21" s="38" t="n"/>
+      <c r="Z21" s="39" t="n"/>
+      <c r="AA21" s="38" t="n"/>
+      <c r="AB21" s="39" t="n"/>
+      <c r="AC21" s="38" t="n"/>
+      <c r="AD21" s="39" t="n"/>
+      <c r="AE21" s="38" t="n"/>
+      <c r="AF21" s="39" t="n"/>
+      <c r="AG21" s="40" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="40" t="n"/>
+      <c r="A22" s="41" t="n"/>
       <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Lớp 1</t>
         </is>
       </c>
-      <c r="C22" s="37" t="n"/>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="37" t="n"/>
-      <c r="F22" s="38" t="n"/>
-      <c r="G22" s="37" t="n"/>
-      <c r="H22" s="38" t="n"/>
-      <c r="I22" s="37" t="n"/>
-      <c r="J22" s="38" t="n"/>
-      <c r="K22" s="37" t="n"/>
-      <c r="L22" s="38" t="n"/>
-      <c r="M22" s="37" t="n"/>
-      <c r="N22" s="38" t="n"/>
-      <c r="O22" s="37" t="n"/>
-      <c r="P22" s="38" t="n"/>
-      <c r="Q22" s="37" t="n"/>
-      <c r="R22" s="38" t="n"/>
-      <c r="S22" s="37" t="n"/>
-      <c r="T22" s="38" t="n"/>
-      <c r="U22" s="37" t="n"/>
-      <c r="V22" s="38" t="n"/>
-      <c r="W22" s="37" t="n"/>
-      <c r="X22" s="38" t="n"/>
-      <c r="Y22" s="37" t="n"/>
-      <c r="Z22" s="38" t="n"/>
-      <c r="AA22" s="37" t="n"/>
-      <c r="AB22" s="38" t="n"/>
-      <c r="AC22" s="37" t="n"/>
-      <c r="AD22" s="38" t="n"/>
-      <c r="AE22" s="37" t="n"/>
-      <c r="AF22" s="38" t="n"/>
-      <c r="AG22" s="39" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="38" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="38" t="n"/>
+      <c r="H22" s="39" t="n"/>
+      <c r="I22" s="38" t="n"/>
+      <c r="J22" s="39" t="n"/>
+      <c r="K22" s="38" t="n"/>
+      <c r="L22" s="39" t="n"/>
+      <c r="M22" s="38" t="n"/>
+      <c r="N22" s="39" t="n"/>
+      <c r="O22" s="38" t="n"/>
+      <c r="P22" s="39" t="n"/>
+      <c r="Q22" s="38" t="n"/>
+      <c r="R22" s="39" t="n"/>
+      <c r="S22" s="38" t="n"/>
+      <c r="T22" s="39" t="n"/>
+      <c r="U22" s="38" t="n"/>
+      <c r="V22" s="39" t="n"/>
+      <c r="W22" s="38" t="n"/>
+      <c r="X22" s="39" t="n"/>
+      <c r="Y22" s="38" t="n"/>
+      <c r="Z22" s="39" t="n"/>
+      <c r="AA22" s="38" t="n"/>
+      <c r="AB22" s="39" t="n"/>
+      <c r="AC22" s="38" t="n"/>
+      <c r="AD22" s="39" t="n"/>
+      <c r="AE22" s="38" t="n"/>
+      <c r="AF22" s="39" t="n"/>
+      <c r="AG22" s="40" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>Gối: ẩn cột  ·  Nhịp: đổi thép chạy TRÊN</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="41" t="n"/>
-      <c r="D23" s="34" t="n"/>
-      <c r="E23" s="41" t="n"/>
-      <c r="F23" s="34" t="n"/>
-      <c r="G23" s="41" t="n"/>
-      <c r="H23" s="34" t="n"/>
-      <c r="I23" s="41" t="n"/>
-      <c r="J23" s="34" t="n"/>
-      <c r="K23" s="41" t="n"/>
-      <c r="L23" s="34" t="n"/>
-      <c r="M23" s="41" t="n"/>
-      <c r="N23" s="34" t="n"/>
-      <c r="O23" s="41" t="n"/>
-      <c r="P23" s="34" t="n"/>
-      <c r="Q23" s="41" t="n"/>
-      <c r="R23" s="34" t="n"/>
-      <c r="S23" s="41" t="n"/>
-      <c r="T23" s="34" t="n"/>
-      <c r="U23" s="41" t="n"/>
-      <c r="V23" s="34" t="n"/>
-      <c r="W23" s="41" t="n"/>
-      <c r="X23" s="34" t="n"/>
-      <c r="Y23" s="41" t="n"/>
-      <c r="Z23" s="34" t="n"/>
-      <c r="AA23" s="41" t="n"/>
-      <c r="AB23" s="34" t="n"/>
-      <c r="AC23" s="41" t="n"/>
-      <c r="AD23" s="34" t="n"/>
-      <c r="AE23" s="41" t="n"/>
-      <c r="AF23" s="34" t="n"/>
-      <c r="AG23" s="42" t="n"/>
+      <c r="C23" s="42" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="42" t="n"/>
+      <c r="H23" s="35" t="n"/>
+      <c r="I23" s="42" t="n"/>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="42" t="n"/>
+      <c r="L23" s="35" t="n"/>
+      <c r="M23" s="42" t="n"/>
+      <c r="N23" s="35" t="n"/>
+      <c r="O23" s="42" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="42" t="n"/>
+      <c r="R23" s="35" t="n"/>
+      <c r="S23" s="42" t="n"/>
+      <c r="T23" s="35" t="n"/>
+      <c r="U23" s="42" t="n"/>
+      <c r="V23" s="35" t="n"/>
+      <c r="W23" s="42" t="n"/>
+      <c r="X23" s="35" t="n"/>
+      <c r="Y23" s="42" t="n"/>
+      <c r="Z23" s="35" t="n"/>
+      <c r="AA23" s="42" t="n"/>
+      <c r="AB23" s="35" t="n"/>
+      <c r="AC23" s="42" t="n"/>
+      <c r="AD23" s="35" t="n"/>
+      <c r="AE23" s="42" t="n"/>
+      <c r="AF23" s="35" t="n"/>
+      <c r="AG23" s="43" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>Gối: dầm giao tại cột  ·  Nhịp: thép giá</t>
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
-      <c r="C24" s="41" t="n"/>
-      <c r="D24" s="34" t="n"/>
-      <c r="E24" s="41" t="n"/>
-      <c r="F24" s="34" t="n"/>
-      <c r="G24" s="41" t="n"/>
-      <c r="H24" s="34" t="n"/>
-      <c r="I24" s="41" t="n"/>
-      <c r="J24" s="34" t="n"/>
-      <c r="K24" s="41" t="n"/>
-      <c r="L24" s="34" t="n"/>
-      <c r="M24" s="41" t="n"/>
-      <c r="N24" s="34" t="n"/>
-      <c r="O24" s="41" t="n"/>
-      <c r="P24" s="34" t="n"/>
-      <c r="Q24" s="41" t="n"/>
-      <c r="R24" s="34" t="n"/>
-      <c r="S24" s="41" t="n"/>
-      <c r="T24" s="34" t="n"/>
-      <c r="U24" s="41" t="n"/>
-      <c r="V24" s="34" t="n"/>
-      <c r="W24" s="41" t="n"/>
-      <c r="X24" s="34" t="n"/>
-      <c r="Y24" s="41" t="n"/>
-      <c r="Z24" s="34" t="n"/>
-      <c r="AA24" s="41" t="n"/>
-      <c r="AB24" s="34" t="n"/>
-      <c r="AC24" s="41" t="n"/>
-      <c r="AD24" s="34" t="n"/>
-      <c r="AE24" s="41" t="n"/>
-      <c r="AF24" s="34" t="n"/>
-      <c r="AG24" s="42" t="n"/>
+      <c r="C24" s="42" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="42" t="n"/>
+      <c r="H24" s="35" t="n"/>
+      <c r="I24" s="42" t="n"/>
+      <c r="J24" s="35" t="n"/>
+      <c r="K24" s="42" t="n"/>
+      <c r="L24" s="35" t="n"/>
+      <c r="M24" s="42" t="n"/>
+      <c r="N24" s="35" t="n"/>
+      <c r="O24" s="42" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="42" t="n"/>
+      <c r="R24" s="35" t="n"/>
+      <c r="S24" s="42" t="n"/>
+      <c r="T24" s="35" t="n"/>
+      <c r="U24" s="42" t="n"/>
+      <c r="V24" s="35" t="n"/>
+      <c r="W24" s="42" t="n"/>
+      <c r="X24" s="35" t="n"/>
+      <c r="Y24" s="42" t="n"/>
+      <c r="Z24" s="35" t="n"/>
+      <c r="AA24" s="42" t="n"/>
+      <c r="AB24" s="35" t="n"/>
+      <c r="AC24" s="42" t="n"/>
+      <c r="AD24" s="35" t="n"/>
+      <c r="AE24" s="42" t="n"/>
+      <c r="AF24" s="35" t="n"/>
+      <c r="AG24" s="43" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>Gối: lệch dầm giao  ·  Nhịp: đổi thép chạy DƯỚI</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
-      <c r="C25" s="41" t="n"/>
-      <c r="D25" s="34" t="n"/>
-      <c r="E25" s="41" t="n"/>
-      <c r="F25" s="34" t="n"/>
-      <c r="G25" s="41" t="n"/>
-      <c r="H25" s="34" t="n"/>
-      <c r="I25" s="41" t="n"/>
-      <c r="J25" s="34" t="n"/>
-      <c r="K25" s="41" t="n"/>
-      <c r="L25" s="34" t="n"/>
-      <c r="M25" s="41" t="n"/>
-      <c r="N25" s="34" t="n"/>
-      <c r="O25" s="41" t="n"/>
-      <c r="P25" s="34" t="n"/>
-      <c r="Q25" s="41" t="n"/>
-      <c r="R25" s="34" t="n"/>
-      <c r="S25" s="41" t="n"/>
-      <c r="T25" s="34" t="n"/>
-      <c r="U25" s="41" t="n"/>
-      <c r="V25" s="34" t="n"/>
-      <c r="W25" s="41" t="n"/>
-      <c r="X25" s="34" t="n"/>
-      <c r="Y25" s="41" t="n"/>
-      <c r="Z25" s="34" t="n"/>
-      <c r="AA25" s="41" t="n"/>
-      <c r="AB25" s="34" t="n"/>
-      <c r="AC25" s="41" t="n"/>
-      <c r="AD25" s="34" t="n"/>
-      <c r="AE25" s="41" t="n"/>
-      <c r="AF25" s="34" t="n"/>
-      <c r="AG25" s="42" t="n"/>
+      <c r="C25" s="42" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="42" t="n"/>
+      <c r="H25" s="35" t="n"/>
+      <c r="I25" s="42" t="n"/>
+      <c r="J25" s="35" t="n"/>
+      <c r="K25" s="42" t="n"/>
+      <c r="L25" s="35" t="n"/>
+      <c r="M25" s="42" t="n"/>
+      <c r="N25" s="35" t="n"/>
+      <c r="O25" s="42" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="42" t="n"/>
+      <c r="R25" s="35" t="n"/>
+      <c r="S25" s="42" t="n"/>
+      <c r="T25" s="35" t="n"/>
+      <c r="U25" s="42" t="n"/>
+      <c r="V25" s="35" t="n"/>
+      <c r="W25" s="42" t="n"/>
+      <c r="X25" s="35" t="n"/>
+      <c r="Y25" s="42" t="n"/>
+      <c r="Z25" s="35" t="n"/>
+      <c r="AA25" s="42" t="n"/>
+      <c r="AB25" s="35" t="n"/>
+      <c r="AC25" s="42" t="n"/>
+      <c r="AD25" s="35" t="n"/>
+      <c r="AE25" s="42" t="n"/>
+      <c r="AF25" s="35" t="n"/>
+      <c r="AG25" s="43" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>Gối: tên trục  ·  Nhịp: thép đai</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
-      <c r="C26" s="41" t="n"/>
-      <c r="D26" s="34" t="n"/>
-      <c r="E26" s="41" t="n"/>
-      <c r="F26" s="34" t="n"/>
-      <c r="G26" s="41" t="n"/>
-      <c r="H26" s="34" t="n"/>
-      <c r="I26" s="41" t="n"/>
-      <c r="J26" s="34" t="n"/>
-      <c r="K26" s="41" t="n"/>
-      <c r="L26" s="34" t="n"/>
-      <c r="M26" s="41" t="n"/>
-      <c r="N26" s="34" t="n"/>
-      <c r="O26" s="41" t="n"/>
-      <c r="P26" s="34" t="n"/>
-      <c r="Q26" s="41" t="n"/>
-      <c r="R26" s="34" t="n"/>
-      <c r="S26" s="41" t="n"/>
-      <c r="T26" s="34" t="n"/>
-      <c r="U26" s="41" t="n"/>
-      <c r="V26" s="34" t="n"/>
-      <c r="W26" s="41" t="n"/>
-      <c r="X26" s="34" t="n"/>
-      <c r="Y26" s="41" t="n"/>
-      <c r="Z26" s="34" t="n"/>
-      <c r="AA26" s="41" t="n"/>
-      <c r="AB26" s="34" t="n"/>
-      <c r="AC26" s="41" t="n"/>
-      <c r="AD26" s="34" t="n"/>
-      <c r="AE26" s="41" t="n"/>
-      <c r="AF26" s="34" t="n"/>
-      <c r="AG26" s="42" t="n"/>
+      <c r="C26" s="42" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="42" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="42" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="42" t="n"/>
+      <c r="J26" s="35" t="n"/>
+      <c r="K26" s="42" t="n"/>
+      <c r="L26" s="35" t="n"/>
+      <c r="M26" s="42" t="n"/>
+      <c r="N26" s="35" t="n"/>
+      <c r="O26" s="42" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="42" t="n"/>
+      <c r="R26" s="35" t="n"/>
+      <c r="S26" s="42" t="n"/>
+      <c r="T26" s="35" t="n"/>
+      <c r="U26" s="42" t="n"/>
+      <c r="V26" s="35" t="n"/>
+      <c r="W26" s="42" t="n"/>
+      <c r="X26" s="35" t="n"/>
+      <c r="Y26" s="42" t="n"/>
+      <c r="Z26" s="35" t="n"/>
+      <c r="AA26" s="42" t="n"/>
+      <c r="AB26" s="35" t="n"/>
+      <c r="AC26" s="42" t="n"/>
+      <c r="AD26" s="35" t="n"/>
+      <c r="AE26" s="42" t="n"/>
+      <c r="AF26" s="35" t="n"/>
+      <c r="AG26" s="43" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>Gối: lệch trục  ·  Nhịp: đai trong / cắt thép</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
-      <c r="C27" s="41" t="n"/>
-      <c r="D27" s="34" t="n"/>
-      <c r="E27" s="41" t="n"/>
-      <c r="F27" s="34" t="n"/>
-      <c r="G27" s="41" t="n"/>
-      <c r="H27" s="34" t="n"/>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="34" t="n"/>
-      <c r="K27" s="41" t="n"/>
-      <c r="L27" s="34" t="n"/>
-      <c r="M27" s="41" t="n"/>
-      <c r="N27" s="34" t="n"/>
-      <c r="O27" s="41" t="n"/>
-      <c r="P27" s="34" t="n"/>
-      <c r="Q27" s="41" t="n"/>
-      <c r="R27" s="34" t="n"/>
-      <c r="S27" s="41" t="n"/>
-      <c r="T27" s="34" t="n"/>
-      <c r="U27" s="41" t="n"/>
-      <c r="V27" s="34" t="n"/>
-      <c r="W27" s="41" t="n"/>
-      <c r="X27" s="34" t="n"/>
-      <c r="Y27" s="41" t="n"/>
-      <c r="Z27" s="34" t="n"/>
-      <c r="AA27" s="41" t="n"/>
-      <c r="AB27" s="34" t="n"/>
-      <c r="AC27" s="41" t="n"/>
-      <c r="AD27" s="34" t="n"/>
-      <c r="AE27" s="41" t="n"/>
-      <c r="AF27" s="34" t="n"/>
-      <c r="AG27" s="42" t="n"/>
+      <c r="C27" s="42" t="n"/>
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="42" t="n"/>
+      <c r="H27" s="35" t="n"/>
+      <c r="I27" s="42" t="n"/>
+      <c r="J27" s="35" t="n"/>
+      <c r="K27" s="42" t="n"/>
+      <c r="L27" s="35" t="n"/>
+      <c r="M27" s="42" t="n"/>
+      <c r="N27" s="35" t="n"/>
+      <c r="O27" s="42" t="n"/>
+      <c r="P27" s="35" t="n"/>
+      <c r="Q27" s="42" t="n"/>
+      <c r="R27" s="35" t="n"/>
+      <c r="S27" s="42" t="n"/>
+      <c r="T27" s="35" t="n"/>
+      <c r="U27" s="42" t="n"/>
+      <c r="V27" s="35" t="n"/>
+      <c r="W27" s="42" t="n"/>
+      <c r="X27" s="35" t="n"/>
+      <c r="Y27" s="42" t="n"/>
+      <c r="Z27" s="35" t="n"/>
+      <c r="AA27" s="42" t="n"/>
+      <c r="AB27" s="35" t="n"/>
+      <c r="AC27" s="42" t="n"/>
+      <c r="AD27" s="35" t="n"/>
+      <c r="AE27" s="42" t="n"/>
+      <c r="AF27" s="35" t="n"/>
+      <c r="AG27" s="43" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>Gối: dầm giao trong nhịp phải  ·  Nhịp: kiểu đai</t>
         </is>
       </c>
       <c r="B28" s="6" t="n"/>
-      <c r="C28" s="41" t="n"/>
-      <c r="D28" s="34" t="n"/>
-      <c r="E28" s="41" t="n"/>
-      <c r="F28" s="34" t="n"/>
-      <c r="G28" s="41" t="n"/>
-      <c r="H28" s="34" t="n"/>
-      <c r="I28" s="41" t="n"/>
-      <c r="J28" s="34" t="n"/>
-      <c r="K28" s="41" t="n"/>
-      <c r="L28" s="34" t="n"/>
-      <c r="M28" s="41" t="n"/>
-      <c r="N28" s="34" t="n"/>
-      <c r="O28" s="41" t="n"/>
-      <c r="P28" s="34" t="n"/>
-      <c r="Q28" s="41" t="n"/>
-      <c r="R28" s="34" t="n"/>
-      <c r="S28" s="41" t="n"/>
-      <c r="T28" s="34" t="n"/>
-      <c r="U28" s="41" t="n"/>
-      <c r="V28" s="34" t="n"/>
-      <c r="W28" s="41" t="n"/>
-      <c r="X28" s="34" t="n"/>
-      <c r="Y28" s="41" t="n"/>
-      <c r="Z28" s="34" t="n"/>
-      <c r="AA28" s="41" t="n"/>
-      <c r="AB28" s="34" t="n"/>
-      <c r="AC28" s="41" t="n"/>
-      <c r="AD28" s="34" t="n"/>
-      <c r="AE28" s="41" t="n"/>
-      <c r="AF28" s="34" t="n"/>
-      <c r="AG28" s="42" t="n"/>
+      <c r="C28" s="42" t="n"/>
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="42" t="n"/>
+      <c r="H28" s="35" t="n"/>
+      <c r="I28" s="42" t="n"/>
+      <c r="J28" s="35" t="n"/>
+      <c r="K28" s="42" t="n"/>
+      <c r="L28" s="35" t="n"/>
+      <c r="M28" s="42" t="n"/>
+      <c r="N28" s="35" t="n"/>
+      <c r="O28" s="42" t="n"/>
+      <c r="P28" s="35" t="n"/>
+      <c r="Q28" s="42" t="n"/>
+      <c r="R28" s="35" t="n"/>
+      <c r="S28" s="42" t="n"/>
+      <c r="T28" s="35" t="n"/>
+      <c r="U28" s="42" t="n"/>
+      <c r="V28" s="35" t="n"/>
+      <c r="W28" s="42" t="n"/>
+      <c r="X28" s="35" t="n"/>
+      <c r="Y28" s="42" t="n"/>
+      <c r="Z28" s="35" t="n"/>
+      <c r="AA28" s="42" t="n"/>
+      <c r="AB28" s="35" t="n"/>
+      <c r="AC28" s="42" t="n"/>
+      <c r="AD28" s="35" t="n"/>
+      <c r="AE28" s="42" t="n"/>
+      <c r="AF28" s="35" t="n"/>
+      <c r="AG28" s="43" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>Gối: vị trí dầm giao  ·  Nhịp: đai gia cường</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
-      <c r="C29" s="41" t="n"/>
-      <c r="D29" s="34" t="n"/>
-      <c r="E29" s="41" t="n"/>
-      <c r="F29" s="34" t="n"/>
-      <c r="G29" s="41" t="n"/>
-      <c r="H29" s="34" t="n"/>
-      <c r="I29" s="41" t="n"/>
-      <c r="J29" s="34" t="n"/>
-      <c r="K29" s="41" t="n"/>
-      <c r="L29" s="34" t="n"/>
-      <c r="M29" s="41" t="n"/>
-      <c r="N29" s="34" t="n"/>
-      <c r="O29" s="41" t="n"/>
-      <c r="P29" s="34" t="n"/>
-      <c r="Q29" s="41" t="n"/>
-      <c r="R29" s="34" t="n"/>
-      <c r="S29" s="41" t="n"/>
-      <c r="T29" s="34" t="n"/>
-      <c r="U29" s="41" t="n"/>
-      <c r="V29" s="34" t="n"/>
-      <c r="W29" s="41" t="n"/>
-      <c r="X29" s="34" t="n"/>
-      <c r="Y29" s="41" t="n"/>
-      <c r="Z29" s="34" t="n"/>
-      <c r="AA29" s="41" t="n"/>
-      <c r="AB29" s="34" t="n"/>
-      <c r="AC29" s="41" t="n"/>
-      <c r="AD29" s="34" t="n"/>
-      <c r="AE29" s="41" t="n"/>
-      <c r="AF29" s="34" t="n"/>
-      <c r="AG29" s="42" t="n"/>
+      <c r="C29" s="42" t="n"/>
+      <c r="D29" s="35" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="F29" s="35" t="n"/>
+      <c r="G29" s="42" t="n"/>
+      <c r="H29" s="35" t="n"/>
+      <c r="I29" s="42" t="n"/>
+      <c r="J29" s="35" t="n"/>
+      <c r="K29" s="42" t="n"/>
+      <c r="L29" s="35" t="n"/>
+      <c r="M29" s="42" t="n"/>
+      <c r="N29" s="35" t="n"/>
+      <c r="O29" s="42" t="n"/>
+      <c r="P29" s="35" t="n"/>
+      <c r="Q29" s="42" t="n"/>
+      <c r="R29" s="35" t="n"/>
+      <c r="S29" s="42" t="n"/>
+      <c r="T29" s="35" t="n"/>
+      <c r="U29" s="42" t="n"/>
+      <c r="V29" s="35" t="n"/>
+      <c r="W29" s="42" t="n"/>
+      <c r="X29" s="35" t="n"/>
+      <c r="Y29" s="42" t="n"/>
+      <c r="Z29" s="35" t="n"/>
+      <c r="AA29" s="42" t="n"/>
+      <c r="AB29" s="35" t="n"/>
+      <c r="AC29" s="42" t="n"/>
+      <c r="AD29" s="35" t="n"/>
+      <c r="AE29" s="42" t="n"/>
+      <c r="AF29" s="35" t="n"/>
+      <c r="AG29" s="43" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>Nhịp: thép vai bò tại dầm giao</t>
         </is>
       </c>
-      <c r="B30" s="44" t="n"/>
-      <c r="C30" s="45" t="inlineStr"/>
-      <c r="D30" s="46" t="n"/>
-      <c r="E30" s="45" t="inlineStr"/>
-      <c r="F30" s="46" t="n"/>
-      <c r="G30" s="45" t="inlineStr"/>
-      <c r="H30" s="46" t="n"/>
-      <c r="I30" s="45" t="inlineStr"/>
-      <c r="J30" s="46" t="n"/>
-      <c r="K30" s="45" t="inlineStr"/>
-      <c r="L30" s="46" t="n"/>
-      <c r="M30" s="45" t="inlineStr"/>
-      <c r="N30" s="46" t="n"/>
-      <c r="O30" s="45" t="inlineStr"/>
-      <c r="P30" s="46" t="n"/>
-      <c r="Q30" s="45" t="inlineStr"/>
-      <c r="R30" s="46" t="n"/>
-      <c r="S30" s="45" t="inlineStr"/>
-      <c r="T30" s="46" t="n"/>
-      <c r="U30" s="45" t="inlineStr"/>
-      <c r="V30" s="46" t="n"/>
-      <c r="W30" s="45" t="inlineStr"/>
-      <c r="X30" s="46" t="n"/>
-      <c r="Y30" s="45" t="inlineStr"/>
-      <c r="Z30" s="46" t="n"/>
-      <c r="AA30" s="45" t="inlineStr"/>
-      <c r="AB30" s="46" t="n"/>
-      <c r="AC30" s="45" t="inlineStr"/>
-      <c r="AD30" s="46" t="n"/>
-      <c r="AE30" s="45" t="inlineStr"/>
-      <c r="AF30" s="46" t="n"/>
-      <c r="AG30" s="47" t="inlineStr"/>
+      <c r="B30" s="45" t="n"/>
+      <c r="C30" s="46" t="inlineStr"/>
+      <c r="D30" s="47" t="n"/>
+      <c r="E30" s="46" t="inlineStr"/>
+      <c r="F30" s="47" t="n"/>
+      <c r="G30" s="46" t="inlineStr"/>
+      <c r="H30" s="47" t="n"/>
+      <c r="I30" s="46" t="inlineStr"/>
+      <c r="J30" s="47" t="n"/>
+      <c r="K30" s="46" t="inlineStr"/>
+      <c r="L30" s="47" t="n"/>
+      <c r="M30" s="46" t="inlineStr"/>
+      <c r="N30" s="47" t="n"/>
+      <c r="O30" s="46" t="inlineStr"/>
+      <c r="P30" s="47" t="n"/>
+      <c r="Q30" s="46" t="inlineStr"/>
+      <c r="R30" s="47" t="n"/>
+      <c r="S30" s="46" t="inlineStr"/>
+      <c r="T30" s="47" t="n"/>
+      <c r="U30" s="46" t="inlineStr"/>
+      <c r="V30" s="47" t="n"/>
+      <c r="W30" s="46" t="inlineStr"/>
+      <c r="X30" s="47" t="n"/>
+      <c r="Y30" s="46" t="inlineStr"/>
+      <c r="Z30" s="47" t="n"/>
+      <c r="AA30" s="46" t="inlineStr"/>
+      <c r="AB30" s="47" t="n"/>
+      <c r="AC30" s="46" t="inlineStr"/>
+      <c r="AD30" s="47" t="n"/>
+      <c r="AE30" s="46" t="inlineStr"/>
+      <c r="AF30" s="47" t="n"/>
+      <c r="AG30" s="48" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="48" t="inlineStr">
+      <c r="A32" s="49" t="inlineStr">
         <is>
           <t>KIỂM TRA HÌNH HỌC (tự tính – đối chiếu mặt bằng kết cấu)</t>
         </is>
       </c>
-      <c r="B32" s="49" t="n"/>
-      <c r="C32" s="49" t="n"/>
-      <c r="D32" s="49" t="n"/>
-      <c r="E32" s="49" t="n"/>
-      <c r="F32" s="49" t="n"/>
-      <c r="G32" s="49" t="n"/>
-      <c r="H32" s="49" t="n"/>
-      <c r="I32" s="49" t="n"/>
-      <c r="J32" s="49" t="n"/>
-      <c r="K32" s="49" t="n"/>
-      <c r="L32" s="49" t="n"/>
-      <c r="M32" s="49" t="n"/>
-      <c r="N32" s="49" t="n"/>
-      <c r="O32" s="49" t="n"/>
-      <c r="P32" s="49" t="n"/>
-      <c r="Q32" s="49" t="n"/>
-      <c r="R32" s="49" t="n"/>
-      <c r="S32" s="49" t="n"/>
-      <c r="T32" s="49" t="n"/>
-      <c r="U32" s="49" t="n"/>
-      <c r="V32" s="49" t="n"/>
-      <c r="W32" s="49" t="n"/>
-      <c r="X32" s="49" t="n"/>
-      <c r="Y32" s="49" t="n"/>
-      <c r="Z32" s="49" t="n"/>
-      <c r="AA32" s="49" t="n"/>
-      <c r="AB32" s="49" t="n"/>
-      <c r="AC32" s="49" t="n"/>
-      <c r="AD32" s="49" t="n"/>
-      <c r="AE32" s="49" t="n"/>
-      <c r="AF32" s="49" t="n"/>
-      <c r="AG32" s="49" t="n"/>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+      <c r="E32" s="50" t="n"/>
+      <c r="F32" s="50" t="n"/>
+      <c r="G32" s="50" t="n"/>
+      <c r="H32" s="50" t="n"/>
+      <c r="I32" s="50" t="n"/>
+      <c r="J32" s="50" t="n"/>
+      <c r="K32" s="50" t="n"/>
+      <c r="L32" s="50" t="n"/>
+      <c r="M32" s="50" t="n"/>
+      <c r="N32" s="50" t="n"/>
+      <c r="O32" s="50" t="n"/>
+      <c r="P32" s="50" t="n"/>
+      <c r="Q32" s="50" t="n"/>
+      <c r="R32" s="50" t="n"/>
+      <c r="S32" s="50" t="n"/>
+      <c r="T32" s="50" t="n"/>
+      <c r="U32" s="50" t="n"/>
+      <c r="V32" s="50" t="n"/>
+      <c r="W32" s="50" t="n"/>
+      <c r="X32" s="50" t="n"/>
+      <c r="Y32" s="50" t="n"/>
+      <c r="Z32" s="50" t="n"/>
+      <c r="AA32" s="50" t="n"/>
+      <c r="AB32" s="50" t="n"/>
+      <c r="AC32" s="50" t="n"/>
+      <c r="AD32" s="50" t="n"/>
+      <c r="AE32" s="50" t="n"/>
+      <c r="AF32" s="50" t="n"/>
+      <c r="AG32" s="50" t="n"/>
     </row>
     <row r="33" ht="27" customHeight="1">
-      <c r="A33" s="50" t="inlineStr">
+      <c r="A33" s="51" t="inlineStr">
         <is>
           <t>Gối: tọa độ trục (gốc = trục gối 1)  ·  Nhịp: KC trục-trục (mm)</t>
         </is>
       </c>
       <c r="B33" s="6" t="n"/>
-      <c r="C33" s="51">
+      <c r="C33" s="52">
         <f>IF(C63=1,C62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="52">
         <f>IF(D63=1,IFERROR(E62-C62,""),"")</f>
         <v/>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="52">
         <f>IF(E63=1,E62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="F33" s="51">
+      <c r="F33" s="52">
         <f>IF(F63=1,IFERROR(G62-E62,""),"")</f>
         <v/>
       </c>
-      <c r="G33" s="51">
+      <c r="G33" s="52">
         <f>IF(G63=1,G62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="H33" s="51">
+      <c r="H33" s="52">
         <f>IF(H63=1,IFERROR(I62-G62,""),"")</f>
         <v/>
       </c>
-      <c r="I33" s="51">
+      <c r="I33" s="52">
         <f>IF(I63=1,I62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="J33" s="51">
+      <c r="J33" s="52">
         <f>IF(J63=1,IFERROR(K62-I62,""),"")</f>
         <v/>
       </c>
-      <c r="K33" s="51">
+      <c r="K33" s="52">
         <f>IF(K63=1,K62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="L33" s="51">
+      <c r="L33" s="52">
         <f>IF(L63=1,IFERROR(M62-K62,""),"")</f>
         <v/>
       </c>
-      <c r="M33" s="51">
+      <c r="M33" s="52">
         <f>IF(M63=1,M62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="N33" s="51">
+      <c r="N33" s="52">
         <f>IF(N63=1,IFERROR(O62-M62,""),"")</f>
         <v/>
       </c>
-      <c r="O33" s="51">
+      <c r="O33" s="52">
         <f>IF(O63=1,O62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="P33" s="51">
+      <c r="P33" s="52">
         <f>IF(P63=1,IFERROR(Q62-O62,""),"")</f>
         <v/>
       </c>
-      <c r="Q33" s="51">
+      <c r="Q33" s="52">
         <f>IF(Q63=1,Q62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="R33" s="51">
+      <c r="R33" s="52">
         <f>IF(R63=1,IFERROR(S62-Q62,""),"")</f>
         <v/>
       </c>
-      <c r="S33" s="51">
+      <c r="S33" s="52">
         <f>IF(S63=1,S62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="T33" s="51">
+      <c r="T33" s="52">
         <f>IF(T63=1,IFERROR(U62-S62,""),"")</f>
         <v/>
       </c>
-      <c r="U33" s="51">
+      <c r="U33" s="52">
         <f>IF(U63=1,U62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="V33" s="51">
+      <c r="V33" s="52">
         <f>IF(V63=1,IFERROR(W62-U62,""),"")</f>
         <v/>
       </c>
-      <c r="W33" s="51">
+      <c r="W33" s="52">
         <f>IF(W63=1,W62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="X33" s="51">
+      <c r="X33" s="52">
         <f>IF(X63=1,IFERROR(Y62-W62,""),"")</f>
         <v/>
       </c>
-      <c r="Y33" s="51">
+      <c r="Y33" s="52">
         <f>IF(Y63=1,Y62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="Z33" s="51">
+      <c r="Z33" s="52">
         <f>IF(Z63=1,IFERROR(AA62-Y62,""),"")</f>
         <v/>
       </c>
-      <c r="AA33" s="51">
+      <c r="AA33" s="52">
         <f>IF(AA63=1,AA62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="AB33" s="51">
+      <c r="AB33" s="52">
         <f>IF(AB63=1,IFERROR(AC62-AA62,""),"")</f>
         <v/>
       </c>
-      <c r="AC33" s="51">
+      <c r="AC33" s="52">
         <f>IF(AC63=1,AC62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="AD33" s="51">
+      <c r="AD33" s="52">
         <f>IF(AD63=1,IFERROR(AE62-AC62,""),"")</f>
         <v/>
       </c>
-      <c r="AE33" s="51">
+      <c r="AE33" s="52">
         <f>IF(AE63=1,AE62-$C$62,"")</f>
         <v/>
       </c>
-      <c r="AF33" s="51">
+      <c r="AF33" s="52">
         <f>IF(AF63=1,IFERROR(AG62-AE62,""),"")</f>
         <v/>
       </c>
-      <c r="AG33" s="51">
+      <c r="AG33" s="52">
         <f>IF(AG63=1,AG62-$C$62,"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="27" customHeight="1">
-      <c r="A34" s="52" t="inlineStr">
+      <c r="A34" s="53" t="inlineStr">
         <is>
           <t>Nhịp: KC trục theo mặt bằng (nhập để đối chiếu)</t>
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="54" t="n"/>
-      <c r="E34" s="53" t="n"/>
-      <c r="F34" s="54" t="n"/>
-      <c r="G34" s="53" t="n"/>
-      <c r="H34" s="54" t="n"/>
-      <c r="I34" s="53" t="n"/>
-      <c r="J34" s="54" t="n"/>
-      <c r="K34" s="53" t="n"/>
-      <c r="L34" s="54" t="n"/>
-      <c r="M34" s="53" t="n"/>
-      <c r="N34" s="54" t="n"/>
-      <c r="O34" s="53" t="n"/>
-      <c r="P34" s="54" t="n"/>
-      <c r="Q34" s="53" t="n"/>
-      <c r="R34" s="54" t="n"/>
-      <c r="S34" s="53" t="n"/>
-      <c r="T34" s="54" t="n"/>
-      <c r="U34" s="53" t="n"/>
-      <c r="V34" s="54" t="n"/>
-      <c r="W34" s="53" t="n"/>
-      <c r="X34" s="54" t="n"/>
-      <c r="Y34" s="53" t="n"/>
-      <c r="Z34" s="54" t="n"/>
-      <c r="AA34" s="53" t="n"/>
-      <c r="AB34" s="54" t="n"/>
-      <c r="AC34" s="53" t="n"/>
-      <c r="AD34" s="54" t="n"/>
-      <c r="AE34" s="53" t="n"/>
-      <c r="AF34" s="54" t="n"/>
-      <c r="AG34" s="53" t="n"/>
+      <c r="C34" s="54" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="54" t="n"/>
+      <c r="F34" s="55" t="n"/>
+      <c r="G34" s="54" t="n"/>
+      <c r="H34" s="55" t="n"/>
+      <c r="I34" s="54" t="n"/>
+      <c r="J34" s="55" t="n"/>
+      <c r="K34" s="54" t="n"/>
+      <c r="L34" s="55" t="n"/>
+      <c r="M34" s="54" t="n"/>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="54" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="54" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="54" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="54" t="n"/>
+      <c r="V34" s="55" t="n"/>
+      <c r="W34" s="54" t="n"/>
+      <c r="X34" s="55" t="n"/>
+      <c r="Y34" s="54" t="n"/>
+      <c r="Z34" s="55" t="n"/>
+      <c r="AA34" s="54" t="n"/>
+      <c r="AB34" s="55" t="n"/>
+      <c r="AC34" s="54" t="n"/>
+      <c r="AD34" s="55" t="n"/>
+      <c r="AE34" s="54" t="n"/>
+      <c r="AF34" s="55" t="n"/>
+      <c r="AG34" s="54" t="n"/>
     </row>
     <row r="35" ht="27" customHeight="1">
-      <c r="A35" s="50" t="inlineStr">
+      <c r="A35" s="51" t="inlineStr">
         <is>
           <t>Nhịp: Ltt suy ra từ KC trục ở dòng 34 (mm)</t>
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
-      <c r="C35" s="51" t="n"/>
-      <c r="D35" s="51">
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52">
         <f>IF(D34="","",D34-(N(C60)/2-C67)-(N(E60)/2+E67))</f>
         <v/>
       </c>
-      <c r="E35" s="51" t="n"/>
-      <c r="F35" s="51">
+      <c r="E35" s="52" t="n"/>
+      <c r="F35" s="52">
         <f>IF(F34="","",F34-(N(E60)/2-E67)-(N(G60)/2+G67))</f>
         <v/>
       </c>
-      <c r="G35" s="51" t="n"/>
-      <c r="H35" s="51">
+      <c r="G35" s="52" t="n"/>
+      <c r="H35" s="52">
         <f>IF(H34="","",H34-(N(G60)/2-G67)-(N(I60)/2+I67))</f>
         <v/>
       </c>
-      <c r="I35" s="51" t="n"/>
-      <c r="J35" s="51">
+      <c r="I35" s="52" t="n"/>
+      <c r="J35" s="52">
         <f>IF(J34="","",J34-(N(I60)/2-I67)-(N(K60)/2+K67))</f>
         <v/>
       </c>
-      <c r="K35" s="51" t="n"/>
-      <c r="L35" s="51">
+      <c r="K35" s="52" t="n"/>
+      <c r="L35" s="52">
         <f>IF(L34="","",L34-(N(K60)/2-K67)-(N(M60)/2+M67))</f>
         <v/>
       </c>
-      <c r="M35" s="51" t="n"/>
-      <c r="N35" s="51">
+      <c r="M35" s="52" t="n"/>
+      <c r="N35" s="52">
         <f>IF(N34="","",N34-(N(M60)/2-M67)-(N(O60)/2+O67))</f>
         <v/>
       </c>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51">
+      <c r="O35" s="52" t="n"/>
+      <c r="P35" s="52">
         <f>IF(P34="","",P34-(N(O60)/2-O67)-(N(Q60)/2+Q67))</f>
         <v/>
       </c>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51">
+      <c r="Q35" s="52" t="n"/>
+      <c r="R35" s="52">
         <f>IF(R34="","",R34-(N(Q60)/2-Q67)-(N(S60)/2+S67))</f>
         <v/>
       </c>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51">
+      <c r="S35" s="52" t="n"/>
+      <c r="T35" s="52">
         <f>IF(T34="","",T34-(N(S60)/2-S67)-(N(U60)/2+U67))</f>
         <v/>
       </c>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="51">
+      <c r="U35" s="52" t="n"/>
+      <c r="V35" s="52">
         <f>IF(V34="","",V34-(N(U60)/2-U67)-(N(W60)/2+W67))</f>
         <v/>
       </c>
-      <c r="W35" s="51" t="n"/>
-      <c r="X35" s="51">
+      <c r="W35" s="52" t="n"/>
+      <c r="X35" s="52">
         <f>IF(X34="","",X34-(N(W60)/2-W67)-(N(Y60)/2+Y67))</f>
         <v/>
       </c>
-      <c r="Y35" s="51" t="n"/>
-      <c r="Z35" s="51">
+      <c r="Y35" s="52" t="n"/>
+      <c r="Z35" s="52">
         <f>IF(Z34="","",Z34-(N(Y60)/2-Y67)-(N(AA60)/2+AA67))</f>
         <v/>
       </c>
-      <c r="AA35" s="51" t="n"/>
-      <c r="AB35" s="51">
+      <c r="AA35" s="52" t="n"/>
+      <c r="AB35" s="52">
         <f>IF(AB34="","",AB34-(N(AA60)/2-AA67)-(N(AC60)/2+AC67))</f>
         <v/>
       </c>
-      <c r="AC35" s="51" t="n"/>
-      <c r="AD35" s="51">
+      <c r="AC35" s="52" t="n"/>
+      <c r="AD35" s="52">
         <f>IF(AD34="","",AD34-(N(AC60)/2-AC67)-(N(AE60)/2+AE67))</f>
         <v/>
       </c>
-      <c r="AE35" s="51" t="n"/>
-      <c r="AF35" s="51">
+      <c r="AE35" s="52" t="n"/>
+      <c r="AF35" s="52">
         <f>IF(AF34="","",AF34-(N(AE60)/2-AE67)-(N(AG60)/2+AG67))</f>
         <v/>
       </c>
-      <c r="AG35" s="51" t="n"/>
+      <c r="AG35" s="52" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="48" t="inlineStr">
+      <c r="A36" s="49" t="inlineStr">
         <is>
           <t>KIỂM TRA DIỆN TÍCH THÉP (cm²) – thép chạy suốt hiệu dụng + tăng cường lớp 1..5 (gối: trái/phải)</t>
         </is>
       </c>
-      <c r="B36" s="49" t="n"/>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="49" t="n"/>
-      <c r="E36" s="49" t="n"/>
-      <c r="F36" s="49" t="n"/>
-      <c r="G36" s="49" t="n"/>
-      <c r="H36" s="49" t="n"/>
-      <c r="I36" s="49" t="n"/>
-      <c r="J36" s="49" t="n"/>
-      <c r="K36" s="49" t="n"/>
-      <c r="L36" s="49" t="n"/>
-      <c r="M36" s="49" t="n"/>
-      <c r="N36" s="49" t="n"/>
-      <c r="O36" s="49" t="n"/>
-      <c r="P36" s="49" t="n"/>
-      <c r="Q36" s="49" t="n"/>
-      <c r="R36" s="49" t="n"/>
-      <c r="S36" s="49" t="n"/>
-      <c r="T36" s="49" t="n"/>
-      <c r="U36" s="49" t="n"/>
-      <c r="V36" s="49" t="n"/>
-      <c r="W36" s="49" t="n"/>
-      <c r="X36" s="49" t="n"/>
-      <c r="Y36" s="49" t="n"/>
-      <c r="Z36" s="49" t="n"/>
-      <c r="AA36" s="49" t="n"/>
-      <c r="AB36" s="49" t="n"/>
-      <c r="AC36" s="49" t="n"/>
-      <c r="AD36" s="49" t="n"/>
-      <c r="AE36" s="49" t="n"/>
-      <c r="AF36" s="49" t="n"/>
-      <c r="AG36" s="49" t="n"/>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+      <c r="E36" s="50" t="n"/>
+      <c r="F36" s="50" t="n"/>
+      <c r="G36" s="50" t="n"/>
+      <c r="H36" s="50" t="n"/>
+      <c r="I36" s="50" t="n"/>
+      <c r="J36" s="50" t="n"/>
+      <c r="K36" s="50" t="n"/>
+      <c r="L36" s="50" t="n"/>
+      <c r="M36" s="50" t="n"/>
+      <c r="N36" s="50" t="n"/>
+      <c r="O36" s="50" t="n"/>
+      <c r="P36" s="50" t="n"/>
+      <c r="Q36" s="50" t="n"/>
+      <c r="R36" s="50" t="n"/>
+      <c r="S36" s="50" t="n"/>
+      <c r="T36" s="50" t="n"/>
+      <c r="U36" s="50" t="n"/>
+      <c r="V36" s="50" t="n"/>
+      <c r="W36" s="50" t="n"/>
+      <c r="X36" s="50" t="n"/>
+      <c r="Y36" s="50" t="n"/>
+      <c r="Z36" s="50" t="n"/>
+      <c r="AA36" s="50" t="n"/>
+      <c r="AB36" s="50" t="n"/>
+      <c r="AC36" s="50" t="n"/>
+      <c r="AD36" s="50" t="n"/>
+      <c r="AE36" s="50" t="n"/>
+      <c r="AF36" s="50" t="n"/>
+      <c r="AG36" s="50" t="n"/>
     </row>
     <row r="37" ht="27" customHeight="1">
-      <c r="A37" s="52" t="inlineStr">
+      <c r="A37" s="53" t="inlineStr">
         <is>
           <t>As yêu cầu TRÊN (nhập; gối: trái/phải vd 2.63/1.45)</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
-      <c r="C37" s="55" t="n"/>
-      <c r="D37" s="55" t="n"/>
-      <c r="E37" s="55" t="n"/>
-      <c r="F37" s="55" t="n"/>
-      <c r="G37" s="55" t="n"/>
-      <c r="H37" s="55" t="n"/>
-      <c r="I37" s="55" t="n"/>
-      <c r="J37" s="55" t="n"/>
-      <c r="K37" s="55" t="n"/>
-      <c r="L37" s="55" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="55" t="n"/>
-      <c r="W37" s="55" t="n"/>
-      <c r="X37" s="55" t="n"/>
-      <c r="Y37" s="55" t="n"/>
-      <c r="Z37" s="55" t="n"/>
-      <c r="AA37" s="55" t="n"/>
-      <c r="AB37" s="55" t="n"/>
-      <c r="AC37" s="55" t="n"/>
-      <c r="AD37" s="55" t="n"/>
-      <c r="AE37" s="55" t="n"/>
-      <c r="AF37" s="55" t="n"/>
-      <c r="AG37" s="55" t="n"/>
+      <c r="C37" s="56" t="n"/>
+      <c r="D37" s="56" t="n"/>
+      <c r="E37" s="56" t="n"/>
+      <c r="F37" s="56" t="n"/>
+      <c r="G37" s="56" t="n"/>
+      <c r="H37" s="56" t="n"/>
+      <c r="I37" s="56" t="n"/>
+      <c r="J37" s="56" t="n"/>
+      <c r="K37" s="56" t="n"/>
+      <c r="L37" s="56" t="n"/>
+      <c r="M37" s="56" t="n"/>
+      <c r="N37" s="56" t="n"/>
+      <c r="O37" s="56" t="n"/>
+      <c r="P37" s="56" t="n"/>
+      <c r="Q37" s="56" t="n"/>
+      <c r="R37" s="56" t="n"/>
+      <c r="S37" s="56" t="n"/>
+      <c r="T37" s="56" t="n"/>
+      <c r="U37" s="56" t="n"/>
+      <c r="V37" s="56" t="n"/>
+      <c r="W37" s="56" t="n"/>
+      <c r="X37" s="56" t="n"/>
+      <c r="Y37" s="56" t="n"/>
+      <c r="Z37" s="56" t="n"/>
+      <c r="AA37" s="56" t="n"/>
+      <c r="AB37" s="56" t="n"/>
+      <c r="AC37" s="56" t="n"/>
+      <c r="AD37" s="56" t="n"/>
+      <c r="AE37" s="56" t="n"/>
+      <c r="AF37" s="56" t="n"/>
+      <c r="AG37" s="56" t="n"/>
     </row>
     <row r="38" ht="27" customHeight="1">
-      <c r="A38" s="50" t="inlineStr">
+      <c r="A38" s="51" t="inlineStr">
         <is>
           <t>As bố trí TRÊN</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
-      <c r="C38" s="56">
+      <c r="C38" s="57">
         <f>IF(C63=1,IF(C65*C66=1,FIXED(C116,2,TRUE)&amp;"/"&amp;FIXED(C117,2,TRUE),IF(C65=1,FIXED(C116,2,TRUE),FIXED(C117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="D38" s="57">
+      <c r="D38" s="58">
         <f>IF(D63=1,ROUND(D116,2),"")</f>
         <v/>
       </c>
-      <c r="E38" s="56">
+      <c r="E38" s="57">
         <f>IF(E63=1,IF(E65*E66=1,FIXED(E116,2,TRUE)&amp;"/"&amp;FIXED(E117,2,TRUE),IF(E65=1,FIXED(E116,2,TRUE),FIXED(E117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="F38" s="57">
+      <c r="F38" s="58">
         <f>IF(F63=1,ROUND(F116,2),"")</f>
         <v/>
       </c>
-      <c r="G38" s="56">
+      <c r="G38" s="57">
         <f>IF(G63=1,IF(G65*G66=1,FIXED(G116,2,TRUE)&amp;"/"&amp;FIXED(G117,2,TRUE),IF(G65=1,FIXED(G116,2,TRUE),FIXED(G117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="H38" s="57">
+      <c r="H38" s="58">
         <f>IF(H63=1,ROUND(H116,2),"")</f>
         <v/>
       </c>
-      <c r="I38" s="56">
+      <c r="I38" s="57">
         <f>IF(I63=1,IF(I65*I66=1,FIXED(I116,2,TRUE)&amp;"/"&amp;FIXED(I117,2,TRUE),IF(I65=1,FIXED(I116,2,TRUE),FIXED(I117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="J38" s="57">
+      <c r="J38" s="58">
         <f>IF(J63=1,ROUND(J116,2),"")</f>
         <v/>
       </c>
-      <c r="K38" s="56">
+      <c r="K38" s="57">
         <f>IF(K63=1,IF(K65*K66=1,FIXED(K116,2,TRUE)&amp;"/"&amp;FIXED(K117,2,TRUE),IF(K65=1,FIXED(K116,2,TRUE),FIXED(K117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="L38" s="57">
+      <c r="L38" s="58">
         <f>IF(L63=1,ROUND(L116,2),"")</f>
         <v/>
       </c>
-      <c r="M38" s="56">
+      <c r="M38" s="57">
         <f>IF(M63=1,IF(M65*M66=1,FIXED(M116,2,TRUE)&amp;"/"&amp;FIXED(M117,2,TRUE),IF(M65=1,FIXED(M116,2,TRUE),FIXED(M117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="N38" s="57">
+      <c r="N38" s="58">
         <f>IF(N63=1,ROUND(N116,2),"")</f>
         <v/>
       </c>
-      <c r="O38" s="56">
+      <c r="O38" s="57">
         <f>IF(O63=1,IF(O65*O66=1,FIXED(O116,2,TRUE)&amp;"/"&amp;FIXED(O117,2,TRUE),IF(O65=1,FIXED(O116,2,TRUE),FIXED(O117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="P38" s="57">
+      <c r="P38" s="58">
         <f>IF(P63=1,ROUND(P116,2),"")</f>
         <v/>
       </c>
-      <c r="Q38" s="56">
+      <c r="Q38" s="57">
         <f>IF(Q63=1,IF(Q65*Q66=1,FIXED(Q116,2,TRUE)&amp;"/"&amp;FIXED(Q117,2,TRUE),IF(Q65=1,FIXED(Q116,2,TRUE),FIXED(Q117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="R38" s="57">
+      <c r="R38" s="58">
         <f>IF(R63=1,ROUND(R116,2),"")</f>
         <v/>
       </c>
-      <c r="S38" s="56">
+      <c r="S38" s="57">
         <f>IF(S63=1,IF(S65*S66=1,FIXED(S116,2,TRUE)&amp;"/"&amp;FIXED(S117,2,TRUE),IF(S65=1,FIXED(S116,2,TRUE),FIXED(S117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="T38" s="57">
+      <c r="T38" s="58">
         <f>IF(T63=1,ROUND(T116,2),"")</f>
         <v/>
       </c>
-      <c r="U38" s="56">
+      <c r="U38" s="57">
         <f>IF(U63=1,IF(U65*U66=1,FIXED(U116,2,TRUE)&amp;"/"&amp;FIXED(U117,2,TRUE),IF(U65=1,FIXED(U116,2,TRUE),FIXED(U117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="V38" s="57">
+      <c r="V38" s="58">
         <f>IF(V63=1,ROUND(V116,2),"")</f>
         <v/>
       </c>
-      <c r="W38" s="56">
+      <c r="W38" s="57">
         <f>IF(W63=1,IF(W65*W66=1,FIXED(W116,2,TRUE)&amp;"/"&amp;FIXED(W117,2,TRUE),IF(W65=1,FIXED(W116,2,TRUE),FIXED(W117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="X38" s="57">
+      <c r="X38" s="58">
         <f>IF(X63=1,ROUND(X116,2),"")</f>
         <v/>
       </c>
-      <c r="Y38" s="56">
+      <c r="Y38" s="57">
         <f>IF(Y63=1,IF(Y65*Y66=1,FIXED(Y116,2,TRUE)&amp;"/"&amp;FIXED(Y117,2,TRUE),IF(Y65=1,FIXED(Y116,2,TRUE),FIXED(Y117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="Z38" s="57">
+      <c r="Z38" s="58">
         <f>IF(Z63=1,ROUND(Z116,2),"")</f>
         <v/>
       </c>
-      <c r="AA38" s="56">
+      <c r="AA38" s="57">
         <f>IF(AA63=1,IF(AA65*AA66=1,FIXED(AA116,2,TRUE)&amp;"/"&amp;FIXED(AA117,2,TRUE),IF(AA65=1,FIXED(AA116,2,TRUE),FIXED(AA117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AB38" s="57">
+      <c r="AB38" s="58">
         <f>IF(AB63=1,ROUND(AB116,2),"")</f>
         <v/>
       </c>
-      <c r="AC38" s="56">
+      <c r="AC38" s="57">
         <f>IF(AC63=1,IF(AC65*AC66=1,FIXED(AC116,2,TRUE)&amp;"/"&amp;FIXED(AC117,2,TRUE),IF(AC65=1,FIXED(AC116,2,TRUE),FIXED(AC117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AD38" s="57">
+      <c r="AD38" s="58">
         <f>IF(AD63=1,ROUND(AD116,2),"")</f>
         <v/>
       </c>
-      <c r="AE38" s="56">
+      <c r="AE38" s="57">
         <f>IF(AE63=1,IF(AE65*AE66=1,FIXED(AE116,2,TRUE)&amp;"/"&amp;FIXED(AE117,2,TRUE),IF(AE65=1,FIXED(AE116,2,TRUE),FIXED(AE117,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AF38" s="57">
+      <c r="AF38" s="58">
         <f>IF(AF63=1,ROUND(AF116,2),"")</f>
         <v/>
       </c>
-      <c r="AG38" s="56">
+      <c r="AG38" s="57">
         <f>IF(AG63=1,IF(AG65*AG66=1,FIXED(AG116,2,TRUE)&amp;"/"&amp;FIXED(AG117,2,TRUE),IF(AG65=1,FIXED(AG116,2,TRUE),FIXED(AG117,2,TRUE))),"")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="27" customHeight="1">
-      <c r="A39" s="50" t="inlineStr">
+      <c r="A39" s="51" t="inlineStr">
         <is>
           <t>Hệ số As bố trí / yêu cầu TRÊN</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
-      <c r="C39" s="57">
+      <c r="C39" s="58">
         <f>IF(OR(C63=0,C120=""),"",IF(MIN(IF(AND(C65=1,N(C120)&gt;0),C116/C120,99),IF(AND(C66=1,N(C121)&gt;0),C117/C121,99))=99,"",ROUND(MIN(IF(AND(C65=1,N(C120)&gt;0),C116/C120,99),IF(AND(C66=1,N(C121)&gt;0),C117/C121,99)),2)))</f>
         <v/>
       </c>
-      <c r="D39" s="57">
+      <c r="D39" s="58">
         <f>IF(OR(D63=0,D120=""),"",IF(MIN(IF(AND(D65=1,N(D120)&gt;0),D116/D120,99),IF(AND(D66=1,N(D121)&gt;0),D117/D121,99))=99,"",ROUND(MIN(IF(AND(D65=1,N(D120)&gt;0),D116/D120,99),IF(AND(D66=1,N(D121)&gt;0),D117/D121,99)),2)))</f>
         <v/>
       </c>
-      <c r="E39" s="57">
+      <c r="E39" s="58">
         <f>IF(OR(E63=0,E120=""),"",IF(MIN(IF(AND(E65=1,N(E120)&gt;0),E116/E120,99),IF(AND(E66=1,N(E121)&gt;0),E117/E121,99))=99,"",ROUND(MIN(IF(AND(E65=1,N(E120)&gt;0),E116/E120,99),IF(AND(E66=1,N(E121)&gt;0),E117/E121,99)),2)))</f>
         <v/>
       </c>
-      <c r="F39" s="57">
+      <c r="F39" s="58">
         <f>IF(OR(F63=0,F120=""),"",IF(MIN(IF(AND(F65=1,N(F120)&gt;0),F116/F120,99),IF(AND(F66=1,N(F121)&gt;0),F117/F121,99))=99,"",ROUND(MIN(IF(AND(F65=1,N(F120)&gt;0),F116/F120,99),IF(AND(F66=1,N(F121)&gt;0),F117/F121,99)),2)))</f>
         <v/>
       </c>
-      <c r="G39" s="57">
+      <c r="G39" s="58">
         <f>IF(OR(G63=0,G120=""),"",IF(MIN(IF(AND(G65=1,N(G120)&gt;0),G116/G120,99),IF(AND(G66=1,N(G121)&gt;0),G117/G121,99))=99,"",ROUND(MIN(IF(AND(G65=1,N(G120)&gt;0),G116/G120,99),IF(AND(G66=1,N(G121)&gt;0),G117/G121,99)),2)))</f>
         <v/>
       </c>
-      <c r="H39" s="57">
+      <c r="H39" s="58">
         <f>IF(OR(H63=0,H120=""),"",IF(MIN(IF(AND(H65=1,N(H120)&gt;0),H116/H120,99),IF(AND(H66=1,N(H121)&gt;0),H117/H121,99))=99,"",ROUND(MIN(IF(AND(H65=1,N(H120)&gt;0),H116/H120,99),IF(AND(H66=1,N(H121)&gt;0),H117/H121,99)),2)))</f>
         <v/>
       </c>
-      <c r="I39" s="57">
+      <c r="I39" s="58">
         <f>IF(OR(I63=0,I120=""),"",IF(MIN(IF(AND(I65=1,N(I120)&gt;0),I116/I120,99),IF(AND(I66=1,N(I121)&gt;0),I117/I121,99))=99,"",ROUND(MIN(IF(AND(I65=1,N(I120)&gt;0),I116/I120,99),IF(AND(I66=1,N(I121)&gt;0),I117/I121,99)),2)))</f>
         <v/>
       </c>
-      <c r="J39" s="57">
+      <c r="J39" s="58">
         <f>IF(OR(J63=0,J120=""),"",IF(MIN(IF(AND(J65=1,N(J120)&gt;0),J116/J120,99),IF(AND(J66=1,N(J121)&gt;0),J117/J121,99))=99,"",ROUND(MIN(IF(AND(J65=1,N(J120)&gt;0),J116/J120,99),IF(AND(J66=1,N(J121)&gt;0),J117/J121,99)),2)))</f>
         <v/>
       </c>
-      <c r="K39" s="57">
+      <c r="K39" s="58">
         <f>IF(OR(K63=0,K120=""),"",IF(MIN(IF(AND(K65=1,N(K120)&gt;0),K116/K120,99),IF(AND(K66=1,N(K121)&gt;0),K117/K121,99))=99,"",ROUND(MIN(IF(AND(K65=1,N(K120)&gt;0),K116/K120,99),IF(AND(K66=1,N(K121)&gt;0),K117/K121,99)),2)))</f>
         <v/>
       </c>
-      <c r="L39" s="57">
+      <c r="L39" s="58">
         <f>IF(OR(L63=0,L120=""),"",IF(MIN(IF(AND(L65=1,N(L120)&gt;0),L116/L120,99),IF(AND(L66=1,N(L121)&gt;0),L117/L121,99))=99,"",ROUND(MIN(IF(AND(L65=1,N(L120)&gt;0),L116/L120,99),IF(AND(L66=1,N(L121)&gt;0),L117/L121,99)),2)))</f>
         <v/>
       </c>
-      <c r="M39" s="57">
+      <c r="M39" s="58">
         <f>IF(OR(M63=0,M120=""),"",IF(MIN(IF(AND(M65=1,N(M120)&gt;0),M116/M120,99),IF(AND(M66=1,N(M121)&gt;0),M117/M121,99))=99,"",ROUND(MIN(IF(AND(M65=1,N(M120)&gt;0),M116/M120,99),IF(AND(M66=1,N(M121)&gt;0),M117/M121,99)),2)))</f>
         <v/>
       </c>
-      <c r="N39" s="57">
+      <c r="N39" s="58">
         <f>IF(OR(N63=0,N120=""),"",IF(MIN(IF(AND(N65=1,N(N120)&gt;0),N116/N120,99),IF(AND(N66=1,N(N121)&gt;0),N117/N121,99))=99,"",ROUND(MIN(IF(AND(N65=1,N(N120)&gt;0),N116/N120,99),IF(AND(N66=1,N(N121)&gt;0),N117/N121,99)),2)))</f>
         <v/>
       </c>
-      <c r="O39" s="57">
+      <c r="O39" s="58">
         <f>IF(OR(O63=0,O120=""),"",IF(MIN(IF(AND(O65=1,N(O120)&gt;0),O116/O120,99),IF(AND(O66=1,N(O121)&gt;0),O117/O121,99))=99,"",ROUND(MIN(IF(AND(O65=1,N(O120)&gt;0),O116/O120,99),IF(AND(O66=1,N(O121)&gt;0),O117/O121,99)),2)))</f>
         <v/>
       </c>
-      <c r="P39" s="57">
+      <c r="P39" s="58">
         <f>IF(OR(P63=0,P120=""),"",IF(MIN(IF(AND(P65=1,N(P120)&gt;0),P116/P120,99),IF(AND(P66=1,N(P121)&gt;0),P117/P121,99))=99,"",ROUND(MIN(IF(AND(P65=1,N(P120)&gt;0),P116/P120,99),IF(AND(P66=1,N(P121)&gt;0),P117/P121,99)),2)))</f>
         <v/>
       </c>
-      <c r="Q39" s="57">
+      <c r="Q39" s="58">
         <f>IF(OR(Q63=0,Q120=""),"",IF(MIN(IF(AND(Q65=1,N(Q120)&gt;0),Q116/Q120,99),IF(AND(Q66=1,N(Q121)&gt;0),Q117/Q121,99))=99,"",ROUND(MIN(IF(AND(Q65=1,N(Q120)&gt;0),Q116/Q120,99),IF(AND(Q66=1,N(Q121)&gt;0),Q117/Q121,99)),2)))</f>
         <v/>
       </c>
-      <c r="R39" s="57">
+      <c r="R39" s="58">
         <f>IF(OR(R63=0,R120=""),"",IF(MIN(IF(AND(R65=1,N(R120)&gt;0),R116/R120,99),IF(AND(R66=1,N(R121)&gt;0),R117/R121,99))=99,"",ROUND(MIN(IF(AND(R65=1,N(R120)&gt;0),R116/R120,99),IF(AND(R66=1,N(R121)&gt;0),R117/R121,99)),2)))</f>
         <v/>
       </c>
-      <c r="S39" s="57">
+      <c r="S39" s="58">
         <f>IF(OR(S63=0,S120=""),"",IF(MIN(IF(AND(S65=1,N(S120)&gt;0),S116/S120,99),IF(AND(S66=1,N(S121)&gt;0),S117/S121,99))=99,"",ROUND(MIN(IF(AND(S65=1,N(S120)&gt;0),S116/S120,99),IF(AND(S66=1,N(S121)&gt;0),S117/S121,99)),2)))</f>
         <v/>
       </c>
-      <c r="T39" s="57">
+      <c r="T39" s="58">
         <f>IF(OR(T63=0,T120=""),"",IF(MIN(IF(AND(T65=1,N(T120)&gt;0),T116/T120,99),IF(AND(T66=1,N(T121)&gt;0),T117/T121,99))=99,"",ROUND(MIN(IF(AND(T65=1,N(T120)&gt;0),T116/T120,99),IF(AND(T66=1,N(T121)&gt;0),T117/T121,99)),2)))</f>
         <v/>
       </c>
-      <c r="U39" s="57">
+      <c r="U39" s="58">
         <f>IF(OR(U63=0,U120=""),"",IF(MIN(IF(AND(U65=1,N(U120)&gt;0),U116/U120,99),IF(AND(U66=1,N(U121)&gt;0),U117/U121,99))=99,"",ROUND(MIN(IF(AND(U65=1,N(U120)&gt;0),U116/U120,99),IF(AND(U66=1,N(U121)&gt;0),U117/U121,99)),2)))</f>
         <v/>
       </c>
-      <c r="V39" s="57">
+      <c r="V39" s="58">
         <f>IF(OR(V63=0,V120=""),"",IF(MIN(IF(AND(V65=1,N(V120)&gt;0),V116/V120,99),IF(AND(V66=1,N(V121)&gt;0),V117/V121,99))=99,"",ROUND(MIN(IF(AND(V65=1,N(V120)&gt;0),V116/V120,99),IF(AND(V66=1,N(V121)&gt;0),V117/V121,99)),2)))</f>
         <v/>
       </c>
-      <c r="W39" s="57">
+      <c r="W39" s="58">
         <f>IF(OR(W63=0,W120=""),"",IF(MIN(IF(AND(W65=1,N(W120)&gt;0),W116/W120,99),IF(AND(W66=1,N(W121)&gt;0),W117/W121,99))=99,"",ROUND(MIN(IF(AND(W65=1,N(W120)&gt;0),W116/W120,99),IF(AND(W66=1,N(W121)&gt;0),W117/W121,99)),2)))</f>
         <v/>
       </c>
-      <c r="X39" s="57">
+      <c r="X39" s="58">
         <f>IF(OR(X63=0,X120=""),"",IF(MIN(IF(AND(X65=1,N(X120)&gt;0),X116/X120,99),IF(AND(X66=1,N(X121)&gt;0),X117/X121,99))=99,"",ROUND(MIN(IF(AND(X65=1,N(X120)&gt;0),X116/X120,99),IF(AND(X66=1,N(X121)&gt;0),X117/X121,99)),2)))</f>
         <v/>
       </c>
-      <c r="Y39" s="57">
+      <c r="Y39" s="58">
         <f>IF(OR(Y63=0,Y120=""),"",IF(MIN(IF(AND(Y65=1,N(Y120)&gt;0),Y116/Y120,99),IF(AND(Y66=1,N(Y121)&gt;0),Y117/Y121,99))=99,"",ROUND(MIN(IF(AND(Y65=1,N(Y120)&gt;0),Y116/Y120,99),IF(AND(Y66=1,N(Y121)&gt;0),Y117/Y121,99)),2)))</f>
         <v/>
       </c>
-      <c r="Z39" s="57">
+      <c r="Z39" s="58">
         <f>IF(OR(Z63=0,Z120=""),"",IF(MIN(IF(AND(Z65=1,N(Z120)&gt;0),Z116/Z120,99),IF(AND(Z66=1,N(Z121)&gt;0),Z117/Z121,99))=99,"",ROUND(MIN(IF(AND(Z65=1,N(Z120)&gt;0),Z116/Z120,99),IF(AND(Z66=1,N(Z121)&gt;0),Z117/Z121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AA39" s="57">
+      <c r="AA39" s="58">
         <f>IF(OR(AA63=0,AA120=""),"",IF(MIN(IF(AND(AA65=1,N(AA120)&gt;0),AA116/AA120,99),IF(AND(AA66=1,N(AA121)&gt;0),AA117/AA121,99))=99,"",ROUND(MIN(IF(AND(AA65=1,N(AA120)&gt;0),AA116/AA120,99),IF(AND(AA66=1,N(AA121)&gt;0),AA117/AA121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AB39" s="57">
+      <c r="AB39" s="58">
         <f>IF(OR(AB63=0,AB120=""),"",IF(MIN(IF(AND(AB65=1,N(AB120)&gt;0),AB116/AB120,99),IF(AND(AB66=1,N(AB121)&gt;0),AB117/AB121,99))=99,"",ROUND(MIN(IF(AND(AB65=1,N(AB120)&gt;0),AB116/AB120,99),IF(AND(AB66=1,N(AB121)&gt;0),AB117/AB121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AC39" s="57">
+      <c r="AC39" s="58">
         <f>IF(OR(AC63=0,AC120=""),"",IF(MIN(IF(AND(AC65=1,N(AC120)&gt;0),AC116/AC120,99),IF(AND(AC66=1,N(AC121)&gt;0),AC117/AC121,99))=99,"",ROUND(MIN(IF(AND(AC65=1,N(AC120)&gt;0),AC116/AC120,99),IF(AND(AC66=1,N(AC121)&gt;0),AC117/AC121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AD39" s="57">
+      <c r="AD39" s="58">
         <f>IF(OR(AD63=0,AD120=""),"",IF(MIN(IF(AND(AD65=1,N(AD120)&gt;0),AD116/AD120,99),IF(AND(AD66=1,N(AD121)&gt;0),AD117/AD121,99))=99,"",ROUND(MIN(IF(AND(AD65=1,N(AD120)&gt;0),AD116/AD120,99),IF(AND(AD66=1,N(AD121)&gt;0),AD117/AD121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AE39" s="57">
+      <c r="AE39" s="58">
         <f>IF(OR(AE63=0,AE120=""),"",IF(MIN(IF(AND(AE65=1,N(AE120)&gt;0),AE116/AE120,99),IF(AND(AE66=1,N(AE121)&gt;0),AE117/AE121,99))=99,"",ROUND(MIN(IF(AND(AE65=1,N(AE120)&gt;0),AE116/AE120,99),IF(AND(AE66=1,N(AE121)&gt;0),AE117/AE121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AF39" s="57">
+      <c r="AF39" s="58">
         <f>IF(OR(AF63=0,AF120=""),"",IF(MIN(IF(AND(AF65=1,N(AF120)&gt;0),AF116/AF120,99),IF(AND(AF66=1,N(AF121)&gt;0),AF117/AF121,99))=99,"",ROUND(MIN(IF(AND(AF65=1,N(AF120)&gt;0),AF116/AF120,99),IF(AND(AF66=1,N(AF121)&gt;0),AF117/AF121,99)),2)))</f>
         <v/>
       </c>
-      <c r="AG39" s="57">
+      <c r="AG39" s="58">
         <f>IF(OR(AG63=0,AG120=""),"",IF(MIN(IF(AND(AG65=1,N(AG120)&gt;0),AG116/AG120,99),IF(AND(AG66=1,N(AG121)&gt;0),AG117/AG121,99))=99,"",ROUND(MIN(IF(AND(AG65=1,N(AG120)&gt;0),AG116/AG120,99),IF(AND(AG66=1,N(AG121)&gt;0),AG117/AG121,99)),2)))</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="27" customHeight="1">
-      <c r="A40" s="52" t="inlineStr">
+      <c r="A40" s="53" t="inlineStr">
         <is>
           <t>As yêu cầu DƯỚI (nhập)</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
-      <c r="C40" s="55" t="n"/>
-      <c r="D40" s="55" t="n"/>
-      <c r="E40" s="55" t="n"/>
-      <c r="F40" s="55" t="n"/>
-      <c r="G40" s="55" t="n"/>
-      <c r="H40" s="55" t="n"/>
-      <c r="I40" s="55" t="n"/>
-      <c r="J40" s="55" t="n"/>
-      <c r="K40" s="55" t="n"/>
-      <c r="L40" s="55" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n"/>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="55" t="n"/>
-      <c r="W40" s="55" t="n"/>
-      <c r="X40" s="55" t="n"/>
-      <c r="Y40" s="55" t="n"/>
-      <c r="Z40" s="55" t="n"/>
-      <c r="AA40" s="55" t="n"/>
-      <c r="AB40" s="55" t="n"/>
-      <c r="AC40" s="55" t="n"/>
-      <c r="AD40" s="55" t="n"/>
-      <c r="AE40" s="55" t="n"/>
-      <c r="AF40" s="55" t="n"/>
-      <c r="AG40" s="55" t="n"/>
+      <c r="C40" s="56" t="n"/>
+      <c r="D40" s="56" t="n"/>
+      <c r="E40" s="56" t="n"/>
+      <c r="F40" s="56" t="n"/>
+      <c r="G40" s="56" t="n"/>
+      <c r="H40" s="56" t="n"/>
+      <c r="I40" s="56" t="n"/>
+      <c r="J40" s="56" t="n"/>
+      <c r="K40" s="56" t="n"/>
+      <c r="L40" s="56" t="n"/>
+      <c r="M40" s="56" t="n"/>
+      <c r="N40" s="56" t="n"/>
+      <c r="O40" s="56" t="n"/>
+      <c r="P40" s="56" t="n"/>
+      <c r="Q40" s="56" t="n"/>
+      <c r="R40" s="56" t="n"/>
+      <c r="S40" s="56" t="n"/>
+      <c r="T40" s="56" t="n"/>
+      <c r="U40" s="56" t="n"/>
+      <c r="V40" s="56" t="n"/>
+      <c r="W40" s="56" t="n"/>
+      <c r="X40" s="56" t="n"/>
+      <c r="Y40" s="56" t="n"/>
+      <c r="Z40" s="56" t="n"/>
+      <c r="AA40" s="56" t="n"/>
+      <c r="AB40" s="56" t="n"/>
+      <c r="AC40" s="56" t="n"/>
+      <c r="AD40" s="56" t="n"/>
+      <c r="AE40" s="56" t="n"/>
+      <c r="AF40" s="56" t="n"/>
+      <c r="AG40" s="56" t="n"/>
     </row>
     <row r="41" ht="27" customHeight="1">
-      <c r="A41" s="50" t="inlineStr">
+      <c r="A41" s="51" t="inlineStr">
         <is>
           <t>As bố trí DƯỚI</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
-      <c r="C41" s="56">
+      <c r="C41" s="57">
         <f>IF(C63=1,IF(C65*C66=1,FIXED(C118,2,TRUE)&amp;"/"&amp;FIXED(C119,2,TRUE),IF(C65=1,FIXED(C118,2,TRUE),FIXED(C119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="D41" s="57">
+      <c r="D41" s="58">
         <f>IF(D63=1,ROUND(D118,2),"")</f>
         <v/>
       </c>
-      <c r="E41" s="56">
+      <c r="E41" s="57">
         <f>IF(E63=1,IF(E65*E66=1,FIXED(E118,2,TRUE)&amp;"/"&amp;FIXED(E119,2,TRUE),IF(E65=1,FIXED(E118,2,TRUE),FIXED(E119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="F41" s="57">
+      <c r="F41" s="58">
         <f>IF(F63=1,ROUND(F118,2),"")</f>
         <v/>
       </c>
-      <c r="G41" s="56">
+      <c r="G41" s="57">
         <f>IF(G63=1,IF(G65*G66=1,FIXED(G118,2,TRUE)&amp;"/"&amp;FIXED(G119,2,TRUE),IF(G65=1,FIXED(G118,2,TRUE),FIXED(G119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="H41" s="57">
+      <c r="H41" s="58">
         <f>IF(H63=1,ROUND(H118,2),"")</f>
         <v/>
       </c>
-      <c r="I41" s="56">
+      <c r="I41" s="57">
         <f>IF(I63=1,IF(I65*I66=1,FIXED(I118,2,TRUE)&amp;"/"&amp;FIXED(I119,2,TRUE),IF(I65=1,FIXED(I118,2,TRUE),FIXED(I119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="J41" s="57">
+      <c r="J41" s="58">
         <f>IF(J63=1,ROUND(J118,2),"")</f>
         <v/>
       </c>
-      <c r="K41" s="56">
+      <c r="K41" s="57">
         <f>IF(K63=1,IF(K65*K66=1,FIXED(K118,2,TRUE)&amp;"/"&amp;FIXED(K119,2,TRUE),IF(K65=1,FIXED(K118,2,TRUE),FIXED(K119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="L41" s="57">
+      <c r="L41" s="58">
         <f>IF(L63=1,ROUND(L118,2),"")</f>
         <v/>
       </c>
-      <c r="M41" s="56">
+      <c r="M41" s="57">
         <f>IF(M63=1,IF(M65*M66=1,FIXED(M118,2,TRUE)&amp;"/"&amp;FIXED(M119,2,TRUE),IF(M65=1,FIXED(M118,2,TRUE),FIXED(M119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="N41" s="57">
+      <c r="N41" s="58">
         <f>IF(N63=1,ROUND(N118,2),"")</f>
         <v/>
       </c>
-      <c r="O41" s="56">
+      <c r="O41" s="57">
         <f>IF(O63=1,IF(O65*O66=1,FIXED(O118,2,TRUE)&amp;"/"&amp;FIXED(O119,2,TRUE),IF(O65=1,FIXED(O118,2,TRUE),FIXED(O119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="P41" s="57">
+      <c r="P41" s="58">
         <f>IF(P63=1,ROUND(P118,2),"")</f>
         <v/>
       </c>
-      <c r="Q41" s="56">
+      <c r="Q41" s="57">
         <f>IF(Q63=1,IF(Q65*Q66=1,FIXED(Q118,2,TRUE)&amp;"/"&amp;FIXED(Q119,2,TRUE),IF(Q65=1,FIXED(Q118,2,TRUE),FIXED(Q119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="R41" s="57">
+      <c r="R41" s="58">
         <f>IF(R63=1,ROUND(R118,2),"")</f>
         <v/>
       </c>
-      <c r="S41" s="56">
+      <c r="S41" s="57">
         <f>IF(S63=1,IF(S65*S66=1,FIXED(S118,2,TRUE)&amp;"/"&amp;FIXED(S119,2,TRUE),IF(S65=1,FIXED(S118,2,TRUE),FIXED(S119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="T41" s="57">
+      <c r="T41" s="58">
         <f>IF(T63=1,ROUND(T118,2),"")</f>
         <v/>
       </c>
-      <c r="U41" s="56">
+      <c r="U41" s="57">
         <f>IF(U63=1,IF(U65*U66=1,FIXED(U118,2,TRUE)&amp;"/"&amp;FIXED(U119,2,TRUE),IF(U65=1,FIXED(U118,2,TRUE),FIXED(U119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="V41" s="57">
+      <c r="V41" s="58">
         <f>IF(V63=1,ROUND(V118,2),"")</f>
         <v/>
       </c>
-      <c r="W41" s="56">
+      <c r="W41" s="57">
         <f>IF(W63=1,IF(W65*W66=1,FIXED(W118,2,TRUE)&amp;"/"&amp;FIXED(W119,2,TRUE),IF(W65=1,FIXED(W118,2,TRUE),FIXED(W119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="X41" s="57">
+      <c r="X41" s="58">
         <f>IF(X63=1,ROUND(X118,2),"")</f>
         <v/>
       </c>
-      <c r="Y41" s="56">
+      <c r="Y41" s="57">
         <f>IF(Y63=1,IF(Y65*Y66=1,FIXED(Y118,2,TRUE)&amp;"/"&amp;FIXED(Y119,2,TRUE),IF(Y65=1,FIXED(Y118,2,TRUE),FIXED(Y119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="Z41" s="57">
+      <c r="Z41" s="58">
         <f>IF(Z63=1,ROUND(Z118,2),"")</f>
         <v/>
       </c>
-      <c r="AA41" s="56">
+      <c r="AA41" s="57">
         <f>IF(AA63=1,IF(AA65*AA66=1,FIXED(AA118,2,TRUE)&amp;"/"&amp;FIXED(AA119,2,TRUE),IF(AA65=1,FIXED(AA118,2,TRUE),FIXED(AA119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AB41" s="57">
+      <c r="AB41" s="58">
         <f>IF(AB63=1,ROUND(AB118,2),"")</f>
         <v/>
       </c>
-      <c r="AC41" s="56">
+      <c r="AC41" s="57">
         <f>IF(AC63=1,IF(AC65*AC66=1,FIXED(AC118,2,TRUE)&amp;"/"&amp;FIXED(AC119,2,TRUE),IF(AC65=1,FIXED(AC118,2,TRUE),FIXED(AC119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AD41" s="57">
+      <c r="AD41" s="58">
         <f>IF(AD63=1,ROUND(AD118,2),"")</f>
         <v/>
       </c>
-      <c r="AE41" s="56">
+      <c r="AE41" s="57">
         <f>IF(AE63=1,IF(AE65*AE66=1,FIXED(AE118,2,TRUE)&amp;"/"&amp;FIXED(AE119,2,TRUE),IF(AE65=1,FIXED(AE118,2,TRUE),FIXED(AE119,2,TRUE))),"")</f>
         <v/>
       </c>
-      <c r="AF41" s="57">
+      <c r="AF41" s="58">
         <f>IF(AF63=1,ROUND(AF118,2),"")</f>
         <v/>
       </c>
-      <c r="AG41" s="56">
+      <c r="AG41" s="57">
         <f>IF(AG63=1,IF(AG65*AG66=1,FIXED(AG118,2,TRUE)&amp;"/"&amp;FIXED(AG119,2,TRUE),IF(AG65=1,FIXED(AG118,2,TRUE),FIXED(AG119,2,TRUE))),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="27" customHeight="1">
-      <c r="A42" s="50" t="inlineStr">
+      <c r="A42" s="51" t="inlineStr">
         <is>
           <t>Hệ số As bố trí / yêu cầu DƯỚI</t>
         </is>
       </c>
       <c r="B42" s="6" t="n"/>
-      <c r="C42" s="57">
+      <c r="C42" s="58">
         <f>IF(OR(C63=0,C122=""),"",IF(MIN(IF(AND(C65=1,N(C122)&gt;0),C118/C122,99),IF(AND(C66=1,N(C123)&gt;0),C119/C123,99))=99,"",ROUND(MIN(IF(AND(C65=1,N(C122)&gt;0),C118/C122,99),IF(AND(C66=1,N(C123)&gt;0),C119/C123,99)),2)))</f>
         <v/>
       </c>
-      <c r="D42" s="57">
+      <c r="D42" s="58">
         <f>IF(OR(D63=0,D122=""),"",IF(MIN(IF(AND(D65=1,N(D122)&gt;0),D118/D122,99),IF(AND(D66=1,N(D123)&gt;0),D119/D123,99))=99,"",ROUND(MIN(IF(AND(D65=1,N(D122)&gt;0),D118/D122,99),IF(AND(D66=1,N(D123)&gt;0),D119/D123,99)),2)))</f>
         <v/>
       </c>
-      <c r="E42" s="57">
+      <c r="E42" s="58">
         <f>IF(OR(E63=0,E122=""),"",IF(MIN(IF(AND(E65=1,N(E122)&gt;0),E118/E122,99),IF(AND(E66=1,N(E123)&gt;0),E119/E123,99))=99,"",ROUND(MIN(IF(AND(E65=1,N(E122)&gt;0),E118/E122,99),IF(AND(E66=1,N(E123)&gt;0),E119/E123,99)),2)))</f>
         <v/>
       </c>
-      <c r="F42" s="57">
+      <c r="F42" s="58">
         <f>IF(OR(F63=0,F122=""),"",IF(MIN(IF(AND(F65=1,N(F122)&gt;0),F118/F122,99),IF(AND(F66=1,N(F123)&gt;0),F119/F123,99))=99,"",ROUND(MIN(IF(AND(F65=1,N(F122)&gt;0),F118/F122,99),IF(AND(F66=1,N(F123)&gt;0),F119/F123,99)),2)))</f>
         <v/>
       </c>
-      <c r="G42" s="57">
+      <c r="G42" s="58">
         <f>IF(OR(G63=0,G122=""),"",IF(MIN(IF(AND(G65=1,N(G122)&gt;0),G118/G122,99),IF(AND(G66=1,N(G123)&gt;0),G119/G123,99))=99,"",ROUND(MIN(IF(AND(G65=1,N(G122)&gt;0),G118/G122,99),IF(AND(G66=1,N(G123)&gt;0),G119/G123,99)),2)))</f>
         <v/>
       </c>
-      <c r="H42" s="57">
+      <c r="H42" s="58">
         <f>IF(OR(H63=0,H122=""),"",IF(MIN(IF(AND(H65=1,N(H122)&gt;0),H118/H122,99),IF(AND(H66=1,N(H123)&gt;0),H119/H123,99))=99,"",ROUND(MIN(IF(AND(H65=1,N(H122)&gt;0),H118/H122,99),IF(AND(H66=1,N(H123)&gt;0),H119/H123,99)),2)))</f>
         <v/>
       </c>
-      <c r="I42" s="57">
+      <c r="I42" s="58">
         <f>IF(OR(I63=0,I122=""),"",IF(MIN(IF(AND(I65=1,N(I122)&gt;0),I118/I122,99),IF(AND(I66=1,N(I123)&gt;0),I119/I123,99))=99,"",ROUND(MIN(IF(AND(I65=1,N(I122)&gt;0),I118/I122,99),IF(AND(I66=1,N(I123)&gt;0),I119/I123,99)),2)))</f>
         <v/>
       </c>
-      <c r="J42" s="57">
+      <c r="J42" s="58">
         <f>IF(OR(J63=0,J122=""),"",IF(MIN(IF(AND(J65=1,N(J122)&gt;0),J118/J122,99),IF(AND(J66=1,N(J123)&gt;0),J119/J123,99))=99,"",ROUND(MIN(IF(AND(J65=1,N(J122)&gt;0),J118/J122,99),IF(AND(J66=1,N(J123)&gt;0),J119/J123,99)),2)))</f>
         <v/>
       </c>
-      <c r="K42" s="57">
+      <c r="K42" s="58">
         <f>IF(OR(K63=0,K122=""),"",IF(MIN(IF(AND(K65=1,N(K122)&gt;0),K118/K122,99),IF(AND(K66=1,N(K123)&gt;0),K119/K123,99))=99,"",ROUND(MIN(IF(AND(K65=1,N(K122)&gt;0),K118/K122,99),IF(AND(K66=1,N(K123)&gt;0),K119/K123,99)),2)))</f>
         <v/>
       </c>
-      <c r="L42" s="57">
+      <c r="L42" s="58">
         <f>IF(OR(L63=0,L122=""),"",IF(MIN(IF(AND(L65=1,N(L122)&gt;0),L118/L122,99),IF(AND(L66=1,N(L123)&gt;0),L119/L123,99))=99,"",ROUND(MIN(IF(AND(L65=1,N(L122)&gt;0),L118/L122,99),IF(AND(L66=1,N(L123)&gt;0),L119/L123,99)),2)))</f>
         <v/>
       </c>
-      <c r="M42" s="57">
+      <c r="M42" s="58">
         <f>IF(OR(M63=0,M122=""),"",IF(MIN(IF(AND(M65=1,N(M122)&gt;0),M118/M122,99),IF(AND(M66=1,N(M123)&gt;0),M119/M123,99))=99,"",ROUND(MIN(IF(AND(M65=1,N(M122)&gt;0),M118/M122,99),IF(AND(M66=1,N(M123)&gt;0),M119/M123,99)),2)))</f>
         <v/>
       </c>
-      <c r="N42" s="57">
+      <c r="N42" s="58">
         <f>IF(OR(N63=0,N122=""),"",IF(MIN(IF(AND(N65=1,N(N122)&gt;0),N118/N122,99),IF(AND(N66=1,N(N123)&gt;0),N119/N123,99))=99,"",ROUND(MIN(IF(AND(N65=1,N(N122)&gt;0),N118/N122,99),IF(AND(N66=1,N(N123)&gt;0),N119/N123,99)),2)))</f>
         <v/>
       </c>
-      <c r="O42" s="57">
+      <c r="O42" s="58">
         <f>IF(OR(O63=0,O122=""),"",IF(MIN(IF(AND(O65=1,N(O122)&gt;0),O118/O122,99),IF(AND(O66=1,N(O123)&gt;0),O119/O123,99))=99,"",ROUND(MIN(IF(AND(O65=1,N(O122)&gt;0),O118/O122,99),IF(AND(O66=1,N(O123)&gt;0),O119/O123,99)),2)))</f>
         <v/>
       </c>
-      <c r="P42" s="57">
+      <c r="P42" s="58">
         <f>IF(OR(P63=0,P122=""),"",IF(MIN(IF(AND(P65=1,N(P122)&gt;0),P118/P122,99),IF(AND(P66=1,N(P123)&gt;0),P119/P123,99))=99,"",ROUND(MIN(IF(AND(P65=1,N(P122)&gt;0),P118/P122,99),IF(AND(P66=1,N(P123)&gt;0),P119/P123,99)),2)))</f>
         <v/>
       </c>
-      <c r="Q42" s="57">
+      <c r="Q42" s="58">
         <f>IF(OR(Q63=0,Q122=""),"",IF(MIN(IF(AND(Q65=1,N(Q122)&gt;0),Q118/Q122,99),IF(AND(Q66=1,N(Q123)&gt;0),Q119/Q123,99))=99,"",ROUND(MIN(IF(AND(Q65=1,N(Q122)&gt;0),Q118/Q122,99),IF(AND(Q66=1,N(Q123)&gt;0),Q119/Q123,99)),2)))</f>
         <v/>
       </c>
-      <c r="R42" s="57">
+      <c r="R42" s="58">
         <f>IF(OR(R63=0,R122=""),"",IF(MIN(IF(AND(R65=1,N(R122)&gt;0),R118/R122,99),IF(AND(R66=1,N(R123)&gt;0),R119/R123,99))=99,"",ROUND(MIN(IF(AND(R65=1,N(R122)&gt;0),R118/R122,99),IF(AND(R66=1,N(R123)&gt;0),R119/R123,99)),2)))</f>
         <v/>
       </c>
-      <c r="S42" s="57">
+      <c r="S42" s="58">
         <f>IF(OR(S63=0,S122=""),"",IF(MIN(IF(AND(S65=1,N(S122)&gt;0),S118/S122,99),IF(AND(S66=1,N(S123)&gt;0),S119/S123,99))=99,"",ROUND(MIN(IF(AND(S65=1,N(S122)&gt;0),S118/S122,99),IF(AND(S66=1,N(S123)&gt;0),S119/S123,99)),2)))</f>
         <v/>
       </c>
-      <c r="T42" s="57">
+      <c r="T42" s="58">
         <f>IF(OR(T63=0,T122=""),"",IF(MIN(IF(AND(T65=1,N(T122)&gt;0),T118/T122,99),IF(AND(T66=1,N(T123)&gt;0),T119/T123,99))=99,"",ROUND(MIN(IF(AND(T65=1,N(T122)&gt;0),T118/T122,99),IF(AND(T66=1,N(T123)&gt;0),T119/T123,99)),2)))</f>
         <v/>
       </c>
-      <c r="U42" s="57">
+      <c r="U42" s="58">
         <f>IF(OR(U63=0,U122=""),"",IF(MIN(IF(AND(U65=1,N(U122)&gt;0),U118/U122,99),IF(AND(U66=1,N(U123)&gt;0),U119/U123,99))=99,"",ROUND(MIN(IF(AND(U65=1,N(U122)&gt;0),U118/U122,99),IF(AND(U66=1,N(U123)&gt;0),U119/U123,99)),2)))</f>
         <v/>
       </c>
-      <c r="V42" s="57">
+      <c r="V42" s="58">
         <f>IF(OR(V63=0,V122=""),"",IF(MIN(IF(AND(V65=1,N(V122)&gt;0),V118/V122,99),IF(AND(V66=1,N(V123)&gt;0),V119/V123,99))=99,"",ROUND(MIN(IF(AND(V65=1,N(V122)&gt;0),V118/V122,99),IF(AND(V66=1,N(V123)&gt;0),V119/V123,99)),2)))</f>
         <v/>
       </c>
-      <c r="W42" s="57">
+      <c r="W42" s="58">
         <f>IF(OR(W63=0,W122=""),"",IF(MIN(IF(AND(W65=1,N(W122)&gt;0),W118/W122,99),IF(AND(W66=1,N(W123)&gt;0),W119/W123,99))=99,"",ROUND(MIN(IF(AND(W65=1,N(W122)&gt;0),W118/W122,99),IF(AND(W66=1,N(W123)&gt;0),W119/W123,99)),2)))</f>
         <v/>
       </c>
-      <c r="X42" s="57">
+      <c r="X42" s="58">
         <f>IF(OR(X63=0,X122=""),"",IF(MIN(IF(AND(X65=1,N(X122)&gt;0),X118/X122,99),IF(AND(X66=1,N(X123)&gt;0),X119/X123,99))=99,"",ROUND(MIN(IF(AND(X65=1,N(X122)&gt;0),X118/X122,99),IF(AND(X66=1,N(X123)&gt;0),X119/X123,99)),2)))</f>
         <v/>
       </c>
-      <c r="Y42" s="57">
+      <c r="Y42" s="58">
         <f>IF(OR(Y63=0,Y122=""),"",IF(MIN(IF(AND(Y65=1,N(Y122)&gt;0),Y118/Y122,99),IF(AND(Y66=1,N(Y123)&gt;0),Y119/Y123,99))=99,"",ROUND(MIN(IF(AND(Y65=1,N(Y122)&gt;0),Y118/Y122,99),IF(AND(Y66=1,N(Y123)&gt;0),Y119/Y123,99)),2)))</f>
         <v/>
       </c>
-      <c r="Z42" s="57">
+      <c r="Z42" s="58">
         <f>IF(OR(Z63=0,Z122=""),"",IF(MIN(IF(AND(Z65=1,N(Z122)&gt;0),Z118/Z122,99),IF(AND(Z66=1,N(Z123)&gt;0),Z119/Z123,99))=99,"",ROUND(MIN(IF(AND(Z65=1,N(Z122)&gt;0),Z118/Z122,99),IF(AND(Z66=1,N(Z123)&gt;0),Z119/Z123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AA42" s="57">
+      <c r="AA42" s="58">
         <f>IF(OR(AA63=0,AA122=""),"",IF(MIN(IF(AND(AA65=1,N(AA122)&gt;0),AA118/AA122,99),IF(AND(AA66=1,N(AA123)&gt;0),AA119/AA123,99))=99,"",ROUND(MIN(IF(AND(AA65=1,N(AA122)&gt;0),AA118/AA122,99),IF(AND(AA66=1,N(AA123)&gt;0),AA119/AA123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AB42" s="57">
+      <c r="AB42" s="58">
         <f>IF(OR(AB63=0,AB122=""),"",IF(MIN(IF(AND(AB65=1,N(AB122)&gt;0),AB118/AB122,99),IF(AND(AB66=1,N(AB123)&gt;0),AB119/AB123,99))=99,"",ROUND(MIN(IF(AND(AB65=1,N(AB122)&gt;0),AB118/AB122,99),IF(AND(AB66=1,N(AB123)&gt;0),AB119/AB123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AC42" s="57">
+      <c r="AC42" s="58">
         <f>IF(OR(AC63=0,AC122=""),"",IF(MIN(IF(AND(AC65=1,N(AC122)&gt;0),AC118/AC122,99),IF(AND(AC66=1,N(AC123)&gt;0),AC119/AC123,99))=99,"",ROUND(MIN(IF(AND(AC65=1,N(AC122)&gt;0),AC118/AC122,99),IF(AND(AC66=1,N(AC123)&gt;0),AC119/AC123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AD42" s="57">
+      <c r="AD42" s="58">
         <f>IF(OR(AD63=0,AD122=""),"",IF(MIN(IF(AND(AD65=1,N(AD122)&gt;0),AD118/AD122,99),IF(AND(AD66=1,N(AD123)&gt;0),AD119/AD123,99))=99,"",ROUND(MIN(IF(AND(AD65=1,N(AD122)&gt;0),AD118/AD122,99),IF(AND(AD66=1,N(AD123)&gt;0),AD119/AD123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AE42" s="57">
+      <c r="AE42" s="58">
         <f>IF(OR(AE63=0,AE122=""),"",IF(MIN(IF(AND(AE65=1,N(AE122)&gt;0),AE118/AE122,99),IF(AND(AE66=1,N(AE123)&gt;0),AE119/AE123,99))=99,"",ROUND(MIN(IF(AND(AE65=1,N(AE122)&gt;0),AE118/AE122,99),IF(AND(AE66=1,N(AE123)&gt;0),AE119/AE123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AF42" s="57">
+      <c r="AF42" s="58">
         <f>IF(OR(AF63=0,AF122=""),"",IF(MIN(IF(AND(AF65=1,N(AF122)&gt;0),AF118/AF122,99),IF(AND(AF66=1,N(AF123)&gt;0),AF119/AF123,99))=99,"",ROUND(MIN(IF(AND(AF65=1,N(AF122)&gt;0),AF118/AF122,99),IF(AND(AF66=1,N(AF123)&gt;0),AF119/AF123,99)),2)))</f>
         <v/>
       </c>
-      <c r="AG42" s="57">
+      <c r="AG42" s="58">
         <f>IF(OR(AG63=0,AG122=""),"",IF(MIN(IF(AND(AG65=1,N(AG122)&gt;0),AG118/AG122,99),IF(AND(AG66=1,N(AG123)&gt;0),AG119/AG123,99))=99,"",ROUND(MIN(IF(AND(AG65=1,N(AG122)&gt;0),AG118/AG122,99),IF(AND(AG66=1,N(AG123)&gt;0),AG119/AG123,99)),2)))</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="48" t="inlineStr">
+      <c r="A43" s="49" t="inlineStr">
         <is>
           <t>KIỂM TRA SỐ LIỆU</t>
         </is>
       </c>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="49" t="n"/>
-      <c r="D43" s="49" t="n"/>
-      <c r="E43" s="49" t="n"/>
-      <c r="F43" s="49" t="n"/>
-      <c r="G43" s="49" t="n"/>
-      <c r="H43" s="49" t="n"/>
-      <c r="I43" s="49" t="n"/>
-      <c r="J43" s="49" t="n"/>
-      <c r="K43" s="49" t="n"/>
-      <c r="L43" s="49" t="n"/>
-      <c r="M43" s="49" t="n"/>
-      <c r="N43" s="49" t="n"/>
-      <c r="O43" s="49" t="n"/>
-      <c r="P43" s="49" t="n"/>
-      <c r="Q43" s="49" t="n"/>
-      <c r="R43" s="49" t="n"/>
-      <c r="S43" s="49" t="n"/>
-      <c r="T43" s="49" t="n"/>
-      <c r="U43" s="49" t="n"/>
-      <c r="V43" s="49" t="n"/>
-      <c r="W43" s="49" t="n"/>
-      <c r="X43" s="49" t="n"/>
-      <c r="Y43" s="49" t="n"/>
-      <c r="Z43" s="49" t="n"/>
-      <c r="AA43" s="49" t="n"/>
-      <c r="AB43" s="49" t="n"/>
-      <c r="AC43" s="49" t="n"/>
-      <c r="AD43" s="49" t="n"/>
-      <c r="AE43" s="49" t="n"/>
-      <c r="AF43" s="49" t="n"/>
-      <c r="AG43" s="49" t="n"/>
+      <c r="B43" s="50" t="n"/>
+      <c r="C43" s="50" t="n"/>
+      <c r="D43" s="50" t="n"/>
+      <c r="E43" s="50" t="n"/>
+      <c r="F43" s="50" t="n"/>
+      <c r="G43" s="50" t="n"/>
+      <c r="H43" s="50" t="n"/>
+      <c r="I43" s="50" t="n"/>
+      <c r="J43" s="50" t="n"/>
+      <c r="K43" s="50" t="n"/>
+      <c r="L43" s="50" t="n"/>
+      <c r="M43" s="50" t="n"/>
+      <c r="N43" s="50" t="n"/>
+      <c r="O43" s="50" t="n"/>
+      <c r="P43" s="50" t="n"/>
+      <c r="Q43" s="50" t="n"/>
+      <c r="R43" s="50" t="n"/>
+      <c r="S43" s="50" t="n"/>
+      <c r="T43" s="50" t="n"/>
+      <c r="U43" s="50" t="n"/>
+      <c r="V43" s="50" t="n"/>
+      <c r="W43" s="50" t="n"/>
+      <c r="X43" s="50" t="n"/>
+      <c r="Y43" s="50" t="n"/>
+      <c r="Z43" s="50" t="n"/>
+      <c r="AA43" s="50" t="n"/>
+      <c r="AB43" s="50" t="n"/>
+      <c r="AC43" s="50" t="n"/>
+      <c r="AD43" s="50" t="n"/>
+      <c r="AE43" s="50" t="n"/>
+      <c r="AF43" s="50" t="n"/>
+      <c r="AG43" s="50" t="n"/>
     </row>
     <row r="44" ht="27" customHeight="1">
-      <c r="A44" s="50" t="inlineStr">
+      <c r="A44" s="51" t="inlineStr">
         <is>
           <t>Kết quả kiểm tra từng cột</t>
         </is>
       </c>
       <c r="B44" s="6" t="n"/>
-      <c r="C44" s="58">
+      <c r="C44" s="59">
         <f>IF(C63=0,"",IF(C60="","Thiếu KT gối",IF(C26="","Thiếu tên trục",IF(C124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="D44" s="58">
+      <c r="D44" s="59">
         <f>IF(D63=0,IF(D11="","","Sai Ltt"),IF(FALSE,"Nhịp đứt quãng",IF(D26="","Thiếu đai",IF(D124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="E44" s="58">
+      <c r="E44" s="59">
         <f>IF(E63=0,"",IF(E60="","Thiếu KT gối",IF(E26="","Thiếu tên trục",IF(E124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="F44" s="58">
+      <c r="F44" s="59">
         <f>IF(F63=0,IF(F11="","","Sai Ltt"),IF(AND(D$63=0,F63=1),"Nhịp đứt quãng",IF(F26="","Thiếu đai",IF(F124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="G44" s="58">
+      <c r="G44" s="59">
         <f>IF(G63=0,"",IF(G60="","Thiếu KT gối",IF(G26="","Thiếu tên trục",IF(G124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="H44" s="58">
+      <c r="H44" s="59">
         <f>IF(H63=0,IF(H11="","","Sai Ltt"),IF(AND(F$63=0,H63=1),"Nhịp đứt quãng",IF(H26="","Thiếu đai",IF(H124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="I44" s="58">
+      <c r="I44" s="59">
         <f>IF(I63=0,"",IF(I60="","Thiếu KT gối",IF(I26="","Thiếu tên trục",IF(I124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="J44" s="58">
+      <c r="J44" s="59">
         <f>IF(J63=0,IF(J11="","","Sai Ltt"),IF(AND(H$63=0,J63=1),"Nhịp đứt quãng",IF(J26="","Thiếu đai",IF(J124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="K44" s="58">
+      <c r="K44" s="59">
         <f>IF(K63=0,"",IF(K60="","Thiếu KT gối",IF(K26="","Thiếu tên trục",IF(K124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="L44" s="58">
+      <c r="L44" s="59">
         <f>IF(L63=0,IF(L11="","","Sai Ltt"),IF(AND(J$63=0,L63=1),"Nhịp đứt quãng",IF(L26="","Thiếu đai",IF(L124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="M44" s="58">
+      <c r="M44" s="59">
         <f>IF(M63=0,"",IF(M60="","Thiếu KT gối",IF(M26="","Thiếu tên trục",IF(M124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="N44" s="58">
+      <c r="N44" s="59">
         <f>IF(N63=0,IF(N11="","","Sai Ltt"),IF(AND(L$63=0,N63=1),"Nhịp đứt quãng",IF(N26="","Thiếu đai",IF(N124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="O44" s="58">
+      <c r="O44" s="59">
         <f>IF(O63=0,"",IF(O60="","Thiếu KT gối",IF(O26="","Thiếu tên trục",IF(O124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="P44" s="58">
+      <c r="P44" s="59">
         <f>IF(P63=0,IF(P11="","","Sai Ltt"),IF(AND(N$63=0,P63=1),"Nhịp đứt quãng",IF(P26="","Thiếu đai",IF(P124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Q44" s="58">
+      <c r="Q44" s="59">
         <f>IF(Q63=0,"",IF(Q60="","Thiếu KT gối",IF(Q26="","Thiếu tên trục",IF(Q124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="R44" s="58">
+      <c r="R44" s="59">
         <f>IF(R63=0,IF(R11="","","Sai Ltt"),IF(AND(P$63=0,R63=1),"Nhịp đứt quãng",IF(R26="","Thiếu đai",IF(R124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="S44" s="58">
+      <c r="S44" s="59">
         <f>IF(S63=0,"",IF(S60="","Thiếu KT gối",IF(S26="","Thiếu tên trục",IF(S124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="T44" s="58">
+      <c r="T44" s="59">
         <f>IF(T63=0,IF(T11="","","Sai Ltt"),IF(AND(R$63=0,T63=1),"Nhịp đứt quãng",IF(T26="","Thiếu đai",IF(T124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="U44" s="58">
+      <c r="U44" s="59">
         <f>IF(U63=0,"",IF(U60="","Thiếu KT gối",IF(U26="","Thiếu tên trục",IF(U124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="V44" s="58">
+      <c r="V44" s="59">
         <f>IF(V63=0,IF(V11="","","Sai Ltt"),IF(AND(T$63=0,V63=1),"Nhịp đứt quãng",IF(V26="","Thiếu đai",IF(V124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="W44" s="58">
+      <c r="W44" s="59">
         <f>IF(W63=0,"",IF(W60="","Thiếu KT gối",IF(W26="","Thiếu tên trục",IF(W124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="X44" s="58">
+      <c r="X44" s="59">
         <f>IF(X63=0,IF(X11="","","Sai Ltt"),IF(AND(V$63=0,X63=1),"Nhịp đứt quãng",IF(X26="","Thiếu đai",IF(X124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Y44" s="58">
+      <c r="Y44" s="59">
         <f>IF(Y63=0,"",IF(Y60="","Thiếu KT gối",IF(Y26="","Thiếu tên trục",IF(Y124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Z44" s="58">
+      <c r="Z44" s="59">
         <f>IF(Z63=0,IF(Z11="","","Sai Ltt"),IF(AND(X$63=0,Z63=1),"Nhịp đứt quãng",IF(Z26="","Thiếu đai",IF(Z124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AA44" s="58">
+      <c r="AA44" s="59">
         <f>IF(AA63=0,"",IF(AA60="","Thiếu KT gối",IF(AA26="","Thiếu tên trục",IF(AA124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AB44" s="58">
+      <c r="AB44" s="59">
         <f>IF(AB63=0,IF(AB11="","","Sai Ltt"),IF(AND(Z$63=0,AB63=1),"Nhịp đứt quãng",IF(AB26="","Thiếu đai",IF(AB124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AC44" s="58">
+      <c r="AC44" s="59">
         <f>IF(AC63=0,"",IF(AC60="","Thiếu KT gối",IF(AC26="","Thiếu tên trục",IF(AC124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AD44" s="58">
+      <c r="AD44" s="59">
         <f>IF(AD63=0,IF(AD11="","","Sai Ltt"),IF(AND(AB$63=0,AD63=1),"Nhịp đứt quãng",IF(AD26="","Thiếu đai",IF(AD124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AE44" s="58">
+      <c r="AE44" s="59">
         <f>IF(AE63=0,"",IF(AE60="","Thiếu KT gối",IF(AE26="","Thiếu tên trục",IF(AE124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AF44" s="58">
+      <c r="AF44" s="59">
         <f>IF(AF63=0,IF(AF11="","","Sai Ltt"),IF(AND(AD$63=0,AF63=1),"Nhịp đứt quãng",IF(AF26="","Thiếu đai",IF(AF124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AG44" s="58">
+      <c r="AG44" s="59">
         <f>IF(AG63=0,"",IF(AG60="","Thiếu KT gối",IF(AG26="","Thiếu tên trục",IF(AG124&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="59" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr">
         <is>
           <t>▼ Hàng ẩn phụ trợ (dòng 60+) – dùng cho kiểm tra, không nhập.</t>
         </is>
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="1">
-      <c r="A60" s="60" t="inlineStr">
+      <c r="A60" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) W</t>
         </is>
@@ -16302,7 +16404,7 @@
       </c>
     </row>
     <row r="61" hidden="1" outlineLevel="1">
-      <c r="A61" s="60" t="inlineStr">
+      <c r="A61" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) X</t>
         </is>
@@ -16433,7 +16535,7 @@
       </c>
     </row>
     <row r="62" hidden="1" outlineLevel="1">
-      <c r="A62" s="60" t="inlineStr">
+      <c r="A62" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) AX</t>
         </is>
@@ -16504,7 +16606,7 @@
       </c>
     </row>
     <row r="63" hidden="1" outlineLevel="1">
-      <c r="A63" s="60" t="inlineStr">
+      <c r="A63" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ACT</t>
         </is>
@@ -16635,7 +16737,7 @@
       </c>
     </row>
     <row r="64" hidden="1" outlineLevel="1">
-      <c r="A64" s="60" t="inlineStr">
+      <c r="A64" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) SHOW</t>
         </is>
@@ -16766,7 +16868,7 @@
       </c>
     </row>
     <row r="65" hidden="1" outlineLevel="1">
-      <c r="A65" s="60" t="inlineStr">
+      <c r="A65" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) HASL</t>
         </is>
@@ -16897,7 +16999,7 @@
       </c>
     </row>
     <row r="66" hidden="1" outlineLevel="1">
-      <c r="A66" s="60" t="inlineStr">
+      <c r="A66" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) HASR</t>
         </is>
@@ -17028,7 +17130,7 @@
       </c>
     </row>
     <row r="67" hidden="1" outlineLevel="1">
-      <c r="A67" s="60" t="inlineStr">
+      <c r="A67" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) LECH</t>
         </is>
@@ -17099,7 +17201,7 @@
       </c>
     </row>
     <row r="68" hidden="1" outlineLevel="1">
-      <c r="A68" s="60" t="inlineStr">
+      <c r="A68" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T0L</t>
         </is>
@@ -17230,7 +17332,7 @@
       </c>
     </row>
     <row r="69" hidden="1" outlineLevel="1">
-      <c r="A69" s="60" t="inlineStr">
+      <c r="A69" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T0L</t>
         </is>
@@ -17361,7 +17463,7 @@
       </c>
     </row>
     <row r="70" hidden="1" outlineLevel="1">
-      <c r="A70" s="60" t="inlineStr">
+      <c r="A70" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T0R</t>
         </is>
@@ -17492,7 +17594,7 @@
       </c>
     </row>
     <row r="71" hidden="1" outlineLevel="1">
-      <c r="A71" s="60" t="inlineStr">
+      <c r="A71" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T0R</t>
         </is>
@@ -17623,7 +17725,7 @@
       </c>
     </row>
     <row r="72" hidden="1" outlineLevel="1">
-      <c r="A72" s="60" t="inlineStr">
+      <c r="A72" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T1L</t>
         </is>
@@ -17754,7 +17856,7 @@
       </c>
     </row>
     <row r="73" hidden="1" outlineLevel="1">
-      <c r="A73" s="60" t="inlineStr">
+      <c r="A73" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T1L</t>
         </is>
@@ -17885,7 +17987,7 @@
       </c>
     </row>
     <row r="74" hidden="1" outlineLevel="1">
-      <c r="A74" s="60" t="inlineStr">
+      <c r="A74" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T1R</t>
         </is>
@@ -18016,7 +18118,7 @@
       </c>
     </row>
     <row r="75" hidden="1" outlineLevel="1">
-      <c r="A75" s="60" t="inlineStr">
+      <c r="A75" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T1R</t>
         </is>
@@ -18147,7 +18249,7 @@
       </c>
     </row>
     <row r="76" hidden="1" outlineLevel="1">
-      <c r="A76" s="60" t="inlineStr">
+      <c r="A76" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T2L</t>
         </is>
@@ -18278,7 +18380,7 @@
       </c>
     </row>
     <row r="77" hidden="1" outlineLevel="1">
-      <c r="A77" s="60" t="inlineStr">
+      <c r="A77" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T2L</t>
         </is>
@@ -18409,7 +18511,7 @@
       </c>
     </row>
     <row r="78" hidden="1" outlineLevel="1">
-      <c r="A78" s="60" t="inlineStr">
+      <c r="A78" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T2R</t>
         </is>
@@ -18540,7 +18642,7 @@
       </c>
     </row>
     <row r="79" hidden="1" outlineLevel="1">
-      <c r="A79" s="60" t="inlineStr">
+      <c r="A79" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T2R</t>
         </is>
@@ -18671,7 +18773,7 @@
       </c>
     </row>
     <row r="80" hidden="1" outlineLevel="1">
-      <c r="A80" s="60" t="inlineStr">
+      <c r="A80" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T3L</t>
         </is>
@@ -18802,7 +18904,7 @@
       </c>
     </row>
     <row r="81" hidden="1" outlineLevel="1">
-      <c r="A81" s="60" t="inlineStr">
+      <c r="A81" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T3L</t>
         </is>
@@ -18933,7 +19035,7 @@
       </c>
     </row>
     <row r="82" hidden="1" outlineLevel="1">
-      <c r="A82" s="60" t="inlineStr">
+      <c r="A82" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T3R</t>
         </is>
@@ -19064,7 +19166,7 @@
       </c>
     </row>
     <row r="83" hidden="1" outlineLevel="1">
-      <c r="A83" s="60" t="inlineStr">
+      <c r="A83" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T3R</t>
         </is>
@@ -19195,7 +19297,7 @@
       </c>
     </row>
     <row r="84" hidden="1" outlineLevel="1">
-      <c r="A84" s="60" t="inlineStr">
+      <c r="A84" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T4L</t>
         </is>
@@ -19326,7 +19428,7 @@
       </c>
     </row>
     <row r="85" hidden="1" outlineLevel="1">
-      <c r="A85" s="60" t="inlineStr">
+      <c r="A85" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T4L</t>
         </is>
@@ -19457,7 +19559,7 @@
       </c>
     </row>
     <row r="86" hidden="1" outlineLevel="1">
-      <c r="A86" s="60" t="inlineStr">
+      <c r="A86" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T4R</t>
         </is>
@@ -19588,7 +19690,7 @@
       </c>
     </row>
     <row r="87" hidden="1" outlineLevel="1">
-      <c r="A87" s="60" t="inlineStr">
+      <c r="A87" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T4R</t>
         </is>
@@ -19719,7 +19821,7 @@
       </c>
     </row>
     <row r="88" hidden="1" outlineLevel="1">
-      <c r="A88" s="60" t="inlineStr">
+      <c r="A88" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T5L</t>
         </is>
@@ -19850,7 +19952,7 @@
       </c>
     </row>
     <row r="89" hidden="1" outlineLevel="1">
-      <c r="A89" s="60" t="inlineStr">
+      <c r="A89" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T5L</t>
         </is>
@@ -19981,7 +20083,7 @@
       </c>
     </row>
     <row r="90" hidden="1" outlineLevel="1">
-      <c r="A90" s="60" t="inlineStr">
+      <c r="A90" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_T5R</t>
         </is>
@@ -20112,7 +20214,7 @@
       </c>
     </row>
     <row r="91" hidden="1" outlineLevel="1">
-      <c r="A91" s="60" t="inlineStr">
+      <c r="A91" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_T5R</t>
         </is>
@@ -20243,7 +20345,7 @@
       </c>
     </row>
     <row r="92" hidden="1" outlineLevel="1">
-      <c r="A92" s="60" t="inlineStr">
+      <c r="A92" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B0L</t>
         </is>
@@ -20374,7 +20476,7 @@
       </c>
     </row>
     <row r="93" hidden="1" outlineLevel="1">
-      <c r="A93" s="60" t="inlineStr">
+      <c r="A93" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B0L</t>
         </is>
@@ -20505,7 +20607,7 @@
       </c>
     </row>
     <row r="94" hidden="1" outlineLevel="1">
-      <c r="A94" s="60" t="inlineStr">
+      <c r="A94" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B0R</t>
         </is>
@@ -20636,7 +20738,7 @@
       </c>
     </row>
     <row r="95" hidden="1" outlineLevel="1">
-      <c r="A95" s="60" t="inlineStr">
+      <c r="A95" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B0R</t>
         </is>
@@ -20767,7 +20869,7 @@
       </c>
     </row>
     <row r="96" hidden="1" outlineLevel="1">
-      <c r="A96" s="60" t="inlineStr">
+      <c r="A96" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B1L</t>
         </is>
@@ -20898,7 +21000,7 @@
       </c>
     </row>
     <row r="97" hidden="1" outlineLevel="1">
-      <c r="A97" s="60" t="inlineStr">
+      <c r="A97" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B1L</t>
         </is>
@@ -21029,7 +21131,7 @@
       </c>
     </row>
     <row r="98" hidden="1" outlineLevel="1">
-      <c r="A98" s="60" t="inlineStr">
+      <c r="A98" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B1R</t>
         </is>
@@ -21160,7 +21262,7 @@
       </c>
     </row>
     <row r="99" hidden="1" outlineLevel="1">
-      <c r="A99" s="60" t="inlineStr">
+      <c r="A99" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B1R</t>
         </is>
@@ -21291,7 +21393,7 @@
       </c>
     </row>
     <row r="100" hidden="1" outlineLevel="1">
-      <c r="A100" s="60" t="inlineStr">
+      <c r="A100" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B2L</t>
         </is>
@@ -21422,7 +21524,7 @@
       </c>
     </row>
     <row r="101" hidden="1" outlineLevel="1">
-      <c r="A101" s="60" t="inlineStr">
+      <c r="A101" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B2L</t>
         </is>
@@ -21553,7 +21655,7 @@
       </c>
     </row>
     <row r="102" hidden="1" outlineLevel="1">
-      <c r="A102" s="60" t="inlineStr">
+      <c r="A102" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B2R</t>
         </is>
@@ -21684,7 +21786,7 @@
       </c>
     </row>
     <row r="103" hidden="1" outlineLevel="1">
-      <c r="A103" s="60" t="inlineStr">
+      <c r="A103" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B2R</t>
         </is>
@@ -21815,7 +21917,7 @@
       </c>
     </row>
     <row r="104" hidden="1" outlineLevel="1">
-      <c r="A104" s="60" t="inlineStr">
+      <c r="A104" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B3L</t>
         </is>
@@ -21946,7 +22048,7 @@
       </c>
     </row>
     <row r="105" hidden="1" outlineLevel="1">
-      <c r="A105" s="60" t="inlineStr">
+      <c r="A105" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B3L</t>
         </is>
@@ -22077,7 +22179,7 @@
       </c>
     </row>
     <row r="106" hidden="1" outlineLevel="1">
-      <c r="A106" s="60" t="inlineStr">
+      <c r="A106" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B3R</t>
         </is>
@@ -22208,7 +22310,7 @@
       </c>
     </row>
     <row r="107" hidden="1" outlineLevel="1">
-      <c r="A107" s="60" t="inlineStr">
+      <c r="A107" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B3R</t>
         </is>
@@ -22339,7 +22441,7 @@
       </c>
     </row>
     <row r="108" hidden="1" outlineLevel="1">
-      <c r="A108" s="60" t="inlineStr">
+      <c r="A108" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B4L</t>
         </is>
@@ -22470,7 +22572,7 @@
       </c>
     </row>
     <row r="109" hidden="1" outlineLevel="1">
-      <c r="A109" s="60" t="inlineStr">
+      <c r="A109" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B4L</t>
         </is>
@@ -22601,7 +22703,7 @@
       </c>
     </row>
     <row r="110" hidden="1" outlineLevel="1">
-      <c r="A110" s="60" t="inlineStr">
+      <c r="A110" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B4R</t>
         </is>
@@ -22732,7 +22834,7 @@
       </c>
     </row>
     <row r="111" hidden="1" outlineLevel="1">
-      <c r="A111" s="60" t="inlineStr">
+      <c r="A111" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B4R</t>
         </is>
@@ -22863,7 +22965,7 @@
       </c>
     </row>
     <row r="112" hidden="1" outlineLevel="1">
-      <c r="A112" s="60" t="inlineStr">
+      <c r="A112" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B5L</t>
         </is>
@@ -22994,7 +23096,7 @@
       </c>
     </row>
     <row r="113" hidden="1" outlineLevel="1">
-      <c r="A113" s="60" t="inlineStr">
+      <c r="A113" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B5L</t>
         </is>
@@ -23125,7 +23227,7 @@
       </c>
     </row>
     <row r="114" hidden="1" outlineLevel="1">
-      <c r="A114" s="60" t="inlineStr">
+      <c r="A114" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) N_B5R</t>
         </is>
@@ -23256,7 +23358,7 @@
       </c>
     </row>
     <row r="115" hidden="1" outlineLevel="1">
-      <c r="A115" s="60" t="inlineStr">
+      <c r="A115" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) A_B5R</t>
         </is>
@@ -23387,7 +23489,7 @@
       </c>
     </row>
     <row r="116" hidden="1" outlineLevel="1">
-      <c r="A116" s="60" t="inlineStr">
+      <c r="A116" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ASTL</t>
         </is>
@@ -23518,7 +23620,7 @@
       </c>
     </row>
     <row r="117" hidden="1" outlineLevel="1">
-      <c r="A117" s="60" t="inlineStr">
+      <c r="A117" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ASTR</t>
         </is>
@@ -23649,7 +23751,7 @@
       </c>
     </row>
     <row r="118" hidden="1" outlineLevel="1">
-      <c r="A118" s="60" t="inlineStr">
+      <c r="A118" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ASBL</t>
         </is>
@@ -23780,7 +23882,7 @@
       </c>
     </row>
     <row r="119" hidden="1" outlineLevel="1">
-      <c r="A119" s="60" t="inlineStr">
+      <c r="A119" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) ASBR</t>
         </is>
@@ -23911,7 +24013,7 @@
       </c>
     </row>
     <row r="120" hidden="1" outlineLevel="1">
-      <c r="A120" s="60" t="inlineStr">
+      <c r="A120" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) YTL</t>
         </is>
@@ -24042,7 +24144,7 @@
       </c>
     </row>
     <row r="121" hidden="1" outlineLevel="1">
-      <c r="A121" s="60" t="inlineStr">
+      <c r="A121" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) YTR</t>
         </is>
@@ -24173,7 +24275,7 @@
       </c>
     </row>
     <row r="122" hidden="1" outlineLevel="1">
-      <c r="A122" s="60" t="inlineStr">
+      <c r="A122" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) YBL</t>
         </is>
@@ -24304,7 +24406,7 @@
       </c>
     </row>
     <row r="123" hidden="1" outlineLevel="1">
-      <c r="A123" s="60" t="inlineStr">
+      <c r="A123" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) YBR</t>
         </is>
@@ -24435,7 +24537,7 @@
       </c>
     </row>
     <row r="124" hidden="1" outlineLevel="1">
-      <c r="A124" s="60" t="inlineStr">
+      <c r="A124" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) BAD</t>
         </is>
@@ -24566,7 +24668,7 @@
       </c>
     </row>
     <row r="125" hidden="1" outlineLevel="1">
-      <c r="A125" s="60" t="inlineStr">
+      <c r="A125" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) NB11</t>
         </is>
@@ -24577,7 +24679,7 @@
       </c>
     </row>
     <row r="126" hidden="1" outlineLevel="1">
-      <c r="A126" s="60" t="inlineStr">
+      <c r="A126" s="61" t="inlineStr">
         <is>
           <t>(phụ trợ) NB12</t>
         </is>
@@ -24588,7 +24690,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="64">
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
@@ -24599,6 +24701,7 @@
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="A1:B3"/>
+    <mergeCell ref="V6:X6"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="P7:R7"/>
     <mergeCell ref="K8:M8"/>
@@ -24638,11 +24741,13 @@
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="C5:E5"/>
+    <mergeCell ref="V5:X5"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="A5:B7"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="G8:I8"/>
+    <mergeCell ref="V4:X4"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="C9:AG9"/>
@@ -24758,7 +24863,7 @@
       <formula>LEFT($C$9,1)="✔"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="73">
+  <dataValidations count="76">
     <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm" prompt="Tên dầm (ghi trên bản vẽ, tên file CSV)."/>
     <dataValidation sqref="F3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="b dầm (mm)" prompt="Bề rộng dầm (mm), vd 400."/>
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="h dầm (mm)" prompt="Chiều cao dầm (mm), vd 1000."/>
@@ -24819,10 +24924,19 @@
     </dataValidation>
     <dataValidation sqref="S8 T8" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm chờ nối" prompt="Tên dầm / zone sau mà thép chờ (thẳng hoặc coupler) nối sang, vd B138 – ghi lên MC dọc và shop: 'COUPLER NỐI DẦM B138'. Để trống = không ghi."/>
     <dataValidation sqref="Y2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tai sàn (phía có sàn)" prompt="2 ben / Trai / Phai / Khong&#10;Chỉ dùng khi F7 là số." type="list">
-      <formula1>LIST!$X$2:$X$5</formula1>
+      <formula1>LIST!$Y$2:$Y$5</formula1>
     </dataValidation>
     <dataValidation sqref="Y3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Sàn lật (dầm úp)" prompt="Co = sàn nằm ở đáy dầm. Chỉ dùng khi F7 là số." type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Đai con đi hết dầm" prompt="Co = 1 khai báo (Y5) cho cả dầm.&#10;Khong = vùng gối (vùng đai dày 2 đầu nhịp) dùng Y5, vùng nhịp dùng Y6.&#10;Trống = theo QS_DAMSET trang 2." type="list">
+      <formula1>LIST!$W$2:$W$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="Theo số thứ tự thanh lớp 1 trên (trái → phải):&#10;3 = đai C tại thanh 3&#10;2_4 = đai Q (kín) ôm thanh 2..4&#10;2-4 = đai U thanh 2..4&#10;Ghép: 3,2_4 · 0 = không có · AUTO/trống = tự động" type="list">
+      <formula1>LIST!$X$2:$X$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con vùng nhịp" prompt="Dùng khi Y4 = Khong. Cú pháp như Y5: 2 · 2_4 · 2-4 · 3,2_4 · 0 · AUTO" type="list">
+      <formula1>LIST!$X$2:$X$10</formula1>
     </dataValidation>
     <dataValidation sqref="C11 E11 G11 I11 K11 M11 O11 Q11 S11 U11 W11 Y11 AA11 AC11 AE11 AG11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Gối: bề rộng (mm)" prompt="300 = cột 300&#10;0 = console (đầu tự do)&#10;220x500 = gối là DẦM 220x500&#10;1000/220 = cột dưới 1000, cột trên 220&#10;1000/200/-400 = cột trên 200 lệch tim -400"/>
     <dataValidation sqref="D11 F11 H11 J11 L11 N11 P11 R11 T11 V11 X11 Z11 AB11 AD11 AF11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Nhịp: L thông thủy (mm)" prompt="Khoảng cách 2 mép gối (mm).&#10;Để trống = hết dầm (các nhịp phải liền nhau).&#10;Dòng 34-35: suy Ltt từ khoảng cách trục."/>
@@ -24943,7 +25057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24970,125 +25084,131 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>THEP</t>
         </is>
       </c>
-      <c r="B1" s="61" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>DAI</t>
         </is>
       </c>
-      <c r="C1" s="61" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>GIA</t>
         </is>
       </c>
-      <c r="D1" s="61" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>DAITRONG</t>
         </is>
       </c>
-      <c r="E1" s="61" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>TLINK</t>
         </is>
       </c>
-      <c r="F1" s="61" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>DAIGC</t>
         </is>
       </c>
-      <c r="G1" s="61" t="inlineStr">
+      <c r="G1" s="62" t="inlineStr">
         <is>
           <t>VAIBO</t>
         </is>
       </c>
-      <c r="H1" s="61" t="inlineStr">
+      <c r="H1" s="62" t="inlineStr">
         <is>
           <t>ANCOT</t>
         </is>
       </c>
-      <c r="I1" s="61" t="inlineStr">
+      <c r="I1" s="62" t="inlineStr">
         <is>
           <t>DOITHEP</t>
         </is>
       </c>
-      <c r="J1" s="61" t="inlineStr">
+      <c r="J1" s="62" t="inlineStr">
         <is>
           <t>KGOI</t>
         </is>
       </c>
-      <c r="K1" s="61" t="inlineStr">
+      <c r="K1" s="62" t="inlineStr">
         <is>
           <t>KNHIP</t>
         </is>
       </c>
-      <c r="L1" s="61" t="inlineStr">
+      <c r="L1" s="62" t="inlineStr">
         <is>
           <t>NEO</t>
         </is>
       </c>
-      <c r="M1" s="61" t="inlineStr">
+      <c r="M1" s="62" t="inlineStr">
         <is>
           <t>DAIC</t>
         </is>
       </c>
-      <c r="N1" s="61" t="inlineStr">
+      <c r="N1" s="62" t="inlineStr">
         <is>
           <t>GIATCD</t>
         </is>
       </c>
-      <c r="O1" s="61" t="inlineStr">
+      <c r="O1" s="62" t="inlineStr">
         <is>
           <t>CDOKC</t>
         </is>
       </c>
-      <c r="P1" s="61" t="inlineStr">
+      <c r="P1" s="62" t="inlineStr">
         <is>
           <t>KCDAIC</t>
         </is>
       </c>
-      <c r="Q1" s="61" t="inlineStr">
+      <c r="Q1" s="62" t="inlineStr">
         <is>
           <t>LECHMCN</t>
         </is>
       </c>
-      <c r="R1" s="61" t="inlineStr">
+      <c r="R1" s="62" t="inlineStr">
         <is>
           <t>NCK</t>
         </is>
       </c>
-      <c r="S1" s="61" t="inlineStr">
+      <c r="S1" s="62" t="inlineStr">
         <is>
           <t>CHOKIEU</t>
         </is>
       </c>
-      <c r="T1" s="61" t="inlineStr">
+      <c r="T1" s="62" t="inlineStr">
         <is>
           <t>CHOLOP</t>
         </is>
       </c>
-      <c r="U1" s="61" t="inlineStr">
+      <c r="U1" s="62" t="inlineStr">
         <is>
           <t>CHOTHEP</t>
         </is>
       </c>
-      <c r="V1" s="61" t="inlineStr">
+      <c r="V1" s="62" t="inlineStr">
         <is>
           <t>CHOL</t>
         </is>
       </c>
-      <c r="W1" s="61" t="inlineStr">
+      <c r="W1" s="62" t="inlineStr">
         <is>
           <t>KHONGCO</t>
         </is>
       </c>
-      <c r="X1" s="61" t="inlineStr">
+      <c r="X1" s="62" t="inlineStr">
+        <is>
+          <t>DAICON</t>
+        </is>
+      </c>
+      <c r="Y1" s="62" t="inlineStr">
         <is>
           <t>TAISAN</t>
         </is>
@@ -25212,6 +25332,11 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>2 ben</t>
         </is>
       </c>
@@ -25329,6 +25454,11 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>Trai</t>
         </is>
       </c>
@@ -25431,6 +25561,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>Phai</t>
         </is>
       </c>
@@ -25503,6 +25638,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>Khong</t>
         </is>
       </c>
@@ -25553,6 +25693,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2_3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25585,6 +25730,11 @@
           <t>100</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2_4</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25612,6 +25762,11 @@
           <t>100/300</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25634,6 +25789,11 @@
           <t>TR</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3,2_4</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25649,6 +25809,11 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>BL</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,4</t>
         </is>
       </c>
     </row>

--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -805,7 +805,8 @@
 • 2_4 → đai Q (đai kín) ôm từ thanh 2 đến thanh 4
 • 2-4 → đai U từ thanh 2 đến thanh 4
 • ghép nhiều loại: 3,2_4 (đai C thanh 3 + đai Q thanh 2..4)
-• 0 = không có đai con ; AUTO / trống = tự động (QS_DAMSET trang 2)
+• 0 = không có đai con ; AUTO / trống = tra bảng theo số lượng thép (QS_DAMSET trang 7)
+• theo số lượng thép riêng cho dầm: 4:2_3;5:3,2_4 (4 thanh → Q 2..3 ; 5 thanh → C 3 + Q 2..4)
 Vùng gối có gia cường nên số thanh khác vùng nhịp → Y4 = Khong để khai báo riêng vùng gối (Y5) và vùng nhịp (Y6).
 Chỉ số vượt số thanh thực tế được tự thu về thanh cuối.</t>
       </text>
@@ -994,7 +995,8 @@
 • 2_4 → đai Q (đai kín) ôm từ thanh 2 đến thanh 4
 • 2-4 → đai U từ thanh 2 đến thanh 4
 • ghép nhiều loại: 3,2_4 (đai C thanh 3 + đai Q thanh 2..4)
-• 0 = không có đai con ; AUTO / trống = tự động (QS_DAMSET trang 2)
+• 0 = không có đai con ; AUTO / trống = tra bảng theo số lượng thép (QS_DAMSET trang 7)
+• theo số lượng thép riêng cho dầm: 4:2_3;5:3,2_4 (4 thanh → Q 2..3 ; 5 thanh → C 3 + Q 2..4)
 Vùng gối có gia cường nên số thanh khác vùng nhịp → Y4 = Khong để khai báo riêng vùng gối (Y5) và vùng nhịp (Y6).
 Chỉ số vượt số thanh thực tế được tự thu về thanh cuối.</t>
       </text>
@@ -1510,7 +1512,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="85" customHeight="1">
+    <row r="9" ht="112" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>ĐAI CON (Y4:Y6)</t>
@@ -1520,7 +1522,9 @@
         <is>
           <t>Nhánh đai bên trong theo số thứ tự thanh lớp 1 trên (1..n từ trái sang phải): 2 = đai C tại thanh 2 ; 2_4 = đai Q (kín) ôm thanh 2..4 ;
 2-4 = đai U thanh 2..4 ; ghép 3,2_4 ; 0 = không có ; AUTO / trống = tự động.
-Y4 = Co: Y5 áp dụng cả dầm. Y4 = Khong: Y5 cho vùng gối (vùng đai dày 2 đầu nhịp), Y6 cho vùng nhịp. Trống = QS_DAMSET trang 2.
+Theo số lượng thép (số thanh lớp 1 trên tại mặt cắt): 4:2_3;5:3,2_4 ; số thanh không có trong bảng → bảng QS_DAMSET trang 7.
+AUTO / trống → bảng QS_DAMSET trang 7 (2 … 10 thanh) ; bảng ghi AUTO → tự động cũ (1 nhánh mỗi thanh giữa khi ≥ 4 thanh).
+Y4 = Co: Y5 áp dụng cả dầm. Y4 = Khong: Y5 cho vùng gối (vùng đai dày 2 đầu nhịp), Y6 cho vùng nhịp. Trống = QS_DAMSET trang 7.
 Đường kính / bước đai con = đai trong dòng 27 nếu có, không thì theo đai chính của vùng.</t>
         </is>
       </c>
@@ -13639,11 +13643,11 @@
     <dataValidation sqref="Y4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Đai con đi hết dầm" prompt="Co = 1 khai báo (Y5) cho cả dầm.&#10;Khong = vùng gối (vùng đai dày 2 đầu nhịp) dùng Y5, vùng nhịp dùng Y6.&#10;Trống = theo QS_DAMSET trang 2." type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
     </dataValidation>
-    <dataValidation sqref="Y5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="Theo số thứ tự thanh lớp 1 trên (trái → phải):&#10;3 = đai C tại thanh 3&#10;2_4 = đai Q (kín) ôm thanh 2..4&#10;2-4 = đai U thanh 2..4&#10;Ghép: 3,2_4 · 0 = không có · AUTO/trống = tự động" type="list">
-      <formula1>LIST!$X$2:$X$10</formula1>
+    <dataValidation sqref="Y5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="Theo số thứ tự thanh lớp 1 trên (trái → phải): 3 = đai C thanh 3 · 2_4 = đai Q ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có&#10;Theo số lượng thép: 4:2_3;5:3,2_4&#10;AUTO/trống = tra bảng QS_DAMSET trang 7" type="list">
+      <formula1>LIST!$X$2:$X$11</formula1>
     </dataValidation>
-    <dataValidation sqref="Y6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con vùng nhịp" prompt="Dùng khi Y4 = Khong. Cú pháp như Y5: 2 · 2_4 · 2-4 · 3,2_4 · 0 · AUTO" type="list">
-      <formula1>LIST!$X$2:$X$10</formula1>
+    <dataValidation sqref="Y6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con vùng nhịp" prompt="Dùng khi Y4 = Khong. Cú pháp như Y5: 2 · 2_4 · 2-4 · 3,2_4 · 4:2_3;5:3,2_4 · 0 · AUTO" type="list">
+      <formula1>LIST!$X$2:$X$11</formula1>
     </dataValidation>
     <dataValidation sqref="C11 E11 G11 I11 K11 M11 O11 Q11 S11 U11 W11 Y11 AA11 AC11 AE11 AG11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Gối: bề rộng (mm)" prompt="300 = cột 300&#10;0 = console (đầu tự do)&#10;220x500 = gối là DẦM 220x500&#10;1000/220 = cột dưới 1000, cột trên 220&#10;1000/200/-400 = cột trên 200 lệch tim -400"/>
     <dataValidation sqref="D11 F11 H11 J11 L11 N11 P11 R11 T11 V11 X11 Z11 AB11 AD11 AF11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Nhịp: L thông thủy (mm)" prompt="Khoảng cách 2 mép gối (mm).&#10;Để trống = hết dầm (các nhịp phải liền nhau).&#10;Dòng 34-35: suy Ltt từ khoảng cách trục."/>
@@ -24932,11 +24936,11 @@
     <dataValidation sqref="Y4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Đai con đi hết dầm" prompt="Co = 1 khai báo (Y5) cho cả dầm.&#10;Khong = vùng gối (vùng đai dày 2 đầu nhịp) dùng Y5, vùng nhịp dùng Y6.&#10;Trống = theo QS_DAMSET trang 2." type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
     </dataValidation>
-    <dataValidation sqref="Y5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="Theo số thứ tự thanh lớp 1 trên (trái → phải):&#10;3 = đai C tại thanh 3&#10;2_4 = đai Q (kín) ôm thanh 2..4&#10;2-4 = đai U thanh 2..4&#10;Ghép: 3,2_4 · 0 = không có · AUTO/trống = tự động" type="list">
-      <formula1>LIST!$X$2:$X$10</formula1>
+    <dataValidation sqref="Y5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="Theo số thứ tự thanh lớp 1 trên (trái → phải): 3 = đai C thanh 3 · 2_4 = đai Q ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có&#10;Theo số lượng thép: 4:2_3;5:3,2_4&#10;AUTO/trống = tra bảng QS_DAMSET trang 7" type="list">
+      <formula1>LIST!$X$2:$X$11</formula1>
     </dataValidation>
-    <dataValidation sqref="Y6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con vùng nhịp" prompt="Dùng khi Y4 = Khong. Cú pháp như Y5: 2 · 2_4 · 2-4 · 3,2_4 · 0 · AUTO" type="list">
-      <formula1>LIST!$X$2:$X$10</formula1>
+    <dataValidation sqref="Y6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con vùng nhịp" prompt="Dùng khi Y4 = Khong. Cú pháp như Y5: 2 · 2_4 · 2-4 · 3,2_4 · 4:2_3;5:3,2_4 · 0 · AUTO" type="list">
+      <formula1>LIST!$X$2:$X$11</formula1>
     </dataValidation>
     <dataValidation sqref="C11 E11 G11 I11 K11 M11 O11 Q11 S11 U11 W11 Y11 AA11 AC11 AE11 AG11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Gối: bề rộng (mm)" prompt="300 = cột 300&#10;0 = console (đầu tự do)&#10;220x500 = gối là DẦM 220x500&#10;1000/220 = cột dưới 1000, cột trên 220&#10;1000/200/-400 = cột trên 200 lệch tim -400"/>
     <dataValidation sqref="D11 F11 H11 J11 L11 N11 P11 R11 T11 V11 X11 Z11 AB11 AD11 AF11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Nhịp: L thông thủy (mm)" prompt="Khoảng cách 2 mép gối (mm).&#10;Để trống = hết dầm (các nhịp phải liền nhau).&#10;Dòng 34-35: suy Ltt từ khoảng cách trục."/>
@@ -25833,6 +25837,11 @@
           <t>BR</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4:2_3;5:3,2_4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/QS_DAM_NhapLieu.xlsx
+++ b/QS_DAM_NhapLieu.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'VD_L1.B137'!$A:$B</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'VD_L1.B137'!$A$1:$AG$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'VD_L1.B137'!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'MAU'!$A:$B</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'MAU'!$A$1:$AG$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'MAU'!$A$1:$AG$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -923,7 +923,7 @@
 • 2_4 → đai Q (đai kín) ôm từ thanh 2 đến thanh 4
 • 2-4 → đai U từ thanh 2 đến thanh 4
 • ghép nhiều loại: 3,2_4 (đai C thanh 3 + đai Q thanh 2..4)
-• 0 = không có đai con ; AUTO / trống = tra bảng dòng 38 (số thanh ở dòng 37) → bảng QS_DAMSET trang 7
+• 0 = không có đai con ; AUTO / trống = tra bảng: dòng 38 đai C + dòng 39 đai U / Q (số thanh ở dòng 37)
 Vùng gối có gia cường nên số thanh khác vùng nhịp → C33 = Khong để khai báo riêng vùng gối (C34) và vùng nhịp (C35).
 Chỉ số vượt số thanh thực tế được tự thu về thanh cuối. QS_DAMXL ghi lại khối này từ dầm đã vẽ.</t>
       </text>
@@ -1120,7 +1120,7 @@
 • 2_4 → đai Q (đai kín) ôm từ thanh 2 đến thanh 4
 • 2-4 → đai U từ thanh 2 đến thanh 4
 • ghép nhiều loại: 3,2_4 (đai C thanh 3 + đai Q thanh 2..4)
-• 0 = không có đai con ; AUTO / trống = tra bảng dòng 38 (số thanh ở dòng 37) → bảng QS_DAMSET trang 7
+• 0 = không có đai con ; AUTO / trống = tra bảng: dòng 38 đai C + dòng 39 đai U / Q (số thanh ở dòng 37)
 Vùng gối có gia cường nên số thanh khác vùng nhịp → C33 = Khong để khai báo riêng vùng gối (C34) và vùng nhịp (C35).
 Chỉ số vượt số thanh thực tế được tự thu về thanh cuối. QS_DAMXL ghi lại khối này từ dầm đã vẽ.</t>
       </text>
@@ -1443,7 +1443,7 @@
         <is>
           <t>1. Mỗi dầm 1 sheet: chuột phải sheet MAU (hoặc sheet ví dụ) → Move or Copy → Create a copy, đổi tên theo dầm.
 2. Nhập ô trắng. Chọn ô sẽ hiện gợi ý; ô có ▼ có danh sách chọn (vẫn gõ tay được, trừ ô bắt buộc chọn).
-3. Xem dòng 9 (TÌNH TRẠNG SỐ LIỆU) và dòng 41 (KIỂM TRA) – sửa hết ô đỏ.
+3. Xem dòng 9 (TÌNH TRẠNG SỐ LIỆU) và dòng 42 (KIỂM TRA) – sửa hết ô đỏ.
 4. AutoCAD / ZWCAD: để sheet dầm cần vẽ ĐANG MỞ trong Excel → lệnh QS_VEDAM → nguồn Excel → chọn điểm mép TRÊN-TRÁI dầm.
 5. QS_SHOPDAM: cắt thép / shop. QS_DAMSET, QS_DAMNOI: cài đặt móc đai, neo, chiều dài nối.
 6. QS_DAMXL: quét chọn tên dầm (hoặc thép) các dầm ĐÃ VẼ → ghi lại toàn bộ số liệu (kể cả đai con, thép chờ, tên nhịp)
@@ -1477,7 +1477,7 @@
   thanh (Tat ca / Chay suot / TỰ ĐIỀN T:3t28;B:2t25), L chờ / sâu khoan (AUTO / 40 = 40d / 1200 mm; coupler 0 / 100 / 100/300 so le),
   so le, dòng 8 = tên dầm chờ nối hoặc ghi chú khoan cấy.
 • TÙY CHỌN SÀN (Y2:Y3): tai sàn 2 ben / Trai / Phai / Khong, sàn lật – dùng khi F7 chỉ là số (nhập mã DCE 150/1, _150 thì bỏ qua Y2:Y3).
-• Dòng 31: tên dầm theo nhịp (ghi dưới MC dọc). Dòng 32–38: ĐAI CON. Dòng 41 + dòng 9: báo thiếu KT gối, thiếu tên trục,
+• Dòng 31: tên dầm theo nhịp (ghi dưới MC dọc). Dòng 32–39: ĐAI CON. Dòng 42 + dòng 9: báo thiếu KT gối, thiếu tên trục,
   thiếu đai, Ltt sai, nhịp đứt quãng, ký hiệu thép sai (ô thép sai tô đỏ).</t>
         </is>
       </c>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="85" customHeight="1">
+    <row r="10" ht="139" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ĐAI CON (dòng 32–38)</t>
+          <t>ĐAI CON (dòng 32–39)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1554,8 +1554,9 @@
           <t>Nhánh đai bên trong theo số thứ tự thanh lớp 1 trên (1..n từ trái sang phải): 2 = đai C tại thanh 2 ; 2_4 = đai Q (kín) ôm thanh 2..4 ;
 2-4 = đai U thanh 2..4 ; ghép 3,2_4 ; 0 = không có ; AUTO / trống = tra bảng.
 C33 = Co: C34 áp dụng cả dầm. C33 = Khong: C34 cho vùng gối (vùng đai dày 2 đầu nhịp), C35 cho vùng nhịp.
-C36 = Co: tra bảng dòng 38 theo số thanh lớp 1 trên tại mặt cắt (2 … 30 thanh, dòng 37); ô trống → bảng QS_DAMSET trang 7.
-Ô trống ở C33:C36 = theo QS_DAMSET trang 7. Đường kính / bước đai con = đai trong dòng 27 nếu có, không thì theo đai chính.</t>
+C36 = Co / trống: tra bảng theo số thanh lớp 1 trên tại mặt cắt (2 … 30 thanh, dòng 37): dòng 38 = ĐAI C (2,4 ; 2_4 = C tại thanh 2..4),
+dòng 39 = ĐAI U / Q (2_4 = Q, 2-4 = U ; số đơn = đai C). Hai dòng cộng lại. Ô trống / C36 = Khong = đai trong tự động (QS_DAMSET trang 2).
+Đường kính / bước đai con = đai trong dòng 27 nếu có, không thì theo đai chính. (Trang 7 QS_DAMSET đã bỏ – đai con chỉ khai trên Excel.)</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2566,7 @@
       </c>
       <c r="B9" s="20" t="n"/>
       <c r="C9" s="21">
-        <f>IF(SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)=0,"Chưa có nhịp: nhập bề rộng gối + L thông thủy ở dòng 11",IF(SUMPRODUCT((C41:AG41&lt;&gt;"")*(C41:AG41&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))-1)*MID(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))-1)*MID(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))-1)*MID(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))-1)*MID(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)=0,"✔  Số liệu hợp lệ – "&amp;SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)&amp;" nhịp, tổng chiều dài dầm L = "&amp;FIXED(SUMIF(C63:AG63,1,C60:AG60),0)&amp;" mm","✖  Có "&amp;(SUMPRODUCT((C41:AG41&lt;&gt;"")*(C41:AG41&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))-1)*MID(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))-1)*MID(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))-1)*MID(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))-1)*MID(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0))&amp;" lỗi – xem dòng 41 (KIỂM TRA SỐ LIỆU) và ô B11 / B12"))</f>
+        <f>IF(SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)=0,"Chưa có nhịp: nhập bề rộng gối + L thông thủy ở dòng 11",IF(SUMPRODUCT((C42:AG42&lt;&gt;"")*(C42:AG42&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))-1)*MID(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))-1)*MID(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))-1)*MID(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))-1)*MID(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)=0,"✔  Số liệu hợp lệ – "&amp;SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)&amp;" nhịp, tổng chiều dài dầm L = "&amp;FIXED(SUMIF(C63:AG63,1,C60:AG60),0)&amp;" mm","✖  Có "&amp;(SUMPRODUCT((C42:AG42&lt;&gt;"")*(C42:AG42&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))-1)*MID(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))-1)*MID(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))-1)*MID(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))-1)*MID(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0))&amp;" lỗi – xem dòng 42 (KIỂM TRA SỐ LIỆU) và ô B11 / B12"))</f>
         <v/>
       </c>
       <c r="D9" s="22" t="n"/>
@@ -3890,7 +3891,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="50" t="inlineStr">
         <is>
-          <t>ĐAI CON – NHÁNH ĐAI BÊN TRONG theo vị trí thanh lớp 1 trên (đánh số 1..n từ trái sang phải) · ô trống = theo QS_DAMSET trang 7</t>
+          <t>ĐAI CON – NHÁNH ĐAI BÊN TRONG theo vị trí thanh lớp 1 trên (đánh số 1..n từ trái sang phải) · trống = đai trong tự động</t>
         </is>
       </c>
       <c r="B32" s="51" t="n"/>
@@ -3937,7 +3938,7 @@
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Co = khai báo ô C34 áp dụng cả dầm · Khong = C34 cho vùng gối (vùng đai dày 2 đầu nhịp), C35 cho vùng nhịp · trống = QS_DAMSET</t>
+          <t>Co / trống = khai báo ô C34 áp dụng cả dầm · Khong = C34 cho vùng gối (vùng đai dày 2 đầu nhịp), C35 cho vùng nhịp</t>
         </is>
       </c>
       <c r="F33" s="6" t="n"/>
@@ -3980,7 +3981,7 @@
       <c r="D34" s="6" t="n"/>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>3 = đai C (1 nhánh) tại thanh 3 · 2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có · AUTO / trống = tra bảng dòng 38</t>
+          <t>3 = đai C (1 nhánh) tại thanh 3 · 2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có · AUTO / trống = tra bảng dòng 38 + 39</t>
         </is>
       </c>
       <c r="F34" s="6" t="n"/>
@@ -4066,7 +4067,7 @@
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Co = khi C34 / C35 là AUTO / trống: tra bảng dòng 38 theo số thanh lớp 1 trên tại mặt cắt (ô trống → bảng QS_DAMSET trang 7) · Khong = đai trong tự động cũ</t>
+          <t>Co / trống = khi C34 / C35 là AUTO / trống: tra bảng dòng 38 (đai C) + 39 (đai U / Q) theo số thanh lớp 1 trên tại mặt cắt · Khong / ô bảng trống = đai trong tự động</t>
         </is>
       </c>
       <c r="F36" s="6" t="n"/>
@@ -4198,7 +4199,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="52" t="inlineStr">
         <is>
-          <t>Nhánh đai con theo số thanh</t>
+          <t>Đai C (1 nhánh) theo số thanh</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
@@ -4234,173 +4235,212 @@
       <c r="AF38" s="57" t="inlineStr"/>
       <c r="AG38" s="57" t="inlineStr"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="50" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="52" t="inlineStr">
+        <is>
+          <t>Đai U / Q theo số thanh</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="58" t="n"/>
+      <c r="D39" s="58" t="n"/>
+      <c r="E39" s="58" t="n"/>
+      <c r="F39" s="58" t="n"/>
+      <c r="G39" s="58" t="n"/>
+      <c r="H39" s="58" t="n"/>
+      <c r="I39" s="58" t="n"/>
+      <c r="J39" s="58" t="n"/>
+      <c r="K39" s="58" t="n"/>
+      <c r="L39" s="58" t="n"/>
+      <c r="M39" s="58" t="n"/>
+      <c r="N39" s="58" t="n"/>
+      <c r="O39" s="58" t="n"/>
+      <c r="P39" s="58" t="n"/>
+      <c r="Q39" s="58" t="n"/>
+      <c r="R39" s="58" t="n"/>
+      <c r="S39" s="58" t="n"/>
+      <c r="T39" s="58" t="n"/>
+      <c r="U39" s="58" t="n"/>
+      <c r="V39" s="58" t="n"/>
+      <c r="W39" s="58" t="n"/>
+      <c r="X39" s="58" t="n"/>
+      <c r="Y39" s="58" t="n"/>
+      <c r="Z39" s="58" t="n"/>
+      <c r="AA39" s="58" t="n"/>
+      <c r="AB39" s="58" t="n"/>
+      <c r="AC39" s="58" t="n"/>
+      <c r="AD39" s="58" t="n"/>
+      <c r="AE39" s="58" t="n"/>
+      <c r="AF39" s="57" t="inlineStr"/>
+      <c r="AG39" s="57" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="50" t="inlineStr">
         <is>
           <t>KIỂM TRA SỐ LIỆU</t>
         </is>
       </c>
-      <c r="B40" s="51" t="n"/>
-      <c r="C40" s="51" t="n"/>
-      <c r="D40" s="51" t="n"/>
-      <c r="E40" s="51" t="n"/>
-      <c r="F40" s="51" t="n"/>
-      <c r="G40" s="51" t="n"/>
-      <c r="H40" s="51" t="n"/>
-      <c r="I40" s="51" t="n"/>
-      <c r="J40" s="51" t="n"/>
-      <c r="K40" s="51" t="n"/>
-      <c r="L40" s="51" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="51" t="n"/>
-      <c r="W40" s="51" t="n"/>
-      <c r="X40" s="51" t="n"/>
-      <c r="Y40" s="51" t="n"/>
-      <c r="Z40" s="51" t="n"/>
-      <c r="AA40" s="51" t="n"/>
-      <c r="AB40" s="51" t="n"/>
-      <c r="AC40" s="51" t="n"/>
-      <c r="AD40" s="51" t="n"/>
-      <c r="AE40" s="51" t="n"/>
-      <c r="AF40" s="51" t="n"/>
-      <c r="AG40" s="51" t="n"/>
-    </row>
-    <row r="41" ht="27" customHeight="1">
-      <c r="A41" s="59" t="inlineStr">
+      <c r="B41" s="51" t="n"/>
+      <c r="C41" s="51" t="n"/>
+      <c r="D41" s="51" t="n"/>
+      <c r="E41" s="51" t="n"/>
+      <c r="F41" s="51" t="n"/>
+      <c r="G41" s="51" t="n"/>
+      <c r="H41" s="51" t="n"/>
+      <c r="I41" s="51" t="n"/>
+      <c r="J41" s="51" t="n"/>
+      <c r="K41" s="51" t="n"/>
+      <c r="L41" s="51" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="51" t="n"/>
+      <c r="W41" s="51" t="n"/>
+      <c r="X41" s="51" t="n"/>
+      <c r="Y41" s="51" t="n"/>
+      <c r="Z41" s="51" t="n"/>
+      <c r="AA41" s="51" t="n"/>
+      <c r="AB41" s="51" t="n"/>
+      <c r="AC41" s="51" t="n"/>
+      <c r="AD41" s="51" t="n"/>
+      <c r="AE41" s="51" t="n"/>
+      <c r="AF41" s="51" t="n"/>
+      <c r="AG41" s="51" t="n"/>
+    </row>
+    <row r="42" ht="27" customHeight="1">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>Kết quả kiểm tra từng cột</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="60">
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="60">
         <f>IF(C63=0,"",IF(C60="","Thiếu KT gối",IF(C26="","Thiếu tên trục",IF(C116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="D41" s="60">
+      <c r="D42" s="60">
         <f>IF(D63=0,IF(D11="","","Sai Ltt"),IF(FALSE,"Nhịp đứt quãng",IF(D26="","Thiếu đai",IF(D116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="E41" s="60">
+      <c r="E42" s="60">
         <f>IF(E63=0,"",IF(E60="","Thiếu KT gối",IF(E26="","Thiếu tên trục",IF(E116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="F41" s="60">
+      <c r="F42" s="60">
         <f>IF(F63=0,IF(F11="","","Sai Ltt"),IF(AND(D$63=0,F63=1),"Nhịp đứt quãng",IF(F26="","Thiếu đai",IF(F116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="G41" s="60">
+      <c r="G42" s="60">
         <f>IF(G63=0,"",IF(G60="","Thiếu KT gối",IF(G26="","Thiếu tên trục",IF(G116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="H41" s="60">
+      <c r="H42" s="60">
         <f>IF(H63=0,IF(H11="","","Sai Ltt"),IF(AND(F$63=0,H63=1),"Nhịp đứt quãng",IF(H26="","Thiếu đai",IF(H116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="I41" s="60">
+      <c r="I42" s="60">
         <f>IF(I63=0,"",IF(I60="","Thiếu KT gối",IF(I26="","Thiếu tên trục",IF(I116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="J41" s="60">
+      <c r="J42" s="60">
         <f>IF(J63=0,IF(J11="","","Sai Ltt"),IF(AND(H$63=0,J63=1),"Nhịp đứt quãng",IF(J26="","Thiếu đai",IF(J116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="K41" s="60">
+      <c r="K42" s="60">
         <f>IF(K63=0,"",IF(K60="","Thiếu KT gối",IF(K26="","Thiếu tên trục",IF(K116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="L41" s="60">
+      <c r="L42" s="60">
         <f>IF(L63=0,IF(L11="","","Sai Ltt"),IF(AND(J$63=0,L63=1),"Nhịp đứt quãng",IF(L26="","Thiếu đai",IF(L116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="M41" s="60">
+      <c r="M42" s="60">
         <f>IF(M63=0,"",IF(M60="","Thiếu KT gối",IF(M26="","Thiếu tên trục",IF(M116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="N41" s="60">
+      <c r="N42" s="60">
         <f>IF(N63=0,IF(N11="","","Sai Ltt"),IF(AND(L$63=0,N63=1),"Nhịp đứt quãng",IF(N26="","Thiếu đai",IF(N116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="O41" s="60">
+      <c r="O42" s="60">
         <f>IF(O63=0,"",IF(O60="","Thiếu KT gối",IF(O26="","Thiếu tên trục",IF(O116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="P41" s="60">
+      <c r="P42" s="60">
         <f>IF(P63=0,IF(P11="","","Sai Ltt"),IF(AND(N$63=0,P63=1),"Nhịp đứt quãng",IF(P26="","Thiếu đai",IF(P116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Q41" s="60">
+      <c r="Q42" s="60">
         <f>IF(Q63=0,"",IF(Q60="","Thiếu KT gối",IF(Q26="","Thiếu tên trục",IF(Q116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="R41" s="60">
+      <c r="R42" s="60">
         <f>IF(R63=0,IF(R11="","","Sai Ltt"),IF(AND(P$63=0,R63=1),"Nhịp đứt quãng",IF(R26="","Thiếu đai",IF(R116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="S41" s="60">
+      <c r="S42" s="60">
         <f>IF(S63=0,"",IF(S60="","Thiếu KT gối",IF(S26="","Thiếu tên trục",IF(S116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="T41" s="60">
+      <c r="T42" s="60">
         <f>IF(T63=0,IF(T11="","","Sai Ltt"),IF(AND(R$63=0,T63=1),"Nhịp đứt quãng",IF(T26="","Thiếu đai",IF(T116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="U41" s="60">
+      <c r="U42" s="60">
         <f>IF(U63=0,"",IF(U60="","Thiếu KT gối",IF(U26="","Thiếu tên trục",IF(U116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="V41" s="60">
+      <c r="V42" s="60">
         <f>IF(V63=0,IF(V11="","","Sai Ltt"),IF(AND(T$63=0,V63=1),"Nhịp đứt quãng",IF(V26="","Thiếu đai",IF(V116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="W41" s="60">
+      <c r="W42" s="60">
         <f>IF(W63=0,"",IF(W60="","Thiếu KT gối",IF(W26="","Thiếu tên trục",IF(W116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="X41" s="60">
+      <c r="X42" s="60">
         <f>IF(X63=0,IF(X11="","","Sai Ltt"),IF(AND(V$63=0,X63=1),"Nhịp đứt quãng",IF(X26="","Thiếu đai",IF(X116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Y41" s="60">
+      <c r="Y42" s="60">
         <f>IF(Y63=0,"",IF(Y60="","Thiếu KT gối",IF(Y26="","Thiếu tên trục",IF(Y116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Z41" s="60">
+      <c r="Z42" s="60">
         <f>IF(Z63=0,IF(Z11="","","Sai Ltt"),IF(AND(X$63=0,Z63=1),"Nhịp đứt quãng",IF(Z26="","Thiếu đai",IF(Z116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AA41" s="60">
+      <c r="AA42" s="60">
         <f>IF(AA63=0,"",IF(AA60="","Thiếu KT gối",IF(AA26="","Thiếu tên trục",IF(AA116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AB41" s="60">
+      <c r="AB42" s="60">
         <f>IF(AB63=0,IF(AB11="","","Sai Ltt"),IF(AND(Z$63=0,AB63=1),"Nhịp đứt quãng",IF(AB26="","Thiếu đai",IF(AB116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AC41" s="60">
+      <c r="AC42" s="60">
         <f>IF(AC63=0,"",IF(AC60="","Thiếu KT gối",IF(AC26="","Thiếu tên trục",IF(AC116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AD41" s="60">
+      <c r="AD42" s="60">
         <f>IF(AD63=0,IF(AD11="","","Sai Ltt"),IF(AND(AB$63=0,AD63=1),"Nhịp đứt quãng",IF(AD26="","Thiếu đai",IF(AD116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AE41" s="60">
+      <c r="AE42" s="60">
         <f>IF(AE63=0,"",IF(AE60="","Thiếu KT gối",IF(AE26="","Thiếu tên trục",IF(AE116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AF41" s="60">
+      <c r="AF42" s="60">
         <f>IF(AF63=0,IF(AF11="","","Sai Ltt"),IF(AND(AD$63=0,AF63=1),"Nhịp đứt quãng",IF(AF26="","Thiếu đai",IF(AF116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AG41" s="60">
+      <c r="AG42" s="60">
         <f>IF(AG63=0,"",IF(AG60="","Thiếu KT gối",IF(AG26="","Thiếu tên trục",IF(AG116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
@@ -11782,7 +11822,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A24:B24"/>
@@ -11796,6 +11836,7 @@
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A41:AG41"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C2:E2"/>
@@ -11805,7 +11846,6 @@
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A41:B41"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="G4:I4"/>
@@ -11822,6 +11862,7 @@
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="E34:AG34"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="V3:X3"/>
@@ -11837,7 +11878,6 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="E36:AG36"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A40:AG40"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="K5:M5"/>
@@ -11848,6 +11888,7 @@
     <mergeCell ref="C9:AG9"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="P6:R6"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
   <conditionalFormatting sqref="C11:AG31">
@@ -11855,15 +11896,15 @@
       <formula>C$64=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:AG41">
+  <conditionalFormatting sqref="C42:AG42">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>C$63=0</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="2">
-      <formula>C41="OK"</formula>
+      <formula>C42="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" dxfId="3">
-      <formula>AND(C41&lt;&gt;"",C41&lt;&gt;"OK")</formula>
+      <formula>AND(C42&lt;&gt;"",C42&lt;&gt;"OK")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:AG13">
@@ -11934,7 +11975,7 @@
       <formula>LEFT($C$9,1)="✔"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="76">
+  <dataValidations count="77">
     <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm" prompt="Tên dầm (ghi trên bản vẽ, tên file CSV)."/>
     <dataValidation sqref="F3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="b dầm (mm)" prompt="Bề rộng dầm (mm), vd 400."/>
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="h dầm (mm)" prompt="Chiều cao dầm (mm), vd 1000."/>
@@ -11995,7 +12036,7 @@
     </dataValidation>
     <dataValidation sqref="S8 T8" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm nối / ghi chú KC" prompt="Chờ / coupler: tên dầm nối sang, vd B138 → 'COUPLER NỐI DẦM B138'.&#10;Khoan cấy: nội dung ghi chú (leader), vd KHOAN CẤY {BAR} SÂU {L} KEO HILTI RE500 · {BAR} {N} {D} {L} tự thay · trống = QS_DAMSET."/>
     <dataValidation sqref="Y2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tai sàn (phía có sàn)" prompt="2 ben / Trai / Phai / Khong&#10;Chỉ dùng khi F7 là số." type="list">
-      <formula1>LIST!$Y$2:$Y$5</formula1>
+      <formula1>LIST!$Z$2:$Z$5</formula1>
     </dataValidation>
     <dataValidation sqref="Y3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Sàn lật (dầm úp)" prompt="Co = sàn nằm ở đáy dầm. Chỉ dùng khi F7 là số." type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
@@ -12104,19 +12145,22 @@
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Thép chạy suốt DƯỚI" prompt="Thép chạy suốt DƯỚI, vd 3t28 · 2t28+1t25.&#10;Đổi thép theo nhịp: dòng 25." type="list">
       <formula1>LIST!$A$2:$A$42</formula1>
     </dataValidation>
-    <dataValidation sqref="C33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Đai con đi hết dầm" prompt="Co = khai báo ô C34 áp dụng cả dầm · Khong = C34 cho vùng gối (vùng đai dày 2 đầu nhịp), C35 cho vùng nhịp · trống = QS_DAMSET" type="list">
+    <dataValidation sqref="C33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Đai con đi hết dầm" prompt="Co / trống = khai báo ô C34 áp dụng cả dầm · Khong = C34 cho vùng gối (vùng đai dày 2 đầu nhịp), C35 cho vùng nhịp" type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
     </dataValidation>
-    <dataValidation sqref="C34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="3 = đai C (1 nhánh) tại thanh 3 · 2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có · AUTO / trống = tra bảng dòng 38" type="list">
+    <dataValidation sqref="C34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="3 = đai C (1 nhánh) tại thanh 3 · 2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có · AUTO / trống = tra bảng dòng 38 + 39" type="list">
       <formula1>LIST!$X$2:$X$12</formula1>
     </dataValidation>
     <dataValidation sqref="C35" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con vùng nhịp" prompt="Dùng khi C33 = Khong. Cú pháp như C34." type="list">
       <formula1>LIST!$X$2:$X$12</formula1>
     </dataValidation>
-    <dataValidation sqref="C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tra bảng theo số lượng thép" prompt="Co = khi C34 / C35 là AUTO / trống: tra bảng dòng 38 theo số thanh lớp 1 trên tại mặt cắt (ô trống → bảng QS_DAMSET trang 7) · Khong = đai trong tự động cũ" type="list">
+    <dataValidation sqref="C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tra bảng theo số lượng thép" prompt="Co / trống = khi C34 / C35 là AUTO / trống: tra bảng dòng 38 (đai C) + 39 (đai U / Q) theo số thanh lớp 1 trên tại mặt cắt · Khong / ô bảng trống = đai trong tự động" type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
     </dataValidation>
-    <dataValidation sqref="C38 D38 E38 F38 G38 H38 I38 J38 K38 L38 M38 N38 O38 P38 Q38 R38 S38 T38 U38 V38 W38 X38 Y38 Z38 AA38 AB38 AC38 AD38 AE38" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con theo số thanh" prompt="Số thanh lớp 1 trên ở dòng 37.&#10;2 = đai C thanh 2 · 2_3 = đai Q thanh 2..3 · 2-4 = đai U · 3,2_4 · 0 = không · trống = QS_DAMSET trang 7" type="list">
+    <dataValidation sqref="C38 D38 E38 F38 G38 H38 I38 J38 K38 L38 M38 N38 O38 P38 Q38 R38 S38 T38 U38 V38 W38 X38 Y38 Z38 AA38 AB38 AC38 AD38 AE38" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai C theo số thanh" prompt="Số thanh lớp 1 trên ở dòng 37.&#10;Đai C (1 nhánh) tại thanh: 2 · 2,4 · 2_4 (= C tại thanh 2, 3, 4) · 0 = không · trống = không có đai C" type="list">
+      <formula1>LIST!$Y$2:$Y$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="C39 D39 E39 F39 G39 H39 I39 J39 K39 L39 M39 N39 O39 P39 Q39 R39 S39 T39 U39 V39 W39 X39 Y39 Z39 AA39 AB39 AC39 AD39 AE39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai U / Q theo số thanh" prompt="2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 2_3,4_5 · số đơn (vd 2) = đai C tại thanh 2 · trống = không có" type="list">
       <formula1>LIST!$X$2:$X$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -12508,7 +12552,7 @@
       </c>
       <c r="B9" s="20" t="n"/>
       <c r="C9" s="21">
-        <f>IF(SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)=0,"Chưa có nhịp: nhập bề rộng gối + L thông thủy ở dòng 11",IF(SUMPRODUCT((C41:AG41&lt;&gt;"")*(C41:AG41&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))-1)*MID(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))-1)*MID(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))-1)*MID(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))-1)*MID(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)=0,"✔  Số liệu hợp lệ – "&amp;SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)&amp;" nhịp, tổng chiều dài dầm L = "&amp;FIXED(SUMIF(C63:AG63,1,C60:AG60),0)&amp;" mm","✖  Có "&amp;(SUMPRODUCT((C41:AG41&lt;&gt;"")*(C41:AG41&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))-1)*MID(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))-1)*MID(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))-1)*MID(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))-1)*MID(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0))&amp;" lỗi – xem dòng 41 (KIỂM TRA SỐ LIỆU) và ô B11 / B12"))</f>
+        <f>IF(SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)=0,"Chưa có nhịp: nhập bề rộng gối + L thông thủy ở dòng 11",IF(SUMPRODUCT((C42:AG42&lt;&gt;"")*(C42:AG42&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))-1)*MID(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))-1)*MID(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))-1)*MID(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))-1)*MID(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)=0,"✔  Số liệu hợp lệ – "&amp;SUMPRODUCT((MOD(COLUMN(C63:AG63),2)=0)*C63:AG63)&amp;" nhịp, tổng chiều dài dầm L = "&amp;FIXED(SUMIF(C63:AG63,1,C60:AG60),0)&amp;" mm","✖  Có "&amp;(SUMPRODUCT((C42:AG42&lt;&gt;"")*(C42:AG42&lt;&gt;"OK"))+((IFERROR(LEFT(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))-1)*MID(LEFT($B$117,FIND("+",$B$117&amp;"+")-1),FIND("t",LEFT($B$117,FIND("+",$B$117&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))-1)*MID(MID($B$117,FIND("+",$B$117&amp;"+")+1,99),FIND("t",MID($B$117,FIND("+",$B$117&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0)+((IFERROR(LEFT(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))-1)*MID(LEFT($B$118,FIND("+",$B$118&amp;"+")-1),FIND("t",LEFT($B$118,FIND("+",$B$118&amp;"+")-1))+1,2)^2*PI()/400,0)+IFERROR(LEFT(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))-1)*MID(MID($B$118,FIND("+",$B$118&amp;"+")+1,99),FIND("t",MID($B$118,FIND("+",$B$118&amp;"+")+1,99))+1,2)^2*PI()/400,0))=0))&amp;" lỗi – xem dòng 42 (KIỂM TRA SỐ LIỆU) và ô B11 / B12"))</f>
         <v/>
       </c>
       <c r="D9" s="22" t="n"/>
@@ -13541,7 +13585,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="50" t="inlineStr">
         <is>
-          <t>ĐAI CON – NHÁNH ĐAI BÊN TRONG theo vị trí thanh lớp 1 trên (đánh số 1..n từ trái sang phải) · ô trống = theo QS_DAMSET trang 7</t>
+          <t>ĐAI CON – NHÁNH ĐAI BÊN TRONG theo vị trí thanh lớp 1 trên (đánh số 1..n từ trái sang phải) · trống = đai trong tự động</t>
         </is>
       </c>
       <c r="B32" s="51" t="n"/>
@@ -13588,7 +13632,7 @@
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Co = khai báo ô C34 áp dụng cả dầm · Khong = C34 cho vùng gối (vùng đai dày 2 đầu nhịp), C35 cho vùng nhịp · trống = QS_DAMSET</t>
+          <t>Co / trống = khai báo ô C34 áp dụng cả dầm · Khong = C34 cho vùng gối (vùng đai dày 2 đầu nhịp), C35 cho vùng nhịp</t>
         </is>
       </c>
       <c r="F33" s="6" t="n"/>
@@ -13631,7 +13675,7 @@
       <c r="D34" s="6" t="n"/>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>3 = đai C (1 nhánh) tại thanh 3 · 2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có · AUTO / trống = tra bảng dòng 38</t>
+          <t>3 = đai C (1 nhánh) tại thanh 3 · 2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có · AUTO / trống = tra bảng dòng 38 + 39</t>
         </is>
       </c>
       <c r="F34" s="6" t="n"/>
@@ -13717,7 +13761,7 @@
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Co = khi C34 / C35 là AUTO / trống: tra bảng dòng 38 theo số thanh lớp 1 trên tại mặt cắt (ô trống → bảng QS_DAMSET trang 7) · Khong = đai trong tự động cũ</t>
+          <t>Co / trống = khi C34 / C35 là AUTO / trống: tra bảng dòng 38 (đai C) + 39 (đai U / Q) theo số thanh lớp 1 trên tại mặt cắt · Khong / ô bảng trống = đai trong tự động</t>
         </is>
       </c>
       <c r="F36" s="6" t="n"/>
@@ -13849,7 +13893,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="52" t="inlineStr">
         <is>
-          <t>Nhánh đai con theo số thanh</t>
+          <t>Đai C (1 nhánh) theo số thanh</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
@@ -13885,173 +13929,212 @@
       <c r="AF38" s="57" t="inlineStr"/>
       <c r="AG38" s="57" t="inlineStr"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="50" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="52" t="inlineStr">
+        <is>
+          <t>Đai U / Q theo số thanh</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="58" t="n"/>
+      <c r="D39" s="58" t="n"/>
+      <c r="E39" s="58" t="n"/>
+      <c r="F39" s="58" t="n"/>
+      <c r="G39" s="58" t="n"/>
+      <c r="H39" s="58" t="n"/>
+      <c r="I39" s="58" t="n"/>
+      <c r="J39" s="58" t="n"/>
+      <c r="K39" s="58" t="n"/>
+      <c r="L39" s="58" t="n"/>
+      <c r="M39" s="58" t="n"/>
+      <c r="N39" s="58" t="n"/>
+      <c r="O39" s="58" t="n"/>
+      <c r="P39" s="58" t="n"/>
+      <c r="Q39" s="58" t="n"/>
+      <c r="R39" s="58" t="n"/>
+      <c r="S39" s="58" t="n"/>
+      <c r="T39" s="58" t="n"/>
+      <c r="U39" s="58" t="n"/>
+      <c r="V39" s="58" t="n"/>
+      <c r="W39" s="58" t="n"/>
+      <c r="X39" s="58" t="n"/>
+      <c r="Y39" s="58" t="n"/>
+      <c r="Z39" s="58" t="n"/>
+      <c r="AA39" s="58" t="n"/>
+      <c r="AB39" s="58" t="n"/>
+      <c r="AC39" s="58" t="n"/>
+      <c r="AD39" s="58" t="n"/>
+      <c r="AE39" s="58" t="n"/>
+      <c r="AF39" s="57" t="inlineStr"/>
+      <c r="AG39" s="57" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="50" t="inlineStr">
         <is>
           <t>KIỂM TRA SỐ LIỆU</t>
         </is>
       </c>
-      <c r="B40" s="51" t="n"/>
-      <c r="C40" s="51" t="n"/>
-      <c r="D40" s="51" t="n"/>
-      <c r="E40" s="51" t="n"/>
-      <c r="F40" s="51" t="n"/>
-      <c r="G40" s="51" t="n"/>
-      <c r="H40" s="51" t="n"/>
-      <c r="I40" s="51" t="n"/>
-      <c r="J40" s="51" t="n"/>
-      <c r="K40" s="51" t="n"/>
-      <c r="L40" s="51" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="51" t="n"/>
-      <c r="W40" s="51" t="n"/>
-      <c r="X40" s="51" t="n"/>
-      <c r="Y40" s="51" t="n"/>
-      <c r="Z40" s="51" t="n"/>
-      <c r="AA40" s="51" t="n"/>
-      <c r="AB40" s="51" t="n"/>
-      <c r="AC40" s="51" t="n"/>
-      <c r="AD40" s="51" t="n"/>
-      <c r="AE40" s="51" t="n"/>
-      <c r="AF40" s="51" t="n"/>
-      <c r="AG40" s="51" t="n"/>
-    </row>
-    <row r="41" ht="27" customHeight="1">
-      <c r="A41" s="59" t="inlineStr">
+      <c r="B41" s="51" t="n"/>
+      <c r="C41" s="51" t="n"/>
+      <c r="D41" s="51" t="n"/>
+      <c r="E41" s="51" t="n"/>
+      <c r="F41" s="51" t="n"/>
+      <c r="G41" s="51" t="n"/>
+      <c r="H41" s="51" t="n"/>
+      <c r="I41" s="51" t="n"/>
+      <c r="J41" s="51" t="n"/>
+      <c r="K41" s="51" t="n"/>
+      <c r="L41" s="51" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="51" t="n"/>
+      <c r="W41" s="51" t="n"/>
+      <c r="X41" s="51" t="n"/>
+      <c r="Y41" s="51" t="n"/>
+      <c r="Z41" s="51" t="n"/>
+      <c r="AA41" s="51" t="n"/>
+      <c r="AB41" s="51" t="n"/>
+      <c r="AC41" s="51" t="n"/>
+      <c r="AD41" s="51" t="n"/>
+      <c r="AE41" s="51" t="n"/>
+      <c r="AF41" s="51" t="n"/>
+      <c r="AG41" s="51" t="n"/>
+    </row>
+    <row r="42" ht="27" customHeight="1">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>Kết quả kiểm tra từng cột</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="60">
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="60">
         <f>IF(C63=0,"",IF(C60="","Thiếu KT gối",IF(C26="","Thiếu tên trục",IF(C116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="D41" s="60">
+      <c r="D42" s="60">
         <f>IF(D63=0,IF(D11="","","Sai Ltt"),IF(FALSE,"Nhịp đứt quãng",IF(D26="","Thiếu đai",IF(D116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="E41" s="60">
+      <c r="E42" s="60">
         <f>IF(E63=0,"",IF(E60="","Thiếu KT gối",IF(E26="","Thiếu tên trục",IF(E116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="F41" s="60">
+      <c r="F42" s="60">
         <f>IF(F63=0,IF(F11="","","Sai Ltt"),IF(AND(D$63=0,F63=1),"Nhịp đứt quãng",IF(F26="","Thiếu đai",IF(F116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="G41" s="60">
+      <c r="G42" s="60">
         <f>IF(G63=0,"",IF(G60="","Thiếu KT gối",IF(G26="","Thiếu tên trục",IF(G116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="H41" s="60">
+      <c r="H42" s="60">
         <f>IF(H63=0,IF(H11="","","Sai Ltt"),IF(AND(F$63=0,H63=1),"Nhịp đứt quãng",IF(H26="","Thiếu đai",IF(H116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="I41" s="60">
+      <c r="I42" s="60">
         <f>IF(I63=0,"",IF(I60="","Thiếu KT gối",IF(I26="","Thiếu tên trục",IF(I116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="J41" s="60">
+      <c r="J42" s="60">
         <f>IF(J63=0,IF(J11="","","Sai Ltt"),IF(AND(H$63=0,J63=1),"Nhịp đứt quãng",IF(J26="","Thiếu đai",IF(J116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="K41" s="60">
+      <c r="K42" s="60">
         <f>IF(K63=0,"",IF(K60="","Thiếu KT gối",IF(K26="","Thiếu tên trục",IF(K116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="L41" s="60">
+      <c r="L42" s="60">
         <f>IF(L63=0,IF(L11="","","Sai Ltt"),IF(AND(J$63=0,L63=1),"Nhịp đứt quãng",IF(L26="","Thiếu đai",IF(L116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="M41" s="60">
+      <c r="M42" s="60">
         <f>IF(M63=0,"",IF(M60="","Thiếu KT gối",IF(M26="","Thiếu tên trục",IF(M116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="N41" s="60">
+      <c r="N42" s="60">
         <f>IF(N63=0,IF(N11="","","Sai Ltt"),IF(AND(L$63=0,N63=1),"Nhịp đứt quãng",IF(N26="","Thiếu đai",IF(N116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="O41" s="60">
+      <c r="O42" s="60">
         <f>IF(O63=0,"",IF(O60="","Thiếu KT gối",IF(O26="","Thiếu tên trục",IF(O116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="P41" s="60">
+      <c r="P42" s="60">
         <f>IF(P63=0,IF(P11="","","Sai Ltt"),IF(AND(N$63=0,P63=1),"Nhịp đứt quãng",IF(P26="","Thiếu đai",IF(P116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Q41" s="60">
+      <c r="Q42" s="60">
         <f>IF(Q63=0,"",IF(Q60="","Thiếu KT gối",IF(Q26="","Thiếu tên trục",IF(Q116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="R41" s="60">
+      <c r="R42" s="60">
         <f>IF(R63=0,IF(R11="","","Sai Ltt"),IF(AND(P$63=0,R63=1),"Nhịp đứt quãng",IF(R26="","Thiếu đai",IF(R116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="S41" s="60">
+      <c r="S42" s="60">
         <f>IF(S63=0,"",IF(S60="","Thiếu KT gối",IF(S26="","Thiếu tên trục",IF(S116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="T41" s="60">
+      <c r="T42" s="60">
         <f>IF(T63=0,IF(T11="","","Sai Ltt"),IF(AND(R$63=0,T63=1),"Nhịp đứt quãng",IF(T26="","Thiếu đai",IF(T116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="U41" s="60">
+      <c r="U42" s="60">
         <f>IF(U63=0,"",IF(U60="","Thiếu KT gối",IF(U26="","Thiếu tên trục",IF(U116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="V41" s="60">
+      <c r="V42" s="60">
         <f>IF(V63=0,IF(V11="","","Sai Ltt"),IF(AND(T$63=0,V63=1),"Nhịp đứt quãng",IF(V26="","Thiếu đai",IF(V116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="W41" s="60">
+      <c r="W42" s="60">
         <f>IF(W63=0,"",IF(W60="","Thiếu KT gối",IF(W26="","Thiếu tên trục",IF(W116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="X41" s="60">
+      <c r="X42" s="60">
         <f>IF(X63=0,IF(X11="","","Sai Ltt"),IF(AND(V$63=0,X63=1),"Nhịp đứt quãng",IF(X26="","Thiếu đai",IF(X116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Y41" s="60">
+      <c r="Y42" s="60">
         <f>IF(Y63=0,"",IF(Y60="","Thiếu KT gối",IF(Y26="","Thiếu tên trục",IF(Y116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="Z41" s="60">
+      <c r="Z42" s="60">
         <f>IF(Z63=0,IF(Z11="","","Sai Ltt"),IF(AND(X$63=0,Z63=1),"Nhịp đứt quãng",IF(Z26="","Thiếu đai",IF(Z116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AA41" s="60">
+      <c r="AA42" s="60">
         <f>IF(AA63=0,"",IF(AA60="","Thiếu KT gối",IF(AA26="","Thiếu tên trục",IF(AA116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AB41" s="60">
+      <c r="AB42" s="60">
         <f>IF(AB63=0,IF(AB11="","","Sai Ltt"),IF(AND(Z$63=0,AB63=1),"Nhịp đứt quãng",IF(AB26="","Thiếu đai",IF(AB116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AC41" s="60">
+      <c r="AC42" s="60">
         <f>IF(AC63=0,"",IF(AC60="","Thiếu KT gối",IF(AC26="","Thiếu tên trục",IF(AC116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AD41" s="60">
+      <c r="AD42" s="60">
         <f>IF(AD63=0,IF(AD11="","","Sai Ltt"),IF(AND(AB$63=0,AD63=1),"Nhịp đứt quãng",IF(AD26="","Thiếu đai",IF(AD116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AE41" s="60">
+      <c r="AE42" s="60">
         <f>IF(AE63=0,"",IF(AE60="","Thiếu KT gối",IF(AE26="","Thiếu tên trục",IF(AE116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AF41" s="60">
+      <c r="AF42" s="60">
         <f>IF(AF63=0,IF(AF11="","","Sai Ltt"),IF(AND(AD$63=0,AF63=1),"Nhịp đứt quãng",IF(AF26="","Thiếu đai",IF(AF116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
-      <c r="AG41" s="60">
+      <c r="AG42" s="60">
         <f>IF(AG63=0,"",IF(AG60="","Thiếu KT gối",IF(AG26="","Thiếu tên trục",IF(AG116&gt;0,"Sai KH thép","OK"))))</f>
         <v/>
       </c>
@@ -21433,7 +21516,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A24:B24"/>
@@ -21447,6 +21530,7 @@
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A41:AG41"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C2:E2"/>
@@ -21456,7 +21540,6 @@
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A41:B41"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="G4:I4"/>
@@ -21473,6 +21556,7 @@
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="E34:AG34"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="V3:X3"/>
@@ -21488,7 +21572,6 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="E36:AG36"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A40:AG40"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="K5:M5"/>
@@ -21499,6 +21582,7 @@
     <mergeCell ref="C9:AG9"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="P6:R6"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
   <conditionalFormatting sqref="C11:AG31">
@@ -21506,15 +21590,15 @@
       <formula>C$64=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:AG41">
+  <conditionalFormatting sqref="C42:AG42">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>C$63=0</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="2">
-      <formula>C41="OK"</formula>
+      <formula>C42="OK"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" dxfId="3">
-      <formula>AND(C41&lt;&gt;"",C41&lt;&gt;"OK")</formula>
+      <formula>AND(C42&lt;&gt;"",C42&lt;&gt;"OK")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:AG13">
@@ -21585,7 +21669,7 @@
       <formula>LEFT($C$9,1)="✔"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="76">
+  <dataValidations count="77">
     <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm" prompt="Tên dầm (ghi trên bản vẽ, tên file CSV)."/>
     <dataValidation sqref="F3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="b dầm (mm)" prompt="Bề rộng dầm (mm), vd 400."/>
     <dataValidation sqref="F4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="h dầm (mm)" prompt="Chiều cao dầm (mm), vd 1000."/>
@@ -21646,7 +21730,7 @@
     </dataValidation>
     <dataValidation sqref="S8 T8" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Tên dầm nối / ghi chú KC" prompt="Chờ / coupler: tên dầm nối sang, vd B138 → 'COUPLER NỐI DẦM B138'.&#10;Khoan cấy: nội dung ghi chú (leader), vd KHOAN CẤY {BAR} SÂU {L} KEO HILTI RE500 · {BAR} {N} {D} {L} tự thay · trống = QS_DAMSET."/>
     <dataValidation sqref="Y2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tai sàn (phía có sàn)" prompt="2 ben / Trai / Phai / Khong&#10;Chỉ dùng khi F7 là số." type="list">
-      <formula1>LIST!$Y$2:$Y$5</formula1>
+      <formula1>LIST!$Z$2:$Z$5</formula1>
     </dataValidation>
     <dataValidation sqref="Y3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Sàn lật (dầm úp)" prompt="Co = sàn nằm ở đáy dầm. Chỉ dùng khi F7 là số." type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
@@ -21755,19 +21839,22 @@
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Thép chạy suốt DƯỚI" prompt="Thép chạy suốt DƯỚI, vd 3t28 · 2t28+1t25.&#10;Đổi thép theo nhịp: dòng 25." type="list">
       <formula1>LIST!$A$2:$A$42</formula1>
     </dataValidation>
-    <dataValidation sqref="C33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Đai con đi hết dầm" prompt="Co = khai báo ô C34 áp dụng cả dầm · Khong = C34 cho vùng gối (vùng đai dày 2 đầu nhịp), C35 cho vùng nhịp · trống = QS_DAMSET" type="list">
+    <dataValidation sqref="C33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Đai con đi hết dầm" prompt="Co / trống = khai báo ô C34 áp dụng cả dầm · Khong = C34 cho vùng gối (vùng đai dày 2 đầu nhịp), C35 cho vùng nhịp" type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
     </dataValidation>
-    <dataValidation sqref="C34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="3 = đai C (1 nhánh) tại thanh 3 · 2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có · AUTO / trống = tra bảng dòng 38" type="list">
+    <dataValidation sqref="C34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con toàn dầm / vùng gối" prompt="3 = đai C (1 nhánh) tại thanh 3 · 2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 3,2_4 · 0 = không có · AUTO / trống = tra bảng dòng 38 + 39" type="list">
       <formula1>LIST!$X$2:$X$12</formula1>
     </dataValidation>
     <dataValidation sqref="C35" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con vùng nhịp" prompt="Dùng khi C33 = Khong. Cú pháp như C34." type="list">
       <formula1>LIST!$X$2:$X$12</formula1>
     </dataValidation>
-    <dataValidation sqref="C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tra bảng theo số lượng thép" prompt="Co = khi C34 / C35 là AUTO / trống: tra bảng dòng 38 theo số thanh lớp 1 trên tại mặt cắt (ô trống → bảng QS_DAMSET trang 7) · Khong = đai trong tự động cũ" type="list">
+    <dataValidation sqref="C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="QS_DAM" error="Chọn giá trị trong danh sách." promptTitle="Tra bảng theo số lượng thép" prompt="Co / trống = khi C34 / C35 là AUTO / trống: tra bảng dòng 38 (đai C) + 39 (đai U / Q) theo số thanh lớp 1 trên tại mặt cắt · Khong / ô bảng trống = đai trong tự động" type="list">
       <formula1>LIST!$W$2:$W$3</formula1>
     </dataValidation>
-    <dataValidation sqref="C38 D38 E38 F38 G38 H38 I38 J38 K38 L38 M38 N38 O38 P38 Q38 R38 S38 T38 U38 V38 W38 X38 Y38 Z38 AA38 AB38 AC38 AD38 AE38" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai con theo số thanh" prompt="Số thanh lớp 1 trên ở dòng 37.&#10;2 = đai C thanh 2 · 2_3 = đai Q thanh 2..3 · 2-4 = đai U · 3,2_4 · 0 = không · trống = QS_DAMSET trang 7" type="list">
+    <dataValidation sqref="C38 D38 E38 F38 G38 H38 I38 J38 K38 L38 M38 N38 O38 P38 Q38 R38 S38 T38 U38 V38 W38 X38 Y38 Z38 AA38 AB38 AC38 AD38 AE38" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai C theo số thanh" prompt="Số thanh lớp 1 trên ở dòng 37.&#10;Đai C (1 nhánh) tại thanh: 2 · 2,4 · 2_4 (= C tại thanh 2, 3, 4) · 0 = không · trống = không có đai C" type="list">
+      <formula1>LIST!$Y$2:$Y$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="C39 D39 E39 F39 G39 H39 I39 J39 K39 L39 M39 N39 O39 P39 Q39 R39 S39 T39 U39 V39 W39 X39 Y39 Z39 AA39 AB39 AC39 AD39 AE39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Đai U / Q theo số thanh" prompt="2_4 = đai Q (kín) ôm thanh 2..4 · 2-4 = đai U · ghép 2_3,4_5 · số đơn (vd 2) = đai C tại thanh 2 · trống = không có" type="list">
       <formula1>LIST!$X$2:$X$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -21783,7 +21870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21811,6 +21898,7 @@
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21936,6 +22024,11 @@
       </c>
       <c r="Y1" s="63" t="inlineStr">
         <is>
+          <t>DAICONC</t>
+        </is>
+      </c>
+      <c r="Z1" s="63" t="inlineStr">
+        <is>
           <t>TAISAN</t>
         </is>
       </c>
@@ -22063,6 +22156,11 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>2 ben</t>
         </is>
       </c>
@@ -22185,6 +22283,11 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>Trai</t>
         </is>
       </c>
@@ -22297,6 +22400,11 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>Phai</t>
         </is>
       </c>
@@ -22384,6 +22492,11 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>Khong</t>
         </is>
       </c>
@@ -22444,6 +22557,11 @@
           <t>2_3</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22481,6 +22599,11 @@
           <t>2_4</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22511,6 +22634,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>2-4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
